--- a/public/docs/tarifa-italgres.xlsx
+++ b/public/docs/tarifa-italgres.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/carlos/Dropbox/TODO/TODO/USA/Todo USA/PAJARITO/Tarifas Miami tile/Tarifas nuevas USA 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{178B26EC-4FE7-C94E-AD92-520DF6A4E58A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{642CE9A0-CD50-2E4E-9B8E-6AA98B40B320}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="39420" yWindow="820" windowWidth="38400" windowHeight="19460" tabRatio="500" firstSheet="33" activeTab="47" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1900" yWindow="480" windowWidth="38400" windowHeight="19460" tabRatio="500" firstSheet="24" activeTab="26" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ALAPLANA" sheetId="116" r:id="rId1"/>
@@ -64,7 +64,7 @@
     <sheet name="VENATTO" sheetId="45" r:id="rId49"/>
     <sheet name="VIVES" sheetId="47" r:id="rId50"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2585" uniqueCount="1711">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2591" uniqueCount="1715">
   <si>
     <t>SIZE</t>
   </si>
@@ -5376,9 +5376,6 @@
     <t xml:space="preserve">Lucena </t>
   </si>
   <si>
-    <t>Lucena  aslip</t>
-  </si>
-  <si>
     <t>20.02.26</t>
   </si>
   <si>
@@ -5446,6 +5443,21 @@
   </si>
   <si>
     <t>MATERIA HARI</t>
+  </si>
+  <si>
+    <t>Breccia imperiale natural</t>
+  </si>
+  <si>
+    <t>Lucena aslip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ribera </t>
+  </si>
+  <si>
+    <t>White balance</t>
+  </si>
+  <si>
+    <t>05.04.26</t>
   </si>
 </sst>
 </file>
@@ -5461,8 +5473,8 @@
     <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="169" formatCode="[$$-409]#,##0.00"/>
     <numFmt numFmtId="170" formatCode="[$$-409]#,##0"/>
-    <numFmt numFmtId="172" formatCode="_-[$€-2]\ * #,##0.00_-;\-[$€-2]\ * #,##0.00_-;_-[$€-2]\ * \-??_-;_-@_-"/>
-    <numFmt numFmtId="173" formatCode="#,##0.00\ _€"/>
+    <numFmt numFmtId="171" formatCode="_-[$€-2]\ * #,##0.00_-;\-[$€-2]\ * #,##0.00_-;_-[$€-2]\ * \-??_-;_-@_-"/>
+    <numFmt numFmtId="172" formatCode="#,##0.00\ _€"/>
   </numFmts>
   <fonts count="110" x14ac:knownFonts="1">
     <font>
@@ -7254,7 +7266,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="421">
+  <cellXfs count="435">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="42" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
@@ -7664,17 +7676,17 @@
     <xf numFmtId="0" fontId="69" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="67" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="67" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="67" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="67" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="67" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="67" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="67" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="67" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="96" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="172" fontId="96" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="96" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="96" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="172" fontId="96" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="96" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="49" fillId="0" borderId="29" xfId="282" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="49" fillId="0" borderId="29" xfId="282" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="54" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7716,11 +7728,6 @@
     <xf numFmtId="0" fontId="102" fillId="0" borderId="21" xfId="246" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="21" xfId="246" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="21" xfId="246" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="19" xfId="246" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="104" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
@@ -7788,7 +7795,7 @@
     <xf numFmtId="168" fontId="81" fillId="0" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="67" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="105" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="173" fontId="67" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="67" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="246" applyFont="1"/>
     <xf numFmtId="0" fontId="106" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="106" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -7818,8 +7825,8 @@
     <xf numFmtId="0" fontId="104" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="89" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="173" fontId="67" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="173" fontId="81" fillId="0" borderId="29" xfId="298" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="67" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="81" fillId="0" borderId="29" xfId="298" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="76" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
@@ -7836,6 +7843,12 @@
     </xf>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="83" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="70" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="167" fontId="70" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="51" fillId="4" borderId="0" xfId="246" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -8044,12 +8057,33 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="67" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="70" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="21" xfId="246" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="167" fontId="70" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
+    <xf numFmtId="0" fontId="99" fillId="0" borderId="21" xfId="246" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="99" fillId="0" borderId="19" xfId="246" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="246" applyFont="1"/>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="246" applyFont="1"/>
+    <xf numFmtId="0" fontId="54" fillId="2" borderId="32" xfId="246" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="2" borderId="32" xfId="246" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="102" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="101" fillId="0" borderId="28" xfId="246" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="27" xfId="246" applyBorder="1"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="26" xfId="246" applyBorder="1"/>
+    <xf numFmtId="4" fontId="102" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="101" fillId="0" borderId="30" xfId="246" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="8" xfId="246" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="313">
     <cellStyle name="Comma [0] 2" xfId="248" xr:uid="{00000000-0005-0000-0000-000025010000}"/>
@@ -8714,28 +8748,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="30" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="342" t="s">
+      <c r="A1" s="339" t="s">
+        <v>1696</v>
+      </c>
+      <c r="B1" s="346" t="s">
         <v>1697</v>
       </c>
-      <c r="B1" s="347" t="s">
-        <v>1698</v>
-      </c>
-      <c r="C1" s="347"/>
-      <c r="D1" s="347"/>
-      <c r="E1" s="347"/>
-      <c r="F1" s="347"/>
-      <c r="G1" s="347"/>
-      <c r="H1" s="347"/>
+      <c r="C1" s="346"/>
+      <c r="D1" s="346"/>
+      <c r="E1" s="346"/>
+      <c r="F1" s="346"/>
+      <c r="G1" s="346"/>
+      <c r="H1" s="346"/>
       <c r="I1" s="38"/>
     </row>
     <row r="2" spans="1:17" s="30" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="347"/>
-      <c r="C2" s="347"/>
-      <c r="D2" s="347"/>
-      <c r="E2" s="347"/>
-      <c r="F2" s="347"/>
-      <c r="G2" s="347"/>
-      <c r="H2" s="347"/>
+      <c r="B2" s="346"/>
+      <c r="C2" s="346"/>
+      <c r="D2" s="346"/>
+      <c r="E2" s="346"/>
+      <c r="F2" s="346"/>
+      <c r="G2" s="346"/>
+      <c r="H2" s="346"/>
       <c r="I2" s="38"/>
     </row>
     <row r="3" spans="1:17" s="30" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -8745,10 +8779,10 @@
       <c r="Q4" s="41"/>
     </row>
     <row r="5" spans="1:17" s="30" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="348" t="s">
+      <c r="B5" s="347" t="s">
         <v>102</v>
       </c>
-      <c r="C5" s="348" t="s">
+      <c r="C5" s="347" t="s">
         <v>0</v>
       </c>
       <c r="D5" s="114" t="s">
@@ -8766,8 +8800,8 @@
       <c r="Q5" s="41"/>
     </row>
     <row r="6" spans="1:17" s="30" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="348"/>
-      <c r="C6" s="348"/>
+      <c r="B6" s="347"/>
+      <c r="C6" s="347"/>
       <c r="D6" s="114" t="s">
         <v>104</v>
       </c>
@@ -8784,7 +8818,7 @@
     </row>
     <row r="7" spans="1:17" s="30" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="121" t="s">
-        <v>1696</v>
+        <v>1695</v>
       </c>
       <c r="C7" s="121" t="s">
         <v>105</v>
@@ -8805,7 +8839,7 @@
     </row>
     <row r="8" spans="1:17" s="30" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="121" t="s">
-        <v>1696</v>
+        <v>1695</v>
       </c>
       <c r="C8" s="121" t="s">
         <v>83</v>
@@ -8815,9 +8849,9 @@
       </c>
       <c r="E8" s="31"/>
       <c r="F8" s="32"/>
-      <c r="G8" s="349"/>
-      <c r="H8" s="349"/>
-      <c r="I8" s="349"/>
+      <c r="G8" s="348"/>
+      <c r="H8" s="348"/>
+      <c r="I8" s="348"/>
       <c r="J8" s="32"/>
       <c r="L8" s="31"/>
       <c r="M8" s="32"/>
@@ -8831,9 +8865,9 @@
       <c r="D9" s="202"/>
       <c r="E9" s="31"/>
       <c r="F9" s="32"/>
-      <c r="G9" s="349"/>
-      <c r="H9" s="349"/>
-      <c r="I9" s="349"/>
+      <c r="G9" s="348"/>
+      <c r="H9" s="348"/>
+      <c r="I9" s="348"/>
       <c r="J9" s="32"/>
       <c r="L9" s="31"/>
       <c r="M9" s="32"/>
@@ -8866,32 +8900,32 @@
   <sheetData>
     <row r="1" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="350" t="s">
+      <c r="B2" s="349" t="s">
         <v>1599</v>
       </c>
-      <c r="C2" s="350"/>
-      <c r="D2" s="350"/>
-      <c r="E2" s="350"/>
-      <c r="F2" s="350"/>
-      <c r="G2" s="350"/>
-      <c r="H2" s="350"/>
-      <c r="I2" s="350"/>
-      <c r="J2" s="350"/>
-      <c r="K2" s="350"/>
-      <c r="L2" s="350"/>
+      <c r="C2" s="349"/>
+      <c r="D2" s="349"/>
+      <c r="E2" s="349"/>
+      <c r="F2" s="349"/>
+      <c r="G2" s="349"/>
+      <c r="H2" s="349"/>
+      <c r="I2" s="349"/>
+      <c r="J2" s="349"/>
+      <c r="K2" s="349"/>
+      <c r="L2" s="349"/>
     </row>
     <row r="3" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="350"/>
-      <c r="C3" s="350"/>
-      <c r="D3" s="350"/>
-      <c r="E3" s="350"/>
-      <c r="F3" s="350"/>
-      <c r="G3" s="350"/>
-      <c r="H3" s="350"/>
-      <c r="I3" s="350"/>
-      <c r="J3" s="350"/>
-      <c r="K3" s="350"/>
-      <c r="L3" s="350"/>
+      <c r="B3" s="349"/>
+      <c r="C3" s="349"/>
+      <c r="D3" s="349"/>
+      <c r="E3" s="349"/>
+      <c r="F3" s="349"/>
+      <c r="G3" s="349"/>
+      <c r="H3" s="349"/>
+      <c r="I3" s="349"/>
+      <c r="J3" s="349"/>
+      <c r="K3" s="349"/>
+      <c r="L3" s="349"/>
     </row>
     <row r="4" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
@@ -8901,10 +8935,10 @@
     <row r="5" spans="2:12" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="2:12" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="13"/>
-      <c r="C6" s="361" t="s">
+      <c r="C6" s="360" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="363" t="s">
+      <c r="D6" s="362" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="138" t="s">
@@ -8915,8 +8949,8 @@
     </row>
     <row r="7" spans="2:12" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="13"/>
-      <c r="C7" s="362"/>
-      <c r="D7" s="364"/>
+      <c r="C7" s="361"/>
+      <c r="D7" s="363"/>
       <c r="E7" s="236" t="s">
         <v>100</v>
       </c>
@@ -9423,32 +9457,32 @@
       <c r="K1" s="177"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" s="365" t="s">
+      <c r="A2" s="364" t="s">
         <v>1604</v>
       </c>
-      <c r="B2" s="365"/>
-      <c r="C2" s="365"/>
-      <c r="D2" s="365"/>
-      <c r="E2" s="365"/>
-      <c r="F2" s="365"/>
-      <c r="G2" s="365"/>
-      <c r="H2" s="365"/>
-      <c r="I2" s="365"/>
-      <c r="J2" s="365"/>
-      <c r="K2" s="365"/>
+      <c r="B2" s="364"/>
+      <c r="C2" s="364"/>
+      <c r="D2" s="364"/>
+      <c r="E2" s="364"/>
+      <c r="F2" s="364"/>
+      <c r="G2" s="364"/>
+      <c r="H2" s="364"/>
+      <c r="I2" s="364"/>
+      <c r="J2" s="364"/>
+      <c r="K2" s="364"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A3" s="365"/>
-      <c r="B3" s="365"/>
-      <c r="C3" s="365"/>
-      <c r="D3" s="365"/>
-      <c r="E3" s="365"/>
-      <c r="F3" s="365"/>
-      <c r="G3" s="365"/>
-      <c r="H3" s="365"/>
-      <c r="I3" s="365"/>
-      <c r="J3" s="365"/>
-      <c r="K3" s="365"/>
+      <c r="A3" s="364"/>
+      <c r="B3" s="364"/>
+      <c r="C3" s="364"/>
+      <c r="D3" s="364"/>
+      <c r="E3" s="364"/>
+      <c r="F3" s="364"/>
+      <c r="G3" s="364"/>
+      <c r="H3" s="364"/>
+      <c r="I3" s="364"/>
+      <c r="J3" s="364"/>
+      <c r="K3" s="364"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="177" t="s">
@@ -9480,10 +9514,10 @@
     </row>
     <row r="6" spans="1:11" ht="20" x14ac:dyDescent="0.2">
       <c r="A6" s="13"/>
-      <c r="B6" s="361" t="s">
+      <c r="B6" s="360" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="363" t="s">
+      <c r="C6" s="362" t="s">
         <v>0</v>
       </c>
       <c r="D6" s="180" t="s">
@@ -9499,8 +9533,8 @@
     </row>
     <row r="7" spans="1:11" ht="21" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="13"/>
-      <c r="B7" s="362"/>
-      <c r="C7" s="364"/>
+      <c r="B7" s="361"/>
+      <c r="C7" s="363"/>
       <c r="D7" s="191" t="s">
         <v>100</v>
       </c>
@@ -9795,24 +9829,24 @@
   <sheetData>
     <row r="1" spans="2:10" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:10" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="347" t="s">
+      <c r="B2" s="346" t="s">
         <v>1605</v>
       </c>
-      <c r="C2" s="347"/>
-      <c r="D2" s="347"/>
-      <c r="E2" s="347"/>
-      <c r="F2" s="347"/>
+      <c r="C2" s="346"/>
+      <c r="D2" s="346"/>
+      <c r="E2" s="346"/>
+      <c r="F2" s="346"/>
       <c r="G2" s="38"/>
       <c r="H2" s="38"/>
       <c r="I2" s="38"/>
       <c r="J2" s="38"/>
     </row>
     <row r="3" spans="2:10" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="347"/>
-      <c r="C3" s="347"/>
-      <c r="D3" s="347"/>
-      <c r="E3" s="347"/>
-      <c r="F3" s="347"/>
+      <c r="B3" s="346"/>
+      <c r="C3" s="346"/>
+      <c r="D3" s="346"/>
+      <c r="E3" s="346"/>
+      <c r="F3" s="346"/>
       <c r="G3" s="38"/>
       <c r="H3" s="38"/>
       <c r="I3" s="38"/>
@@ -9830,13 +9864,13 @@
       <c r="J4" s="38"/>
     </row>
     <row r="5" spans="2:10" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="319" t="s">
+      <c r="B5" s="316" t="s">
         <v>1589</v>
       </c>
     </row>
     <row r="6" spans="2:10" s="35" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="33"/>
-      <c r="C6" s="366" t="s">
+      <c r="C6" s="365" t="s">
         <v>99</v>
       </c>
       <c r="D6" s="192" t="s">
@@ -9844,7 +9878,7 @@
       </c>
       <c r="E6" s="193"/>
       <c r="F6" s="194"/>
-      <c r="G6" s="366" t="s">
+      <c r="G6" s="365" t="s">
         <v>99</v>
       </c>
       <c r="H6" s="192" t="s">
@@ -9853,13 +9887,13 @@
     </row>
     <row r="7" spans="2:10" s="35" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="33"/>
-      <c r="C7" s="366"/>
+      <c r="C7" s="365"/>
       <c r="D7" s="192" t="s">
         <v>98</v>
       </c>
       <c r="E7" s="193"/>
       <c r="F7" s="194"/>
-      <c r="G7" s="366"/>
+      <c r="G7" s="365"/>
       <c r="H7" s="192" t="s">
         <v>100</v>
       </c>
@@ -10173,7 +10207,7 @@
       </c>
       <c r="E27" s="195"/>
       <c r="F27" s="195"/>
-      <c r="G27" s="315" t="s">
+      <c r="G27" s="312" t="s">
         <v>70</v>
       </c>
       <c r="H27" s="234">
@@ -10189,7 +10223,7 @@
       </c>
       <c r="E28" s="195"/>
       <c r="F28" s="195"/>
-      <c r="G28" s="316" t="s">
+      <c r="G28" s="313" t="s">
         <v>71</v>
       </c>
       <c r="H28" s="234">
@@ -10205,7 +10239,7 @@
       </c>
       <c r="E29" s="195"/>
       <c r="F29" s="195"/>
-      <c r="G29" s="316" t="s">
+      <c r="G29" s="313" t="s">
         <v>72</v>
       </c>
       <c r="H29" s="234">
@@ -10221,7 +10255,7 @@
       </c>
       <c r="E30" s="195"/>
       <c r="F30" s="195"/>
-      <c r="G30" s="316" t="s">
+      <c r="G30" s="313" t="s">
         <v>73</v>
       </c>
       <c r="H30" s="234">
@@ -10237,7 +10271,7 @@
       </c>
       <c r="E31" s="195"/>
       <c r="F31" s="195"/>
-      <c r="G31" s="316" t="s">
+      <c r="G31" s="313" t="s">
         <v>74</v>
       </c>
       <c r="H31" s="234">
@@ -10253,7 +10287,7 @@
       </c>
       <c r="E32" s="195"/>
       <c r="F32" s="195"/>
-      <c r="G32" s="316" t="s">
+      <c r="G32" s="313" t="s">
         <v>75</v>
       </c>
       <c r="H32" s="234">
@@ -10269,7 +10303,7 @@
       </c>
       <c r="E33" s="195"/>
       <c r="F33" s="195"/>
-      <c r="G33" s="316" t="s">
+      <c r="G33" s="313" t="s">
         <v>76</v>
       </c>
       <c r="H33" s="234">
@@ -10285,7 +10319,7 @@
       </c>
       <c r="E34" s="195"/>
       <c r="F34" s="195"/>
-      <c r="G34" s="316" t="s">
+      <c r="G34" s="313" t="s">
         <v>77</v>
       </c>
       <c r="H34" s="234">
@@ -10301,7 +10335,7 @@
       </c>
       <c r="E35" s="195"/>
       <c r="F35" s="195"/>
-      <c r="G35" s="316" t="s">
+      <c r="G35" s="313" t="s">
         <v>78</v>
       </c>
       <c r="H35" s="234">
@@ -10309,7 +10343,7 @@
       </c>
     </row>
     <row r="36" spans="3:8" s="37" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C36" s="313" t="s">
+      <c r="C36" s="310" t="s">
         <v>32</v>
       </c>
       <c r="D36" s="228">
@@ -10317,7 +10351,7 @@
       </c>
       <c r="E36" s="195"/>
       <c r="F36" s="195"/>
-      <c r="G36" s="316" t="s">
+      <c r="G36" s="313" t="s">
         <v>79</v>
       </c>
       <c r="H36" s="234">
@@ -10333,7 +10367,7 @@
       </c>
       <c r="E37" s="195"/>
       <c r="F37" s="195"/>
-      <c r="G37" s="316" t="s">
+      <c r="G37" s="313" t="s">
         <v>80</v>
       </c>
       <c r="H37" s="234">
@@ -10349,7 +10383,7 @@
       </c>
       <c r="E38" s="195"/>
       <c r="F38" s="195"/>
-      <c r="G38" s="316" t="s">
+      <c r="G38" s="313" t="s">
         <v>81</v>
       </c>
       <c r="H38" s="234">
@@ -10365,7 +10399,7 @@
       </c>
       <c r="E39" s="195"/>
       <c r="F39" s="195"/>
-      <c r="G39" s="317" t="s">
+      <c r="G39" s="314" t="s">
         <v>1223</v>
       </c>
       <c r="H39" s="234">
@@ -10381,7 +10415,7 @@
       </c>
       <c r="E40" s="195"/>
       <c r="F40" s="195"/>
-      <c r="G40" s="317" t="s">
+      <c r="G40" s="314" t="s">
         <v>1224</v>
       </c>
       <c r="H40" s="234">
@@ -10397,7 +10431,7 @@
       </c>
       <c r="E41" s="195"/>
       <c r="F41" s="195"/>
-      <c r="G41" s="317" t="s">
+      <c r="G41" s="314" t="s">
         <v>1225</v>
       </c>
       <c r="H41" s="234">
@@ -10409,7 +10443,7 @@
       <c r="D42" s="229"/>
       <c r="E42" s="195"/>
       <c r="F42" s="195"/>
-      <c r="G42" s="317" t="s">
+      <c r="G42" s="314" t="s">
         <v>1226</v>
       </c>
       <c r="H42" s="235">
@@ -10417,7 +10451,7 @@
       </c>
     </row>
     <row r="43" spans="3:8" s="37" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C43" s="314" t="s">
+      <c r="C43" s="311" t="s">
         <v>38</v>
       </c>
       <c r="D43" s="225">
@@ -10425,7 +10459,7 @@
       </c>
       <c r="E43" s="195"/>
       <c r="F43" s="195"/>
-      <c r="G43" s="317" t="s">
+      <c r="G43" s="314" t="s">
         <v>1227</v>
       </c>
       <c r="H43" s="234">
@@ -10433,7 +10467,7 @@
       </c>
     </row>
     <row r="44" spans="3:8" s="37" customFormat="1" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C44" s="314" t="s">
+      <c r="C44" s="311" t="s">
         <v>39</v>
       </c>
       <c r="D44" s="225">
@@ -10441,7 +10475,7 @@
       </c>
       <c r="E44" s="195"/>
       <c r="F44" s="195"/>
-      <c r="G44" s="318" t="s">
+      <c r="G44" s="315" t="s">
         <v>1228</v>
       </c>
       <c r="H44" s="234">
@@ -10449,7 +10483,7 @@
       </c>
     </row>
     <row r="45" spans="3:8" s="37" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C45" s="314" t="s">
+      <c r="C45" s="311" t="s">
         <v>40</v>
       </c>
       <c r="D45" s="231">
@@ -10461,7 +10495,7 @@
       <c r="H45" s="196"/>
     </row>
     <row r="46" spans="3:8" s="37" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C46" s="314" t="s">
+      <c r="C46" s="311" t="s">
         <v>41</v>
       </c>
       <c r="D46" s="231">
@@ -10473,7 +10507,7 @@
       <c r="H46" s="198"/>
     </row>
     <row r="47" spans="3:8" s="37" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C47" s="314" t="s">
+      <c r="C47" s="311" t="s">
         <v>42</v>
       </c>
       <c r="D47" s="231">
@@ -10485,7 +10519,7 @@
       <c r="H47" s="199"/>
     </row>
     <row r="48" spans="3:8" s="37" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C48" s="314" t="s">
+      <c r="C48" s="311" t="s">
         <v>43</v>
       </c>
       <c r="D48" s="231">
@@ -10497,7 +10531,7 @@
       <c r="H48" s="195"/>
     </row>
     <row r="49" spans="3:8" s="37" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C49" s="314" t="s">
+      <c r="C49" s="311" t="s">
         <v>44</v>
       </c>
       <c r="D49" s="231">
@@ -10509,7 +10543,7 @@
       <c r="H49" s="195"/>
     </row>
     <row r="50" spans="3:8" s="37" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C50" s="314" t="s">
+      <c r="C50" s="311" t="s">
         <v>45</v>
       </c>
       <c r="D50" s="231">
@@ -10521,7 +10555,7 @@
       <c r="H50" s="195"/>
     </row>
     <row r="51" spans="3:8" s="37" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C51" s="314" t="s">
+      <c r="C51" s="311" t="s">
         <v>46</v>
       </c>
       <c r="D51" s="231">
@@ -10533,7 +10567,7 @@
       <c r="H51" s="195"/>
     </row>
     <row r="52" spans="3:8" s="37" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C52" s="314" t="s">
+      <c r="C52" s="311" t="s">
         <v>47</v>
       </c>
       <c r="D52" s="231">
@@ -10545,7 +10579,7 @@
       <c r="H52" s="195"/>
     </row>
     <row r="53" spans="3:8" s="37" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C53" s="314" t="s">
+      <c r="C53" s="311" t="s">
         <v>48</v>
       </c>
       <c r="D53" s="231">
@@ -10557,7 +10591,7 @@
       <c r="H53" s="195"/>
     </row>
     <row r="54" spans="3:8" s="37" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C54" s="314" t="s">
+      <c r="C54" s="311" t="s">
         <v>1222</v>
       </c>
       <c r="D54" s="231">
@@ -10569,7 +10603,7 @@
       <c r="H54" s="195"/>
     </row>
     <row r="55" spans="3:8" s="37" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C55" s="314" t="s">
+      <c r="C55" s="311" t="s">
         <v>49</v>
       </c>
       <c r="D55" s="231">
@@ -10581,7 +10615,7 @@
       <c r="H55" s="195"/>
     </row>
     <row r="56" spans="3:8" s="37" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C56" s="314" t="s">
+      <c r="C56" s="311" t="s">
         <v>50</v>
       </c>
       <c r="D56" s="231">
@@ -10593,7 +10627,7 @@
       <c r="H56" s="195"/>
     </row>
     <row r="57" spans="3:8" s="37" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C57" s="314" t="s">
+      <c r="C57" s="311" t="s">
         <v>51</v>
       </c>
       <c r="D57" s="231">
@@ -10605,7 +10639,7 @@
       <c r="H57" s="195"/>
     </row>
     <row r="58" spans="3:8" s="37" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C58" s="314" t="s">
+      <c r="C58" s="311" t="s">
         <v>52</v>
       </c>
       <c r="D58" s="231">
@@ -10617,7 +10651,7 @@
       <c r="H58" s="195"/>
     </row>
     <row r="59" spans="3:8" s="37" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C59" s="314" t="s">
+      <c r="C59" s="311" t="s">
         <v>53</v>
       </c>
       <c r="D59" s="231">
@@ -10790,32 +10824,32 @@
       <c r="K1" s="177"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" s="365" t="s">
+      <c r="A2" s="364" t="s">
         <v>1606</v>
       </c>
-      <c r="B2" s="365"/>
-      <c r="C2" s="365"/>
-      <c r="D2" s="365"/>
-      <c r="E2" s="365"/>
-      <c r="F2" s="365"/>
-      <c r="G2" s="365"/>
-      <c r="H2" s="365"/>
-      <c r="I2" s="365"/>
-      <c r="J2" s="365"/>
-      <c r="K2" s="365"/>
+      <c r="B2" s="364"/>
+      <c r="C2" s="364"/>
+      <c r="D2" s="364"/>
+      <c r="E2" s="364"/>
+      <c r="F2" s="364"/>
+      <c r="G2" s="364"/>
+      <c r="H2" s="364"/>
+      <c r="I2" s="364"/>
+      <c r="J2" s="364"/>
+      <c r="K2" s="364"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A3" s="365"/>
-      <c r="B3" s="365"/>
-      <c r="C3" s="365"/>
-      <c r="D3" s="365"/>
-      <c r="E3" s="365"/>
-      <c r="F3" s="365"/>
-      <c r="G3" s="365"/>
-      <c r="H3" s="365"/>
-      <c r="I3" s="365"/>
-      <c r="J3" s="365"/>
-      <c r="K3" s="365"/>
+      <c r="A3" s="364"/>
+      <c r="B3" s="364"/>
+      <c r="C3" s="364"/>
+      <c r="D3" s="364"/>
+      <c r="E3" s="364"/>
+      <c r="F3" s="364"/>
+      <c r="G3" s="364"/>
+      <c r="H3" s="364"/>
+      <c r="I3" s="364"/>
+      <c r="J3" s="364"/>
+      <c r="K3" s="364"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="177" t="s">
@@ -10847,13 +10881,13 @@
     </row>
     <row r="6" spans="1:11" ht="20" x14ac:dyDescent="0.2">
       <c r="A6" s="13"/>
-      <c r="B6" s="351" t="s">
+      <c r="B6" s="350" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="351" t="s">
+      <c r="C6" s="350" t="s">
         <v>0</v>
       </c>
-      <c r="D6" s="293" t="s">
+      <c r="D6" s="290" t="s">
         <v>101</v>
       </c>
       <c r="E6" s="13"/>
@@ -10866,9 +10900,9 @@
     </row>
     <row r="7" spans="1:11" ht="21" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="13"/>
-      <c r="B7" s="364"/>
-      <c r="C7" s="364"/>
-      <c r="D7" s="294" t="s">
+      <c r="B7" s="363"/>
+      <c r="C7" s="363"/>
+      <c r="D7" s="291" t="s">
         <v>100</v>
       </c>
       <c r="E7" s="13"/>
@@ -10881,13 +10915,13 @@
     </row>
     <row r="8" spans="1:11" ht="21" x14ac:dyDescent="0.25">
       <c r="A8" s="28"/>
-      <c r="B8" s="291" t="s">
+      <c r="B8" s="288" t="s">
         <v>1150</v>
       </c>
-      <c r="C8" s="291" t="s">
+      <c r="C8" s="288" t="s">
         <v>874</v>
       </c>
-      <c r="D8" s="295">
+      <c r="D8" s="292">
         <v>10.591679287713985</v>
       </c>
       <c r="E8" s="28"/>
@@ -10900,10 +10934,10 @@
     </row>
     <row r="9" spans="1:11" ht="21" x14ac:dyDescent="0.25">
       <c r="A9" s="28"/>
-      <c r="B9" s="292" t="s">
+      <c r="B9" s="289" t="s">
         <v>1151</v>
       </c>
-      <c r="C9" s="292" t="s">
+      <c r="C9" s="289" t="s">
         <v>874</v>
       </c>
       <c r="D9" s="202">
@@ -11128,7 +11162,7 @@
       <c r="C22" s="130" t="s">
         <v>871</v>
       </c>
-      <c r="D22" s="296">
+      <c r="D22" s="293">
         <v>6.6240763688099493</v>
       </c>
     </row>
@@ -11139,7 +11173,7 @@
       <c r="C23" s="130" t="s">
         <v>893</v>
       </c>
-      <c r="D23" s="297">
+      <c r="D23" s="294">
         <v>7.8850704483913923</v>
       </c>
     </row>
@@ -11150,7 +11184,7 @@
       <c r="C24" s="130" t="s">
         <v>1116</v>
       </c>
-      <c r="D24" s="298">
+      <c r="D24" s="295">
         <v>8.6096195327917755</v>
       </c>
     </row>
@@ -11177,32 +11211,32 @@
   <sheetData>
     <row r="1" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="350" t="s">
+      <c r="B2" s="349" t="s">
         <v>1607</v>
       </c>
-      <c r="C2" s="350"/>
-      <c r="D2" s="350"/>
-      <c r="E2" s="350"/>
-      <c r="F2" s="350"/>
-      <c r="G2" s="350"/>
-      <c r="H2" s="350"/>
-      <c r="I2" s="350"/>
-      <c r="J2" s="350"/>
-      <c r="K2" s="350"/>
-      <c r="L2" s="350"/>
+      <c r="C2" s="349"/>
+      <c r="D2" s="349"/>
+      <c r="E2" s="349"/>
+      <c r="F2" s="349"/>
+      <c r="G2" s="349"/>
+      <c r="H2" s="349"/>
+      <c r="I2" s="349"/>
+      <c r="J2" s="349"/>
+      <c r="K2" s="349"/>
+      <c r="L2" s="349"/>
     </row>
     <row r="3" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="350"/>
-      <c r="C3" s="350"/>
-      <c r="D3" s="350"/>
-      <c r="E3" s="350"/>
-      <c r="F3" s="350"/>
-      <c r="G3" s="350"/>
-      <c r="H3" s="350"/>
-      <c r="I3" s="350"/>
-      <c r="J3" s="350"/>
-      <c r="K3" s="350"/>
-      <c r="L3" s="350"/>
+      <c r="B3" s="349"/>
+      <c r="C3" s="349"/>
+      <c r="D3" s="349"/>
+      <c r="E3" s="349"/>
+      <c r="F3" s="349"/>
+      <c r="G3" s="349"/>
+      <c r="H3" s="349"/>
+      <c r="I3" s="349"/>
+      <c r="J3" s="349"/>
+      <c r="K3" s="349"/>
+      <c r="L3" s="349"/>
     </row>
     <row r="4" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
@@ -11212,10 +11246,10 @@
     <row r="5" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="6" spans="2:12" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="13"/>
-      <c r="C6" s="351" t="s">
+      <c r="C6" s="350" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="351" t="s">
+      <c r="D6" s="350" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="120" t="s">
@@ -11226,8 +11260,8 @@
     </row>
     <row r="7" spans="2:12" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="13"/>
-      <c r="C7" s="351"/>
-      <c r="D7" s="351"/>
+      <c r="C7" s="350"/>
+      <c r="D7" s="350"/>
       <c r="E7" s="120" t="s">
         <v>100</v>
       </c>
@@ -11753,32 +11787,32 @@
   <sheetData>
     <row r="1" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="350" t="s">
+      <c r="B2" s="349" t="s">
         <v>1608</v>
       </c>
-      <c r="C2" s="350"/>
-      <c r="D2" s="350"/>
-      <c r="E2" s="350"/>
-      <c r="F2" s="350"/>
-      <c r="G2" s="350"/>
-      <c r="H2" s="350"/>
-      <c r="I2" s="350"/>
-      <c r="J2" s="350"/>
-      <c r="K2" s="350"/>
-      <c r="L2" s="350"/>
+      <c r="C2" s="349"/>
+      <c r="D2" s="349"/>
+      <c r="E2" s="349"/>
+      <c r="F2" s="349"/>
+      <c r="G2" s="349"/>
+      <c r="H2" s="349"/>
+      <c r="I2" s="349"/>
+      <c r="J2" s="349"/>
+      <c r="K2" s="349"/>
+      <c r="L2" s="349"/>
     </row>
     <row r="3" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="350"/>
-      <c r="C3" s="350"/>
-      <c r="D3" s="350"/>
-      <c r="E3" s="350"/>
-      <c r="F3" s="350"/>
-      <c r="G3" s="350"/>
-      <c r="H3" s="350"/>
-      <c r="I3" s="350"/>
-      <c r="J3" s="350"/>
-      <c r="K3" s="350"/>
-      <c r="L3" s="350"/>
+      <c r="B3" s="349"/>
+      <c r="C3" s="349"/>
+      <c r="D3" s="349"/>
+      <c r="E3" s="349"/>
+      <c r="F3" s="349"/>
+      <c r="G3" s="349"/>
+      <c r="H3" s="349"/>
+      <c r="I3" s="349"/>
+      <c r="J3" s="349"/>
+      <c r="K3" s="349"/>
+      <c r="L3" s="349"/>
     </row>
     <row r="4" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
@@ -11788,10 +11822,10 @@
     <row r="5" spans="2:12" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="2:12" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="13"/>
-      <c r="C6" s="361" t="s">
+      <c r="C6" s="360" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="363" t="s">
+      <c r="D6" s="362" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="138" t="s">
@@ -11804,8 +11838,8 @@
     </row>
     <row r="7" spans="2:12" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="13"/>
-      <c r="C7" s="362"/>
-      <c r="D7" s="364"/>
+      <c r="C7" s="361"/>
+      <c r="D7" s="363"/>
       <c r="E7" s="236" t="s">
         <v>100</v>
       </c>
@@ -12324,21 +12358,21 @@
       </c>
     </row>
     <row r="2" spans="1:12" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="368" t="s">
+      <c r="B2" s="367" t="s">
         <v>1609</v>
       </c>
-      <c r="C2" s="368"/>
+      <c r="C2" s="367"/>
     </row>
     <row r="3" spans="1:12" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="368"/>
-      <c r="C3" s="368"/>
+      <c r="B3" s="367"/>
+      <c r="C3" s="367"/>
     </row>
     <row r="6" spans="1:12" ht="20" x14ac:dyDescent="0.2">
       <c r="A6" s="13"/>
-      <c r="B6" s="351" t="s">
+      <c r="B6" s="350" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="351" t="s">
+      <c r="C6" s="350" t="s">
         <v>0</v>
       </c>
       <c r="D6" s="157" t="s">
@@ -12357,8 +12391,8 @@
     </row>
     <row r="7" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="13"/>
-      <c r="B7" s="364"/>
-      <c r="C7" s="364"/>
+      <c r="B7" s="363"/>
+      <c r="C7" s="363"/>
       <c r="D7" s="185" t="s">
         <v>1052</v>
       </c>
@@ -12923,21 +12957,21 @@
       <c r="E43" s="175"/>
     </row>
     <row r="44" spans="2:5" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B44" s="367" t="s">
+      <c r="B44" s="366" t="s">
         <v>1020</v>
       </c>
-      <c r="C44" s="367"/>
-      <c r="D44" s="367"/>
-      <c r="E44" s="367"/>
+      <c r="C44" s="366"/>
+      <c r="D44" s="366"/>
+      <c r="E44" s="366"/>
     </row>
     <row r="45" spans="2:5" ht="21" x14ac:dyDescent="0.25">
-      <c r="B45" s="301" t="s">
+      <c r="B45" s="298" t="s">
         <v>1566</v>
       </c>
-      <c r="C45" s="302" t="s">
+      <c r="C45" s="299" t="s">
         <v>1567</v>
       </c>
-      <c r="D45" s="303">
+      <c r="D45" s="300">
         <v>14</v>
       </c>
       <c r="E45" s="206">
@@ -12945,13 +12979,13 @@
       </c>
     </row>
     <row r="46" spans="2:5" ht="21" x14ac:dyDescent="0.25">
-      <c r="B46" s="264" t="s">
+      <c r="B46" s="261" t="s">
         <v>1568</v>
       </c>
       <c r="C46" s="160" t="s">
         <v>1569</v>
       </c>
-      <c r="D46" s="304">
+      <c r="D46" s="301">
         <v>14</v>
       </c>
       <c r="E46" s="207">
@@ -12959,13 +12993,13 @@
       </c>
     </row>
     <row r="47" spans="2:5" ht="21" x14ac:dyDescent="0.25">
-      <c r="B47" s="264" t="s">
+      <c r="B47" s="261" t="s">
         <v>1570</v>
       </c>
       <c r="C47" s="160" t="s">
         <v>1571</v>
       </c>
-      <c r="D47" s="304">
+      <c r="D47" s="301">
         <v>10</v>
       </c>
       <c r="E47" s="207">
@@ -12973,13 +13007,13 @@
       </c>
     </row>
     <row r="48" spans="2:5" ht="21" x14ac:dyDescent="0.25">
-      <c r="B48" s="264" t="s">
+      <c r="B48" s="261" t="s">
         <v>1572</v>
       </c>
       <c r="C48" s="160" t="s">
         <v>1573</v>
       </c>
-      <c r="D48" s="304">
+      <c r="D48" s="301">
         <v>10</v>
       </c>
       <c r="E48" s="207">
@@ -12987,13 +13021,13 @@
       </c>
     </row>
     <row r="49" spans="2:5" ht="21" x14ac:dyDescent="0.25">
-      <c r="B49" s="264" t="s">
+      <c r="B49" s="261" t="s">
         <v>1574</v>
       </c>
       <c r="C49" s="160" t="s">
         <v>1575</v>
       </c>
-      <c r="D49" s="304">
+      <c r="D49" s="301">
         <v>10</v>
       </c>
       <c r="E49" s="207">
@@ -13001,13 +13035,13 @@
       </c>
     </row>
     <row r="50" spans="2:5" ht="21" x14ac:dyDescent="0.25">
-      <c r="B50" s="264" t="s">
+      <c r="B50" s="261" t="s">
         <v>1576</v>
       </c>
       <c r="C50" s="160" t="s">
         <v>1019</v>
       </c>
-      <c r="D50" s="304">
+      <c r="D50" s="301">
         <v>15</v>
       </c>
       <c r="E50" s="207">
@@ -13016,9 +13050,9 @@
     </row>
     <row r="51" spans="2:5" ht="20" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B51" s="116"/>
-      <c r="C51" s="276"/>
-      <c r="D51" s="277"/>
-      <c r="E51" s="278"/>
+      <c r="C51" s="273"/>
+      <c r="D51" s="274"/>
+      <c r="E51" s="275"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -13044,32 +13078,32 @@
   <sheetData>
     <row r="1" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="350" t="s">
+      <c r="B2" s="349" t="s">
         <v>1666</v>
       </c>
-      <c r="C2" s="350"/>
-      <c r="D2" s="350"/>
-      <c r="E2" s="350"/>
-      <c r="F2" s="350"/>
-      <c r="G2" s="350"/>
-      <c r="H2" s="350"/>
-      <c r="I2" s="350"/>
-      <c r="J2" s="350"/>
-      <c r="K2" s="350"/>
-      <c r="L2" s="350"/>
+      <c r="C2" s="349"/>
+      <c r="D2" s="349"/>
+      <c r="E2" s="349"/>
+      <c r="F2" s="349"/>
+      <c r="G2" s="349"/>
+      <c r="H2" s="349"/>
+      <c r="I2" s="349"/>
+      <c r="J2" s="349"/>
+      <c r="K2" s="349"/>
+      <c r="L2" s="349"/>
     </row>
     <row r="3" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="350"/>
-      <c r="C3" s="350"/>
-      <c r="D3" s="350"/>
-      <c r="E3" s="350"/>
-      <c r="F3" s="350"/>
-      <c r="G3" s="350"/>
-      <c r="H3" s="350"/>
-      <c r="I3" s="350"/>
-      <c r="J3" s="350"/>
-      <c r="K3" s="350"/>
-      <c r="L3" s="350"/>
+      <c r="B3" s="349"/>
+      <c r="C3" s="349"/>
+      <c r="D3" s="349"/>
+      <c r="E3" s="349"/>
+      <c r="F3" s="349"/>
+      <c r="G3" s="349"/>
+      <c r="H3" s="349"/>
+      <c r="I3" s="349"/>
+      <c r="J3" s="349"/>
+      <c r="K3" s="349"/>
+      <c r="L3" s="349"/>
     </row>
     <row r="4" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
@@ -13079,10 +13113,10 @@
     <row r="5" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="6" spans="2:12" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="13"/>
-      <c r="C6" s="351" t="s">
+      <c r="C6" s="350" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="351" t="s">
+      <c r="D6" s="350" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="120" t="s">
@@ -13093,8 +13127,8 @@
     </row>
     <row r="7" spans="2:12" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="13"/>
-      <c r="C7" s="351"/>
-      <c r="D7" s="351"/>
+      <c r="C7" s="350"/>
+      <c r="D7" s="350"/>
       <c r="E7" s="120" t="s">
         <v>100</v>
       </c>
@@ -13561,11 +13595,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="3:7" ht="34" x14ac:dyDescent="0.4">
-      <c r="D1" s="369" t="s">
+      <c r="D1" s="368" t="s">
         <v>1179</v>
       </c>
-      <c r="E1" s="369"/>
-      <c r="F1" s="369"/>
+      <c r="E1" s="368"/>
+      <c r="F1" s="368"/>
     </row>
     <row r="2" spans="3:7" ht="29" x14ac:dyDescent="0.35">
       <c r="D2" s="216"/>
@@ -13584,10 +13618,10 @@
     </row>
     <row r="5" spans="3:7" ht="20" x14ac:dyDescent="0.2">
       <c r="C5" s="13"/>
-      <c r="D5" s="354" t="s">
+      <c r="D5" s="353" t="s">
         <v>102</v>
       </c>
-      <c r="E5" s="354" t="s">
+      <c r="E5" s="353" t="s">
         <v>0</v>
       </c>
       <c r="F5" s="8" t="s">
@@ -13597,8 +13631,8 @@
     </row>
     <row r="6" spans="3:7" ht="20" x14ac:dyDescent="0.2">
       <c r="C6" s="13"/>
-      <c r="D6" s="355"/>
-      <c r="E6" s="355"/>
+      <c r="D6" s="354"/>
+      <c r="E6" s="354"/>
       <c r="F6" s="16" t="s">
         <v>100</v>
       </c>
@@ -13606,18 +13640,18 @@
     </row>
     <row r="7" spans="3:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C7" s="13"/>
-      <c r="D7" s="382" t="s">
+      <c r="D7" s="381" t="s">
         <v>965</v>
       </c>
-      <c r="E7" s="383"/>
-      <c r="F7" s="384"/>
+      <c r="E7" s="382"/>
+      <c r="F7" s="383"/>
       <c r="G7" s="13"/>
     </row>
     <row r="8" spans="3:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C8" s="13"/>
-      <c r="D8" s="385"/>
-      <c r="E8" s="386"/>
-      <c r="F8" s="387"/>
+      <c r="D8" s="384"/>
+      <c r="E8" s="385"/>
+      <c r="F8" s="386"/>
       <c r="G8" s="13"/>
     </row>
     <row r="9" spans="3:7" ht="21" x14ac:dyDescent="0.25">
@@ -13948,16 +13982,16 @@
       </c>
     </row>
     <row r="38" spans="4:6" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D38" s="370" t="s">
+      <c r="D38" s="369" t="s">
         <v>966</v>
       </c>
-      <c r="E38" s="388"/>
-      <c r="F38" s="389"/>
+      <c r="E38" s="387"/>
+      <c r="F38" s="388"/>
     </row>
     <row r="39" spans="4:6" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D39" s="390"/>
-      <c r="E39" s="391"/>
-      <c r="F39" s="392"/>
+      <c r="D39" s="389"/>
+      <c r="E39" s="390"/>
+      <c r="F39" s="391"/>
     </row>
     <row r="40" spans="4:6" ht="19" x14ac:dyDescent="0.25">
       <c r="D40" s="169" t="s">
@@ -14048,16 +14082,16 @@
       </c>
     </row>
     <row r="48" spans="4:6" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D48" s="376" t="s">
+      <c r="D48" s="375" t="s">
         <v>967</v>
       </c>
-      <c r="E48" s="377"/>
-      <c r="F48" s="378"/>
+      <c r="E48" s="376"/>
+      <c r="F48" s="377"/>
     </row>
     <row r="49" spans="4:6" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D49" s="379"/>
-      <c r="E49" s="380"/>
-      <c r="F49" s="381"/>
+      <c r="D49" s="378"/>
+      <c r="E49" s="379"/>
+      <c r="F49" s="380"/>
     </row>
     <row r="50" spans="4:6" ht="19" x14ac:dyDescent="0.25">
       <c r="D50" s="169" t="s">
@@ -14203,16 +14237,16 @@
       </c>
     </row>
     <row r="63" spans="4:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D63" s="370" t="s">
+      <c r="D63" s="369" t="s">
         <v>968</v>
       </c>
-      <c r="E63" s="371"/>
-      <c r="F63" s="372"/>
+      <c r="E63" s="370"/>
+      <c r="F63" s="371"/>
     </row>
     <row r="64" spans="4:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D64" s="373"/>
-      <c r="E64" s="374"/>
-      <c r="F64" s="375"/>
+      <c r="D64" s="372"/>
+      <c r="E64" s="373"/>
+      <c r="F64" s="374"/>
     </row>
     <row r="65" spans="4:6" ht="19" x14ac:dyDescent="0.25">
       <c r="D65" s="169" t="s">
@@ -14270,16 +14304,16 @@
       </c>
     </row>
     <row r="70" spans="4:6" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D70" s="376" t="s">
+      <c r="D70" s="375" t="s">
         <v>969</v>
       </c>
-      <c r="E70" s="377"/>
-      <c r="F70" s="378"/>
+      <c r="E70" s="376"/>
+      <c r="F70" s="377"/>
     </row>
     <row r="71" spans="4:6" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D71" s="379"/>
-      <c r="E71" s="380"/>
-      <c r="F71" s="381"/>
+      <c r="D71" s="378"/>
+      <c r="E71" s="379"/>
+      <c r="F71" s="380"/>
     </row>
     <row r="72" spans="4:6" ht="19" x14ac:dyDescent="0.25">
       <c r="D72" s="169" t="s">
@@ -14392,16 +14426,16 @@
       </c>
     </row>
     <row r="82" spans="4:6" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D82" s="376" t="s">
+      <c r="D82" s="375" t="s">
         <v>970</v>
       </c>
-      <c r="E82" s="377"/>
-      <c r="F82" s="378"/>
+      <c r="E82" s="376"/>
+      <c r="F82" s="377"/>
     </row>
     <row r="83" spans="4:6" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D83" s="379"/>
-      <c r="E83" s="380"/>
-      <c r="F83" s="381"/>
+      <c r="D83" s="378"/>
+      <c r="E83" s="379"/>
+      <c r="F83" s="380"/>
     </row>
     <row r="84" spans="4:6" ht="19" x14ac:dyDescent="0.25">
       <c r="D84" s="169" t="s">
@@ -14569,16 +14603,16 @@
       </c>
     </row>
     <row r="99" spans="4:6" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D99" s="376" t="s">
+      <c r="D99" s="375" t="s">
         <v>971</v>
       </c>
-      <c r="E99" s="377"/>
-      <c r="F99" s="378"/>
+      <c r="E99" s="376"/>
+      <c r="F99" s="377"/>
     </row>
     <row r="100" spans="4:6" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D100" s="379"/>
-      <c r="E100" s="380"/>
-      <c r="F100" s="381"/>
+      <c r="D100" s="378"/>
+      <c r="E100" s="379"/>
+      <c r="F100" s="380"/>
     </row>
     <row r="101" spans="4:6" ht="19" x14ac:dyDescent="0.25">
       <c r="D101" s="169" t="s">
@@ -14647,41 +14681,41 @@
       </c>
     </row>
     <row r="2" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="350" t="s">
+      <c r="B2" s="349" t="s">
         <v>1177</v>
       </c>
-      <c r="C2" s="350"/>
-      <c r="D2" s="350"/>
-      <c r="E2" s="350"/>
-      <c r="F2" s="350"/>
-      <c r="G2" s="350"/>
-      <c r="H2" s="350"/>
-      <c r="I2" s="350"/>
-      <c r="J2" s="350"/>
-      <c r="K2" s="350"/>
-      <c r="L2" s="350"/>
+      <c r="C2" s="349"/>
+      <c r="D2" s="349"/>
+      <c r="E2" s="349"/>
+      <c r="F2" s="349"/>
+      <c r="G2" s="349"/>
+      <c r="H2" s="349"/>
+      <c r="I2" s="349"/>
+      <c r="J2" s="349"/>
+      <c r="K2" s="349"/>
+      <c r="L2" s="349"/>
     </row>
     <row r="3" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="350"/>
-      <c r="C3" s="350"/>
-      <c r="D3" s="350"/>
-      <c r="E3" s="350"/>
-      <c r="F3" s="350"/>
-      <c r="G3" s="350"/>
-      <c r="H3" s="350"/>
-      <c r="I3" s="350"/>
-      <c r="J3" s="350"/>
-      <c r="K3" s="350"/>
-      <c r="L3" s="350"/>
+      <c r="B3" s="349"/>
+      <c r="C3" s="349"/>
+      <c r="D3" s="349"/>
+      <c r="E3" s="349"/>
+      <c r="F3" s="349"/>
+      <c r="G3" s="349"/>
+      <c r="H3" s="349"/>
+      <c r="I3" s="349"/>
+      <c r="J3" s="349"/>
+      <c r="K3" s="349"/>
+      <c r="L3" s="349"/>
     </row>
     <row r="4" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="6" spans="2:12" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="13"/>
-      <c r="C6" s="351" t="s">
+      <c r="C6" s="350" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="351" t="s">
+      <c r="D6" s="350" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="120" t="s">
@@ -14692,8 +14726,8 @@
     </row>
     <row r="7" spans="2:12" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="13"/>
-      <c r="C7" s="364"/>
-      <c r="D7" s="364"/>
+      <c r="C7" s="363"/>
+      <c r="D7" s="363"/>
       <c r="E7" s="157" t="s">
         <v>100</v>
       </c>
@@ -15145,45 +15179,45 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="350" t="s">
+      <c r="A2" s="349" t="s">
         <v>1590</v>
       </c>
-      <c r="B2" s="350"/>
-      <c r="C2" s="350"/>
-      <c r="D2" s="350"/>
-      <c r="E2" s="350"/>
-      <c r="F2" s="350"/>
-      <c r="G2" s="350"/>
-      <c r="H2" s="350"/>
-      <c r="I2" s="350"/>
-      <c r="J2" s="350"/>
-      <c r="K2" s="350"/>
+      <c r="B2" s="349"/>
+      <c r="C2" s="349"/>
+      <c r="D2" s="349"/>
+      <c r="E2" s="349"/>
+      <c r="F2" s="349"/>
+      <c r="G2" s="349"/>
+      <c r="H2" s="349"/>
+      <c r="I2" s="349"/>
+      <c r="J2" s="349"/>
+      <c r="K2" s="349"/>
     </row>
     <row r="3" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="350"/>
-      <c r="B3" s="350"/>
-      <c r="C3" s="350"/>
-      <c r="D3" s="350"/>
-      <c r="E3" s="350"/>
-      <c r="F3" s="350"/>
-      <c r="G3" s="350"/>
-      <c r="H3" s="350"/>
-      <c r="I3" s="350"/>
-      <c r="J3" s="350"/>
-      <c r="K3" s="350"/>
+      <c r="A3" s="349"/>
+      <c r="B3" s="349"/>
+      <c r="C3" s="349"/>
+      <c r="D3" s="349"/>
+      <c r="E3" s="349"/>
+      <c r="F3" s="349"/>
+      <c r="G3" s="349"/>
+      <c r="H3" s="349"/>
+      <c r="I3" s="349"/>
+      <c r="J3" s="349"/>
+      <c r="K3" s="349"/>
     </row>
     <row r="4" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="350"/>
-      <c r="B4" s="350"/>
-      <c r="C4" s="350"/>
-      <c r="D4" s="350"/>
-      <c r="E4" s="350"/>
-      <c r="F4" s="350"/>
-      <c r="G4" s="350"/>
-      <c r="H4" s="350"/>
-      <c r="I4" s="350"/>
-      <c r="J4" s="350"/>
-      <c r="K4" s="350"/>
+      <c r="A4" s="349"/>
+      <c r="B4" s="349"/>
+      <c r="C4" s="349"/>
+      <c r="D4" s="349"/>
+      <c r="E4" s="349"/>
+      <c r="F4" s="349"/>
+      <c r="G4" s="349"/>
+      <c r="H4" s="349"/>
+      <c r="I4" s="349"/>
+      <c r="J4" s="349"/>
+      <c r="K4" s="349"/>
     </row>
     <row r="5" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="119"/>
@@ -15200,10 +15234,10 @@
     </row>
     <row r="6" spans="1:11" ht="20" x14ac:dyDescent="0.2">
       <c r="A6" s="13"/>
-      <c r="B6" s="351" t="s">
+      <c r="B6" s="350" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="351" t="s">
+      <c r="C6" s="350" t="s">
         <v>0</v>
       </c>
       <c r="D6" s="120" t="s">
@@ -15221,8 +15255,8 @@
     </row>
     <row r="7" spans="1:11" ht="20" x14ac:dyDescent="0.2">
       <c r="A7" s="13"/>
-      <c r="B7" s="351"/>
-      <c r="C7" s="351"/>
+      <c r="B7" s="350"/>
+      <c r="C7" s="350"/>
       <c r="D7" s="120" t="s">
         <v>100</v>
       </c>
@@ -15554,32 +15588,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A1" s="393" t="s">
+      <c r="A1" s="392" t="s">
         <v>1617</v>
       </c>
-      <c r="B1" s="393"/>
-      <c r="C1" s="393"/>
-      <c r="D1" s="393"/>
-      <c r="E1" s="393"/>
-      <c r="F1" s="393"/>
-      <c r="G1" s="393"/>
-      <c r="H1" s="393"/>
-      <c r="I1" s="393"/>
-      <c r="J1" s="393"/>
-      <c r="K1" s="393"/>
+      <c r="B1" s="392"/>
+      <c r="C1" s="392"/>
+      <c r="D1" s="392"/>
+      <c r="E1" s="392"/>
+      <c r="F1" s="392"/>
+      <c r="G1" s="392"/>
+      <c r="H1" s="392"/>
+      <c r="I1" s="392"/>
+      <c r="J1" s="392"/>
+      <c r="K1" s="392"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" s="393"/>
-      <c r="B2" s="393"/>
-      <c r="C2" s="393"/>
-      <c r="D2" s="393"/>
-      <c r="E2" s="393"/>
-      <c r="F2" s="393"/>
-      <c r="G2" s="393"/>
-      <c r="H2" s="393"/>
-      <c r="I2" s="393"/>
-      <c r="J2" s="393"/>
-      <c r="K2" s="393"/>
+      <c r="A2" s="392"/>
+      <c r="B2" s="392"/>
+      <c r="C2" s="392"/>
+      <c r="D2" s="392"/>
+      <c r="E2" s="392"/>
+      <c r="F2" s="392"/>
+      <c r="G2" s="392"/>
+      <c r="H2" s="392"/>
+      <c r="I2" s="392"/>
+      <c r="J2" s="392"/>
+      <c r="K2" s="392"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
@@ -15588,10 +15622,10 @@
     </row>
     <row r="5" spans="1:11" ht="20" x14ac:dyDescent="0.2">
       <c r="A5" s="13"/>
-      <c r="B5" s="351" t="s">
+      <c r="B5" s="350" t="s">
         <v>102</v>
       </c>
-      <c r="C5" s="351" t="s">
+      <c r="C5" s="350" t="s">
         <v>0</v>
       </c>
       <c r="D5" s="120" t="s">
@@ -15607,8 +15641,8 @@
     </row>
     <row r="6" spans="1:11" ht="20" x14ac:dyDescent="0.2">
       <c r="A6" s="13"/>
-      <c r="B6" s="351"/>
-      <c r="C6" s="351"/>
+      <c r="B6" s="350"/>
+      <c r="C6" s="350"/>
       <c r="D6" s="120" t="s">
         <v>100</v>
       </c>
@@ -15763,43 +15797,43 @@
   <sheetData>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>1702</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="393" t="s">
-        <v>1707</v>
-      </c>
-      <c r="B3" s="393"/>
-      <c r="C3" s="393"/>
-      <c r="D3" s="393"/>
-      <c r="E3" s="393"/>
-      <c r="F3" s="393"/>
-      <c r="G3" s="393"/>
-      <c r="H3" s="393"/>
-      <c r="I3" s="393"/>
-      <c r="J3" s="393"/>
-      <c r="K3" s="393"/>
+      <c r="A3" s="392" t="s">
+        <v>1706</v>
+      </c>
+      <c r="B3" s="392"/>
+      <c r="C3" s="392"/>
+      <c r="D3" s="392"/>
+      <c r="E3" s="392"/>
+      <c r="F3" s="392"/>
+      <c r="G3" s="392"/>
+      <c r="H3" s="392"/>
+      <c r="I3" s="392"/>
+      <c r="J3" s="392"/>
+      <c r="K3" s="392"/>
     </row>
     <row r="4" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="393"/>
-      <c r="B4" s="393"/>
-      <c r="C4" s="393"/>
-      <c r="D4" s="393"/>
-      <c r="E4" s="393"/>
-      <c r="F4" s="393"/>
-      <c r="G4" s="393"/>
-      <c r="H4" s="393"/>
-      <c r="I4" s="393"/>
-      <c r="J4" s="393"/>
-      <c r="K4" s="393"/>
+      <c r="A4" s="392"/>
+      <c r="B4" s="392"/>
+      <c r="C4" s="392"/>
+      <c r="D4" s="392"/>
+      <c r="E4" s="392"/>
+      <c r="F4" s="392"/>
+      <c r="G4" s="392"/>
+      <c r="H4" s="392"/>
+      <c r="I4" s="392"/>
+      <c r="J4" s="392"/>
+      <c r="K4" s="392"/>
     </row>
     <row r="7" spans="1:11" ht="20" x14ac:dyDescent="0.2">
       <c r="A7" s="13"/>
-      <c r="B7" s="351" t="s">
+      <c r="B7" s="350" t="s">
         <v>102</v>
       </c>
-      <c r="C7" s="351" t="s">
+      <c r="C7" s="350" t="s">
         <v>0</v>
       </c>
       <c r="D7" s="120" t="s">
@@ -15815,8 +15849,8 @@
     </row>
     <row r="8" spans="1:11" ht="20" x14ac:dyDescent="0.2">
       <c r="A8" s="13"/>
-      <c r="B8" s="364"/>
-      <c r="C8" s="364"/>
+      <c r="B8" s="363"/>
+      <c r="C8" s="363"/>
       <c r="D8" s="157" t="s">
         <v>100</v>
       </c>
@@ -15850,7 +15884,7 @@
     <row r="10" spans="1:11" ht="21" x14ac:dyDescent="0.25">
       <c r="A10" s="7"/>
       <c r="B10" s="113" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="C10" s="113" t="s">
         <v>83</v>
@@ -16091,39 +16125,39 @@
       </c>
     </row>
     <row r="3" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="393" t="s">
+      <c r="A3" s="392" t="s">
         <v>1671</v>
       </c>
-      <c r="B3" s="393"/>
-      <c r="C3" s="393"/>
-      <c r="D3" s="393"/>
-      <c r="E3" s="393"/>
-      <c r="F3" s="393"/>
-      <c r="G3" s="393"/>
-      <c r="H3" s="393"/>
-      <c r="I3" s="393"/>
-      <c r="J3" s="393"/>
-      <c r="K3" s="393"/>
+      <c r="B3" s="392"/>
+      <c r="C3" s="392"/>
+      <c r="D3" s="392"/>
+      <c r="E3" s="392"/>
+      <c r="F3" s="392"/>
+      <c r="G3" s="392"/>
+      <c r="H3" s="392"/>
+      <c r="I3" s="392"/>
+      <c r="J3" s="392"/>
+      <c r="K3" s="392"/>
     </row>
     <row r="4" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="393"/>
-      <c r="B4" s="393"/>
-      <c r="C4" s="393"/>
-      <c r="D4" s="393"/>
-      <c r="E4" s="393"/>
-      <c r="F4" s="393"/>
-      <c r="G4" s="393"/>
-      <c r="H4" s="393"/>
-      <c r="I4" s="393"/>
-      <c r="J4" s="393"/>
-      <c r="K4" s="393"/>
+      <c r="A4" s="392"/>
+      <c r="B4" s="392"/>
+      <c r="C4" s="392"/>
+      <c r="D4" s="392"/>
+      <c r="E4" s="392"/>
+      <c r="F4" s="392"/>
+      <c r="G4" s="392"/>
+      <c r="H4" s="392"/>
+      <c r="I4" s="392"/>
+      <c r="J4" s="392"/>
+      <c r="K4" s="392"/>
     </row>
     <row r="7" spans="1:11" ht="20" x14ac:dyDescent="0.2">
       <c r="A7" s="13"/>
-      <c r="B7" s="351" t="s">
+      <c r="B7" s="350" t="s">
         <v>102</v>
       </c>
-      <c r="C7" s="351" t="s">
+      <c r="C7" s="350" t="s">
         <v>0</v>
       </c>
       <c r="D7" s="120" t="s">
@@ -16139,8 +16173,8 @@
     </row>
     <row r="8" spans="1:11" ht="20" x14ac:dyDescent="0.2">
       <c r="A8" s="13"/>
-      <c r="B8" s="364"/>
-      <c r="C8" s="364"/>
+      <c r="B8" s="363"/>
+      <c r="C8" s="363"/>
       <c r="D8" s="157" t="s">
         <v>100</v>
       </c>
@@ -16335,32 +16369,32 @@
   <sheetData>
     <row r="1" spans="2:16" ht="19" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:16" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="350" t="s">
+      <c r="B2" s="349" t="s">
         <v>1628</v>
       </c>
-      <c r="C2" s="350"/>
-      <c r="D2" s="350"/>
-      <c r="E2" s="350"/>
-      <c r="F2" s="350"/>
-      <c r="G2" s="350"/>
-      <c r="H2" s="350"/>
-      <c r="I2" s="350"/>
-      <c r="J2" s="350"/>
-      <c r="K2" s="350"/>
-      <c r="L2" s="350"/>
+      <c r="C2" s="349"/>
+      <c r="D2" s="349"/>
+      <c r="E2" s="349"/>
+      <c r="F2" s="349"/>
+      <c r="G2" s="349"/>
+      <c r="H2" s="349"/>
+      <c r="I2" s="349"/>
+      <c r="J2" s="349"/>
+      <c r="K2" s="349"/>
+      <c r="L2" s="349"/>
     </row>
     <row r="3" spans="2:16" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="350"/>
-      <c r="C3" s="350"/>
-      <c r="D3" s="350"/>
-      <c r="E3" s="350"/>
-      <c r="F3" s="350"/>
-      <c r="G3" s="350"/>
-      <c r="H3" s="350"/>
-      <c r="I3" s="350"/>
-      <c r="J3" s="350"/>
-      <c r="K3" s="350"/>
-      <c r="L3" s="350"/>
+      <c r="B3" s="349"/>
+      <c r="C3" s="349"/>
+      <c r="D3" s="349"/>
+      <c r="E3" s="349"/>
+      <c r="F3" s="349"/>
+      <c r="G3" s="349"/>
+      <c r="H3" s="349"/>
+      <c r="I3" s="349"/>
+      <c r="J3" s="349"/>
+      <c r="K3" s="349"/>
+      <c r="L3" s="349"/>
     </row>
     <row r="4" spans="2:16" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
@@ -16370,10 +16404,10 @@
     <row r="5" spans="2:16" ht="19" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="2:16" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="13"/>
-      <c r="C6" s="351" t="s">
+      <c r="C6" s="350" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="351" t="s">
+      <c r="D6" s="350" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="128" t="s">
@@ -16383,8 +16417,8 @@
     </row>
     <row r="7" spans="2:16" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="13"/>
-      <c r="C7" s="364"/>
-      <c r="D7" s="364"/>
+      <c r="C7" s="363"/>
+      <c r="D7" s="363"/>
       <c r="E7" s="131" t="s">
         <v>100</v>
       </c>
@@ -16692,7 +16726,7 @@
       <c r="D30" s="130" t="s">
         <v>1562</v>
       </c>
-      <c r="E30" s="320">
+      <c r="E30" s="317">
         <v>7.510670521822937</v>
       </c>
       <c r="F30" s="2"/>
@@ -16911,41 +16945,41 @@
       </c>
     </row>
     <row r="2" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="350" t="s">
+      <c r="B2" s="349" t="s">
         <v>1632</v>
       </c>
-      <c r="C2" s="350"/>
-      <c r="D2" s="350"/>
-      <c r="E2" s="350"/>
-      <c r="F2" s="350"/>
-      <c r="G2" s="350"/>
-      <c r="H2" s="350"/>
-      <c r="I2" s="350"/>
-      <c r="J2" s="350"/>
-      <c r="K2" s="350"/>
-      <c r="L2" s="350"/>
+      <c r="C2" s="349"/>
+      <c r="D2" s="349"/>
+      <c r="E2" s="349"/>
+      <c r="F2" s="349"/>
+      <c r="G2" s="349"/>
+      <c r="H2" s="349"/>
+      <c r="I2" s="349"/>
+      <c r="J2" s="349"/>
+      <c r="K2" s="349"/>
+      <c r="L2" s="349"/>
     </row>
     <row r="3" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="350"/>
-      <c r="C3" s="350"/>
-      <c r="D3" s="350"/>
-      <c r="E3" s="350"/>
-      <c r="F3" s="350"/>
-      <c r="G3" s="350"/>
-      <c r="H3" s="350"/>
-      <c r="I3" s="350"/>
-      <c r="J3" s="350"/>
-      <c r="K3" s="350"/>
-      <c r="L3" s="350"/>
+      <c r="B3" s="349"/>
+      <c r="C3" s="349"/>
+      <c r="D3" s="349"/>
+      <c r="E3" s="349"/>
+      <c r="F3" s="349"/>
+      <c r="G3" s="349"/>
+      <c r="H3" s="349"/>
+      <c r="I3" s="349"/>
+      <c r="J3" s="349"/>
+      <c r="K3" s="349"/>
+      <c r="L3" s="349"/>
     </row>
     <row r="4" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="6" spans="2:12" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="13"/>
-      <c r="C6" s="351" t="s">
+      <c r="C6" s="350" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="351" t="s">
+      <c r="D6" s="350" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="120" t="s">
@@ -16956,8 +16990,8 @@
     </row>
     <row r="7" spans="2:12" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="13"/>
-      <c r="C7" s="364"/>
-      <c r="D7" s="364"/>
+      <c r="C7" s="363"/>
+      <c r="D7" s="363"/>
       <c r="E7" s="157" t="s">
         <v>100</v>
       </c>
@@ -17356,41 +17390,41 @@
       </c>
     </row>
     <row r="2" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="350" t="s">
+      <c r="B2" s="349" t="s">
         <v>1633</v>
       </c>
-      <c r="C2" s="350"/>
-      <c r="D2" s="350"/>
-      <c r="E2" s="350"/>
-      <c r="F2" s="350"/>
-      <c r="G2" s="350"/>
-      <c r="H2" s="350"/>
-      <c r="I2" s="350"/>
-      <c r="J2" s="350"/>
-      <c r="K2" s="350"/>
-      <c r="L2" s="350"/>
+      <c r="C2" s="349"/>
+      <c r="D2" s="349"/>
+      <c r="E2" s="349"/>
+      <c r="F2" s="349"/>
+      <c r="G2" s="349"/>
+      <c r="H2" s="349"/>
+      <c r="I2" s="349"/>
+      <c r="J2" s="349"/>
+      <c r="K2" s="349"/>
+      <c r="L2" s="349"/>
     </row>
     <row r="3" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="350"/>
-      <c r="C3" s="350"/>
-      <c r="D3" s="350"/>
-      <c r="E3" s="350"/>
-      <c r="F3" s="350"/>
-      <c r="G3" s="350"/>
-      <c r="H3" s="350"/>
-      <c r="I3" s="350"/>
-      <c r="J3" s="350"/>
-      <c r="K3" s="350"/>
-      <c r="L3" s="350"/>
+      <c r="B3" s="349"/>
+      <c r="C3" s="349"/>
+      <c r="D3" s="349"/>
+      <c r="E3" s="349"/>
+      <c r="F3" s="349"/>
+      <c r="G3" s="349"/>
+      <c r="H3" s="349"/>
+      <c r="I3" s="349"/>
+      <c r="J3" s="349"/>
+      <c r="K3" s="349"/>
+      <c r="L3" s="349"/>
     </row>
     <row r="4" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="6" spans="2:12" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="13"/>
-      <c r="C6" s="351" t="s">
+      <c r="C6" s="350" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="351" t="s">
+      <c r="D6" s="350" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="120" t="s">
@@ -17401,8 +17435,8 @@
     </row>
     <row r="7" spans="2:12" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="13"/>
-      <c r="C7" s="351"/>
-      <c r="D7" s="351"/>
+      <c r="C7" s="350"/>
+      <c r="D7" s="350"/>
       <c r="E7" s="120" t="s">
         <v>100</v>
       </c>
@@ -17751,32 +17785,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A1" s="393" t="s">
+      <c r="A1" s="392" t="s">
         <v>1634</v>
       </c>
-      <c r="B1" s="393"/>
-      <c r="C1" s="393"/>
-      <c r="D1" s="393"/>
-      <c r="E1" s="393"/>
-      <c r="F1" s="393"/>
-      <c r="G1" s="393"/>
-      <c r="H1" s="393"/>
-      <c r="I1" s="393"/>
-      <c r="J1" s="393"/>
-      <c r="K1" s="393"/>
+      <c r="B1" s="392"/>
+      <c r="C1" s="392"/>
+      <c r="D1" s="392"/>
+      <c r="E1" s="392"/>
+      <c r="F1" s="392"/>
+      <c r="G1" s="392"/>
+      <c r="H1" s="392"/>
+      <c r="I1" s="392"/>
+      <c r="J1" s="392"/>
+      <c r="K1" s="392"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" s="393"/>
-      <c r="B2" s="393"/>
-      <c r="C2" s="393"/>
-      <c r="D2" s="393"/>
-      <c r="E2" s="393"/>
-      <c r="F2" s="393"/>
-      <c r="G2" s="393"/>
-      <c r="H2" s="393"/>
-      <c r="I2" s="393"/>
-      <c r="J2" s="393"/>
-      <c r="K2" s="393"/>
+      <c r="A2" s="392"/>
+      <c r="B2" s="392"/>
+      <c r="C2" s="392"/>
+      <c r="D2" s="392"/>
+      <c r="E2" s="392"/>
+      <c r="F2" s="392"/>
+      <c r="G2" s="392"/>
+      <c r="H2" s="392"/>
+      <c r="I2" s="392"/>
+      <c r="J2" s="392"/>
+      <c r="K2" s="392"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
@@ -17785,10 +17819,10 @@
     </row>
     <row r="5" spans="1:11" ht="20" x14ac:dyDescent="0.2">
       <c r="A5" s="13"/>
-      <c r="B5" s="351" t="s">
+      <c r="B5" s="350" t="s">
         <v>102</v>
       </c>
-      <c r="C5" s="351" t="s">
+      <c r="C5" s="350" t="s">
         <v>0</v>
       </c>
       <c r="D5" s="120" t="s">
@@ -17806,8 +17840,8 @@
     </row>
     <row r="6" spans="1:11" ht="20" x14ac:dyDescent="0.2">
       <c r="A6" s="13"/>
-      <c r="B6" s="351"/>
-      <c r="C6" s="351"/>
+      <c r="B6" s="350"/>
+      <c r="C6" s="350"/>
       <c r="D6" s="120" t="s">
         <v>100</v>
       </c>
@@ -17956,7 +17990,7 @@
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
-  <dimension ref="B1:J61"/>
+  <dimension ref="B1:J64"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.5" style="30" customWidth="1"/>
@@ -17972,32 +18006,32 @@
       <c r="B1" s="189"/>
     </row>
     <row r="2" spans="2:10" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="395" t="s">
+      <c r="B2" s="394" t="s">
         <v>1640</v>
       </c>
-      <c r="C2" s="395"/>
-      <c r="D2" s="396"/>
-      <c r="E2" s="396"/>
-      <c r="F2" s="396"/>
-      <c r="G2" s="397"/>
+      <c r="C2" s="394"/>
+      <c r="D2" s="395"/>
+      <c r="E2" s="395"/>
+      <c r="F2" s="395"/>
+      <c r="G2" s="396"/>
       <c r="H2" s="38"/>
       <c r="I2" s="38"/>
       <c r="J2" s="38"/>
     </row>
     <row r="3" spans="2:10" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="396"/>
-      <c r="C3" s="396"/>
-      <c r="D3" s="396"/>
-      <c r="E3" s="396"/>
-      <c r="F3" s="396"/>
-      <c r="G3" s="397"/>
+      <c r="B3" s="395"/>
+      <c r="C3" s="395"/>
+      <c r="D3" s="395"/>
+      <c r="E3" s="395"/>
+      <c r="F3" s="395"/>
+      <c r="G3" s="396"/>
       <c r="H3" s="38"/>
       <c r="I3" s="38"/>
       <c r="J3" s="38"/>
     </row>
     <row r="4" spans="2:10" ht="19" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="142" t="s">
-        <v>1589</v>
+        <v>1714</v>
       </c>
       <c r="C4" s="255"/>
       <c r="D4" s="255"/>
@@ -18005,19 +18039,19 @@
       <c r="F4" s="42"/>
     </row>
     <row r="5" spans="2:10" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="324"/>
-      <c r="C5" s="326"/>
-      <c r="D5" s="326"/>
-      <c r="E5" s="324"/>
+      <c r="B5" s="321"/>
+      <c r="C5" s="323"/>
+      <c r="D5" s="323"/>
+      <c r="E5" s="321"/>
     </row>
     <row r="6" spans="2:10" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="348" t="s">
+      <c r="B6" s="347" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="348" t="s">
+      <c r="C6" s="347" t="s">
         <v>106</v>
       </c>
-      <c r="D6" s="348" t="s">
+      <c r="D6" s="347" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="114" t="s">
@@ -18028,10 +18062,10 @@
       </c>
     </row>
     <row r="7" spans="2:10" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="348"/>
-      <c r="C7" s="348"/>
-      <c r="D7" s="348"/>
-      <c r="E7" s="114" t="s">
+      <c r="B7" s="426"/>
+      <c r="C7" s="426"/>
+      <c r="D7" s="426"/>
+      <c r="E7" s="427" t="s">
         <v>100</v>
       </c>
       <c r="F7" s="260" t="s">
@@ -18039,664 +18073,693 @@
       </c>
     </row>
     <row r="8" spans="2:10" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="121" t="s">
+      <c r="B8" s="113" t="s">
         <v>124</v>
       </c>
-      <c r="C8" s="121">
+      <c r="C8" s="113">
         <v>5.6</v>
       </c>
-      <c r="D8" s="121" t="s">
+      <c r="D8" s="113" t="s">
         <v>129</v>
       </c>
       <c r="E8" s="251">
         <v>17.872320895864885</v>
       </c>
-      <c r="F8" s="261"/>
+      <c r="F8" s="421"/>
     </row>
     <row r="9" spans="2:10" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="121" t="s">
+      <c r="B9" s="113" t="s">
         <v>126</v>
       </c>
-      <c r="C9" s="121">
+      <c r="C9" s="113">
         <v>5.6</v>
       </c>
-      <c r="D9" s="121" t="s">
+      <c r="D9" s="113" t="s">
         <v>129</v>
       </c>
       <c r="E9" s="251">
-        <v>20.595713433383818</v>
-      </c>
-      <c r="F9" s="262"/>
+        <v>16.273119463949694</v>
+      </c>
+      <c r="F9" s="422"/>
     </row>
     <row r="10" spans="2:10" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="121" t="s">
+      <c r="B10" s="113" t="s">
         <v>126</v>
       </c>
-      <c r="C10" s="121">
+      <c r="C10" s="113">
         <v>5.6</v>
       </c>
-      <c r="D10" s="121" t="s">
+      <c r="D10" s="113" t="s">
         <v>105</v>
       </c>
       <c r="E10" s="251">
-        <v>20.05736839689752</v>
-      </c>
-      <c r="F10" s="262"/>
+        <v>15.839276699251913</v>
+      </c>
+      <c r="F10" s="422"/>
     </row>
     <row r="11" spans="2:10" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="121" t="s">
+      <c r="B11" s="113" t="s">
         <v>126</v>
       </c>
-      <c r="C11" s="121">
+      <c r="C11" s="113">
         <v>9</v>
       </c>
-      <c r="D11" s="121" t="s">
+      <c r="D11" s="113" t="s">
         <v>131</v>
       </c>
       <c r="E11" s="251">
         <v>10.87383542154298</v>
       </c>
-      <c r="F11" s="262"/>
+      <c r="F11" s="422"/>
     </row>
     <row r="12" spans="2:10" ht="19" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="121" t="s">
+      <c r="B12" s="113" t="s">
         <v>443</v>
       </c>
-      <c r="C12" s="121"/>
-      <c r="D12" s="121" t="s">
+      <c r="C12" s="113"/>
+      <c r="D12" s="113" t="s">
         <v>109</v>
       </c>
       <c r="E12" s="251">
         <v>5.2022121253843681</v>
       </c>
-      <c r="F12" s="262"/>
-      <c r="G12" s="394"/>
-      <c r="H12" s="394"/>
-      <c r="I12" s="394"/>
-      <c r="J12" s="394"/>
+      <c r="F12" s="422"/>
+      <c r="G12" s="393"/>
+      <c r="H12" s="393"/>
+      <c r="I12" s="393"/>
+      <c r="J12" s="393"/>
     </row>
     <row r="13" spans="2:10" ht="19" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="121" t="s">
+      <c r="B13" s="113" t="s">
         <v>1038</v>
       </c>
-      <c r="C13" s="121">
+      <c r="C13" s="113">
         <v>5.6</v>
       </c>
-      <c r="D13" s="121" t="s">
+      <c r="D13" s="113" t="s">
         <v>113</v>
       </c>
       <c r="E13" s="251">
         <v>13.685896553306712</v>
       </c>
-      <c r="F13" s="262"/>
-      <c r="G13" s="394"/>
-      <c r="H13" s="394"/>
-      <c r="I13" s="394"/>
-      <c r="J13" s="394"/>
+      <c r="F13" s="422"/>
+      <c r="G13" s="393"/>
+      <c r="H13" s="393"/>
+      <c r="I13" s="393"/>
+      <c r="J13" s="393"/>
     </row>
     <row r="14" spans="2:10" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="121" t="s">
+      <c r="B14" s="113" t="s">
+        <v>1710</v>
+      </c>
+      <c r="C14" s="113">
+        <v>5.6</v>
+      </c>
+      <c r="D14" s="113" t="s">
+        <v>113</v>
+      </c>
+      <c r="E14" s="251">
+        <v>14.515581256597367</v>
+      </c>
+      <c r="F14" s="422"/>
+    </row>
+    <row r="15" spans="2:10" ht="19" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="113" t="s">
         <v>119</v>
       </c>
-      <c r="C14" s="121">
+      <c r="C15" s="113">
         <v>5.6</v>
       </c>
-      <c r="D14" s="121" t="s">
+      <c r="D15" s="113" t="s">
         <v>129</v>
       </c>
-      <c r="E14" s="251">
+      <c r="E15" s="251">
         <v>28.702556335765752</v>
       </c>
-      <c r="F14" s="262"/>
-    </row>
-    <row r="15" spans="2:10" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="121" t="s">
+      <c r="F15" s="422"/>
+    </row>
+    <row r="16" spans="2:10" ht="19" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="113" t="s">
         <v>118</v>
       </c>
-      <c r="C15" s="121">
+      <c r="C16" s="113">
         <v>5.6</v>
       </c>
-      <c r="D15" s="121" t="s">
+      <c r="D16" s="113" t="s">
         <v>129</v>
       </c>
-      <c r="E15" s="251">
+      <c r="E16" s="251">
         <v>20.611547110927528</v>
       </c>
-      <c r="F15" s="262"/>
-    </row>
-    <row r="16" spans="2:10" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="121" t="s">
+      <c r="F16" s="422"/>
+    </row>
+    <row r="17" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="113" t="s">
         <v>118</v>
       </c>
-      <c r="C16" s="121">
+      <c r="C17" s="113">
         <v>5.6</v>
       </c>
-      <c r="D16" s="121" t="s">
+      <c r="D17" s="113" t="s">
         <v>441</v>
       </c>
-      <c r="E16" s="251">
+      <c r="E17" s="251">
         <v>20.564046078296389</v>
       </c>
-      <c r="F16" s="262"/>
-    </row>
-    <row r="17" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="121" t="s">
+      <c r="F17" s="422"/>
+    </row>
+    <row r="18" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="113" t="s">
         <v>118</v>
       </c>
-      <c r="C17" s="121">
+      <c r="C18" s="113">
         <v>5.6</v>
       </c>
-      <c r="D17" s="121" t="s">
+      <c r="D18" s="113" t="s">
         <v>105</v>
       </c>
-      <c r="E17" s="251">
+      <c r="E18" s="251">
         <v>20.089035751984948</v>
       </c>
-      <c r="F17" s="262"/>
-    </row>
-    <row r="18" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="121" t="s">
+      <c r="F18" s="422"/>
+    </row>
+    <row r="19" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="113" t="s">
         <v>127</v>
       </c>
-      <c r="C18" s="121">
+      <c r="C19" s="113">
         <v>9</v>
       </c>
-      <c r="D18" s="121" t="s">
+      <c r="D19" s="113" t="s">
         <v>105</v>
       </c>
-      <c r="E18" s="251">
+      <c r="E19" s="251">
         <v>10.424158979301483</v>
       </c>
-      <c r="F18" s="262"/>
-    </row>
-    <row r="19" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="121" t="s">
+      <c r="F19" s="422"/>
+    </row>
+    <row r="20" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="113" t="s">
         <v>1039</v>
       </c>
-      <c r="C19" s="121">
+      <c r="C20" s="113">
         <v>5.6</v>
       </c>
-      <c r="D19" s="121" t="s">
-        <v>113</v>
-      </c>
-      <c r="E19" s="251">
-        <v>15.937445500022946</v>
-      </c>
-      <c r="F19" s="262"/>
-    </row>
-    <row r="20" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="121" t="s">
-        <v>1635</v>
-      </c>
-      <c r="C20" s="121">
-        <v>5.6</v>
-      </c>
-      <c r="D20" s="121" t="s">
+      <c r="D20" s="113" t="s">
         <v>113</v>
       </c>
       <c r="E20" s="251">
         <v>13.685896553306712</v>
       </c>
-      <c r="F20" s="262"/>
+      <c r="F20" s="422"/>
     </row>
     <row r="21" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="121" t="s">
+      <c r="B21" s="113" t="s">
+        <v>1635</v>
+      </c>
+      <c r="C21" s="113">
+        <v>5.6</v>
+      </c>
+      <c r="D21" s="113" t="s">
+        <v>113</v>
+      </c>
+      <c r="E21" s="251">
+        <v>13.685896553306712</v>
+      </c>
+      <c r="F21" s="422"/>
+    </row>
+    <row r="22" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="113" t="s">
         <v>122</v>
       </c>
-      <c r="C21" s="121">
+      <c r="C22" s="113">
         <v>3.5</v>
       </c>
-      <c r="D21" s="121" t="s">
+      <c r="D22" s="113" t="s">
         <v>129</v>
       </c>
-      <c r="E21" s="251">
+      <c r="E22" s="251">
         <v>16.076781862407636</v>
       </c>
-      <c r="F21" s="262"/>
-    </row>
-    <row r="22" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="121" t="s">
+      <c r="F22" s="422"/>
+    </row>
+    <row r="23" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="113" t="s">
         <v>122</v>
       </c>
-      <c r="C22" s="121">
+      <c r="C23" s="113">
         <v>10</v>
       </c>
-      <c r="D22" s="121" t="s">
+      <c r="D23" s="113" t="s">
         <v>105</v>
       </c>
-      <c r="E22" s="251">
+      <c r="E23" s="251">
         <v>8.5114507320207426</v>
       </c>
-      <c r="F22" s="262"/>
-    </row>
-    <row r="23" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="121" t="s">
+      <c r="F23" s="422"/>
+    </row>
+    <row r="24" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="113" t="s">
         <v>122</v>
       </c>
-      <c r="C23" s="121">
+      <c r="C24" s="113">
         <v>10</v>
       </c>
-      <c r="D23" s="121" t="s">
+      <c r="D24" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="E23" s="251">
+      <c r="E24" s="251">
         <v>6.7729129377208688</v>
       </c>
-      <c r="F23" s="262"/>
-    </row>
-    <row r="24" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="121" t="s">
+      <c r="F24" s="422"/>
+    </row>
+    <row r="25" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="113" t="s">
         <v>230</v>
       </c>
-      <c r="C24" s="121">
+      <c r="C25" s="113">
         <v>9</v>
       </c>
-      <c r="D24" s="121" t="s">
-        <v>105</v>
-      </c>
-      <c r="E24" s="251">
-        <v>10.424158979301483</v>
-      </c>
-      <c r="F24" s="262"/>
-    </row>
-    <row r="25" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="121" t="s">
-        <v>128</v>
-      </c>
-      <c r="C25" s="121">
-        <v>9</v>
-      </c>
-      <c r="D25" s="121" t="s">
+      <c r="D25" s="113" t="s">
         <v>105</v>
       </c>
       <c r="E25" s="251">
         <v>10.424158979301483</v>
       </c>
-      <c r="F25" s="262"/>
+      <c r="F25" s="422"/>
     </row>
     <row r="26" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="121" t="s">
+      <c r="B26" s="113" t="s">
+        <v>128</v>
+      </c>
+      <c r="C26" s="113">
+        <v>9</v>
+      </c>
+      <c r="D26" s="113" t="s">
+        <v>105</v>
+      </c>
+      <c r="E26" s="251">
+        <v>10.424158979301483</v>
+      </c>
+      <c r="F26" s="422"/>
+    </row>
+    <row r="27" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="113" t="s">
         <v>477</v>
       </c>
-      <c r="C26" s="121">
+      <c r="C27" s="113">
         <v>3.5</v>
       </c>
-      <c r="D26" s="121" t="s">
+      <c r="D27" s="113" t="s">
         <v>129</v>
       </c>
-      <c r="E26" s="251">
+      <c r="E27" s="251">
         <v>15.877277525356831</v>
       </c>
-      <c r="F26" s="262"/>
-    </row>
-    <row r="27" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="121" t="s">
+      <c r="F27" s="422"/>
+    </row>
+    <row r="28" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="113" t="s">
         <v>444</v>
       </c>
-      <c r="C27" s="121"/>
-      <c r="D27" s="121" t="s">
+      <c r="C28" s="113"/>
+      <c r="D28" s="113" t="s">
         <v>109</v>
       </c>
-      <c r="E27" s="251">
+      <c r="E28" s="251">
         <v>5.5188856762586633</v>
       </c>
-      <c r="F27" s="262"/>
-    </row>
-    <row r="28" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="121" t="s">
+      <c r="F28" s="422"/>
+    </row>
+    <row r="29" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="113" t="s">
         <v>231</v>
       </c>
-      <c r="C28" s="121"/>
-      <c r="D28" s="121" t="s">
+      <c r="C29" s="113"/>
+      <c r="D29" s="113" t="s">
         <v>237</v>
       </c>
-      <c r="E28" s="251">
+      <c r="E29" s="251">
         <v>6.4150718252329142</v>
       </c>
-      <c r="F28" s="262"/>
-    </row>
-    <row r="29" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="121" t="s">
+      <c r="F29" s="422"/>
+    </row>
+    <row r="30" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="113" t="s">
         <v>445</v>
       </c>
-      <c r="C29" s="121"/>
-      <c r="D29" s="121" t="s">
+      <c r="C30" s="113"/>
+      <c r="D30" s="113" t="s">
         <v>83</v>
       </c>
-      <c r="E29" s="251">
+      <c r="E30" s="251">
         <v>6.3770709991280006</v>
       </c>
-      <c r="F29" s="262"/>
-    </row>
-    <row r="30" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="121" t="s">
+      <c r="F30" s="422"/>
+    </row>
+    <row r="31" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="113" t="s">
         <v>232</v>
       </c>
-      <c r="C30" s="121"/>
-      <c r="D30" s="121" t="s">
+      <c r="C31" s="113"/>
+      <c r="D31" s="113" t="s">
         <v>237</v>
       </c>
-      <c r="E30" s="251">
+      <c r="E31" s="251">
         <v>6.9407499196842437</v>
       </c>
-      <c r="F30" s="262"/>
-    </row>
-    <row r="31" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="121" t="s">
+      <c r="F31" s="422"/>
+    </row>
+    <row r="32" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="113" t="s">
         <v>120</v>
       </c>
-      <c r="C31" s="121">
+      <c r="C32" s="113">
         <v>3.5</v>
       </c>
-      <c r="D31" s="121" t="s">
+      <c r="D32" s="113" t="s">
         <v>129</v>
       </c>
-      <c r="E31" s="251">
+      <c r="E32" s="251">
         <v>16.064114920372663</v>
       </c>
-      <c r="F31" s="262"/>
-    </row>
-    <row r="32" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="121" t="s">
+      <c r="F32" s="422"/>
+    </row>
+    <row r="33" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="113" t="s">
         <v>233</v>
       </c>
-      <c r="C32" s="121"/>
-      <c r="D32" s="121" t="s">
+      <c r="C33" s="113"/>
+      <c r="D33" s="113" t="s">
         <v>109</v>
       </c>
-      <c r="E32" s="251">
+      <c r="E33" s="251">
         <v>5.2022121253843681</v>
       </c>
-      <c r="F32" s="262"/>
-    </row>
-    <row r="33" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="121" t="s">
+      <c r="F33" s="422"/>
+    </row>
+    <row r="34" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="113" t="s">
         <v>1686</v>
       </c>
-      <c r="C33" s="121">
+      <c r="C34" s="113">
         <v>9</v>
       </c>
-      <c r="D33" s="121" t="s">
+      <c r="D34" s="113" t="s">
         <v>105</v>
       </c>
-      <c r="E33" s="251">
-        <v>7.17</v>
-      </c>
-      <c r="F33" s="262"/>
-    </row>
-    <row r="34" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="121" t="s">
+      <c r="E34" s="251">
+        <v>7.168754876313737</v>
+      </c>
+      <c r="F34" s="422"/>
+    </row>
+    <row r="35" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="113" t="s">
         <v>1686</v>
       </c>
-      <c r="C34" s="121"/>
-      <c r="D34" s="121" t="s">
+      <c r="C35" s="113"/>
+      <c r="D35" s="113" t="s">
         <v>83</v>
       </c>
-      <c r="E34" s="251">
-        <v>5.74</v>
-      </c>
-      <c r="F34" s="262"/>
-    </row>
-    <row r="35" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="121" t="s">
-        <v>1687</v>
-      </c>
-      <c r="C35" s="121"/>
-      <c r="D35" s="121" t="s">
+      <c r="E35" s="251">
+        <v>5.7437238973794118</v>
+      </c>
+      <c r="F35" s="422"/>
+    </row>
+    <row r="36" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="113" t="s">
+        <v>1711</v>
+      </c>
+      <c r="C36" s="113"/>
+      <c r="D36" s="113" t="s">
         <v>83</v>
       </c>
-      <c r="E35" s="251">
-        <v>5.9</v>
-      </c>
-      <c r="F35" s="262"/>
-    </row>
-    <row r="36" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="121" t="s">
+      <c r="E36" s="251">
+        <v>5.9020606728165594</v>
+      </c>
+      <c r="F36" s="422"/>
+    </row>
+    <row r="37" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="113" t="s">
         <v>446</v>
       </c>
-      <c r="C36" s="121"/>
-      <c r="D36" s="121" t="s">
+      <c r="C37" s="113"/>
+      <c r="D37" s="113" t="s">
         <v>83</v>
       </c>
-      <c r="E36" s="251">
+      <c r="E37" s="251">
         <v>6.8520813254394417</v>
       </c>
-      <c r="F36" s="262"/>
-    </row>
-    <row r="37" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="121" t="s">
+      <c r="F37" s="422"/>
+    </row>
+    <row r="38" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="113" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="121"/>
-      <c r="D37" s="121" t="s">
+      <c r="C38" s="113"/>
+      <c r="D38" s="113" t="s">
         <v>237</v>
       </c>
-      <c r="E37" s="251">
+      <c r="E38" s="251">
         <v>5.9400614989214739</v>
       </c>
-      <c r="F37" s="262"/>
-    </row>
-    <row r="38" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="121" t="s">
+      <c r="F38" s="422"/>
+    </row>
+    <row r="39" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="113" t="s">
         <v>123</v>
       </c>
-      <c r="C38" s="121">
+      <c r="C39" s="113">
         <v>9</v>
       </c>
-      <c r="D38" s="121" t="s">
+      <c r="D39" s="113" t="s">
         <v>105</v>
       </c>
-      <c r="E38" s="251">
+      <c r="E39" s="251">
         <v>8.8534581669649821</v>
       </c>
-      <c r="F38" s="262"/>
-    </row>
-    <row r="39" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="121" t="s">
+      <c r="F39" s="422"/>
+    </row>
+    <row r="40" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="113" t="s">
         <v>235</v>
       </c>
-      <c r="C39" s="121"/>
-      <c r="D39" s="121" t="s">
+      <c r="C40" s="113"/>
+      <c r="D40" s="113" t="s">
         <v>109</v>
       </c>
-      <c r="E39" s="251">
+      <c r="E40" s="251">
         <v>5.2022121253843681</v>
       </c>
-      <c r="F39" s="262"/>
-    </row>
-    <row r="40" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="121" t="s">
+      <c r="F40" s="422"/>
+    </row>
+    <row r="41" spans="2:6" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="113" t="s">
         <v>236</v>
       </c>
-      <c r="C40" s="121"/>
-      <c r="D40" s="121" t="s">
+      <c r="C41" s="113"/>
+      <c r="D41" s="113" t="s">
         <v>238</v>
       </c>
-      <c r="E40" s="251">
+      <c r="E41" s="251">
         <v>7.8971040433246138</v>
       </c>
-      <c r="F40" s="262"/>
-    </row>
-    <row r="41" spans="2:6" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B41" s="121" t="s">
+      <c r="F41" s="423"/>
+    </row>
+    <row r="42" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="113" t="s">
         <v>1636</v>
       </c>
-      <c r="C41" s="121">
+      <c r="C42" s="113">
         <v>9</v>
       </c>
-      <c r="D41" s="121" t="s">
+      <c r="D42" s="113" t="s">
         <v>105</v>
       </c>
-      <c r="E41" s="251">
+      <c r="E42" s="319">
         <v>7.4854284271880305</v>
       </c>
-      <c r="F41" s="263"/>
-    </row>
-    <row r="42" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="121" t="s">
+      <c r="F42" s="424"/>
+    </row>
+    <row r="43" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="113" t="s">
         <v>1636</v>
       </c>
-      <c r="C42" s="121">
+      <c r="C43" s="113">
         <v>9</v>
       </c>
-      <c r="D42" s="121" t="s">
+      <c r="D43" s="113" t="s">
         <v>83</v>
       </c>
-      <c r="E42" s="322">
-        <v>6.13956583597228</v>
-      </c>
-      <c r="F42" s="31"/>
-    </row>
-    <row r="43" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="121" t="s">
+      <c r="E43" s="319">
+        <v>6.0603974482537062</v>
+      </c>
+      <c r="F43" s="322"/>
+    </row>
+    <row r="44" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="113" t="s">
         <v>1637</v>
       </c>
-      <c r="C43" s="121">
+      <c r="C44" s="113">
         <v>9</v>
       </c>
-      <c r="D43" s="121" t="s">
+      <c r="D44" s="113" t="s">
         <v>83</v>
       </c>
-      <c r="E43" s="322">
-        <v>6.4562393868465735</v>
-      </c>
-      <c r="F43" s="325"/>
-    </row>
-    <row r="44" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="121" t="s">
+      <c r="E44" s="319">
+        <v>6.2187342236908529</v>
+      </c>
+      <c r="F44" s="322"/>
+    </row>
+    <row r="45" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="113" t="s">
+        <v>1712</v>
+      </c>
+      <c r="C45" s="113">
+        <v>6.5</v>
+      </c>
+      <c r="D45" s="113" t="s">
+        <v>113</v>
+      </c>
+      <c r="E45" s="319">
+        <v>13.69</v>
+      </c>
+      <c r="F45" s="322"/>
+    </row>
+    <row r="46" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="113" t="s">
         <v>1638</v>
       </c>
-      <c r="C44" s="121">
+      <c r="C46" s="113">
         <v>9</v>
       </c>
-      <c r="D44" s="121" t="s">
+      <c r="D46" s="113" t="s">
         <v>105</v>
       </c>
-      <c r="E44" s="322">
+      <c r="E46" s="319">
         <v>7.4854284271880305</v>
       </c>
-      <c r="F44" s="325"/>
-    </row>
-    <row r="45" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="121" t="s">
+      <c r="F46" s="424"/>
+    </row>
+    <row r="47" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B47" s="113" t="s">
         <v>1638</v>
       </c>
-      <c r="C45" s="121">
+      <c r="C47" s="113">
         <v>9</v>
       </c>
-      <c r="D45" s="121" t="s">
+      <c r="D47" s="113" t="s">
         <v>83</v>
       </c>
-      <c r="E45" s="322">
-        <v>6.13956583597228</v>
-      </c>
-      <c r="F45" s="325"/>
-    </row>
-    <row r="46" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="121" t="s">
+      <c r="E47" s="319">
+        <v>6.0603974482537062</v>
+      </c>
+      <c r="F47" s="425"/>
+    </row>
+    <row r="48" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B48" s="113" t="s">
         <v>1639</v>
       </c>
-      <c r="C46" s="121">
+      <c r="C48" s="113">
         <v>9</v>
       </c>
-      <c r="D46" s="121" t="s">
+      <c r="D48" s="113" t="s">
         <v>83</v>
       </c>
-      <c r="E46" s="322">
-        <v>6.4562393868465735</v>
-      </c>
-      <c r="F46" s="31"/>
-    </row>
-    <row r="47" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="121" t="s">
+      <c r="E48" s="319">
+        <v>6.2187342236908529</v>
+      </c>
+      <c r="F48" s="425"/>
+    </row>
+    <row r="49" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="113" t="s">
         <v>121</v>
       </c>
-      <c r="C47" s="121">
+      <c r="C49" s="113">
         <v>5.6</v>
       </c>
-      <c r="D47" s="121" t="s">
+      <c r="D49" s="113" t="s">
         <v>129</v>
       </c>
-      <c r="E47" s="322">
+      <c r="E49" s="319">
         <v>20.611547110927528</v>
       </c>
-    </row>
-    <row r="48" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="121" t="s">
+      <c r="F49" s="425"/>
+    </row>
+    <row r="50" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B50" s="113" t="s">
         <v>125</v>
       </c>
-      <c r="C48" s="121">
+      <c r="C50" s="113">
         <v>9</v>
       </c>
-      <c r="D48" s="121" t="s">
+      <c r="D50" s="113" t="s">
         <v>83</v>
       </c>
-      <c r="E48" s="322">
+      <c r="E50" s="319">
         <v>7.7862683005186106</v>
       </c>
-    </row>
-    <row r="49" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="252"/>
-      <c r="C49" s="257"/>
-      <c r="D49" s="256"/>
-      <c r="E49" s="321"/>
-    </row>
-    <row r="50" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="121" t="s">
+      <c r="F50" s="425"/>
+    </row>
+    <row r="51" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B51" s="113" t="s">
+        <v>1713</v>
+      </c>
+      <c r="C51" s="113">
+        <v>6.5</v>
+      </c>
+      <c r="D51" s="113" t="s">
+        <v>113</v>
+      </c>
+      <c r="E51" s="319">
+        <v>13.685896553306712</v>
+      </c>
+      <c r="F51" s="425"/>
+    </row>
+    <row r="52" spans="2:6" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B52" s="252"/>
+      <c r="C52" s="257"/>
+      <c r="D52" s="256"/>
+      <c r="E52" s="318"/>
+    </row>
+    <row r="53" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B53" s="418" t="s">
         <v>1247</v>
       </c>
-      <c r="C50" s="323"/>
-      <c r="D50" s="121" t="s">
+      <c r="C53" s="428"/>
+      <c r="D53" s="419" t="s">
         <v>237</v>
       </c>
-      <c r="E50" s="322"/>
-      <c r="F50" s="324">
+      <c r="E53" s="429"/>
+      <c r="F53" s="430">
         <v>51.24</v>
       </c>
     </row>
-    <row r="51" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="121" t="s">
+    <row r="54" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B54" s="115" t="s">
         <v>1248</v>
       </c>
-      <c r="C51" s="323"/>
-      <c r="D51" s="121" t="s">
+      <c r="C54" s="320"/>
+      <c r="D54" s="121" t="s">
         <v>237</v>
       </c>
-      <c r="E51" s="322"/>
-      <c r="F51" s="324">
+      <c r="E54" s="319"/>
+      <c r="F54" s="431">
         <v>70.28</v>
       </c>
     </row>
-    <row r="52" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="121" t="s">
+    <row r="55" spans="2:6" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B55" s="116" t="s">
         <v>1249</v>
       </c>
-      <c r="C52" s="323"/>
-      <c r="D52" s="121" t="s">
+      <c r="C55" s="432"/>
+      <c r="D55" s="420" t="s">
         <v>2</v>
       </c>
-      <c r="E52" s="322"/>
-      <c r="F52" s="324">
+      <c r="E55" s="433"/>
+      <c r="F55" s="434">
         <v>16</v>
       </c>
-    </row>
-    <row r="53" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="252"/>
-      <c r="C53" s="257"/>
-      <c r="D53" s="256"/>
-      <c r="E53" s="252"/>
-    </row>
-    <row r="54" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="253"/>
-      <c r="C54" s="257"/>
-      <c r="D54" s="256"/>
-      <c r="E54" s="252"/>
-    </row>
-    <row r="55" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="252"/>
-      <c r="C55" s="257"/>
-      <c r="D55" s="256"/>
-      <c r="E55" s="252"/>
     </row>
     <row r="56" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="252"/>
@@ -18705,26 +18768,44 @@
       <c r="E56" s="252"/>
     </row>
     <row r="57" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="252"/>
+      <c r="B57" s="253"/>
       <c r="C57" s="257"/>
       <c r="D57" s="256"/>
       <c r="E57" s="252"/>
     </row>
     <row r="58" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="31"/>
-      <c r="C58" s="258"/>
+      <c r="B58" s="252"/>
+      <c r="C58" s="257"/>
+      <c r="D58" s="256"/>
+      <c r="E58" s="252"/>
     </row>
     <row r="59" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="31"/>
-      <c r="C59" s="258"/>
+      <c r="B59" s="252"/>
+      <c r="C59" s="257"/>
+      <c r="D59" s="256"/>
+      <c r="E59" s="252"/>
     </row>
     <row r="60" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="31"/>
-      <c r="C60" s="258"/>
+      <c r="B60" s="252"/>
+      <c r="C60" s="257"/>
+      <c r="D60" s="256"/>
+      <c r="E60" s="252"/>
     </row>
     <row r="61" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="31"/>
       <c r="C61" s="258"/>
+    </row>
+    <row r="62" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B62" s="31"/>
+      <c r="C62" s="258"/>
+    </row>
+    <row r="63" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B63" s="31"/>
+      <c r="C63" s="258"/>
+    </row>
+    <row r="64" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B64" s="31"/>
+      <c r="C64" s="258"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -18738,7 +18819,7 @@
   <pageMargins left="0.5" right="0.5" top="0.39000000000000007" bottom="0.39000000000000007" header="0" footer="0"/>
   <pageSetup scale="54" orientation="portrait" r:id="rId1"/>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="61" max="16383" man="1"/>
+    <brk id="64" max="16383" man="1"/>
   </rowBreaks>
   <colBreaks count="1" manualBreakCount="1">
     <brk id="12" max="1048575" man="1"/>
@@ -18757,11 +18838,11 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="350" t="s">
+      <c r="B2" s="349" t="s">
         <v>1641</v>
       </c>
-      <c r="C2" s="350"/>
-      <c r="D2" s="350"/>
+      <c r="C2" s="349"/>
+      <c r="D2" s="349"/>
       <c r="E2" s="49"/>
       <c r="F2" s="49"/>
       <c r="G2" s="49"/>
@@ -18772,9 +18853,9 @@
       <c r="L2" s="49"/>
     </row>
     <row r="3" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="350"/>
-      <c r="C3" s="350"/>
-      <c r="D3" s="350"/>
+      <c r="B3" s="349"/>
+      <c r="C3" s="349"/>
+      <c r="D3" s="349"/>
       <c r="E3" s="49"/>
       <c r="F3" s="49"/>
       <c r="G3" s="49"/>
@@ -18791,10 +18872,10 @@
     </row>
     <row r="5" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="1:12" ht="20" x14ac:dyDescent="0.2">
-      <c r="B6" s="398" t="s">
+      <c r="B6" s="397" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="400" t="s">
+      <c r="C6" s="399" t="s">
         <v>0</v>
       </c>
       <c r="D6" s="50" t="s">
@@ -18802,14 +18883,14 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="20" x14ac:dyDescent="0.2">
-      <c r="B7" s="399"/>
-      <c r="C7" s="401"/>
+      <c r="B7" s="398"/>
+      <c r="C7" s="400"/>
       <c r="D7" s="132" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:12" s="7" customFormat="1" ht="21" x14ac:dyDescent="0.25">
-      <c r="B8" s="264" t="s">
+      <c r="B8" s="261" t="s">
         <v>772</v>
       </c>
       <c r="C8" s="130" t="s">
@@ -18820,7 +18901,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" s="7" customFormat="1" ht="21" x14ac:dyDescent="0.25">
-      <c r="B9" s="264" t="s">
+      <c r="B9" s="261" t="s">
         <v>773</v>
       </c>
       <c r="C9" s="130" t="s">
@@ -18831,7 +18912,7 @@
       </c>
     </row>
     <row r="10" spans="1:12" s="7" customFormat="1" ht="21" x14ac:dyDescent="0.25">
-      <c r="B10" s="264" t="s">
+      <c r="B10" s="261" t="s">
         <v>773</v>
       </c>
       <c r="C10" s="130" t="s">
@@ -18842,7 +18923,7 @@
       </c>
     </row>
     <row r="11" spans="1:12" s="7" customFormat="1" ht="21" x14ac:dyDescent="0.25">
-      <c r="B11" s="264" t="s">
+      <c r="B11" s="261" t="s">
         <v>774</v>
       </c>
       <c r="C11" s="130" t="s">
@@ -18853,7 +18934,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" s="7" customFormat="1" ht="21" x14ac:dyDescent="0.25">
-      <c r="B12" s="264" t="s">
+      <c r="B12" s="261" t="s">
         <v>775</v>
       </c>
       <c r="C12" s="130" t="s">
@@ -18864,7 +18945,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" s="7" customFormat="1" ht="21" x14ac:dyDescent="0.25">
-      <c r="B13" s="264" t="s">
+      <c r="B13" s="261" t="s">
         <v>776</v>
       </c>
       <c r="C13" s="130" t="s">
@@ -18875,7 +18956,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" s="7" customFormat="1" ht="21" x14ac:dyDescent="0.25">
-      <c r="B14" s="264" t="s">
+      <c r="B14" s="261" t="s">
         <v>777</v>
       </c>
       <c r="C14" s="130" t="s">
@@ -18886,7 +18967,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" s="7" customFormat="1" ht="22" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="265" t="s">
+      <c r="B15" s="262" t="s">
         <v>777</v>
       </c>
       <c r="C15" s="224" t="s">
@@ -18941,32 +19022,32 @@
       <c r="K1" s="177"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" s="365" t="s">
+      <c r="A2" s="364" t="s">
         <v>1643</v>
       </c>
-      <c r="B2" s="365"/>
-      <c r="C2" s="365"/>
-      <c r="D2" s="365"/>
-      <c r="E2" s="365"/>
-      <c r="F2" s="365"/>
-      <c r="G2" s="365"/>
-      <c r="H2" s="365"/>
-      <c r="I2" s="365"/>
-      <c r="J2" s="365"/>
-      <c r="K2" s="365"/>
+      <c r="B2" s="364"/>
+      <c r="C2" s="364"/>
+      <c r="D2" s="364"/>
+      <c r="E2" s="364"/>
+      <c r="F2" s="364"/>
+      <c r="G2" s="364"/>
+      <c r="H2" s="364"/>
+      <c r="I2" s="364"/>
+      <c r="J2" s="364"/>
+      <c r="K2" s="364"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A3" s="365"/>
-      <c r="B3" s="365"/>
-      <c r="C3" s="365"/>
-      <c r="D3" s="365"/>
-      <c r="E3" s="365"/>
-      <c r="F3" s="365"/>
-      <c r="G3" s="365"/>
-      <c r="H3" s="365"/>
-      <c r="I3" s="365"/>
-      <c r="J3" s="365"/>
-      <c r="K3" s="365"/>
+      <c r="A3" s="364"/>
+      <c r="B3" s="364"/>
+      <c r="C3" s="364"/>
+      <c r="D3" s="364"/>
+      <c r="E3" s="364"/>
+      <c r="F3" s="364"/>
+      <c r="G3" s="364"/>
+      <c r="H3" s="364"/>
+      <c r="I3" s="364"/>
+      <c r="J3" s="364"/>
+      <c r="K3" s="364"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="177" t="s">
@@ -18998,10 +19079,10 @@
     </row>
     <row r="6" spans="1:11" ht="20" x14ac:dyDescent="0.2">
       <c r="A6" s="13"/>
-      <c r="B6" s="361" t="s">
+      <c r="B6" s="360" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="363" t="s">
+      <c r="C6" s="362" t="s">
         <v>0</v>
       </c>
       <c r="D6" s="180" t="s">
@@ -19017,8 +19098,8 @@
     </row>
     <row r="7" spans="1:11" ht="20" x14ac:dyDescent="0.2">
       <c r="A7" s="13"/>
-      <c r="B7" s="362"/>
-      <c r="C7" s="364"/>
+      <c r="B7" s="361"/>
+      <c r="C7" s="363"/>
       <c r="D7" s="191" t="s">
         <v>100</v>
       </c>
@@ -19325,45 +19406,45 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="350" t="s">
+      <c r="A2" s="349" t="s">
         <v>1592</v>
       </c>
-      <c r="B2" s="350"/>
-      <c r="C2" s="350"/>
-      <c r="D2" s="350"/>
-      <c r="E2" s="350"/>
-      <c r="F2" s="350"/>
-      <c r="G2" s="350"/>
-      <c r="H2" s="350"/>
-      <c r="I2" s="350"/>
-      <c r="J2" s="350"/>
-      <c r="K2" s="350"/>
+      <c r="B2" s="349"/>
+      <c r="C2" s="349"/>
+      <c r="D2" s="349"/>
+      <c r="E2" s="349"/>
+      <c r="F2" s="349"/>
+      <c r="G2" s="349"/>
+      <c r="H2" s="349"/>
+      <c r="I2" s="349"/>
+      <c r="J2" s="349"/>
+      <c r="K2" s="349"/>
     </row>
     <row r="3" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="350"/>
-      <c r="B3" s="350"/>
-      <c r="C3" s="350"/>
-      <c r="D3" s="350"/>
-      <c r="E3" s="350"/>
-      <c r="F3" s="350"/>
-      <c r="G3" s="350"/>
-      <c r="H3" s="350"/>
-      <c r="I3" s="350"/>
-      <c r="J3" s="350"/>
-      <c r="K3" s="350"/>
+      <c r="A3" s="349"/>
+      <c r="B3" s="349"/>
+      <c r="C3" s="349"/>
+      <c r="D3" s="349"/>
+      <c r="E3" s="349"/>
+      <c r="F3" s="349"/>
+      <c r="G3" s="349"/>
+      <c r="H3" s="349"/>
+      <c r="I3" s="349"/>
+      <c r="J3" s="349"/>
+      <c r="K3" s="349"/>
     </row>
     <row r="4" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="350"/>
-      <c r="B4" s="350"/>
-      <c r="C4" s="350"/>
-      <c r="D4" s="350"/>
-      <c r="E4" s="350"/>
-      <c r="F4" s="350"/>
-      <c r="G4" s="350"/>
-      <c r="H4" s="350"/>
-      <c r="I4" s="350"/>
-      <c r="J4" s="350"/>
-      <c r="K4" s="350"/>
+      <c r="A4" s="349"/>
+      <c r="B4" s="349"/>
+      <c r="C4" s="349"/>
+      <c r="D4" s="349"/>
+      <c r="E4" s="349"/>
+      <c r="F4" s="349"/>
+      <c r="G4" s="349"/>
+      <c r="H4" s="349"/>
+      <c r="I4" s="349"/>
+      <c r="J4" s="349"/>
+      <c r="K4" s="349"/>
     </row>
     <row r="5" spans="1:11" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A5" s="119"/>
@@ -19380,10 +19461,10 @@
     </row>
     <row r="6" spans="1:11" ht="20" x14ac:dyDescent="0.2">
       <c r="A6" s="13"/>
-      <c r="B6" s="352" t="s">
+      <c r="B6" s="351" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="354" t="s">
+      <c r="C6" s="353" t="s">
         <v>0</v>
       </c>
       <c r="D6" s="14" t="s">
@@ -19399,8 +19480,8 @@
     </row>
     <row r="7" spans="1:11" ht="20" x14ac:dyDescent="0.2">
       <c r="A7" s="13"/>
-      <c r="B7" s="353"/>
-      <c r="C7" s="355"/>
+      <c r="B7" s="352"/>
+      <c r="C7" s="354"/>
       <c r="D7" s="190" t="s">
         <v>100</v>
       </c>
@@ -19546,32 +19627,32 @@
       <c r="K1" s="177"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" s="365" t="s">
+      <c r="A2" s="364" t="s">
         <v>1178</v>
       </c>
-      <c r="B2" s="365"/>
-      <c r="C2" s="365"/>
-      <c r="D2" s="365"/>
-      <c r="E2" s="365"/>
-      <c r="F2" s="365"/>
-      <c r="G2" s="365"/>
-      <c r="H2" s="365"/>
-      <c r="I2" s="365"/>
-      <c r="J2" s="365"/>
-      <c r="K2" s="365"/>
+      <c r="B2" s="364"/>
+      <c r="C2" s="364"/>
+      <c r="D2" s="364"/>
+      <c r="E2" s="364"/>
+      <c r="F2" s="364"/>
+      <c r="G2" s="364"/>
+      <c r="H2" s="364"/>
+      <c r="I2" s="364"/>
+      <c r="J2" s="364"/>
+      <c r="K2" s="364"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A3" s="365"/>
-      <c r="B3" s="365"/>
-      <c r="C3" s="365"/>
-      <c r="D3" s="365"/>
-      <c r="E3" s="365"/>
-      <c r="F3" s="365"/>
-      <c r="G3" s="365"/>
-      <c r="H3" s="365"/>
-      <c r="I3" s="365"/>
-      <c r="J3" s="365"/>
-      <c r="K3" s="365"/>
+      <c r="A3" s="364"/>
+      <c r="B3" s="364"/>
+      <c r="C3" s="364"/>
+      <c r="D3" s="364"/>
+      <c r="E3" s="364"/>
+      <c r="F3" s="364"/>
+      <c r="G3" s="364"/>
+      <c r="H3" s="364"/>
+      <c r="I3" s="364"/>
+      <c r="J3" s="364"/>
+      <c r="K3" s="364"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="177" t="s">
@@ -19603,10 +19684,10 @@
     </row>
     <row r="6" spans="1:11" ht="20" x14ac:dyDescent="0.2">
       <c r="A6" s="13"/>
-      <c r="B6" s="361" t="s">
+      <c r="B6" s="360" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="363" t="s">
+      <c r="C6" s="362" t="s">
         <v>0</v>
       </c>
       <c r="D6" s="180" t="s">
@@ -19622,8 +19703,8 @@
     </row>
     <row r="7" spans="1:11" ht="20" x14ac:dyDescent="0.2">
       <c r="A7" s="13"/>
-      <c r="B7" s="402"/>
-      <c r="C7" s="351"/>
+      <c r="B7" s="401"/>
+      <c r="C7" s="350"/>
       <c r="D7" s="181" t="s">
         <v>100</v>
       </c>
@@ -19830,32 +19911,32 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B2" s="393" t="s">
+      <c r="B2" s="392" t="s">
         <v>1644</v>
       </c>
-      <c r="C2" s="393"/>
-      <c r="D2" s="393"/>
-      <c r="E2" s="393"/>
-      <c r="F2" s="393"/>
-      <c r="G2" s="393"/>
-      <c r="H2" s="393"/>
-      <c r="I2" s="393"/>
-      <c r="J2" s="393"/>
-      <c r="K2" s="393"/>
-      <c r="L2" s="393"/>
+      <c r="C2" s="392"/>
+      <c r="D2" s="392"/>
+      <c r="E2" s="392"/>
+      <c r="F2" s="392"/>
+      <c r="G2" s="392"/>
+      <c r="H2" s="392"/>
+      <c r="I2" s="392"/>
+      <c r="J2" s="392"/>
+      <c r="K2" s="392"/>
+      <c r="L2" s="392"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B3" s="393"/>
-      <c r="C3" s="393"/>
-      <c r="D3" s="393"/>
-      <c r="E3" s="393"/>
-      <c r="F3" s="393"/>
-      <c r="G3" s="393"/>
-      <c r="H3" s="393"/>
-      <c r="I3" s="393"/>
-      <c r="J3" s="393"/>
-      <c r="K3" s="393"/>
-      <c r="L3" s="393"/>
+      <c r="B3" s="392"/>
+      <c r="C3" s="392"/>
+      <c r="D3" s="392"/>
+      <c r="E3" s="392"/>
+      <c r="F3" s="392"/>
+      <c r="G3" s="392"/>
+      <c r="H3" s="392"/>
+      <c r="I3" s="392"/>
+      <c r="J3" s="392"/>
+      <c r="K3" s="392"/>
+      <c r="L3" s="392"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
@@ -19865,10 +19946,10 @@
     <row r="6" spans="1:12" ht="20" x14ac:dyDescent="0.2">
       <c r="A6" s="9"/>
       <c r="B6" s="13"/>
-      <c r="C6" s="351" t="s">
+      <c r="C6" s="350" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="351" t="s">
+      <c r="D6" s="350" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="120" t="s">
@@ -19885,8 +19966,8 @@
     <row r="7" spans="1:12" ht="20" x14ac:dyDescent="0.2">
       <c r="A7" s="9"/>
       <c r="B7" s="13"/>
-      <c r="C7" s="351"/>
-      <c r="D7" s="351"/>
+      <c r="C7" s="350"/>
+      <c r="D7" s="350"/>
       <c r="E7" s="120" t="s">
         <v>100</v>
       </c>
@@ -19993,32 +20074,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A1" s="350" t="s">
+      <c r="A1" s="349" t="s">
         <v>1684</v>
       </c>
-      <c r="B1" s="350"/>
-      <c r="C1" s="350"/>
-      <c r="D1" s="350"/>
-      <c r="E1" s="350"/>
-      <c r="F1" s="350"/>
-      <c r="G1" s="350"/>
-      <c r="H1" s="350"/>
-      <c r="I1" s="350"/>
-      <c r="J1" s="350"/>
-      <c r="K1" s="350"/>
+      <c r="B1" s="349"/>
+      <c r="C1" s="349"/>
+      <c r="D1" s="349"/>
+      <c r="E1" s="349"/>
+      <c r="F1" s="349"/>
+      <c r="G1" s="349"/>
+      <c r="H1" s="349"/>
+      <c r="I1" s="349"/>
+      <c r="J1" s="349"/>
+      <c r="K1" s="349"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" s="350"/>
-      <c r="B2" s="350"/>
-      <c r="C2" s="350"/>
-      <c r="D2" s="350"/>
-      <c r="E2" s="350"/>
-      <c r="F2" s="350"/>
-      <c r="G2" s="350"/>
-      <c r="H2" s="350"/>
-      <c r="I2" s="350"/>
-      <c r="J2" s="350"/>
-      <c r="K2" s="350"/>
+      <c r="A2" s="349"/>
+      <c r="B2" s="349"/>
+      <c r="C2" s="349"/>
+      <c r="D2" s="349"/>
+      <c r="E2" s="349"/>
+      <c r="F2" s="349"/>
+      <c r="G2" s="349"/>
+      <c r="H2" s="349"/>
+      <c r="I2" s="349"/>
+      <c r="J2" s="349"/>
+      <c r="K2" s="349"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
@@ -20027,10 +20108,10 @@
     </row>
     <row r="5" spans="1:11" ht="20" x14ac:dyDescent="0.2">
       <c r="A5" s="13"/>
-      <c r="B5" s="351" t="s">
+      <c r="B5" s="350" t="s">
         <v>102</v>
       </c>
-      <c r="C5" s="351" t="s">
+      <c r="C5" s="350" t="s">
         <v>0</v>
       </c>
       <c r="D5" s="120" t="s">
@@ -20046,8 +20127,8 @@
     </row>
     <row r="6" spans="1:11" ht="20" x14ac:dyDescent="0.2">
       <c r="A6" s="13"/>
-      <c r="B6" s="351"/>
-      <c r="C6" s="351"/>
+      <c r="B6" s="350"/>
+      <c r="C6" s="350"/>
       <c r="D6" s="120" t="s">
         <v>100</v>
       </c>
@@ -20061,13 +20142,13 @@
     </row>
     <row r="7" spans="1:11" ht="21" x14ac:dyDescent="0.25">
       <c r="A7" s="7"/>
-      <c r="B7" s="288" t="s">
+      <c r="B7" s="285" t="s">
         <v>1673</v>
       </c>
-      <c r="C7" s="288" t="s">
+      <c r="C7" s="285" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="332">
+      <c r="D7" s="329">
         <v>5.949561705447703</v>
       </c>
       <c r="E7" s="7"/>
@@ -20080,13 +20161,13 @@
     </row>
     <row r="8" spans="1:11" ht="21" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
-      <c r="B8" s="288" t="s">
+      <c r="B8" s="285" t="s">
         <v>1674</v>
       </c>
-      <c r="C8" s="288" t="s">
+      <c r="C8" s="285" t="s">
         <v>105</v>
       </c>
-      <c r="D8" s="332">
+      <c r="D8" s="329">
         <v>8.7521226306852071</v>
       </c>
       <c r="E8" s="1"/>
@@ -20094,136 +20175,136 @@
     </row>
     <row r="9" spans="1:11" ht="21" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
-      <c r="B9" s="288" t="s">
+      <c r="B9" s="285" t="s">
         <v>1674</v>
       </c>
-      <c r="C9" s="288" t="s">
+      <c r="C9" s="285" t="s">
         <v>83</v>
       </c>
-      <c r="D9" s="332">
+      <c r="D9" s="329">
         <v>6.6145761622837211</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="2"/>
     </row>
     <row r="10" spans="1:11" ht="21" x14ac:dyDescent="0.25">
-      <c r="B10" s="288" t="s">
+      <c r="B10" s="285" t="s">
         <v>1675</v>
       </c>
-      <c r="C10" s="288" t="s">
+      <c r="C10" s="285" t="s">
         <v>1</v>
       </c>
-      <c r="D10" s="331">
+      <c r="D10" s="328">
         <v>5.7437238973794118</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="21" x14ac:dyDescent="0.25">
-      <c r="B11" s="288" t="s">
+      <c r="B11" s="285" t="s">
         <v>1676</v>
       </c>
-      <c r="C11" s="288" t="s">
+      <c r="C11" s="285" t="s">
         <v>1</v>
       </c>
-      <c r="D11" s="331">
+      <c r="D11" s="328">
         <v>5.7437238973794118</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="21" x14ac:dyDescent="0.25">
-      <c r="B12" s="288" t="s">
+      <c r="B12" s="285" t="s">
         <v>1677</v>
       </c>
-      <c r="C12" s="288" t="s">
+      <c r="C12" s="285" t="s">
         <v>105</v>
       </c>
-      <c r="D12" s="331">
+      <c r="D12" s="328">
         <v>7.0895864885951623</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="21" x14ac:dyDescent="0.25">
-      <c r="B13" s="288" t="s">
+      <c r="B13" s="285" t="s">
         <v>1677</v>
       </c>
-      <c r="C13" s="288" t="s">
+      <c r="C13" s="285" t="s">
         <v>83</v>
       </c>
-      <c r="D13" s="331">
+      <c r="D13" s="328">
         <v>5.5695534443985499</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="21" x14ac:dyDescent="0.25">
-      <c r="B14" s="288" t="s">
+      <c r="B14" s="285" t="s">
         <v>1678</v>
       </c>
-      <c r="C14" s="288" t="s">
+      <c r="C14" s="285" t="s">
         <v>105</v>
       </c>
-      <c r="D14" s="331">
+      <c r="D14" s="328">
         <v>8.5304511450732008</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="21" x14ac:dyDescent="0.25">
-      <c r="B15" s="288" t="s">
+      <c r="B15" s="285" t="s">
         <v>1678</v>
       </c>
-      <c r="C15" s="288" t="s">
+      <c r="C15" s="285" t="s">
         <v>83</v>
       </c>
-      <c r="D15" s="331">
+      <c r="D15" s="328">
         <v>6.6145761622837211</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="21" x14ac:dyDescent="0.25">
-      <c r="B16" s="288" t="s">
+      <c r="B16" s="285" t="s">
         <v>1679</v>
       </c>
-      <c r="C16" s="288" t="s">
+      <c r="C16" s="285" t="s">
         <v>83</v>
       </c>
-      <c r="D16" s="331">
+      <c r="D16" s="328">
         <v>6.6145761622837211</v>
       </c>
     </row>
     <row r="17" spans="2:4" ht="21" x14ac:dyDescent="0.25">
-      <c r="B17" s="288" t="s">
+      <c r="B17" s="285" t="s">
         <v>1680</v>
       </c>
-      <c r="C17" s="288" t="s">
+      <c r="C17" s="285" t="s">
         <v>1</v>
       </c>
-      <c r="D17" s="331">
+      <c r="D17" s="328">
         <v>5.7437238973794118</v>
       </c>
     </row>
     <row r="18" spans="2:4" ht="21" x14ac:dyDescent="0.25">
-      <c r="B18" s="288" t="s">
+      <c r="B18" s="285" t="s">
         <v>1681</v>
       </c>
-      <c r="C18" s="288" t="s">
+      <c r="C18" s="285" t="s">
         <v>83</v>
       </c>
-      <c r="D18" s="331">
+      <c r="D18" s="328">
         <v>6.6145761622837211</v>
       </c>
     </row>
     <row r="19" spans="2:4" ht="21" x14ac:dyDescent="0.25">
-      <c r="B19" s="288" t="s">
+      <c r="B19" s="285" t="s">
         <v>1682</v>
       </c>
-      <c r="C19" s="288" t="s">
+      <c r="C19" s="285" t="s">
         <v>83</v>
       </c>
-      <c r="D19" s="331">
+      <c r="D19" s="328">
         <v>5.5695534443985499</v>
       </c>
     </row>
     <row r="20" spans="2:4" ht="21" x14ac:dyDescent="0.25">
-      <c r="B20" s="288" t="s">
+      <c r="B20" s="285" t="s">
         <v>1683</v>
       </c>
-      <c r="C20" s="288" t="s">
+      <c r="C20" s="285" t="s">
         <v>83</v>
       </c>
-      <c r="D20" s="331">
+      <c r="D20" s="328">
         <v>5.5695534443985499</v>
       </c>
     </row>
@@ -20276,36 +20357,36 @@
       <c r="K1" s="177"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" s="365" t="s">
+      <c r="A2" s="364" t="s">
         <v>1645</v>
       </c>
-      <c r="B2" s="365"/>
-      <c r="C2" s="365"/>
-      <c r="D2" s="365"/>
-      <c r="E2" s="365"/>
-      <c r="F2" s="365"/>
-      <c r="G2" s="365"/>
-      <c r="H2" s="365"/>
-      <c r="I2" s="365"/>
-      <c r="J2" s="365"/>
-      <c r="K2" s="365"/>
+      <c r="B2" s="364"/>
+      <c r="C2" s="364"/>
+      <c r="D2" s="364"/>
+      <c r="E2" s="364"/>
+      <c r="F2" s="364"/>
+      <c r="G2" s="364"/>
+      <c r="H2" s="364"/>
+      <c r="I2" s="364"/>
+      <c r="J2" s="364"/>
+      <c r="K2" s="364"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A3" s="365"/>
-      <c r="B3" s="365"/>
-      <c r="C3" s="365"/>
-      <c r="D3" s="365"/>
-      <c r="E3" s="365"/>
-      <c r="F3" s="365"/>
-      <c r="G3" s="365"/>
-      <c r="H3" s="365"/>
-      <c r="I3" s="365"/>
-      <c r="J3" s="365"/>
-      <c r="K3" s="365"/>
+      <c r="A3" s="364"/>
+      <c r="B3" s="364"/>
+      <c r="C3" s="364"/>
+      <c r="D3" s="364"/>
+      <c r="E3" s="364"/>
+      <c r="F3" s="364"/>
+      <c r="G3" s="364"/>
+      <c r="H3" s="364"/>
+      <c r="I3" s="364"/>
+      <c r="J3" s="364"/>
+      <c r="K3" s="364"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="177" t="s">
-        <v>1702</v>
+        <v>1701</v>
       </c>
       <c r="B4" s="177"/>
       <c r="C4" s="177"/>
@@ -20333,16 +20414,16 @@
     </row>
     <row r="6" spans="1:11" ht="20" x14ac:dyDescent="0.2">
       <c r="A6" s="13"/>
-      <c r="B6" s="351" t="s">
+      <c r="B6" s="350" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="351" t="s">
+      <c r="C6" s="350" t="s">
         <v>0</v>
       </c>
-      <c r="D6" s="293" t="s">
+      <c r="D6" s="290" t="s">
         <v>101</v>
       </c>
-      <c r="E6" s="344" t="s">
+      <c r="E6" s="341" t="s">
         <v>84</v>
       </c>
       <c r="F6" s="13"/>
@@ -20354,12 +20435,12 @@
     </row>
     <row r="7" spans="1:11" ht="20" x14ac:dyDescent="0.2">
       <c r="A7" s="13"/>
-      <c r="B7" s="351"/>
-      <c r="C7" s="351"/>
-      <c r="D7" s="293" t="s">
+      <c r="B7" s="350"/>
+      <c r="C7" s="350"/>
+      <c r="D7" s="290" t="s">
         <v>100</v>
       </c>
-      <c r="E7" s="344" t="s">
+      <c r="E7" s="341" t="s">
         <v>98</v>
       </c>
       <c r="F7" s="13"/>
@@ -20380,7 +20461,7 @@
       <c r="D8" s="202">
         <v>10.788241773371887</v>
       </c>
-      <c r="E8" s="345"/>
+      <c r="E8" s="342"/>
       <c r="F8" s="29"/>
       <c r="G8" s="28"/>
       <c r="H8" s="28"/>
@@ -20399,7 +20480,7 @@
       <c r="D9" s="202">
         <v>9.1098719537381267</v>
       </c>
-      <c r="E9" s="345"/>
+      <c r="E9" s="342"/>
       <c r="F9" s="29"/>
       <c r="G9" s="28"/>
       <c r="H9" s="28"/>
@@ -20418,7 +20499,7 @@
       <c r="D10" s="202">
         <v>10.202395704254439</v>
       </c>
-      <c r="E10" s="345"/>
+      <c r="E10" s="342"/>
       <c r="F10" s="29"/>
       <c r="G10" s="28"/>
       <c r="H10" s="28"/>
@@ -20437,7 +20518,7 @@
       <c r="D11" s="202">
         <v>20.46261875258158</v>
       </c>
-      <c r="E11" s="345"/>
+      <c r="E11" s="342"/>
       <c r="F11" s="29"/>
       <c r="G11" s="28"/>
       <c r="H11" s="28"/>
@@ -20456,7 +20537,7 @@
       <c r="D12" s="202">
         <v>14.477488641057414</v>
       </c>
-      <c r="E12" s="345"/>
+      <c r="E12" s="342"/>
       <c r="F12" s="29"/>
       <c r="G12" s="28"/>
       <c r="H12" s="28"/>
@@ -20475,7 +20556,7 @@
       <c r="D13" s="202">
         <v>12.102437009500207</v>
       </c>
-      <c r="E13" s="345"/>
+      <c r="E13" s="342"/>
       <c r="F13" s="29"/>
       <c r="G13" s="28"/>
       <c r="H13" s="28"/>
@@ -20494,7 +20575,7 @@
       <c r="D14" s="202">
         <v>10.202395704254439</v>
       </c>
-      <c r="E14" s="346"/>
+      <c r="E14" s="343"/>
       <c r="F14" s="6"/>
       <c r="G14" s="177"/>
       <c r="H14" s="177"/>
@@ -20513,7 +20594,7 @@
       <c r="D15" s="202">
         <v>14.477488641057414</v>
       </c>
-      <c r="E15" s="346"/>
+      <c r="E15" s="343"/>
       <c r="F15" s="6"/>
       <c r="G15" s="177"/>
       <c r="H15" s="177"/>
@@ -20523,7 +20604,7 @@
     </row>
     <row r="16" spans="1:11" ht="21" x14ac:dyDescent="0.25">
       <c r="B16" s="113" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C16" s="113" t="s">
         <v>105</v>
@@ -20535,7 +20616,7 @@
     </row>
     <row r="17" spans="2:5" ht="21" x14ac:dyDescent="0.25">
       <c r="B17" s="113" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C17" s="113" t="s">
         <v>83</v>
@@ -20547,7 +20628,7 @@
     </row>
     <row r="18" spans="2:5" ht="21" x14ac:dyDescent="0.25">
       <c r="B18" s="113" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="C18" s="113" t="s">
         <v>83</v>
@@ -20619,7 +20700,7 @@
     </row>
     <row r="24" spans="2:5" ht="21" x14ac:dyDescent="0.25">
       <c r="B24" s="130" t="s">
-        <v>1709</v>
+        <v>1708</v>
       </c>
       <c r="C24" s="130" t="s">
         <v>83</v>
@@ -20631,7 +20712,7 @@
     </row>
     <row r="25" spans="2:5" ht="21" x14ac:dyDescent="0.25">
       <c r="B25" s="130" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="C25" s="130" t="s">
         <v>1195</v>
@@ -20678,45 +20759,45 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="350" t="s">
+      <c r="A2" s="349" t="s">
         <v>1646</v>
       </c>
-      <c r="B2" s="350"/>
-      <c r="C2" s="350"/>
-      <c r="D2" s="350"/>
-      <c r="E2" s="350"/>
-      <c r="F2" s="350"/>
-      <c r="G2" s="350"/>
-      <c r="H2" s="350"/>
-      <c r="I2" s="350"/>
-      <c r="J2" s="350"/>
-      <c r="K2" s="350"/>
+      <c r="B2" s="349"/>
+      <c r="C2" s="349"/>
+      <c r="D2" s="349"/>
+      <c r="E2" s="349"/>
+      <c r="F2" s="349"/>
+      <c r="G2" s="349"/>
+      <c r="H2" s="349"/>
+      <c r="I2" s="349"/>
+      <c r="J2" s="349"/>
+      <c r="K2" s="349"/>
     </row>
     <row r="3" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="350"/>
-      <c r="B3" s="350"/>
-      <c r="C3" s="350"/>
-      <c r="D3" s="350"/>
-      <c r="E3" s="350"/>
-      <c r="F3" s="350"/>
-      <c r="G3" s="350"/>
-      <c r="H3" s="350"/>
-      <c r="I3" s="350"/>
-      <c r="J3" s="350"/>
-      <c r="K3" s="350"/>
+      <c r="A3" s="349"/>
+      <c r="B3" s="349"/>
+      <c r="C3" s="349"/>
+      <c r="D3" s="349"/>
+      <c r="E3" s="349"/>
+      <c r="F3" s="349"/>
+      <c r="G3" s="349"/>
+      <c r="H3" s="349"/>
+      <c r="I3" s="349"/>
+      <c r="J3" s="349"/>
+      <c r="K3" s="349"/>
     </row>
     <row r="4" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="350"/>
-      <c r="B4" s="350"/>
-      <c r="C4" s="350"/>
-      <c r="D4" s="350"/>
-      <c r="E4" s="350"/>
-      <c r="F4" s="350"/>
-      <c r="G4" s="350"/>
-      <c r="H4" s="350"/>
-      <c r="I4" s="350"/>
-      <c r="J4" s="350"/>
-      <c r="K4" s="350"/>
+      <c r="A4" s="349"/>
+      <c r="B4" s="349"/>
+      <c r="C4" s="349"/>
+      <c r="D4" s="349"/>
+      <c r="E4" s="349"/>
+      <c r="F4" s="349"/>
+      <c r="G4" s="349"/>
+      <c r="H4" s="349"/>
+      <c r="I4" s="349"/>
+      <c r="J4" s="349"/>
+      <c r="K4" s="349"/>
     </row>
     <row r="5" spans="1:11" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A5" s="119"/>
@@ -20733,10 +20814,10 @@
     </row>
     <row r="6" spans="1:11" ht="20" x14ac:dyDescent="0.2">
       <c r="A6" s="13"/>
-      <c r="B6" s="352" t="s">
+      <c r="B6" s="351" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="354" t="s">
+      <c r="C6" s="353" t="s">
         <v>0</v>
       </c>
       <c r="D6" s="14" t="s">
@@ -20752,8 +20833,8 @@
     </row>
     <row r="7" spans="1:11" ht="20" x14ac:dyDescent="0.2">
       <c r="A7" s="13"/>
-      <c r="B7" s="353"/>
-      <c r="C7" s="355"/>
+      <c r="B7" s="352"/>
+      <c r="C7" s="354"/>
       <c r="D7" s="190" t="s">
         <v>100</v>
       </c>
@@ -20969,30 +21050,30 @@
   <sheetData>
     <row r="1" spans="2:11" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:11" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="350" t="s">
+      <c r="B2" s="349" t="s">
         <v>1647</v>
       </c>
-      <c r="C2" s="350"/>
-      <c r="D2" s="350"/>
-      <c r="E2" s="350"/>
-      <c r="F2" s="350"/>
-      <c r="G2" s="350"/>
-      <c r="H2" s="350"/>
-      <c r="I2" s="350"/>
-      <c r="J2" s="350"/>
-      <c r="K2" s="350"/>
+      <c r="C2" s="349"/>
+      <c r="D2" s="349"/>
+      <c r="E2" s="349"/>
+      <c r="F2" s="349"/>
+      <c r="G2" s="349"/>
+      <c r="H2" s="349"/>
+      <c r="I2" s="349"/>
+      <c r="J2" s="349"/>
+      <c r="K2" s="349"/>
     </row>
     <row r="3" spans="2:11" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="350"/>
-      <c r="C3" s="350"/>
-      <c r="D3" s="350"/>
-      <c r="E3" s="350"/>
-      <c r="F3" s="350"/>
-      <c r="G3" s="350"/>
-      <c r="H3" s="350"/>
-      <c r="I3" s="350"/>
-      <c r="J3" s="350"/>
-      <c r="K3" s="350"/>
+      <c r="B3" s="349"/>
+      <c r="C3" s="349"/>
+      <c r="D3" s="349"/>
+      <c r="E3" s="349"/>
+      <c r="F3" s="349"/>
+      <c r="G3" s="349"/>
+      <c r="H3" s="349"/>
+      <c r="I3" s="349"/>
+      <c r="J3" s="349"/>
+      <c r="K3" s="349"/>
     </row>
     <row r="4" spans="2:11" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
@@ -21002,10 +21083,10 @@
     <row r="5" spans="2:11" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="2:11" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="13"/>
-      <c r="C6" s="354" t="s">
+      <c r="C6" s="353" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="354" t="s">
+      <c r="D6" s="353" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="8" t="s">
@@ -21016,8 +21097,8 @@
     </row>
     <row r="7" spans="2:11" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="13"/>
-      <c r="C7" s="355"/>
-      <c r="D7" s="355"/>
+      <c r="C7" s="354"/>
+      <c r="D7" s="354"/>
       <c r="E7" s="16" t="s">
         <v>100</v>
       </c>
@@ -21408,30 +21489,30 @@
   <sheetData>
     <row r="1" spans="2:11" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:11" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="350" t="s">
+      <c r="B2" s="349" t="s">
         <v>1588</v>
       </c>
-      <c r="C2" s="350"/>
-      <c r="D2" s="350"/>
-      <c r="E2" s="350"/>
-      <c r="F2" s="350"/>
-      <c r="G2" s="350"/>
-      <c r="H2" s="350"/>
-      <c r="I2" s="350"/>
-      <c r="J2" s="350"/>
-      <c r="K2" s="350"/>
+      <c r="C2" s="349"/>
+      <c r="D2" s="349"/>
+      <c r="E2" s="349"/>
+      <c r="F2" s="349"/>
+      <c r="G2" s="349"/>
+      <c r="H2" s="349"/>
+      <c r="I2" s="349"/>
+      <c r="J2" s="349"/>
+      <c r="K2" s="349"/>
     </row>
     <row r="3" spans="2:11" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="350"/>
-      <c r="C3" s="350"/>
-      <c r="D3" s="350"/>
-      <c r="E3" s="350"/>
-      <c r="F3" s="350"/>
-      <c r="G3" s="350"/>
-      <c r="H3" s="350"/>
-      <c r="I3" s="350"/>
-      <c r="J3" s="350"/>
-      <c r="K3" s="350"/>
+      <c r="B3" s="349"/>
+      <c r="C3" s="349"/>
+      <c r="D3" s="349"/>
+      <c r="E3" s="349"/>
+      <c r="F3" s="349"/>
+      <c r="G3" s="349"/>
+      <c r="H3" s="349"/>
+      <c r="I3" s="349"/>
+      <c r="J3" s="349"/>
+      <c r="K3" s="349"/>
     </row>
     <row r="4" spans="2:11" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="2:11" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -21441,13 +21522,13 @@
     </row>
     <row r="6" spans="2:11" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="13"/>
-      <c r="C6" s="354" t="s">
+      <c r="C6" s="353" t="s">
         <v>102</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>412</v>
       </c>
-      <c r="E6" s="354" t="s">
+      <c r="E6" s="353" t="s">
         <v>0</v>
       </c>
       <c r="F6" s="8" t="s">
@@ -21458,11 +21539,11 @@
     </row>
     <row r="7" spans="2:11" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="13"/>
-      <c r="C7" s="355"/>
+      <c r="C7" s="354"/>
       <c r="D7" s="16" t="s">
         <v>1581</v>
       </c>
-      <c r="E7" s="355"/>
+      <c r="E7" s="354"/>
       <c r="F7" s="16" t="s">
         <v>100</v>
       </c>
@@ -21470,31 +21551,31 @@
       <c r="H7" s="13"/>
     </row>
     <row r="8" spans="2:11" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C8" s="310" t="s">
+      <c r="C8" s="307" t="s">
         <v>1582</v>
       </c>
-      <c r="D8" s="310" t="s">
+      <c r="D8" s="307" t="s">
         <v>1583</v>
       </c>
       <c r="E8" s="121" t="s">
         <v>1584</v>
       </c>
-      <c r="F8" s="311">
+      <c r="F8" s="308">
         <v>13.05</v>
       </c>
       <c r="H8" s="12"/>
     </row>
     <row r="9" spans="2:11" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C9" s="310" t="s">
+      <c r="C9" s="307" t="s">
         <v>1582</v>
       </c>
-      <c r="D9" s="310" t="s">
+      <c r="D9" s="307" t="s">
         <v>1583</v>
       </c>
       <c r="E9" s="121" t="s">
         <v>1585</v>
       </c>
-      <c r="F9" s="311">
+      <c r="F9" s="308">
         <v>15.25</v>
       </c>
       <c r="H9" s="12"/>
@@ -21509,7 +21590,7 @@
       <c r="E10" s="121" t="s">
         <v>1587</v>
       </c>
-      <c r="F10" s="311">
+      <c r="F10" s="308">
         <v>26.79</v>
       </c>
       <c r="H10" s="12"/>
@@ -21518,7 +21599,7 @@
       <c r="C11" s="113"/>
       <c r="D11" s="113"/>
       <c r="E11" s="113"/>
-      <c r="F11" s="267" t="s">
+      <c r="F11" s="264" t="s">
         <v>1591</v>
       </c>
       <c r="H11" s="12"/>
@@ -21678,28 +21759,28 @@
   <sheetData>
     <row r="1" spans="2:10" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:10" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="350" t="s">
+      <c r="B2" s="349" t="s">
         <v>1670</v>
       </c>
-      <c r="C2" s="350"/>
-      <c r="D2" s="350"/>
-      <c r="E2" s="350"/>
-      <c r="F2" s="350"/>
-      <c r="G2" s="350"/>
-      <c r="H2" s="350"/>
-      <c r="I2" s="350"/>
-      <c r="J2" s="350"/>
+      <c r="C2" s="349"/>
+      <c r="D2" s="349"/>
+      <c r="E2" s="349"/>
+      <c r="F2" s="349"/>
+      <c r="G2" s="349"/>
+      <c r="H2" s="349"/>
+      <c r="I2" s="349"/>
+      <c r="J2" s="349"/>
     </row>
     <row r="3" spans="2:10" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="350"/>
-      <c r="C3" s="350"/>
-      <c r="D3" s="350"/>
-      <c r="E3" s="350"/>
-      <c r="F3" s="350"/>
-      <c r="G3" s="350"/>
-      <c r="H3" s="350"/>
-      <c r="I3" s="350"/>
-      <c r="J3" s="350"/>
+      <c r="B3" s="349"/>
+      <c r="C3" s="349"/>
+      <c r="D3" s="349"/>
+      <c r="E3" s="349"/>
+      <c r="F3" s="349"/>
+      <c r="G3" s="349"/>
+      <c r="H3" s="349"/>
+      <c r="I3" s="349"/>
+      <c r="J3" s="349"/>
     </row>
     <row r="4" spans="2:10" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="2:10" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -21709,10 +21790,10 @@
     </row>
     <row r="6" spans="2:10" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="13"/>
-      <c r="C6" s="354" t="s">
+      <c r="C6" s="353" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="354" t="s">
+      <c r="D6" s="353" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="8" t="s">
@@ -21723,8 +21804,8 @@
     </row>
     <row r="7" spans="2:10" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="13"/>
-      <c r="C7" s="355"/>
-      <c r="D7" s="355"/>
+      <c r="C7" s="354"/>
+      <c r="D7" s="354"/>
       <c r="E7" s="16" t="s">
         <v>100</v>
       </c>
@@ -22251,28 +22332,28 @@
   <sheetData>
     <row r="1" spans="2:10" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:10" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="350" t="s">
+      <c r="B2" s="349" t="s">
         <v>1648</v>
       </c>
-      <c r="C2" s="350"/>
-      <c r="D2" s="350"/>
-      <c r="E2" s="350"/>
-      <c r="F2" s="350"/>
-      <c r="G2" s="350"/>
-      <c r="H2" s="350"/>
-      <c r="I2" s="350"/>
-      <c r="J2" s="350"/>
+      <c r="C2" s="349"/>
+      <c r="D2" s="349"/>
+      <c r="E2" s="349"/>
+      <c r="F2" s="349"/>
+      <c r="G2" s="349"/>
+      <c r="H2" s="349"/>
+      <c r="I2" s="349"/>
+      <c r="J2" s="349"/>
     </row>
     <row r="3" spans="2:10" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="350"/>
-      <c r="C3" s="350"/>
-      <c r="D3" s="350"/>
-      <c r="E3" s="350"/>
-      <c r="F3" s="350"/>
-      <c r="G3" s="350"/>
-      <c r="H3" s="350"/>
-      <c r="I3" s="350"/>
-      <c r="J3" s="350"/>
+      <c r="B3" s="349"/>
+      <c r="C3" s="349"/>
+      <c r="D3" s="349"/>
+      <c r="E3" s="349"/>
+      <c r="F3" s="349"/>
+      <c r="G3" s="349"/>
+      <c r="H3" s="349"/>
+      <c r="I3" s="349"/>
+      <c r="J3" s="349"/>
     </row>
     <row r="4" spans="2:10" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="2:10" ht="19" customHeight="1" x14ac:dyDescent="0.2">
@@ -22282,10 +22363,10 @@
     </row>
     <row r="6" spans="2:10" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="13"/>
-      <c r="C6" s="351" t="s">
+      <c r="C6" s="350" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="351" t="s">
+      <c r="D6" s="350" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="120" t="s">
@@ -22298,12 +22379,12 @@
     </row>
     <row r="7" spans="2:10" s="9" customFormat="1" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B7" s="13"/>
-      <c r="C7" s="364"/>
-      <c r="D7" s="364"/>
+      <c r="C7" s="363"/>
+      <c r="D7" s="363"/>
       <c r="E7" s="157" t="s">
         <v>100</v>
       </c>
-      <c r="F7" s="272" t="s">
+      <c r="F7" s="269" t="s">
         <v>1168</v>
       </c>
       <c r="G7" s="13"/>
@@ -22315,10 +22396,10 @@
       <c r="D8" s="240" t="s">
         <v>1087</v>
       </c>
-      <c r="E8" s="289">
+      <c r="E8" s="286">
         <v>13.939235394006149</v>
       </c>
-      <c r="F8" s="269"/>
+      <c r="F8" s="266"/>
       <c r="G8" s="12"/>
     </row>
     <row r="9" spans="2:10" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
@@ -22328,7 +22409,7 @@
       <c r="D9" s="113" t="s">
         <v>1258</v>
       </c>
-      <c r="E9" s="290">
+      <c r="E9" s="287">
         <v>23.695947496443154</v>
       </c>
       <c r="F9" s="245"/>
@@ -22341,7 +22422,7 @@
       <c r="D10" s="113" t="s">
         <v>906</v>
       </c>
-      <c r="E10" s="290">
+      <c r="E10" s="287">
         <v>16.377621735738217</v>
       </c>
       <c r="F10" s="245"/>
@@ -22354,7 +22435,7 @@
       <c r="D11" s="113" t="s">
         <v>906</v>
       </c>
-      <c r="E11" s="290">
+      <c r="E11" s="287">
         <v>20.953554545871764</v>
       </c>
       <c r="F11" s="245"/>
@@ -22367,7 +22448,7 @@
       <c r="D12" s="113" t="s">
         <v>936</v>
       </c>
-      <c r="E12" s="290">
+      <c r="E12" s="287">
         <v>17.055303134609204</v>
       </c>
       <c r="F12" s="245"/>
@@ -22380,7 +22461,7 @@
       <c r="D13" s="113" t="s">
         <v>906</v>
       </c>
-      <c r="E13" s="290">
+      <c r="E13" s="287">
         <v>17.055303134609204</v>
       </c>
       <c r="F13" s="245"/>
@@ -22393,7 +22474,7 @@
       <c r="D14" s="113" t="s">
         <v>906</v>
       </c>
-      <c r="E14" s="290">
+      <c r="E14" s="287">
         <v>20.36770847675432</v>
       </c>
       <c r="F14" s="245"/>
@@ -22406,7 +22487,7 @@
       <c r="D15" s="113" t="s">
         <v>1087</v>
       </c>
-      <c r="E15" s="290">
+      <c r="E15" s="287">
         <v>13.939235394006149</v>
       </c>
       <c r="F15" s="245"/>
@@ -22419,7 +22500,7 @@
       <c r="D16" s="113" t="s">
         <v>895</v>
       </c>
-      <c r="E16" s="290">
+      <c r="E16" s="287">
         <v>17.055303134609204</v>
       </c>
       <c r="F16" s="245"/>
@@ -22432,7 +22513,7 @@
       <c r="D17" s="113" t="s">
         <v>1265</v>
       </c>
-      <c r="E17" s="290">
+      <c r="E17" s="287">
         <v>17.055303134609204</v>
       </c>
       <c r="F17" s="245"/>
@@ -22458,21 +22539,21 @@
       <c r="D19" s="141" t="s">
         <v>1203</v>
       </c>
-      <c r="E19" s="270">
+      <c r="E19" s="267">
         <v>23.189269815044288</v>
       </c>
-      <c r="F19" s="271"/>
+      <c r="F19" s="268"/>
       <c r="G19" s="12"/>
     </row>
     <row r="20" spans="2:7" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C20" s="226" t="s">
         <v>1268</v>
       </c>
-      <c r="D20" s="268" t="s">
+      <c r="D20" s="265" t="s">
         <v>895</v>
       </c>
-      <c r="E20" s="299"/>
-      <c r="F20" s="300">
+      <c r="E20" s="296"/>
+      <c r="F20" s="297">
         <v>6.13</v>
       </c>
       <c r="G20" s="12"/>
@@ -22484,8 +22565,8 @@
       <c r="D21" s="141" t="s">
         <v>921</v>
       </c>
-      <c r="E21" s="270"/>
-      <c r="F21" s="271">
+      <c r="E21" s="267"/>
+      <c r="F21" s="268">
         <v>26.21</v>
       </c>
       <c r="G21" s="12"/>
@@ -22524,34 +22605,34 @@
   <sheetData>
     <row r="1" spans="2:13" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:13" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="350" t="s">
+      <c r="B2" s="349" t="s">
         <v>1649</v>
       </c>
-      <c r="C2" s="350"/>
-      <c r="D2" s="350"/>
-      <c r="E2" s="350"/>
-      <c r="F2" s="350"/>
-      <c r="G2" s="350"/>
-      <c r="H2" s="350"/>
-      <c r="I2" s="350"/>
-      <c r="J2" s="350"/>
-      <c r="K2" s="350"/>
-      <c r="L2" s="350"/>
-      <c r="M2" s="350"/>
+      <c r="C2" s="349"/>
+      <c r="D2" s="349"/>
+      <c r="E2" s="349"/>
+      <c r="F2" s="349"/>
+      <c r="G2" s="349"/>
+      <c r="H2" s="349"/>
+      <c r="I2" s="349"/>
+      <c r="J2" s="349"/>
+      <c r="K2" s="349"/>
+      <c r="L2" s="349"/>
+      <c r="M2" s="349"/>
     </row>
     <row r="3" spans="2:13" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="350"/>
-      <c r="C3" s="350"/>
-      <c r="D3" s="350"/>
-      <c r="E3" s="350"/>
-      <c r="F3" s="350"/>
-      <c r="G3" s="350"/>
-      <c r="H3" s="350"/>
-      <c r="I3" s="350"/>
-      <c r="J3" s="350"/>
-      <c r="K3" s="350"/>
-      <c r="L3" s="350"/>
-      <c r="M3" s="350"/>
+      <c r="B3" s="349"/>
+      <c r="C3" s="349"/>
+      <c r="D3" s="349"/>
+      <c r="E3" s="349"/>
+      <c r="F3" s="349"/>
+      <c r="G3" s="349"/>
+      <c r="H3" s="349"/>
+      <c r="I3" s="349"/>
+      <c r="J3" s="349"/>
+      <c r="K3" s="349"/>
+      <c r="L3" s="349"/>
+      <c r="M3" s="349"/>
     </row>
     <row r="4" spans="2:13" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
@@ -22560,14 +22641,14 @@
     </row>
     <row r="5" spans="2:13" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="2:13" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="354" t="s">
+      <c r="B6" s="353" t="s">
         <v>99</v>
       </c>
       <c r="C6" s="21" t="s">
         <v>101</v>
       </c>
       <c r="D6" s="9"/>
-      <c r="E6" s="354" t="s">
+      <c r="E6" s="353" t="s">
         <v>99</v>
       </c>
       <c r="F6" s="21" t="s">
@@ -22576,12 +22657,12 @@
       <c r="G6" s="11"/>
     </row>
     <row r="7" spans="2:13" s="7" customFormat="1" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="356"/>
+      <c r="B7" s="355"/>
       <c r="C7" s="22" t="s">
         <v>100</v>
       </c>
       <c r="D7" s="9"/>
-      <c r="E7" s="356"/>
+      <c r="E7" s="355"/>
       <c r="F7" s="22" t="s">
         <v>100</v>
       </c>
@@ -22631,11 +22712,11 @@
         <v>38.655814860709533</v>
       </c>
       <c r="G10" s="12"/>
-      <c r="I10" s="403" t="s">
+      <c r="I10" s="402" t="s">
         <v>97</v>
       </c>
-      <c r="J10" s="404"/>
-      <c r="K10" s="405"/>
+      <c r="J10" s="403"/>
+      <c r="K10" s="404"/>
       <c r="L10" s="23"/>
     </row>
     <row r="11" spans="2:13" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
@@ -22652,10 +22733,10 @@
         <v>41.563020560833436</v>
       </c>
       <c r="G11" s="12"/>
-      <c r="I11" s="403" t="s">
+      <c r="I11" s="402" t="s">
         <v>103</v>
       </c>
-      <c r="J11" s="407" t="s">
+      <c r="J11" s="406" t="s">
         <v>0</v>
       </c>
       <c r="K11" s="24" t="s">
@@ -22676,8 +22757,8 @@
         <v>41.56957570333654</v>
       </c>
       <c r="G12" s="12"/>
-      <c r="I12" s="406"/>
-      <c r="J12" s="408"/>
+      <c r="I12" s="405"/>
+      <c r="J12" s="407"/>
       <c r="K12" s="25" t="s">
         <v>100</v>
       </c>
@@ -23629,38 +23710,38 @@
   <sheetData>
     <row r="1" spans="2:15" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:15" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="350" t="s">
+      <c r="B2" s="349" t="s">
         <v>1166</v>
       </c>
-      <c r="C2" s="350"/>
-      <c r="D2" s="350"/>
-      <c r="E2" s="350"/>
-      <c r="F2" s="350"/>
-      <c r="G2" s="350"/>
-      <c r="H2" s="350"/>
-      <c r="I2" s="350"/>
-      <c r="J2" s="350"/>
-      <c r="K2" s="350"/>
-      <c r="L2" s="350"/>
-      <c r="M2" s="350"/>
-      <c r="N2" s="350"/>
-      <c r="O2" s="350"/>
+      <c r="C2" s="349"/>
+      <c r="D2" s="349"/>
+      <c r="E2" s="349"/>
+      <c r="F2" s="349"/>
+      <c r="G2" s="349"/>
+      <c r="H2" s="349"/>
+      <c r="I2" s="349"/>
+      <c r="J2" s="349"/>
+      <c r="K2" s="349"/>
+      <c r="L2" s="349"/>
+      <c r="M2" s="349"/>
+      <c r="N2" s="349"/>
+      <c r="O2" s="349"/>
     </row>
     <row r="3" spans="2:15" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="350"/>
-      <c r="C3" s="350"/>
-      <c r="D3" s="350"/>
-      <c r="E3" s="350"/>
-      <c r="F3" s="350"/>
-      <c r="G3" s="350"/>
-      <c r="H3" s="350"/>
-      <c r="I3" s="350"/>
-      <c r="J3" s="350"/>
-      <c r="K3" s="350"/>
-      <c r="L3" s="350"/>
-      <c r="M3" s="350"/>
-      <c r="N3" s="350"/>
-      <c r="O3" s="350"/>
+      <c r="B3" s="349"/>
+      <c r="C3" s="349"/>
+      <c r="D3" s="349"/>
+      <c r="E3" s="349"/>
+      <c r="F3" s="349"/>
+      <c r="G3" s="349"/>
+      <c r="H3" s="349"/>
+      <c r="I3" s="349"/>
+      <c r="J3" s="349"/>
+      <c r="K3" s="349"/>
+      <c r="L3" s="349"/>
+      <c r="M3" s="349"/>
+      <c r="N3" s="349"/>
+      <c r="O3" s="349"/>
     </row>
     <row r="4" spans="2:15" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
@@ -23669,32 +23750,32 @@
     </row>
     <row r="5" spans="2:15" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="2:15" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="354" t="s">
+      <c r="B6" s="353" t="s">
         <v>99</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="E6" s="354" t="s">
+      <c r="E6" s="353" t="s">
         <v>99</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>101</v>
       </c>
       <c r="G6" s="101"/>
-      <c r="H6" s="354" t="s">
+      <c r="H6" s="353" t="s">
         <v>99</v>
       </c>
       <c r="I6" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="K6" s="354" t="s">
+      <c r="K6" s="353" t="s">
         <v>99</v>
       </c>
       <c r="L6" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="N6" s="354" t="s">
+      <c r="N6" s="353" t="s">
         <v>99</v>
       </c>
       <c r="O6" s="8" t="s">
@@ -23702,24 +23783,24 @@
       </c>
     </row>
     <row r="7" spans="2:15" s="9" customFormat="1" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="356"/>
+      <c r="B7" s="355"/>
       <c r="C7" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="E7" s="356"/>
+      <c r="E7" s="355"/>
       <c r="F7" s="10" t="s">
         <v>98</v>
       </c>
       <c r="G7" s="101"/>
-      <c r="H7" s="355"/>
+      <c r="H7" s="354"/>
       <c r="I7" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="K7" s="356"/>
+      <c r="K7" s="355"/>
       <c r="L7" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="N7" s="356"/>
+      <c r="N7" s="355"/>
       <c r="O7" s="10" t="s">
         <v>100</v>
       </c>
@@ -23753,7 +23834,7 @@
       <c r="N8" s="144" t="s">
         <v>363</v>
       </c>
-      <c r="O8" s="419">
+      <c r="O8" s="344">
         <v>13.252612624286945</v>
       </c>
     </row>
@@ -23761,7 +23842,7 @@
       <c r="B9" s="146" t="s">
         <v>240</v>
       </c>
-      <c r="C9" s="420">
+      <c r="C9" s="345">
         <v>16.648</v>
       </c>
       <c r="E9" s="146" t="s">
@@ -23780,13 +23861,13 @@
       <c r="K9" s="144" t="s">
         <v>332</v>
       </c>
-      <c r="L9" s="419">
+      <c r="L9" s="344">
         <v>10.950209630871486</v>
       </c>
       <c r="N9" s="144" t="s">
         <v>364</v>
       </c>
-      <c r="O9" s="419">
+      <c r="O9" s="344">
         <v>13.68105331076393</v>
       </c>
     </row>
@@ -23794,7 +23875,7 @@
       <c r="B10" s="146" t="s">
         <v>241</v>
       </c>
-      <c r="C10" s="420">
+      <c r="C10" s="345">
         <v>17.8</v>
       </c>
       <c r="E10" s="146" t="s">
@@ -23813,13 +23894,13 @@
       <c r="K10" s="144" t="s">
         <v>333</v>
       </c>
-      <c r="L10" s="419">
+      <c r="L10" s="344">
         <v>10.525494515581252</v>
       </c>
       <c r="N10" s="144" t="s">
         <v>365</v>
       </c>
-      <c r="O10" s="419">
+      <c r="O10" s="344">
         <v>14.128121853174697</v>
       </c>
     </row>
@@ -23827,7 +23908,7 @@
       <c r="B11" s="146" t="s">
         <v>242</v>
       </c>
-      <c r="C11" s="420">
+      <c r="C11" s="345">
         <v>18.952000000000002</v>
       </c>
       <c r="E11" s="146" t="s">
@@ -23846,13 +23927,13 @@
       <c r="K11" s="144" t="s">
         <v>334</v>
       </c>
-      <c r="L11" s="419">
+      <c r="L11" s="344">
         <v>11.348845747854421</v>
       </c>
       <c r="N11" s="144" t="s">
         <v>366</v>
       </c>
-      <c r="O11" s="419">
+      <c r="O11" s="344">
         <v>14.239888988777393</v>
       </c>
     </row>
@@ -23860,7 +23941,7 @@
       <c r="B12" s="146" t="s">
         <v>243</v>
       </c>
-      <c r="C12" s="420">
+      <c r="C12" s="345">
         <v>25.704000000000001</v>
       </c>
       <c r="E12" s="146" t="s">
@@ -23879,13 +23960,13 @@
       <c r="K12" s="144" t="s">
         <v>336</v>
       </c>
-      <c r="L12" s="419">
+      <c r="L12" s="344">
         <v>11.94121156654869</v>
       </c>
       <c r="N12" s="144" t="s">
         <v>367</v>
       </c>
-      <c r="O12" s="419">
+      <c r="O12" s="344">
         <v>14.571464824398715</v>
       </c>
     </row>
@@ -23893,7 +23974,7 @@
       <c r="B13" s="146" t="s">
         <v>244</v>
       </c>
-      <c r="C13" s="420">
+      <c r="C13" s="345">
         <v>24.552000000000003</v>
       </c>
       <c r="E13" s="146" t="s">
@@ -23912,13 +23993,13 @@
       <c r="K13" s="144" t="s">
         <v>337</v>
       </c>
-      <c r="L13" s="419">
+      <c r="L13" s="344">
         <v>10.514317802020985</v>
       </c>
       <c r="N13" s="144" t="s">
         <v>368</v>
       </c>
-      <c r="O13" s="419">
+      <c r="O13" s="344">
         <v>14.999905510875699</v>
       </c>
     </row>
@@ -23926,7 +24007,7 @@
       <c r="B14" s="146" t="s">
         <v>245</v>
       </c>
-      <c r="C14" s="420">
+      <c r="C14" s="345">
         <v>34.44</v>
       </c>
       <c r="E14" s="146" t="s">
@@ -23945,13 +24026,13 @@
       <c r="K14" s="144" t="s">
         <v>338</v>
       </c>
-      <c r="L14" s="419">
+      <c r="L14" s="344">
         <v>12.183373693687855</v>
       </c>
       <c r="N14" s="144" t="s">
         <v>369</v>
       </c>
-      <c r="O14" s="419">
+      <c r="O14" s="344">
         <v>15.860512455016428</v>
       </c>
     </row>
@@ -23959,7 +24040,7 @@
       <c r="B15" s="146" t="s">
         <v>246</v>
       </c>
-      <c r="C15" s="420">
+      <c r="C15" s="345">
         <v>35.176000000000002</v>
       </c>
       <c r="E15" s="146" t="s">
@@ -23978,13 +24059,13 @@
       <c r="K15" s="144" t="s">
         <v>339</v>
       </c>
-      <c r="L15" s="419">
+      <c r="L15" s="344">
         <v>11.00981876985959</v>
       </c>
       <c r="N15" s="144" t="s">
         <v>370</v>
       </c>
-      <c r="O15" s="419">
+      <c r="O15" s="344">
         <v>16.348562280481513</v>
       </c>
     </row>
@@ -23992,7 +24073,7 @@
       <c r="B16" s="146" t="s">
         <v>247</v>
       </c>
-      <c r="C16" s="420">
+      <c r="C16" s="345">
         <v>43.176000000000002</v>
       </c>
       <c r="E16" s="146" t="s">
@@ -24011,13 +24092,13 @@
       <c r="K16" s="144" t="s">
         <v>340</v>
       </c>
-      <c r="L16" s="419">
+      <c r="L16" s="344">
         <v>11.918858139428153</v>
       </c>
       <c r="N16" s="144" t="s">
         <v>371</v>
       </c>
-      <c r="O16" s="419">
+      <c r="O16" s="344">
         <v>16.460329416084207</v>
       </c>
     </row>
@@ -24025,7 +24106,7 @@
       <c r="B17" s="146" t="s">
         <v>248</v>
       </c>
-      <c r="C17" s="420">
+      <c r="C17" s="345">
         <v>47.751999999999995</v>
       </c>
       <c r="E17" s="146" t="s">
@@ -24044,13 +24125,13 @@
       <c r="K17" s="144" t="s">
         <v>341</v>
       </c>
-      <c r="L17" s="419">
+      <c r="L17" s="344">
         <v>11.762384149584383</v>
       </c>
       <c r="N17" s="144" t="s">
         <v>372</v>
       </c>
-      <c r="O17" s="419">
+      <c r="O17" s="344">
         <v>17.01543952291091</v>
       </c>
     </row>
@@ -24058,7 +24139,7 @@
       <c r="B18" s="146" t="s">
         <v>249</v>
       </c>
-      <c r="C18" s="420">
+      <c r="C18" s="345">
         <v>45.768000000000001</v>
       </c>
       <c r="E18" s="146" t="s">
@@ -24077,13 +24158,13 @@
       <c r="K18" s="144" t="s">
         <v>342</v>
       </c>
-      <c r="L18" s="419">
+      <c r="L18" s="344">
         <v>12.753386085261583</v>
       </c>
       <c r="N18" s="144" t="s">
         <v>373</v>
       </c>
-      <c r="O18" s="419">
+      <c r="O18" s="344">
         <v>17.235248222929538</v>
       </c>
     </row>
@@ -24091,7 +24172,7 @@
       <c r="B19" s="146" t="s">
         <v>250</v>
       </c>
-      <c r="C19" s="420">
+      <c r="C19" s="345">
         <v>66.055999999999997</v>
       </c>
       <c r="E19" s="146" t="s">
@@ -24110,13 +24191,13 @@
       <c r="K19" s="144" t="s">
         <v>343</v>
       </c>
-      <c r="L19" s="419">
+      <c r="L19" s="344">
         <v>12.451614819134319</v>
       </c>
       <c r="N19" s="144" t="s">
         <v>374</v>
       </c>
-      <c r="O19" s="419">
+      <c r="O19" s="344">
         <v>17.637609911099233</v>
       </c>
     </row>
@@ -24124,7 +24205,7 @@
       <c r="B20" s="146" t="s">
         <v>251</v>
       </c>
-      <c r="C20" s="420">
+      <c r="C20" s="345">
         <v>74.376000000000005</v>
       </c>
       <c r="E20" s="146" t="s">
@@ -24143,13 +24224,13 @@
       <c r="K20" s="144" t="s">
         <v>344</v>
       </c>
-      <c r="L20" s="419">
+      <c r="L20" s="344">
         <v>13.360654188702881</v>
       </c>
       <c r="N20" s="144" t="s">
         <v>375</v>
       </c>
-      <c r="O20" s="419">
+      <c r="O20" s="344">
         <v>18.121934165377567</v>
       </c>
     </row>
@@ -24157,7 +24238,7 @@
       <c r="B21" s="146" t="s">
         <v>253</v>
       </c>
-      <c r="C21" s="420">
+      <c r="C21" s="345">
         <v>205.73599999999999</v>
       </c>
       <c r="E21" s="146" t="s">
@@ -24176,13 +24257,13 @@
       <c r="K21" s="144" t="s">
         <v>345</v>
       </c>
-      <c r="L21" s="419">
+      <c r="L21" s="344">
         <v>14.727938814242478</v>
       </c>
       <c r="N21" s="144" t="s">
         <v>376</v>
       </c>
-      <c r="O21" s="419">
+      <c r="O21" s="344">
         <v>18.345468436582948</v>
       </c>
     </row>
@@ -24190,7 +24271,7 @@
       <c r="B22" s="146" t="s">
         <v>254</v>
       </c>
-      <c r="C22" s="420">
+      <c r="C22" s="345">
         <v>200.744</v>
       </c>
       <c r="E22" s="146" t="s">
@@ -24209,13 +24290,13 @@
       <c r="K22" s="144" t="s">
         <v>346</v>
       </c>
-      <c r="L22" s="419">
+      <c r="L22" s="344">
         <v>13.491049180239356</v>
       </c>
       <c r="N22" s="144" t="s">
         <v>377</v>
       </c>
-      <c r="O22" s="419">
+      <c r="O22" s="344">
         <v>18.565277136601576</v>
       </c>
     </row>
@@ -24223,7 +24304,7 @@
       <c r="B23" s="146" t="s">
         <v>255</v>
       </c>
-      <c r="C23" s="420">
+      <c r="C23" s="345">
         <v>76.64800000000001</v>
       </c>
       <c r="E23" s="146" t="s">
@@ -24242,13 +24323,13 @@
       <c r="K23" s="144" t="s">
         <v>347</v>
       </c>
-      <c r="L23" s="419">
+      <c r="L23" s="344">
         <v>15.357560344804313</v>
       </c>
       <c r="N23" s="144" t="s">
         <v>378</v>
       </c>
-      <c r="O23" s="419">
+      <c r="O23" s="344">
         <v>18.893127401036139</v>
       </c>
     </row>
@@ -24256,7 +24337,7 @@
       <c r="B24" s="146" t="s">
         <v>256</v>
       </c>
-      <c r="C24" s="420">
+      <c r="C24" s="345">
         <v>116.712</v>
       </c>
       <c r="E24" s="146" t="s">
@@ -24275,13 +24356,13 @@
       <c r="K24" s="144" t="s">
         <v>348</v>
       </c>
-      <c r="L24" s="419">
+      <c r="L24" s="344">
         <v>15.745019748226978</v>
       </c>
       <c r="N24" s="144" t="s">
         <v>379</v>
       </c>
-      <c r="O24" s="419">
+      <c r="O24" s="344">
         <v>19.112936101054768</v>
       </c>
     </row>
@@ -24289,7 +24370,7 @@
       <c r="B25" s="146" t="s">
         <v>257</v>
       </c>
-      <c r="C25" s="420">
+      <c r="C25" s="345">
         <v>9.3840000000000003</v>
       </c>
       <c r="E25" s="146" t="s">
@@ -24308,13 +24389,13 @@
       <c r="K25" s="144" t="s">
         <v>349</v>
       </c>
-      <c r="L25" s="419">
+      <c r="L25" s="344">
         <v>16.374641278788811</v>
       </c>
       <c r="N25" s="144" t="s">
         <v>380</v>
       </c>
-      <c r="O25" s="419">
+      <c r="O25" s="344">
         <v>19.44451193667609</v>
       </c>
     </row>
@@ -24322,7 +24403,7 @@
       <c r="B26" s="146" t="s">
         <v>258</v>
       </c>
-      <c r="C26" s="420">
+      <c r="C26" s="345">
         <v>18.727999999999998</v>
       </c>
       <c r="E26" s="146" t="s">
@@ -24341,13 +24422,13 @@
       <c r="K26" s="144" t="s">
         <v>350</v>
       </c>
-      <c r="L26" s="419">
+      <c r="L26" s="344">
         <v>18.602532848469142</v>
       </c>
       <c r="N26" s="144" t="s">
         <v>381</v>
       </c>
-      <c r="O26" s="419">
+      <c r="O26" s="344">
         <v>20.003347614689545</v>
       </c>
     </row>
@@ -24355,7 +24436,7 @@
       <c r="B27" s="146" t="s">
         <v>259</v>
       </c>
-      <c r="C27" s="420">
+      <c r="C27" s="345">
         <v>20.903999999999996</v>
       </c>
       <c r="E27" s="146" t="s">
@@ -24374,13 +24455,13 @@
       <c r="K27" s="144" t="s">
         <v>351</v>
       </c>
-      <c r="L27" s="419">
+      <c r="L27" s="344">
         <v>19.850599196032537</v>
       </c>
       <c r="N27" s="144" t="s">
         <v>382</v>
       </c>
-      <c r="O27" s="419">
+      <c r="O27" s="344">
         <v>20.11138917910548</v>
       </c>
     </row>
@@ -24388,7 +24469,7 @@
       <c r="B28" s="146" t="s">
         <v>260</v>
       </c>
-      <c r="C28" s="420">
+      <c r="C28" s="345">
         <v>51.400000000000006</v>
       </c>
       <c r="E28" s="146" t="s">
@@ -24407,13 +24488,13 @@
       <c r="K28" s="144" t="s">
         <v>352</v>
       </c>
-      <c r="L28" s="419">
+      <c r="L28" s="344">
         <v>24.500112037104529</v>
       </c>
       <c r="N28" s="144" t="s">
         <v>383</v>
       </c>
-      <c r="O28" s="419">
+      <c r="O28" s="344">
         <v>20.785717563908396</v>
       </c>
     </row>
@@ -24421,7 +24502,7 @@
       <c r="B29" s="146" t="s">
         <v>261</v>
       </c>
-      <c r="C29" s="420">
+      <c r="C29" s="345">
         <v>67.816000000000003</v>
       </c>
       <c r="E29" s="146" t="s">
@@ -24440,13 +24521,13 @@
       <c r="K29" s="144" t="s">
         <v>353</v>
       </c>
-      <c r="L29" s="419">
+      <c r="L29" s="344">
         <v>21.36318109785563</v>
       </c>
       <c r="N29" s="144" t="s">
         <v>384</v>
       </c>
-      <c r="O29" s="419">
+      <c r="O29" s="344">
         <v>21.668677935169658</v>
       </c>
     </row>
@@ -24454,7 +24535,7 @@
       <c r="B30" s="146" t="s">
         <v>262</v>
       </c>
-      <c r="C30" s="420">
+      <c r="C30" s="345">
         <v>82.376000000000005</v>
       </c>
       <c r="E30" s="146" t="s">
@@ -24473,13 +24554,13 @@
       <c r="K30" s="144" t="s">
         <v>354</v>
       </c>
-      <c r="L30" s="419">
+      <c r="L30" s="344">
         <v>67.616147381436406</v>
       </c>
       <c r="N30" s="144" t="s">
         <v>385</v>
       </c>
-      <c r="O30" s="419">
+      <c r="O30" s="344">
         <v>24.887571440527186</v>
       </c>
     </row>
@@ -24506,13 +24587,13 @@
       <c r="K31" s="144" t="s">
         <v>355</v>
       </c>
-      <c r="L31" s="419">
+      <c r="L31" s="344">
         <v>9.3258605934456948</v>
       </c>
       <c r="N31" s="144" t="s">
         <v>1164</v>
       </c>
-      <c r="O31" s="419">
+      <c r="O31" s="344">
         <v>25.662490247372528</v>
       </c>
     </row>
@@ -24539,13 +24620,13 @@
       <c r="K32" s="144" t="s">
         <v>356</v>
       </c>
-      <c r="L32" s="419">
+      <c r="L32" s="344">
         <v>10.566475798635578</v>
       </c>
       <c r="N32" s="144" t="s">
         <v>386</v>
       </c>
-      <c r="O32" s="419">
+      <c r="O32" s="344">
         <v>26.117009932156808</v>
       </c>
     </row>
@@ -24572,13 +24653,13 @@
       <c r="K33" s="144" t="s">
         <v>357</v>
       </c>
-      <c r="L33" s="419">
+      <c r="L33" s="344">
         <v>11.583556732620076</v>
       </c>
       <c r="N33" s="144" t="s">
         <v>387</v>
       </c>
-      <c r="O33" s="419">
+      <c r="O33" s="344">
         <v>28.765891045940617</v>
       </c>
     </row>
@@ -24605,13 +24686,13 @@
       <c r="K34" s="144" t="s">
         <v>358</v>
       </c>
-      <c r="L34" s="419">
+      <c r="L34" s="344">
         <v>11.918858139428153</v>
       </c>
       <c r="N34" s="144" t="s">
         <v>388</v>
       </c>
-      <c r="O34" s="419">
+      <c r="O34" s="344">
         <v>35.86682972789832</v>
       </c>
     </row>
@@ -24632,13 +24713,13 @@
       <c r="K35" s="144" t="s">
         <v>359</v>
       </c>
-      <c r="L35" s="419">
+      <c r="L35" s="344">
         <v>12.026899703844087</v>
       </c>
       <c r="N35" s="144" t="s">
         <v>1165</v>
       </c>
-      <c r="O35" s="419">
+      <c r="O35" s="344">
         <v>36.969598799178215</v>
       </c>
     </row>
@@ -24659,13 +24740,13 @@
       <c r="K36" s="144" t="s">
         <v>360</v>
       </c>
-      <c r="L36" s="419">
+      <c r="L36" s="344">
         <v>12.362201110652164</v>
       </c>
       <c r="N36" s="144" t="s">
         <v>389</v>
       </c>
-      <c r="O36" s="419">
+      <c r="O36" s="344">
         <v>41.630288353810478</v>
       </c>
     </row>
@@ -24686,13 +24767,13 @@
       <c r="K37" s="144" t="s">
         <v>361</v>
       </c>
-      <c r="L37" s="419">
+      <c r="L37" s="344">
         <v>12.798092939502661</v>
       </c>
       <c r="N37" s="144" t="s">
         <v>390</v>
       </c>
-      <c r="O37" s="419">
+      <c r="O37" s="344">
         <v>50.504598920664222</v>
       </c>
     </row>
@@ -24713,13 +24794,13 @@
       <c r="K38" s="144" t="s">
         <v>362</v>
       </c>
-      <c r="L38" s="419">
+      <c r="L38" s="344">
         <v>13.025352781894803</v>
       </c>
       <c r="N38" s="144" t="s">
         <v>391</v>
       </c>
-      <c r="O38" s="419">
+      <c r="O38" s="344">
         <v>56.271783117763142</v>
       </c>
     </row>
@@ -24740,7 +24821,7 @@
       <c r="N39" s="144" t="s">
         <v>392</v>
       </c>
-      <c r="O39" s="419">
+      <c r="O39" s="344">
         <v>76.233393536403966</v>
       </c>
     </row>
@@ -24761,7 +24842,7 @@
       <c r="N40" s="144" t="s">
         <v>393</v>
       </c>
-      <c r="O40" s="419">
+      <c r="O40" s="344">
         <v>92.208642785215417</v>
       </c>
     </row>
@@ -24770,7 +24851,7 @@
       <c r="N41" s="144" t="s">
         <v>750</v>
       </c>
-      <c r="O41" s="419">
+      <c r="O41" s="344">
         <v>18.98999225189181</v>
       </c>
     </row>
@@ -24927,45 +25008,45 @@
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" s="350" t="s">
+      <c r="A2" s="349" t="s">
         <v>1650</v>
       </c>
-      <c r="B2" s="350"/>
-      <c r="C2" s="350"/>
-      <c r="D2" s="350"/>
-      <c r="E2" s="350"/>
-      <c r="F2" s="350"/>
-      <c r="G2" s="350"/>
-      <c r="H2" s="350"/>
-      <c r="I2" s="350"/>
-      <c r="J2" s="350"/>
-      <c r="K2" s="350"/>
+      <c r="B2" s="349"/>
+      <c r="C2" s="349"/>
+      <c r="D2" s="349"/>
+      <c r="E2" s="349"/>
+      <c r="F2" s="349"/>
+      <c r="G2" s="349"/>
+      <c r="H2" s="349"/>
+      <c r="I2" s="349"/>
+      <c r="J2" s="349"/>
+      <c r="K2" s="349"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A3" s="350"/>
-      <c r="B3" s="350"/>
-      <c r="C3" s="350"/>
-      <c r="D3" s="350"/>
-      <c r="E3" s="350"/>
-      <c r="F3" s="350"/>
-      <c r="G3" s="350"/>
-      <c r="H3" s="350"/>
-      <c r="I3" s="350"/>
-      <c r="J3" s="350"/>
-      <c r="K3" s="350"/>
+      <c r="A3" s="349"/>
+      <c r="B3" s="349"/>
+      <c r="C3" s="349"/>
+      <c r="D3" s="349"/>
+      <c r="E3" s="349"/>
+      <c r="F3" s="349"/>
+      <c r="G3" s="349"/>
+      <c r="H3" s="349"/>
+      <c r="I3" s="349"/>
+      <c r="J3" s="349"/>
+      <c r="K3" s="349"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A4" s="350"/>
-      <c r="B4" s="350"/>
-      <c r="C4" s="350"/>
-      <c r="D4" s="350"/>
-      <c r="E4" s="350"/>
-      <c r="F4" s="350"/>
-      <c r="G4" s="350"/>
-      <c r="H4" s="350"/>
-      <c r="I4" s="350"/>
-      <c r="J4" s="350"/>
-      <c r="K4" s="350"/>
+      <c r="A4" s="349"/>
+      <c r="B4" s="349"/>
+      <c r="C4" s="349"/>
+      <c r="D4" s="349"/>
+      <c r="E4" s="349"/>
+      <c r="F4" s="349"/>
+      <c r="G4" s="349"/>
+      <c r="H4" s="349"/>
+      <c r="I4" s="349"/>
+      <c r="J4" s="349"/>
+      <c r="K4" s="349"/>
     </row>
     <row r="5" spans="1:11" ht="46" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A5" s="119"/>
@@ -24982,13 +25063,13 @@
     </row>
     <row r="6" spans="1:11" ht="20" x14ac:dyDescent="0.2">
       <c r="A6" s="13"/>
-      <c r="B6" s="409" t="s">
+      <c r="B6" s="408" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="411" t="s">
+      <c r="C6" s="410" t="s">
         <v>0</v>
       </c>
-      <c r="D6" s="305" t="s">
+      <c r="D6" s="302" t="s">
         <v>84</v>
       </c>
       <c r="E6" s="13"/>
@@ -25001,9 +25082,9 @@
     </row>
     <row r="7" spans="1:11" ht="20" x14ac:dyDescent="0.2">
       <c r="A7" s="13"/>
-      <c r="B7" s="410"/>
-      <c r="C7" s="412"/>
-      <c r="D7" s="307" t="s">
+      <c r="B7" s="409"/>
+      <c r="C7" s="411"/>
+      <c r="D7" s="304" t="s">
         <v>100</v>
       </c>
       <c r="E7" s="13"/>
@@ -25022,7 +25103,7 @@
       <c r="C8" s="130" t="s">
         <v>83</v>
       </c>
-      <c r="D8" s="308">
+      <c r="D8" s="305">
         <v>12.143742255266419</v>
       </c>
       <c r="E8" s="7"/>
@@ -25041,7 +25122,7 @@
       <c r="C9" s="130" t="s">
         <v>83</v>
       </c>
-      <c r="D9" s="308">
+      <c r="D9" s="305">
         <v>16.260498416632242</v>
       </c>
       <c r="E9" s="7"/>
@@ -25060,7 +25141,7 @@
       <c r="C10" s="130" t="s">
         <v>404</v>
       </c>
-      <c r="D10" s="308">
+      <c r="D10" s="305">
         <v>12.143742255266419</v>
       </c>
       <c r="E10" s="7"/>
@@ -25078,7 +25159,7 @@
       <c r="C11" s="130" t="s">
         <v>404</v>
       </c>
-      <c r="D11" s="309">
+      <c r="D11" s="306">
         <v>16.260498416632242</v>
       </c>
     </row>
@@ -25089,7 +25170,7 @@
       <c r="C12" s="130" t="s">
         <v>83</v>
       </c>
-      <c r="D12" s="309">
+      <c r="D12" s="306">
         <v>14.677130662260772</v>
       </c>
     </row>
@@ -25100,7 +25181,7 @@
       <c r="C13" s="130" t="s">
         <v>83</v>
       </c>
-      <c r="D13" s="309">
+      <c r="D13" s="306">
         <v>20.218917802560924</v>
       </c>
     </row>
@@ -25111,7 +25192,7 @@
       <c r="C14" s="130" t="s">
         <v>404</v>
       </c>
-      <c r="D14" s="309">
+      <c r="D14" s="306">
         <v>14.677130662260772</v>
       </c>
     </row>
@@ -25122,27 +25203,27 @@
       <c r="C15" s="130" t="s">
         <v>404</v>
       </c>
-      <c r="D15" s="309">
+      <c r="D15" s="306">
         <v>20.218917802560924</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="19" x14ac:dyDescent="0.25">
-      <c r="D16" s="306"/>
+      <c r="D16" s="303"/>
     </row>
     <row r="17" spans="4:4" ht="19" x14ac:dyDescent="0.25">
-      <c r="D17" s="306"/>
+      <c r="D17" s="303"/>
     </row>
     <row r="18" spans="4:4" ht="19" x14ac:dyDescent="0.25">
-      <c r="D18" s="306"/>
+      <c r="D18" s="303"/>
     </row>
     <row r="19" spans="4:4" ht="19" x14ac:dyDescent="0.25">
-      <c r="D19" s="306"/>
+      <c r="D19" s="303"/>
     </row>
     <row r="20" spans="4:4" ht="19" x14ac:dyDescent="0.25">
-      <c r="D20" s="306"/>
+      <c r="D20" s="303"/>
     </row>
     <row r="21" spans="4:4" ht="19" x14ac:dyDescent="0.25">
-      <c r="D21" s="306"/>
+      <c r="D21" s="303"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -25170,42 +25251,42 @@
   <sheetData>
     <row r="1" spans="2:9" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="350" t="s">
+      <c r="B2" s="349" t="s">
         <v>1651</v>
       </c>
-      <c r="C2" s="350"/>
-      <c r="D2" s="350"/>
-      <c r="E2" s="350"/>
-      <c r="F2" s="350"/>
-      <c r="G2" s="350"/>
-      <c r="H2" s="350"/>
-      <c r="I2" s="350"/>
+      <c r="C2" s="349"/>
+      <c r="D2" s="349"/>
+      <c r="E2" s="349"/>
+      <c r="F2" s="349"/>
+      <c r="G2" s="349"/>
+      <c r="H2" s="349"/>
+      <c r="I2" s="349"/>
     </row>
     <row r="3" spans="2:9" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="350"/>
-      <c r="C3" s="350"/>
-      <c r="D3" s="350"/>
-      <c r="E3" s="350"/>
-      <c r="F3" s="350"/>
-      <c r="G3" s="350"/>
-      <c r="H3" s="350"/>
-      <c r="I3" s="350"/>
+      <c r="B3" s="349"/>
+      <c r="C3" s="349"/>
+      <c r="D3" s="349"/>
+      <c r="E3" s="349"/>
+      <c r="F3" s="349"/>
+      <c r="G3" s="349"/>
+      <c r="H3" s="349"/>
+      <c r="I3" s="349"/>
     </row>
     <row r="4" spans="2:9" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="5" spans="2:9" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="2:9" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="354" t="s">
+      <c r="B6" s="353" t="s">
         <v>99</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>101</v>
       </c>
       <c r="E6" s="101"/>
-      <c r="G6" s="354" t="s">
+      <c r="G6" s="353" t="s">
         <v>99</v>
       </c>
       <c r="H6" s="8" t="s">
@@ -25213,28 +25294,28 @@
       </c>
     </row>
     <row r="7" spans="2:9" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="355"/>
+      <c r="B7" s="354"/>
       <c r="C7" s="16" t="s">
         <v>98</v>
       </c>
       <c r="E7" s="101"/>
-      <c r="G7" s="355"/>
+      <c r="G7" s="354"/>
       <c r="H7" s="16" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="8" spans="2:9" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="285" t="s">
+      <c r="B8" s="282" t="s">
         <v>787</v>
       </c>
-      <c r="C8" s="286">
+      <c r="C8" s="283">
         <v>24.764646464646457</v>
       </c>
       <c r="E8" s="102"/>
-      <c r="G8" s="282" t="s">
+      <c r="G8" s="279" t="s">
         <v>1421</v>
       </c>
-      <c r="H8" s="287">
+      <c r="H8" s="284">
         <v>8.0073856074165857</v>
       </c>
     </row>
@@ -25242,14 +25323,14 @@
       <c r="B9" s="130" t="s">
         <v>788</v>
       </c>
-      <c r="C9" s="286">
+      <c r="C9" s="283">
         <v>28.249494949494942</v>
       </c>
       <c r="E9" s="102"/>
       <c r="G9" s="130" t="s">
         <v>815</v>
       </c>
-      <c r="H9" s="287">
+      <c r="H9" s="284">
         <v>17.374967491241751</v>
       </c>
     </row>
@@ -25257,14 +25338,14 @@
       <c r="B10" s="130" t="s">
         <v>789</v>
       </c>
-      <c r="C10" s="286">
+      <c r="C10" s="283">
         <v>31.920202020202012</v>
       </c>
       <c r="E10" s="102"/>
       <c r="G10" s="130" t="s">
         <v>816</v>
       </c>
-      <c r="H10" s="287">
+      <c r="H10" s="284">
         <v>8.6711949454617763</v>
       </c>
     </row>
@@ -25272,14 +25353,14 @@
       <c r="B11" s="130" t="s">
         <v>790</v>
       </c>
-      <c r="C11" s="286">
+      <c r="C11" s="283">
         <v>62.401010101010087</v>
       </c>
       <c r="E11" s="102"/>
       <c r="G11" s="130" t="s">
         <v>817</v>
       </c>
-      <c r="H11" s="287">
+      <c r="H11" s="284">
         <v>10.204774580445788</v>
       </c>
     </row>
@@ -25287,14 +25368,14 @@
       <c r="B12" s="130" t="s">
         <v>791</v>
       </c>
-      <c r="C12" s="286">
+      <c r="C12" s="283">
         <v>29.689898989898982</v>
       </c>
       <c r="E12" s="102"/>
       <c r="G12" s="130" t="s">
         <v>818</v>
       </c>
-      <c r="H12" s="287">
+      <c r="H12" s="284">
         <v>8.4729221166643711</v>
       </c>
     </row>
@@ -25302,14 +25383,14 @@
       <c r="B13" s="130" t="s">
         <v>792</v>
       </c>
-      <c r="C13" s="286">
+      <c r="C13" s="283">
         <v>34.522222222222219</v>
       </c>
       <c r="E13" s="102"/>
       <c r="G13" s="130" t="s">
         <v>819</v>
       </c>
-      <c r="H13" s="287">
+      <c r="H13" s="284">
         <v>19.220118714335978</v>
       </c>
     </row>
@@ -25317,14 +25398,14 @@
       <c r="B14" s="130" t="s">
         <v>793</v>
       </c>
-      <c r="C14" s="286">
+      <c r="C14" s="283">
         <v>40.702020202020194</v>
       </c>
       <c r="E14" s="102"/>
       <c r="G14" s="130" t="s">
         <v>820</v>
       </c>
-      <c r="H14" s="287">
+      <c r="H14" s="284">
         <v>10.807685835360346</v>
       </c>
     </row>
@@ -25332,14 +25413,14 @@
       <c r="B15" s="130" t="s">
         <v>794</v>
       </c>
-      <c r="C15" s="286">
+      <c r="C15" s="283">
         <v>20.652525252525248</v>
       </c>
       <c r="E15" s="102"/>
       <c r="G15" s="130" t="s">
         <v>821</v>
       </c>
-      <c r="H15" s="287">
+      <c r="H15" s="284">
         <v>10.807685835360346</v>
       </c>
     </row>
@@ -25347,14 +25428,14 @@
       <c r="B16" s="130" t="s">
         <v>795</v>
       </c>
-      <c r="C16" s="286">
+      <c r="C16" s="283">
         <v>10.732323232323232</v>
       </c>
       <c r="E16" s="102"/>
       <c r="G16" s="130" t="s">
         <v>822</v>
       </c>
-      <c r="H16" s="287">
+      <c r="H16" s="284">
         <v>11.086886349381187</v>
       </c>
     </row>
@@ -25362,14 +25443,14 @@
       <c r="B17" s="130" t="s">
         <v>796</v>
       </c>
-      <c r="C17" s="286">
+      <c r="C17" s="283">
         <v>8.5949494949494945</v>
       </c>
       <c r="E17" s="102"/>
       <c r="G17" s="130" t="s">
         <v>823</v>
       </c>
-      <c r="H17" s="287">
+      <c r="H17" s="284">
         <v>11.633148224639344</v>
       </c>
     </row>
@@ -25377,14 +25458,14 @@
       <c r="B18" s="130" t="s">
         <v>797</v>
       </c>
-      <c r="C18" s="286">
+      <c r="C18" s="283">
         <v>13.752525252525249</v>
       </c>
       <c r="E18" s="102"/>
       <c r="G18" s="130" t="s">
         <v>824</v>
       </c>
-      <c r="H18" s="287">
+      <c r="H18" s="284">
         <v>9.7111157005828623</v>
       </c>
     </row>
@@ -25392,14 +25473,14 @@
       <c r="B19" s="130" t="s">
         <v>798</v>
       </c>
-      <c r="C19" s="286">
+      <c r="C19" s="283">
         <v>14.774747474747471</v>
       </c>
       <c r="E19" s="102"/>
       <c r="G19" s="130" t="s">
         <v>825</v>
       </c>
-      <c r="H19" s="287">
+      <c r="H19" s="284">
         <v>10.807685835360346</v>
       </c>
     </row>
@@ -25407,14 +25488,14 @@
       <c r="B20" s="130" t="s">
         <v>799</v>
       </c>
-      <c r="C20" s="286">
+      <c r="C20" s="283">
         <v>16.05252525252525</v>
       </c>
       <c r="E20" s="102"/>
       <c r="G20" s="130" t="s">
         <v>826</v>
       </c>
-      <c r="H20" s="287">
+      <c r="H20" s="284">
         <v>10.41518656202671</v>
       </c>
     </row>
@@ -25422,14 +25503,14 @@
       <c r="B21" s="130" t="s">
         <v>800</v>
       </c>
-      <c r="C21" s="286">
+      <c r="C21" s="283">
         <v>18.004040404040399</v>
       </c>
       <c r="E21" s="102"/>
       <c r="G21" s="130" t="s">
         <v>827</v>
       </c>
-      <c r="H21" s="287">
+      <c r="H21" s="284">
         <v>11.086886349381187</v>
       </c>
     </row>
@@ -25437,14 +25518,14 @@
       <c r="B22" s="130" t="s">
         <v>801</v>
       </c>
-      <c r="C22" s="286">
+      <c r="C22" s="283">
         <v>5.0868686868686854</v>
       </c>
       <c r="E22" s="102"/>
       <c r="G22" s="130" t="s">
         <v>828</v>
       </c>
-      <c r="H22" s="287">
+      <c r="H22" s="284">
         <v>9.8203680756344927</v>
       </c>
     </row>
@@ -25452,14 +25533,14 @@
       <c r="B23" s="130" t="s">
         <v>802</v>
       </c>
-      <c r="C23" s="286">
+      <c r="C23" s="283">
         <v>6.7595959595959574</v>
       </c>
       <c r="E23" s="102"/>
       <c r="G23" s="130" t="s">
         <v>829</v>
       </c>
-      <c r="H23" s="287">
+      <c r="H23" s="284">
         <v>10.358537182370307</v>
       </c>
     </row>
@@ -25467,14 +25548,14 @@
       <c r="B24" s="130" t="s">
         <v>1058</v>
       </c>
-      <c r="C24" s="286">
+      <c r="C24" s="283">
         <v>7.9909090909090894</v>
       </c>
       <c r="E24" s="102"/>
       <c r="G24" s="130" t="s">
         <v>830</v>
       </c>
-      <c r="H24" s="287">
+      <c r="H24" s="284">
         <v>11.479385622714824</v>
       </c>
     </row>
@@ -25482,14 +25563,14 @@
       <c r="B25" s="130" t="s">
         <v>803</v>
       </c>
-      <c r="C25" s="286">
+      <c r="C25" s="283">
         <v>11.568686868686866</v>
       </c>
       <c r="E25" s="102"/>
       <c r="G25" s="130" t="s">
         <v>831</v>
       </c>
-      <c r="H25" s="287">
+      <c r="H25" s="284">
         <v>11.317530252267963</v>
       </c>
     </row>
@@ -25497,14 +25578,14 @@
       <c r="B26" s="130" t="s">
         <v>804</v>
       </c>
-      <c r="C26" s="286">
+      <c r="C26" s="283">
         <v>10.035353535353533</v>
       </c>
       <c r="E26" s="102"/>
       <c r="G26" s="130" t="s">
         <v>832</v>
       </c>
-      <c r="H26" s="287">
+      <c r="H26" s="284">
         <v>11.912348738660178</v>
       </c>
     </row>
@@ -25512,14 +25593,14 @@
       <c r="B27" s="130" t="s">
         <v>805</v>
       </c>
-      <c r="C27" s="286">
+      <c r="C27" s="283">
         <v>2.322222222222222</v>
       </c>
       <c r="E27" s="102"/>
       <c r="G27" s="130" t="s">
         <v>833</v>
       </c>
-      <c r="H27" s="287">
+      <c r="H27" s="284">
         <v>10.237145654535162</v>
       </c>
     </row>
@@ -25527,14 +25608,14 @@
       <c r="B28" s="130" t="s">
         <v>806</v>
       </c>
-      <c r="C28" s="286">
+      <c r="C28" s="283">
         <v>60.797979797979792</v>
       </c>
       <c r="E28" s="102"/>
       <c r="G28" s="130" t="s">
         <v>834</v>
       </c>
-      <c r="H28" s="287">
+      <c r="H28" s="284">
         <v>10.662016001958174</v>
       </c>
     </row>
@@ -25542,14 +25623,14 @@
       <c r="B29" s="130" t="s">
         <v>1059</v>
       </c>
-      <c r="C29" s="286">
+      <c r="C29" s="283">
         <v>60.797979797979792</v>
       </c>
       <c r="E29" s="102"/>
       <c r="G29" s="130" t="s">
         <v>835</v>
       </c>
-      <c r="H29" s="287">
+      <c r="H29" s="284">
         <v>11.633148224639344</v>
       </c>
     </row>
@@ -25557,14 +25638,14 @@
       <c r="B30" s="130" t="s">
         <v>1060</v>
       </c>
-      <c r="C30" s="286">
+      <c r="C30" s="283">
         <v>16.935353535353531</v>
       </c>
       <c r="E30" s="102"/>
       <c r="G30" s="130" t="s">
         <v>836</v>
       </c>
-      <c r="H30" s="287">
+      <c r="H30" s="284">
         <v>13.88293787385072</v>
       </c>
     </row>
@@ -25572,14 +25653,14 @@
       <c r="B31" s="130" t="s">
         <v>1061</v>
       </c>
-      <c r="C31" s="286">
+      <c r="C31" s="283">
         <v>8.7111111111111086</v>
       </c>
       <c r="E31" s="102"/>
       <c r="G31" s="130" t="s">
         <v>837</v>
       </c>
-      <c r="H31" s="287">
+      <c r="H31" s="284">
         <v>11.244695335566874</v>
       </c>
     </row>
@@ -25587,14 +25668,14 @@
       <c r="B32" s="130" t="s">
         <v>1062</v>
       </c>
-      <c r="C32" s="286">
+      <c r="C32" s="283">
         <v>80.243434343434345</v>
       </c>
       <c r="E32" s="102"/>
       <c r="G32" s="130" t="s">
         <v>838</v>
       </c>
-      <c r="H32" s="287">
+      <c r="H32" s="284">
         <v>11.28515917817859</v>
       </c>
     </row>
@@ -25602,14 +25683,14 @@
       <c r="B33" s="130" t="s">
         <v>1063</v>
       </c>
-      <c r="C33" s="286">
+      <c r="C33" s="283">
         <v>9.3383838383838356</v>
       </c>
       <c r="E33" s="102"/>
       <c r="G33" s="130" t="s">
         <v>839</v>
       </c>
-      <c r="H33" s="287">
+      <c r="H33" s="284">
         <v>9.8810638395520645</v>
       </c>
     </row>
@@ -25617,14 +25698,14 @@
       <c r="B34" s="130" t="s">
         <v>807</v>
       </c>
-      <c r="C34" s="286">
+      <c r="C34" s="283">
         <v>161.32424242424239</v>
       </c>
       <c r="E34" s="102"/>
       <c r="G34" s="130" t="s">
         <v>840</v>
       </c>
-      <c r="H34" s="287">
+      <c r="H34" s="284">
         <v>10.148125200789389</v>
       </c>
     </row>
@@ -25632,14 +25713,14 @@
       <c r="B35" s="130" t="s">
         <v>808</v>
       </c>
-      <c r="C35" s="286">
+      <c r="C35" s="283">
         <v>1058.5333333333331</v>
       </c>
       <c r="E35" s="102"/>
       <c r="G35" s="130" t="s">
         <v>841</v>
       </c>
-      <c r="H35" s="287">
+      <c r="H35" s="284">
         <v>12.393868465739594</v>
       </c>
     </row>
@@ -25647,14 +25728,14 @@
       <c r="B36" s="130" t="s">
         <v>809</v>
       </c>
-      <c r="C36" s="286">
+      <c r="C36" s="283">
         <v>311.73030303030305</v>
       </c>
       <c r="E36" s="102"/>
       <c r="G36" s="130" t="s">
         <v>1065</v>
       </c>
-      <c r="H36" s="287">
+      <c r="H36" s="284">
         <v>11.28515917817859</v>
       </c>
     </row>
@@ -25662,14 +25743,14 @@
       <c r="B37" s="130" t="s">
         <v>810</v>
       </c>
-      <c r="C37" s="286">
+      <c r="C37" s="283">
         <v>1564.9050505050502</v>
       </c>
       <c r="E37" s="102"/>
       <c r="G37" s="130" t="s">
         <v>1066</v>
       </c>
-      <c r="H37" s="287">
+      <c r="H37" s="284">
         <v>10.840056909449721</v>
       </c>
     </row>
@@ -25677,14 +25758,14 @@
       <c r="B38" s="130" t="s">
         <v>811</v>
       </c>
-      <c r="C38" s="286">
+      <c r="C38" s="283">
         <v>1364.5727272727272</v>
       </c>
       <c r="E38" s="102"/>
       <c r="G38" s="130" t="s">
         <v>1067</v>
       </c>
-      <c r="H38" s="287">
+      <c r="H38" s="284">
         <v>11.28515917817859</v>
       </c>
     </row>
@@ -25692,14 +25773,14 @@
       <c r="B39" s="130" t="s">
         <v>812</v>
       </c>
-      <c r="C39" s="286">
+      <c r="C39" s="283">
         <v>1217.2797979797979</v>
       </c>
       <c r="E39" s="102"/>
       <c r="G39" s="130" t="s">
         <v>1068</v>
       </c>
-      <c r="H39" s="287">
+      <c r="H39" s="284">
         <v>11.564359692199425</v>
       </c>
     </row>
@@ -25707,14 +25788,14 @@
       <c r="B40" s="130" t="s">
         <v>813</v>
       </c>
-      <c r="C40" s="286">
+      <c r="C40" s="283">
         <v>1848.9202020202017</v>
       </c>
       <c r="E40" s="102"/>
       <c r="G40" s="130" t="s">
         <v>1069</v>
       </c>
-      <c r="H40" s="287">
+      <c r="H40" s="284">
         <v>11.564359692199425</v>
       </c>
     </row>
@@ -25722,14 +25803,14 @@
       <c r="B41" s="130" t="s">
         <v>814</v>
       </c>
-      <c r="C41" s="286">
+      <c r="C41" s="283">
         <v>3047.1040404040396</v>
       </c>
       <c r="E41" s="102"/>
       <c r="G41" s="130" t="s">
         <v>1070</v>
       </c>
-      <c r="H41" s="287">
+      <c r="H41" s="284">
         <v>9.8851102238132373</v>
       </c>
     </row>
@@ -25737,25 +25818,25 @@
       <c r="B42" s="130" t="s">
         <v>1064</v>
       </c>
-      <c r="C42" s="286">
+      <c r="C42" s="283">
         <v>3696.3080808080804</v>
       </c>
       <c r="E42" s="102"/>
       <c r="G42" s="130" t="s">
         <v>1071</v>
       </c>
-      <c r="H42" s="287">
+      <c r="H42" s="284">
         <v>12.33317270182202</v>
       </c>
     </row>
     <row r="43" spans="2:8" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="283"/>
-      <c r="C43" s="284"/>
+      <c r="B43" s="280"/>
+      <c r="C43" s="281"/>
       <c r="E43" s="102"/>
       <c r="G43" s="130" t="s">
         <v>1072</v>
       </c>
-      <c r="H43" s="287">
+      <c r="H43" s="284">
         <v>11.584591613505287</v>
       </c>
     </row>
@@ -25766,7 +25847,7 @@
       <c r="G44" s="130" t="s">
         <v>1073</v>
       </c>
-      <c r="H44" s="287">
+      <c r="H44" s="284">
         <v>11.98923003962244</v>
       </c>
     </row>
@@ -25777,7 +25858,7 @@
       <c r="G45" s="130" t="s">
         <v>1074</v>
       </c>
-      <c r="H45" s="287">
+      <c r="H45" s="284">
         <v>11.119257423470556</v>
       </c>
     </row>
@@ -25788,7 +25869,7 @@
       <c r="G46" s="130" t="s">
         <v>1075</v>
       </c>
-      <c r="H46" s="287">
+      <c r="H46" s="284">
         <v>11.382272400446709</v>
       </c>
     </row>
@@ -25799,7 +25880,7 @@
       <c r="G47" s="130" t="s">
         <v>1076</v>
       </c>
-      <c r="H47" s="287">
+      <c r="H47" s="284">
         <v>9.8851102238132373</v>
       </c>
     </row>
@@ -25810,7 +25891,7 @@
       <c r="G48" s="130" t="s">
         <v>1422</v>
       </c>
-      <c r="H48" s="287">
+      <c r="H48" s="284">
         <v>16.44025272691113</v>
       </c>
     </row>
@@ -25821,7 +25902,7 @@
       <c r="G49" s="130" t="s">
         <v>1423</v>
       </c>
-      <c r="H49" s="287">
+      <c r="H49" s="284">
         <v>10.977633974329551</v>
       </c>
     </row>
@@ -25832,7 +25913,7 @@
       <c r="G50" s="130" t="s">
         <v>1424</v>
       </c>
-      <c r="H50" s="287">
+      <c r="H50" s="284">
         <v>12.191549252681012</v>
       </c>
     </row>
@@ -25843,7 +25924,7 @@
       <c r="G51" s="130" t="s">
         <v>1425</v>
       </c>
-      <c r="H51" s="287">
+      <c r="H51" s="284">
         <v>12.316987164777331</v>
       </c>
     </row>
@@ -25854,7 +25935,7 @@
       <c r="G52" s="130" t="s">
         <v>1426</v>
       </c>
-      <c r="H52" s="287">
+      <c r="H52" s="284">
         <v>10.572995548212399</v>
       </c>
     </row>
@@ -25865,7 +25946,7 @@
       <c r="G53" s="130" t="s">
         <v>1427</v>
       </c>
-      <c r="H53" s="287">
+      <c r="H53" s="284">
         <v>12.737811127939173</v>
       </c>
     </row>
@@ -25876,7 +25957,7 @@
       <c r="G54" s="130" t="s">
         <v>1428</v>
       </c>
-      <c r="H54" s="287">
+      <c r="H54" s="284">
         <v>11.28515917817859</v>
       </c>
     </row>
@@ -25887,7 +25968,7 @@
       <c r="G55" s="130" t="s">
         <v>1429</v>
       </c>
-      <c r="H55" s="287">
+      <c r="H55" s="284">
         <v>8.7318907093793481</v>
       </c>
     </row>
@@ -25898,7 +25979,7 @@
       <c r="G56" s="130" t="s">
         <v>1430</v>
       </c>
-      <c r="H56" s="287">
+      <c r="H56" s="284">
         <v>11.483432006975995</v>
       </c>
     </row>
@@ -25919,43 +26000,43 @@
       </c>
     </row>
     <row r="59" spans="2:8" ht="19" x14ac:dyDescent="0.25">
-      <c r="G59" s="280"/>
-      <c r="H59" s="281"/>
+      <c r="G59" s="277"/>
+      <c r="H59" s="278"/>
     </row>
     <row r="60" spans="2:8" ht="19" x14ac:dyDescent="0.25">
-      <c r="G60" s="266"/>
+      <c r="G60" s="263"/>
       <c r="H60" s="187"/>
     </row>
     <row r="61" spans="2:8" ht="19" x14ac:dyDescent="0.25">
-      <c r="G61" s="266"/>
+      <c r="G61" s="263"/>
       <c r="H61" s="187"/>
     </row>
     <row r="62" spans="2:8" ht="19" x14ac:dyDescent="0.25">
-      <c r="G62" s="266"/>
+      <c r="G62" s="263"/>
       <c r="H62" s="187"/>
     </row>
     <row r="63" spans="2:8" ht="19" x14ac:dyDescent="0.25">
-      <c r="G63" s="266"/>
+      <c r="G63" s="263"/>
       <c r="H63" s="187"/>
     </row>
     <row r="64" spans="2:8" ht="19" x14ac:dyDescent="0.25">
-      <c r="G64" s="266"/>
+      <c r="G64" s="263"/>
       <c r="H64" s="187"/>
     </row>
     <row r="65" spans="7:8" ht="19" x14ac:dyDescent="0.25">
-      <c r="G65" s="266"/>
+      <c r="G65" s="263"/>
       <c r="H65" s="187"/>
     </row>
     <row r="66" spans="7:8" ht="19" x14ac:dyDescent="0.25">
-      <c r="G66" s="266"/>
+      <c r="G66" s="263"/>
       <c r="H66" s="187"/>
     </row>
     <row r="67" spans="7:8" ht="19" x14ac:dyDescent="0.25">
-      <c r="G67" s="266"/>
+      <c r="G67" s="263"/>
       <c r="H67" s="187"/>
     </row>
     <row r="68" spans="7:8" ht="19" x14ac:dyDescent="0.25">
-      <c r="G68" s="266"/>
+      <c r="G68" s="263"/>
       <c r="H68" s="187"/>
     </row>
   </sheetData>
@@ -25984,26 +26065,26 @@
   <sheetData>
     <row r="1" spans="2:9" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="350" t="s">
+      <c r="B2" s="349" t="s">
         <v>1658</v>
       </c>
-      <c r="C2" s="350"/>
-      <c r="D2" s="350"/>
-      <c r="E2" s="350"/>
-      <c r="F2" s="350"/>
-      <c r="G2" s="350"/>
-      <c r="H2" s="350"/>
-      <c r="I2" s="350"/>
+      <c r="C2" s="349"/>
+      <c r="D2" s="349"/>
+      <c r="E2" s="349"/>
+      <c r="F2" s="349"/>
+      <c r="G2" s="349"/>
+      <c r="H2" s="349"/>
+      <c r="I2" s="349"/>
     </row>
     <row r="3" spans="2:9" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="350"/>
-      <c r="C3" s="350"/>
-      <c r="D3" s="350"/>
-      <c r="E3" s="350"/>
-      <c r="F3" s="350"/>
-      <c r="G3" s="350"/>
-      <c r="H3" s="350"/>
-      <c r="I3" s="350"/>
+      <c r="B3" s="349"/>
+      <c r="C3" s="349"/>
+      <c r="D3" s="349"/>
+      <c r="E3" s="349"/>
+      <c r="F3" s="349"/>
+      <c r="G3" s="349"/>
+      <c r="H3" s="349"/>
+      <c r="I3" s="349"/>
     </row>
     <row r="4" spans="2:9" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
@@ -26012,14 +26093,14 @@
     </row>
     <row r="5" spans="2:9" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="2:9" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="354" t="s">
+      <c r="B6" s="353" t="s">
         <v>99</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>101</v>
       </c>
       <c r="E6" s="101"/>
-      <c r="G6" s="354" t="s">
+      <c r="G6" s="353" t="s">
         <v>99</v>
       </c>
       <c r="H6" s="8" t="s">
@@ -26027,558 +26108,558 @@
       </c>
     </row>
     <row r="7" spans="2:9" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="355"/>
+      <c r="B7" s="354"/>
       <c r="C7" s="16" t="s">
         <v>98</v>
       </c>
       <c r="E7" s="101"/>
-      <c r="G7" s="355"/>
+      <c r="G7" s="354"/>
       <c r="H7" s="16" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="8" spans="2:9" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="288" t="s">
+      <c r="B8" s="285" t="s">
         <v>1433</v>
       </c>
-      <c r="C8" s="286">
+      <c r="C8" s="283">
         <v>6.6777777777777771</v>
       </c>
       <c r="E8" s="102"/>
       <c r="G8" s="130" t="s">
         <v>1474</v>
       </c>
-      <c r="H8" s="287">
+      <c r="H8" s="284">
         <v>10.790307035660197</v>
       </c>
     </row>
     <row r="9" spans="2:9" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="288" t="s">
+      <c r="B9" s="285" t="s">
         <v>1434</v>
       </c>
-      <c r="C9" s="286">
+      <c r="C9" s="283">
         <v>9.593939393939392</v>
       </c>
       <c r="E9" s="102"/>
-      <c r="G9" s="282" t="s">
+      <c r="G9" s="279" t="s">
         <v>1475</v>
       </c>
-      <c r="H9" s="287">
+      <c r="H9" s="284">
         <v>11.716767176098031</v>
       </c>
     </row>
     <row r="10" spans="2:9" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="288" t="s">
+      <c r="B10" s="285" t="s">
         <v>1435</v>
       </c>
-      <c r="C10" s="286">
+      <c r="C10" s="283">
         <v>11.684848484848484</v>
       </c>
       <c r="E10" s="102"/>
       <c r="G10" s="130" t="s">
         <v>1476</v>
       </c>
-      <c r="H10" s="287">
+      <c r="H10" s="284">
         <v>12.975354536692826</v>
       </c>
     </row>
     <row r="11" spans="2:9" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="288" t="s">
+      <c r="B11" s="285" t="s">
         <v>1436</v>
       </c>
-      <c r="C11" s="286">
+      <c r="C11" s="283">
         <v>11.893939393939393</v>
       </c>
       <c r="E11" s="102"/>
       <c r="G11" s="130" t="s">
         <v>1477</v>
       </c>
-      <c r="H11" s="287">
+      <c r="H11" s="284">
         <v>10.498967368855846</v>
       </c>
     </row>
     <row r="12" spans="2:9" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="288" t="s">
+      <c r="B12" s="285" t="s">
         <v>1437</v>
       </c>
-      <c r="C12" s="286">
+      <c r="C12" s="283">
         <v>12.660606060606058</v>
       </c>
       <c r="E12" s="102"/>
       <c r="G12" s="130" t="s">
         <v>1478</v>
       </c>
-      <c r="H12" s="287">
+      <c r="H12" s="284">
         <v>12.392675203084124</v>
       </c>
     </row>
     <row r="13" spans="2:9" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="288" t="s">
+      <c r="B13" s="285" t="s">
         <v>1438</v>
       </c>
-      <c r="C13" s="286">
+      <c r="C13" s="283">
         <v>13.822222222222219</v>
       </c>
       <c r="E13" s="102"/>
       <c r="G13" s="130" t="s">
         <v>1479</v>
       </c>
-      <c r="H13" s="287">
+      <c r="H13" s="284">
         <v>10.061957868649316</v>
       </c>
     </row>
     <row r="14" spans="2:9" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="288" t="s">
+      <c r="B14" s="285" t="s">
         <v>1439</v>
       </c>
-      <c r="C14" s="286">
+      <c r="C14" s="283">
         <v>15.773737373737372</v>
       </c>
       <c r="E14" s="102"/>
       <c r="G14" s="130" t="s">
         <v>1480</v>
       </c>
-      <c r="H14" s="287">
+      <c r="H14" s="284">
         <v>6.9038358804901536</v>
       </c>
     </row>
     <row r="15" spans="2:9" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="288" t="s">
+      <c r="B15" s="285" t="s">
         <v>1440</v>
       </c>
-      <c r="C15" s="286">
+      <c r="C15" s="283">
         <v>16.935353535353531</v>
       </c>
       <c r="E15" s="102"/>
       <c r="G15" s="130" t="s">
         <v>1481</v>
       </c>
-      <c r="H15" s="287">
+      <c r="H15" s="284">
         <v>6.2891091835329753</v>
       </c>
     </row>
     <row r="16" spans="2:9" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="288" t="s">
+      <c r="B16" s="285" t="s">
         <v>1441</v>
       </c>
-      <c r="C16" s="286">
+      <c r="C16" s="283">
         <v>17.702020202020201</v>
       </c>
       <c r="E16" s="102"/>
       <c r="G16" s="130" t="s">
         <v>1482</v>
       </c>
-      <c r="H16" s="287">
+      <c r="H16" s="284">
         <v>8.4595897012253882</v>
       </c>
     </row>
     <row r="17" spans="2:8" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="288" t="s">
+      <c r="B17" s="285" t="s">
         <v>1442</v>
       </c>
-      <c r="C17" s="286">
+      <c r="C17" s="283">
         <v>18.073737373737373</v>
       </c>
       <c r="E17" s="102"/>
       <c r="G17" s="130" t="s">
         <v>1483</v>
       </c>
-      <c r="H17" s="287">
+      <c r="H17" s="284">
         <v>8.7509293680297393</v>
       </c>
     </row>
     <row r="18" spans="2:8" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="288" t="s">
+      <c r="B18" s="285" t="s">
         <v>1443</v>
       </c>
-      <c r="C18" s="286">
+      <c r="C18" s="283">
         <v>19.095959595959592</v>
       </c>
       <c r="E18" s="102"/>
       <c r="G18" s="130" t="s">
         <v>1484</v>
       </c>
-      <c r="H18" s="287">
+      <c r="H18" s="284">
         <v>10.644637202258018</v>
       </c>
     </row>
     <row r="19" spans="2:8" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="288" t="s">
+      <c r="B19" s="285" t="s">
         <v>1444</v>
       </c>
-      <c r="C19" s="286">
+      <c r="C19" s="283">
         <v>23.370707070707063</v>
       </c>
       <c r="E19" s="102"/>
       <c r="G19" s="130" t="s">
         <v>1485</v>
       </c>
-      <c r="H19" s="287">
+      <c r="H19" s="284">
         <v>13.558033870301527</v>
       </c>
     </row>
     <row r="20" spans="2:8" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="288" t="s">
+      <c r="B20" s="285" t="s">
         <v>1445</v>
       </c>
-      <c r="C20" s="286">
+      <c r="C20" s="283">
         <v>25.856565656565653</v>
       </c>
       <c r="E20" s="102"/>
       <c r="G20" s="130" t="s">
         <v>1486</v>
       </c>
-      <c r="H20" s="287">
+      <c r="H20" s="284">
         <v>10.061957868649316</v>
       </c>
     </row>
     <row r="21" spans="2:8" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="288" t="s">
+      <c r="B21" s="285" t="s">
         <v>1446</v>
       </c>
-      <c r="C21" s="286">
+      <c r="C21" s="283">
         <v>97.295959595959573</v>
       </c>
       <c r="E21" s="102"/>
       <c r="G21" s="130" t="s">
         <v>1487</v>
       </c>
-      <c r="H21" s="287">
+      <c r="H21" s="284">
         <v>10.353297535453668</v>
       </c>
     </row>
     <row r="22" spans="2:8" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="288" t="s">
+      <c r="B22" s="285" t="s">
         <v>1447</v>
       </c>
-      <c r="C22" s="286">
+      <c r="C22" s="283">
         <v>26.809090909090902</v>
       </c>
       <c r="E22" s="102"/>
       <c r="G22" s="130" t="s">
         <v>1488</v>
       </c>
-      <c r="H22" s="287">
+      <c r="H22" s="284">
         <v>10.935976869062371</v>
       </c>
     </row>
     <row r="23" spans="2:8" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="288" t="s">
+      <c r="B23" s="285" t="s">
         <v>1448</v>
       </c>
-      <c r="C23" s="286">
+      <c r="C23" s="283">
         <v>29.527272727272724</v>
       </c>
       <c r="E23" s="102"/>
       <c r="G23" s="130" t="s">
         <v>1489</v>
       </c>
-      <c r="H23" s="287">
+      <c r="H23" s="284">
         <v>12.975354536692826</v>
       </c>
     </row>
     <row r="24" spans="2:8" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="288" t="s">
+      <c r="B24" s="285" t="s">
         <v>1449</v>
       </c>
-      <c r="C24" s="286">
+      <c r="C24" s="283">
         <v>65.305050505050488</v>
       </c>
       <c r="E24" s="102"/>
       <c r="G24" s="130" t="s">
         <v>1490</v>
       </c>
-      <c r="H24" s="287">
+      <c r="H24" s="284">
         <v>11.518656202671069</v>
       </c>
     </row>
     <row r="25" spans="2:8" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="288" t="s">
+      <c r="B25" s="285" t="s">
         <v>1450</v>
       </c>
-      <c r="C25" s="286">
+      <c r="C25" s="283">
         <v>33.383838383838373</v>
       </c>
       <c r="E25" s="102"/>
       <c r="G25" s="130" t="s">
         <v>1491</v>
       </c>
-      <c r="H25" s="287">
+      <c r="H25" s="284">
         <v>14.432052870714578</v>
       </c>
     </row>
     <row r="26" spans="2:8" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="288" t="s">
+      <c r="B26" s="285" t="s">
         <v>1451</v>
       </c>
-      <c r="C26" s="286">
+      <c r="C26" s="283">
         <v>38.239393939393935</v>
       </c>
       <c r="E26" s="102"/>
       <c r="G26" s="130" t="s">
         <v>1492</v>
       </c>
-      <c r="H26" s="287">
+      <c r="H26" s="284">
         <v>11.809995869475422</v>
       </c>
     </row>
     <row r="27" spans="2:8" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="288" t="s">
+      <c r="B27" s="285" t="s">
         <v>1452</v>
       </c>
-      <c r="C27" s="286">
+      <c r="C27" s="283">
         <v>42.11919191919192</v>
       </c>
       <c r="E27" s="102"/>
       <c r="G27" s="130" t="s">
         <v>1493</v>
       </c>
-      <c r="H27" s="287">
+      <c r="H27" s="284">
         <v>12.914173206663913</v>
       </c>
     </row>
     <row r="28" spans="2:8" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="288" t="s">
+      <c r="B28" s="285" t="s">
         <v>1453</v>
       </c>
-      <c r="C28" s="286">
+      <c r="C28" s="283">
         <v>132.53939393939393</v>
       </c>
       <c r="E28" s="102"/>
       <c r="G28" s="130" t="s">
         <v>1494</v>
       </c>
-      <c r="H28" s="287">
+      <c r="H28" s="284">
         <v>9.1879388682362659</v>
       </c>
     </row>
     <row r="29" spans="2:8" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="288" t="s">
+      <c r="B29" s="285" t="s">
         <v>1454</v>
       </c>
-      <c r="C29" s="286">
+      <c r="C29" s="283">
         <v>52.364646464646462</v>
       </c>
       <c r="E29" s="102"/>
       <c r="G29" s="130" t="s">
         <v>1495</v>
       </c>
-      <c r="H29" s="287">
+      <c r="H29" s="284">
         <v>9.4792785350406152</v>
       </c>
     </row>
     <row r="30" spans="2:8" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="288" t="s">
+      <c r="B30" s="285" t="s">
         <v>1455</v>
       </c>
-      <c r="C30" s="286">
+      <c r="C30" s="283">
         <v>170.45454545454544</v>
       </c>
       <c r="E30" s="102"/>
       <c r="G30" s="130" t="s">
         <v>1496</v>
       </c>
-      <c r="H30" s="287">
+      <c r="H30" s="284">
         <v>8.7509293680297393</v>
       </c>
     </row>
     <row r="31" spans="2:8" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="288" t="s">
+      <c r="B31" s="285" t="s">
         <v>1456</v>
       </c>
-      <c r="C31" s="286">
+      <c r="C31" s="283">
         <v>195.68484848484846</v>
       </c>
       <c r="E31" s="102"/>
       <c r="G31" s="130" t="s">
         <v>1497</v>
       </c>
-      <c r="H31" s="287">
+      <c r="H31" s="284">
         <v>7.8769103676166852</v>
       </c>
     </row>
     <row r="32" spans="2:8" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="288" t="s">
+      <c r="B32" s="285" t="s">
         <v>1457</v>
       </c>
-      <c r="C32" s="286">
+      <c r="C32" s="283">
         <v>157.11919191919191</v>
       </c>
       <c r="E32" s="102"/>
       <c r="G32" s="130" t="s">
         <v>1498</v>
       </c>
-      <c r="H32" s="287">
+      <c r="H32" s="284">
         <v>8.1682500344210371</v>
       </c>
     </row>
     <row r="33" spans="2:8" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="288" t="s">
+      <c r="B33" s="285" t="s">
         <v>1458</v>
       </c>
-      <c r="C33" s="286">
+      <c r="C33" s="283">
         <v>80.243434343434345</v>
       </c>
       <c r="E33" s="102"/>
       <c r="G33" s="130" t="s">
         <v>1499</v>
       </c>
-      <c r="H33" s="287">
+      <c r="H33" s="284">
         <v>12.975354536692826</v>
       </c>
     </row>
     <row r="34" spans="2:8" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="288" t="s">
+      <c r="B34" s="285" t="s">
         <v>1459</v>
       </c>
-      <c r="C34" s="286">
+      <c r="C34" s="283">
         <v>222.35555555555553</v>
       </c>
       <c r="E34" s="102"/>
       <c r="G34" s="130" t="s">
         <v>1500</v>
       </c>
-      <c r="H34" s="287">
+      <c r="H34" s="284">
         <v>14.432052870714578</v>
       </c>
     </row>
     <row r="35" spans="2:8" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="288" t="s">
+      <c r="B35" s="285" t="s">
         <v>1460</v>
       </c>
-      <c r="C35" s="286">
+      <c r="C35" s="283">
         <v>103.10404040404039</v>
       </c>
       <c r="E35" s="102"/>
       <c r="G35" s="130" t="s">
         <v>1501</v>
       </c>
-      <c r="H35" s="287">
+      <c r="H35" s="284">
         <v>13.558033870301527</v>
       </c>
     </row>
     <row r="36" spans="2:8" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="288" t="s">
+      <c r="B36" s="285" t="s">
         <v>1461</v>
       </c>
-      <c r="C36" s="286">
+      <c r="C36" s="283">
         <v>116.57878787878786</v>
       </c>
       <c r="E36" s="102"/>
       <c r="G36" s="130" t="s">
         <v>1502</v>
       </c>
-      <c r="H36" s="287">
+      <c r="H36" s="284">
         <v>15.888751204736336</v>
       </c>
     </row>
     <row r="37" spans="2:8" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="288" t="s">
+      <c r="B37" s="285" t="s">
         <v>1462</v>
       </c>
-      <c r="C37" s="286">
+      <c r="C37" s="283">
         <v>71.182828282828268</v>
       </c>
       <c r="E37" s="102"/>
       <c r="G37" s="130" t="s">
         <v>1503</v>
       </c>
-      <c r="H37" s="287">
+      <c r="H37" s="284">
         <v>16.61710037174721</v>
       </c>
     </row>
     <row r="38" spans="2:8" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="288" t="s">
+      <c r="B38" s="285" t="s">
         <v>1463</v>
       </c>
-      <c r="C38" s="286">
+      <c r="C38" s="283">
         <v>250.32727272727269</v>
       </c>
       <c r="E38" s="102"/>
       <c r="G38" s="130" t="s">
         <v>1504</v>
       </c>
-      <c r="H38" s="287">
+      <c r="H38" s="284">
         <v>12.392675203084124</v>
       </c>
     </row>
     <row r="39" spans="2:8" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="288" t="s">
+      <c r="B39" s="285" t="s">
         <v>1464</v>
       </c>
-      <c r="C39" s="286">
+      <c r="C39" s="283">
         <v>303.52929292929286</v>
       </c>
       <c r="E39" s="102"/>
       <c r="G39" s="130" t="s">
         <v>1505</v>
       </c>
-      <c r="H39" s="287">
+      <c r="H39" s="284">
         <v>12.975354536692826</v>
       </c>
     </row>
     <row r="40" spans="2:8" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="288" t="s">
+      <c r="B40" s="285" t="s">
         <v>1465</v>
       </c>
-      <c r="C40" s="286">
+      <c r="C40" s="283">
         <v>2877.0202020202019</v>
       </c>
       <c r="E40" s="102"/>
       <c r="G40" s="130" t="s">
         <v>1506</v>
       </c>
-      <c r="H40" s="287">
+      <c r="H40" s="284">
         <v>8.4595897012253882</v>
       </c>
     </row>
     <row r="41" spans="2:8" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="288" t="s">
+      <c r="B41" s="285" t="s">
         <v>1466</v>
       </c>
-      <c r="C41" s="286">
+      <c r="C41" s="283">
         <v>2046.4646464646462</v>
       </c>
       <c r="E41" s="102"/>
       <c r="G41" s="130" t="s">
         <v>1507</v>
       </c>
-      <c r="H41" s="287">
+      <c r="H41" s="284">
         <v>10.061957868649316</v>
       </c>
     </row>
     <row r="42" spans="2:8" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="288" t="s">
+      <c r="B42" s="285" t="s">
         <v>1467</v>
       </c>
-      <c r="C42" s="286">
+      <c r="C42" s="283">
         <v>1957.0202020202016</v>
       </c>
       <c r="E42" s="102"/>
       <c r="G42" s="130" t="s">
         <v>1508</v>
       </c>
-      <c r="H42" s="287">
+      <c r="H42" s="284">
         <v>11.518656202671069</v>
       </c>
     </row>
     <row r="43" spans="2:8" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="288" t="s">
+      <c r="B43" s="285" t="s">
         <v>1468</v>
       </c>
-      <c r="C43" s="284">
+      <c r="C43" s="281">
         <v>3317.6909090909085</v>
       </c>
       <c r="E43" s="102"/>
       <c r="G43" s="130" t="s">
         <v>1509</v>
       </c>
-      <c r="H43" s="287">
+      <c r="H43" s="284">
         <v>12.392675203084124</v>
       </c>
     </row>
     <row r="44" spans="2:8" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="288" t="s">
+      <c r="B44" s="285" t="s">
         <v>1469</v>
       </c>
       <c r="C44" s="188">
@@ -26588,12 +26669,12 @@
       <c r="G44" s="130" t="s">
         <v>1510</v>
       </c>
-      <c r="H44" s="287">
+      <c r="H44" s="284">
         <v>12.975354536692826</v>
       </c>
     </row>
     <row r="45" spans="2:8" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="288" t="s">
+      <c r="B45" s="285" t="s">
         <v>1470</v>
       </c>
       <c r="C45" s="188">
@@ -26603,12 +26684,12 @@
       <c r="G45" s="130" t="s">
         <v>1511</v>
       </c>
-      <c r="H45" s="287">
+      <c r="H45" s="284">
         <v>8.1682500344210371</v>
       </c>
     </row>
     <row r="46" spans="2:8" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="288" t="s">
+      <c r="B46" s="285" t="s">
         <v>1471</v>
       </c>
       <c r="C46" s="188">
@@ -26618,12 +26699,12 @@
       <c r="G46" s="130" t="s">
         <v>1512</v>
       </c>
-      <c r="H46" s="287">
+      <c r="H46" s="284">
         <v>8.4595897012253882</v>
       </c>
     </row>
     <row r="47" spans="2:8" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="288" t="s">
+      <c r="B47" s="285" t="s">
         <v>1472</v>
       </c>
       <c r="C47" s="188">
@@ -26633,12 +26714,12 @@
       <c r="G47" s="130" t="s">
         <v>1513</v>
       </c>
-      <c r="H47" s="287">
+      <c r="H47" s="284">
         <v>7.3087980173482023</v>
       </c>
     </row>
     <row r="48" spans="2:8" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="288" t="s">
+      <c r="B48" s="285" t="s">
         <v>1473</v>
       </c>
       <c r="C48" s="188">
@@ -26648,7 +26729,7 @@
       <c r="G48" s="130" t="s">
         <v>1514</v>
       </c>
-      <c r="H48" s="287">
+      <c r="H48" s="284">
         <v>9.4588847583643112</v>
       </c>
     </row>
@@ -26659,7 +26740,7 @@
       <c r="G49" s="130" t="s">
         <v>1515</v>
       </c>
-      <c r="H49" s="287">
+      <c r="H49" s="284">
         <v>13.558033870301527</v>
       </c>
     </row>
@@ -26670,7 +26751,7 @@
       <c r="G50" s="130" t="s">
         <v>1516</v>
       </c>
-      <c r="H50" s="287">
+      <c r="H50" s="284">
         <v>8.4595897012253882</v>
       </c>
     </row>
@@ -26681,7 +26762,7 @@
       <c r="G51" s="130" t="s">
         <v>1517</v>
       </c>
-      <c r="H51" s="287">
+      <c r="H51" s="284">
         <v>8.7509293680297393</v>
       </c>
     </row>
@@ -26692,7 +26773,7 @@
       <c r="G52" s="130" t="s">
         <v>1518</v>
       </c>
-      <c r="H52" s="287">
+      <c r="H52" s="284">
         <v>10.061957868649316</v>
       </c>
     </row>
@@ -26703,7 +26784,7 @@
       <c r="G53" s="130" t="s">
         <v>1519</v>
       </c>
-      <c r="H53" s="287">
+      <c r="H53" s="284">
         <v>9.7706182018449663</v>
       </c>
     </row>
@@ -26714,7 +26795,7 @@
       <c r="G54" s="130" t="s">
         <v>1520</v>
       </c>
-      <c r="H54" s="287">
+      <c r="H54" s="284">
         <v>8.8965992014319131</v>
       </c>
     </row>
@@ -26725,7 +26806,7 @@
       <c r="G55" s="130" t="s">
         <v>1521</v>
       </c>
-      <c r="H55" s="287">
+      <c r="H55" s="284">
         <v>9.1879388682362659</v>
       </c>
     </row>
@@ -26736,7 +26817,7 @@
       <c r="G56" s="130" t="s">
         <v>1522</v>
       </c>
-      <c r="H56" s="287">
+      <c r="H56" s="284">
         <v>43.566019551149651</v>
       </c>
     </row>
@@ -26760,7 +26841,7 @@
       <c r="G59" s="130" t="s">
         <v>1525</v>
       </c>
-      <c r="H59" s="281">
+      <c r="H59" s="278">
         <v>10.061957868649316</v>
       </c>
     </row>
@@ -26805,22 +26886,22 @@
       </c>
     </row>
     <row r="65" spans="2:8" ht="19" x14ac:dyDescent="0.25">
-      <c r="G65" s="328"/>
-      <c r="H65" s="329"/>
+      <c r="G65" s="325"/>
+      <c r="H65" s="326"/>
     </row>
     <row r="66" spans="2:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="B66" s="330" t="s">
+      <c r="B66" s="327" t="s">
         <v>1656</v>
       </c>
-      <c r="C66" s="335"/>
-      <c r="D66" s="335"/>
-      <c r="E66" s="336"/>
-      <c r="F66" s="336"/>
-      <c r="G66" s="336"/>
-      <c r="H66" s="336"/>
+      <c r="C66" s="332"/>
+      <c r="D66" s="332"/>
+      <c r="E66" s="333"/>
+      <c r="F66" s="333"/>
+      <c r="G66" s="333"/>
+      <c r="H66" s="333"/>
     </row>
     <row r="67" spans="2:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="B67" s="334"/>
+      <c r="B67" s="331"/>
       <c r="C67" s="130" t="s">
         <v>1652</v>
       </c>
@@ -26828,25 +26909,25 @@
       <c r="E67" s="121"/>
       <c r="F67" s="121"/>
       <c r="G67" s="121"/>
-      <c r="H67" s="333">
+      <c r="H67" s="330">
         <v>7.3385653311303862</v>
       </c>
     </row>
     <row r="68" spans="2:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="B68" s="334"/>
+      <c r="B68" s="331"/>
       <c r="C68" s="130" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="D68" s="121"/>
       <c r="E68" s="121"/>
       <c r="F68" s="121"/>
       <c r="G68" s="121"/>
-      <c r="H68" s="333">
+      <c r="H68" s="330">
         <v>9.8719537381247413</v>
       </c>
     </row>
     <row r="69" spans="2:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="B69" s="334"/>
+      <c r="B69" s="331"/>
       <c r="C69" s="130" t="s">
         <v>1653</v>
       </c>
@@ -26854,12 +26935,12 @@
       <c r="E69" s="121"/>
       <c r="F69" s="121"/>
       <c r="G69" s="121"/>
-      <c r="H69" s="333">
+      <c r="H69" s="330">
         <v>7.9719124328789741</v>
       </c>
     </row>
     <row r="70" spans="2:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="B70" s="334"/>
+      <c r="B70" s="331"/>
       <c r="C70" s="130" t="s">
         <v>1654</v>
       </c>
@@ -26867,31 +26948,31 @@
       <c r="E70" s="121"/>
       <c r="F70" s="121"/>
       <c r="G70" s="121"/>
-      <c r="H70" s="333">
+      <c r="H70" s="330">
         <v>9.8719537381247413</v>
       </c>
     </row>
     <row r="71" spans="2:8" ht="21" x14ac:dyDescent="0.25">
       <c r="C71" s="130" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="D71" s="121"/>
       <c r="E71" s="121"/>
       <c r="F71" s="121"/>
       <c r="G71" s="121"/>
-      <c r="H71" s="333">
+      <c r="H71" s="330">
         <v>5.4385240258846208</v>
       </c>
     </row>
     <row r="72" spans="2:8" ht="21" x14ac:dyDescent="0.25">
       <c r="C72" s="130" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="D72" s="121"/>
       <c r="E72" s="121"/>
       <c r="F72" s="121"/>
       <c r="G72" s="121"/>
-      <c r="H72" s="333">
+      <c r="H72" s="330">
         <v>8.6052595346275638</v>
       </c>
     </row>
@@ -26920,40 +27001,40 @@
   <sheetData>
     <row r="1" spans="2:8" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:8" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="350" t="s">
+      <c r="B2" s="349" t="s">
         <v>1657</v>
       </c>
-      <c r="C2" s="350"/>
-      <c r="D2" s="350"/>
-      <c r="E2" s="350"/>
-      <c r="F2" s="350"/>
-      <c r="G2" s="350"/>
-      <c r="H2" s="350"/>
+      <c r="C2" s="349"/>
+      <c r="D2" s="349"/>
+      <c r="E2" s="349"/>
+      <c r="F2" s="349"/>
+      <c r="G2" s="349"/>
+      <c r="H2" s="349"/>
     </row>
     <row r="3" spans="2:8" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="350"/>
-      <c r="C3" s="350"/>
-      <c r="D3" s="350"/>
-      <c r="E3" s="350"/>
-      <c r="F3" s="350"/>
-      <c r="G3" s="350"/>
-      <c r="H3" s="350"/>
+      <c r="B3" s="349"/>
+      <c r="C3" s="349"/>
+      <c r="D3" s="349"/>
+      <c r="E3" s="349"/>
+      <c r="F3" s="349"/>
+      <c r="G3" s="349"/>
+      <c r="H3" s="349"/>
     </row>
     <row r="4" spans="2:8" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="5" spans="2:8" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="2:8" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="354" t="s">
+      <c r="B6" s="353" t="s">
         <v>99</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>101</v>
       </c>
       <c r="E6" s="101"/>
-      <c r="G6" s="354" t="s">
+      <c r="G6" s="353" t="s">
         <v>99</v>
       </c>
       <c r="H6" s="8" t="s">
@@ -26961,12 +27042,12 @@
       </c>
     </row>
     <row r="7" spans="2:8" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="355"/>
+      <c r="B7" s="354"/>
       <c r="C7" s="16" t="s">
         <v>98</v>
       </c>
       <c r="E7" s="101"/>
-      <c r="G7" s="355"/>
+      <c r="G7" s="354"/>
       <c r="H7" s="16" t="s">
         <v>100</v>
       </c>
@@ -26975,14 +27056,14 @@
       <c r="B8" s="166" t="s">
         <v>842</v>
       </c>
-      <c r="C8" s="279">
+      <c r="C8" s="276">
         <v>3.5148282828282822</v>
       </c>
       <c r="E8" s="102"/>
       <c r="G8" s="165" t="s">
         <v>1272</v>
       </c>
-      <c r="H8" s="279">
+      <c r="H8" s="276">
         <v>7.2954242966634553</v>
       </c>
     </row>
@@ -26990,14 +27071,14 @@
       <c r="B9" s="130" t="s">
         <v>842</v>
       </c>
-      <c r="C9" s="279">
+      <c r="C9" s="276">
         <v>3.5148282828282822</v>
       </c>
       <c r="E9" s="102"/>
       <c r="G9" s="130" t="s">
         <v>1273</v>
       </c>
-      <c r="H9" s="279">
+      <c r="H9" s="276">
         <v>6.375804304924503</v>
       </c>
     </row>
@@ -27005,14 +27086,14 @@
       <c r="B10" s="130" t="s">
         <v>843</v>
       </c>
-      <c r="C10" s="279">
+      <c r="C10" s="276">
         <v>4.4160000000000004</v>
       </c>
       <c r="E10" s="102"/>
       <c r="G10" s="130" t="s">
         <v>1274</v>
       </c>
-      <c r="H10" s="279">
+      <c r="H10" s="276">
         <v>6.9939510762311263</v>
       </c>
     </row>
@@ -27020,14 +27101,14 @@
       <c r="B11" s="130" t="s">
         <v>1362</v>
       </c>
-      <c r="C11" s="279">
+      <c r="C11" s="276">
         <v>4.6577777777777776</v>
       </c>
       <c r="E11" s="102"/>
       <c r="G11" s="130" t="s">
         <v>1275</v>
       </c>
-      <c r="H11" s="279">
+      <c r="H11" s="276">
         <v>7.3283583459543813</v>
       </c>
     </row>
@@ -27035,14 +27116,14 @@
       <c r="B12" s="130" t="s">
         <v>1363</v>
       </c>
-      <c r="C12" s="279">
+      <c r="C12" s="276">
         <v>4.9435151515151521</v>
       </c>
       <c r="E12" s="102"/>
       <c r="G12" s="130" t="s">
         <v>1276</v>
       </c>
-      <c r="H12" s="279">
+      <c r="H12" s="276">
         <v>7.9287713984120449</v>
       </c>
     </row>
@@ -27050,14 +27131,14 @@
       <c r="B13" s="130" t="s">
         <v>1364</v>
       </c>
-      <c r="C13" s="279">
+      <c r="C13" s="276">
         <v>5.3171717171717168</v>
       </c>
       <c r="E13" s="102"/>
       <c r="G13" s="130" t="s">
         <v>1277</v>
       </c>
-      <c r="H13" s="279">
+      <c r="H13" s="276">
         <v>6.9939510762311263</v>
       </c>
     </row>
@@ -27065,14 +27146,14 @@
       <c r="B14" s="130" t="s">
         <v>844</v>
       </c>
-      <c r="C14" s="279">
+      <c r="C14" s="276">
         <v>5.4490505050505051</v>
       </c>
       <c r="E14" s="102"/>
       <c r="G14" s="130" t="s">
         <v>1278</v>
       </c>
-      <c r="H14" s="279">
+      <c r="H14" s="276">
         <v>8.1821102391114788</v>
       </c>
     </row>
@@ -27080,14 +27161,14 @@
       <c r="B15" s="130" t="s">
         <v>845</v>
       </c>
-      <c r="C15" s="279">
+      <c r="C15" s="276">
         <v>5.888646464646464</v>
       </c>
       <c r="E15" s="102"/>
       <c r="G15" s="130" t="s">
         <v>1279</v>
       </c>
-      <c r="H15" s="279">
+      <c r="H15" s="276">
         <v>8.6887879205103484</v>
       </c>
     </row>
@@ -28067,15 +28148,15 @@
     </row>
     <row r="98" spans="2:8" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="99" spans="2:8" ht="26" x14ac:dyDescent="0.3">
-      <c r="B99" s="337" t="s">
-        <v>1692</v>
-      </c>
-      <c r="C99" s="338"/>
-      <c r="D99" s="339"/>
-      <c r="E99" s="339"/>
-      <c r="F99" s="339"/>
-      <c r="G99" s="339"/>
-      <c r="H99" s="340"/>
+      <c r="B99" s="334" t="s">
+        <v>1691</v>
+      </c>
+      <c r="C99" s="335"/>
+      <c r="D99" s="336"/>
+      <c r="E99" s="336"/>
+      <c r="F99" s="336"/>
+      <c r="G99" s="336"/>
+      <c r="H99" s="337"/>
     </row>
     <row r="100" spans="2:8" ht="21" x14ac:dyDescent="0.25">
       <c r="B100" s="130"/>
@@ -28106,7 +28187,7 @@
     <row r="102" spans="2:8" ht="21" x14ac:dyDescent="0.25">
       <c r="B102" s="130"/>
       <c r="C102" s="130" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="D102" s="121"/>
       <c r="E102" s="121"/>
@@ -28117,22 +28198,22 @@
       </c>
     </row>
     <row r="103" spans="2:8" ht="29" x14ac:dyDescent="0.35">
-      <c r="B103" s="327"/>
+      <c r="B103" s="324"/>
       <c r="C103" s="130" t="s">
         <v>1654</v>
       </c>
       <c r="D103" s="121"/>
-      <c r="E103" s="327"/>
-      <c r="F103" s="327"/>
-      <c r="G103" s="327"/>
-      <c r="H103" s="341">
+      <c r="E103" s="324"/>
+      <c r="F103" s="324"/>
+      <c r="G103" s="324"/>
+      <c r="H103" s="338">
         <v>10.02</v>
       </c>
     </row>
     <row r="104" spans="2:8" ht="21" x14ac:dyDescent="0.25">
       <c r="B104" s="130"/>
       <c r="C104" s="130" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="D104" s="121"/>
       <c r="E104" s="121"/>
@@ -28177,30 +28258,30 @@
   <sheetData>
     <row r="2" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B3" s="350" t="s">
+      <c r="B3" s="349" t="s">
         <v>1659</v>
       </c>
-      <c r="C3" s="350"/>
-      <c r="D3" s="350"/>
-      <c r="E3" s="350"/>
-      <c r="F3" s="350"/>
-      <c r="G3" s="350"/>
-      <c r="H3" s="350"/>
-      <c r="I3" s="350"/>
-      <c r="J3" s="350"/>
-      <c r="K3" s="350"/>
+      <c r="C3" s="349"/>
+      <c r="D3" s="349"/>
+      <c r="E3" s="349"/>
+      <c r="F3" s="349"/>
+      <c r="G3" s="349"/>
+      <c r="H3" s="349"/>
+      <c r="I3" s="349"/>
+      <c r="J3" s="349"/>
+      <c r="K3" s="349"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B4" s="350"/>
-      <c r="C4" s="350"/>
-      <c r="D4" s="350"/>
-      <c r="E4" s="350"/>
-      <c r="F4" s="350"/>
-      <c r="G4" s="350"/>
-      <c r="H4" s="350"/>
-      <c r="I4" s="350"/>
-      <c r="J4" s="350"/>
-      <c r="K4" s="350"/>
+      <c r="B4" s="349"/>
+      <c r="C4" s="349"/>
+      <c r="D4" s="349"/>
+      <c r="E4" s="349"/>
+      <c r="F4" s="349"/>
+      <c r="G4" s="349"/>
+      <c r="H4" s="349"/>
+      <c r="I4" s="349"/>
+      <c r="J4" s="349"/>
+      <c r="K4" s="349"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
@@ -28211,10 +28292,10 @@
     <row r="7" spans="1:11" ht="20" x14ac:dyDescent="0.2">
       <c r="A7" s="9"/>
       <c r="B7" s="13"/>
-      <c r="C7" s="354" t="s">
+      <c r="C7" s="353" t="s">
         <v>102</v>
       </c>
-      <c r="D7" s="354" t="s">
+      <c r="D7" s="353" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="8" t="s">
@@ -28230,8 +28311,8 @@
     <row r="8" spans="1:11" ht="21" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9"/>
       <c r="B8" s="13"/>
-      <c r="C8" s="356"/>
-      <c r="D8" s="355"/>
+      <c r="C8" s="355"/>
+      <c r="D8" s="354"/>
       <c r="E8" s="16" t="s">
         <v>100</v>
       </c>
@@ -28315,34 +28396,34 @@
   <sheetData>
     <row r="1" spans="2:13" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:13" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="350" t="s">
+      <c r="B2" s="349" t="s">
         <v>1660</v>
       </c>
-      <c r="C2" s="350"/>
-      <c r="D2" s="350"/>
-      <c r="E2" s="350"/>
-      <c r="F2" s="350"/>
-      <c r="G2" s="350"/>
-      <c r="H2" s="350"/>
-      <c r="I2" s="350"/>
-      <c r="J2" s="350"/>
-      <c r="K2" s="350"/>
-      <c r="L2" s="350"/>
-      <c r="M2" s="350"/>
+      <c r="C2" s="349"/>
+      <c r="D2" s="349"/>
+      <c r="E2" s="349"/>
+      <c r="F2" s="349"/>
+      <c r="G2" s="349"/>
+      <c r="H2" s="349"/>
+      <c r="I2" s="349"/>
+      <c r="J2" s="349"/>
+      <c r="K2" s="349"/>
+      <c r="L2" s="349"/>
+      <c r="M2" s="349"/>
     </row>
     <row r="3" spans="2:13" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="350"/>
-      <c r="C3" s="350"/>
-      <c r="D3" s="350"/>
-      <c r="E3" s="350"/>
-      <c r="F3" s="350"/>
-      <c r="G3" s="350"/>
-      <c r="H3" s="350"/>
-      <c r="I3" s="350"/>
-      <c r="J3" s="350"/>
-      <c r="K3" s="350"/>
-      <c r="L3" s="350"/>
-      <c r="M3" s="350"/>
+      <c r="B3" s="349"/>
+      <c r="C3" s="349"/>
+      <c r="D3" s="349"/>
+      <c r="E3" s="349"/>
+      <c r="F3" s="349"/>
+      <c r="G3" s="349"/>
+      <c r="H3" s="349"/>
+      <c r="I3" s="349"/>
+      <c r="J3" s="349"/>
+      <c r="K3" s="349"/>
+      <c r="L3" s="349"/>
+      <c r="M3" s="349"/>
     </row>
     <row r="4" spans="2:13" ht="19" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
@@ -28365,7 +28446,7 @@
       <c r="H5" s="4"/>
     </row>
     <row r="6" spans="2:13" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="352" t="s">
+      <c r="B6" s="351" t="s">
         <v>99</v>
       </c>
       <c r="C6" s="8" t="s">
@@ -28373,7 +28454,7 @@
       </c>
       <c r="D6" s="18"/>
       <c r="E6" s="18"/>
-      <c r="F6" s="352" t="s">
+      <c r="F6" s="351" t="s">
         <v>99</v>
       </c>
       <c r="G6" s="8" t="s">
@@ -28382,13 +28463,13 @@
       <c r="H6" s="19"/>
     </row>
     <row r="7" spans="2:13" s="7" customFormat="1" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="358"/>
+      <c r="B7" s="357"/>
       <c r="C7" s="10" t="s">
         <v>100</v>
       </c>
       <c r="D7" s="18"/>
       <c r="E7" s="18"/>
-      <c r="F7" s="358"/>
+      <c r="F7" s="357"/>
       <c r="G7" s="10" t="s">
         <v>100</v>
       </c>
@@ -29392,34 +29473,34 @@
   <sheetData>
     <row r="1" spans="2:13" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:13" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="350" t="s">
+      <c r="B2" s="349" t="s">
         <v>1661</v>
       </c>
-      <c r="C2" s="350"/>
-      <c r="D2" s="350"/>
-      <c r="E2" s="350"/>
-      <c r="F2" s="350"/>
-      <c r="G2" s="350"/>
-      <c r="H2" s="350"/>
-      <c r="I2" s="350"/>
-      <c r="J2" s="350"/>
-      <c r="K2" s="350"/>
-      <c r="L2" s="350"/>
-      <c r="M2" s="350"/>
+      <c r="C2" s="349"/>
+      <c r="D2" s="349"/>
+      <c r="E2" s="349"/>
+      <c r="F2" s="349"/>
+      <c r="G2" s="349"/>
+      <c r="H2" s="349"/>
+      <c r="I2" s="349"/>
+      <c r="J2" s="349"/>
+      <c r="K2" s="349"/>
+      <c r="L2" s="349"/>
+      <c r="M2" s="349"/>
     </row>
     <row r="3" spans="2:13" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="350"/>
-      <c r="C3" s="350"/>
-      <c r="D3" s="350"/>
-      <c r="E3" s="350"/>
-      <c r="F3" s="350"/>
-      <c r="G3" s="350"/>
-      <c r="H3" s="350"/>
-      <c r="I3" s="350"/>
-      <c r="J3" s="350"/>
-      <c r="K3" s="350"/>
-      <c r="L3" s="350"/>
-      <c r="M3" s="350"/>
+      <c r="B3" s="349"/>
+      <c r="C3" s="349"/>
+      <c r="D3" s="349"/>
+      <c r="E3" s="349"/>
+      <c r="F3" s="349"/>
+      <c r="G3" s="349"/>
+      <c r="H3" s="349"/>
+      <c r="I3" s="349"/>
+      <c r="J3" s="349"/>
+      <c r="K3" s="349"/>
+      <c r="L3" s="349"/>
+      <c r="M3" s="349"/>
     </row>
     <row r="4" spans="2:13" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
@@ -29429,10 +29510,10 @@
     <row r="5" spans="2:13" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="2:13" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="13"/>
-      <c r="C6" s="354" t="s">
+      <c r="C6" s="353" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="354" t="s">
+      <c r="D6" s="353" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="8" t="s">
@@ -29442,15 +29523,15 @@
       <c r="G6" s="13"/>
     </row>
     <row r="7" spans="2:13" s="9" customFormat="1" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C7" s="355"/>
-      <c r="D7" s="355"/>
+      <c r="C7" s="354"/>
+      <c r="D7" s="354"/>
       <c r="E7" s="16" t="s">
         <v>100</v>
       </c>
       <c r="G7" s="20"/>
     </row>
     <row r="8" spans="2:13" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C8" s="273" t="s">
+      <c r="C8" s="270" t="s">
         <v>420</v>
       </c>
       <c r="D8" s="175" t="s">
@@ -29462,10 +29543,10 @@
       <c r="G8" s="12"/>
     </row>
     <row r="9" spans="2:13" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C9" s="274" t="s">
+      <c r="C9" s="271" t="s">
         <v>421</v>
       </c>
-      <c r="D9" s="275" t="s">
+      <c r="D9" s="272" t="s">
         <v>424</v>
       </c>
       <c r="E9" s="207">
@@ -29474,7 +29555,7 @@
       <c r="G9" s="12"/>
     </row>
     <row r="10" spans="2:13" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C10" s="273" t="s">
+      <c r="C10" s="270" t="s">
         <v>419</v>
       </c>
       <c r="D10" s="175" t="s">
@@ -29486,7 +29567,7 @@
       <c r="G10" s="12"/>
     </row>
     <row r="11" spans="2:13" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C11" s="273" t="s">
+      <c r="C11" s="270" t="s">
         <v>1180</v>
       </c>
       <c r="D11" s="175" t="s">
@@ -29498,10 +29579,10 @@
       <c r="G11" s="12"/>
     </row>
     <row r="12" spans="2:13" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C12" s="274" t="s">
+      <c r="C12" s="271" t="s">
         <v>422</v>
       </c>
-      <c r="D12" s="275" t="s">
+      <c r="D12" s="272" t="s">
         <v>425</v>
       </c>
       <c r="E12" s="207">
@@ -29510,10 +29591,10 @@
       <c r="G12" s="12"/>
     </row>
     <row r="13" spans="2:13" s="7" customFormat="1" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C13" s="274" t="s">
+      <c r="C13" s="271" t="s">
         <v>423</v>
       </c>
-      <c r="D13" s="275" t="s">
+      <c r="D13" s="272" t="s">
         <v>83</v>
       </c>
       <c r="E13" s="208">
@@ -29870,34 +29951,34 @@
   <sheetData>
     <row r="1" spans="2:13" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:13" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="350" t="s">
+      <c r="B2" s="349" t="s">
         <v>1662</v>
       </c>
-      <c r="C2" s="350"/>
-      <c r="D2" s="350"/>
-      <c r="E2" s="350"/>
-      <c r="F2" s="350"/>
-      <c r="G2" s="350"/>
-      <c r="H2" s="350"/>
-      <c r="I2" s="350"/>
-      <c r="J2" s="350"/>
-      <c r="K2" s="350"/>
-      <c r="L2" s="350"/>
-      <c r="M2" s="350"/>
+      <c r="C2" s="349"/>
+      <c r="D2" s="349"/>
+      <c r="E2" s="349"/>
+      <c r="F2" s="349"/>
+      <c r="G2" s="349"/>
+      <c r="H2" s="349"/>
+      <c r="I2" s="349"/>
+      <c r="J2" s="349"/>
+      <c r="K2" s="349"/>
+      <c r="L2" s="349"/>
+      <c r="M2" s="349"/>
     </row>
     <row r="3" spans="2:13" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="350"/>
-      <c r="C3" s="350"/>
-      <c r="D3" s="350"/>
-      <c r="E3" s="350"/>
-      <c r="F3" s="350"/>
-      <c r="G3" s="350"/>
-      <c r="H3" s="350"/>
-      <c r="I3" s="350"/>
-      <c r="J3" s="350"/>
-      <c r="K3" s="350"/>
-      <c r="L3" s="350"/>
-      <c r="M3" s="350"/>
+      <c r="B3" s="349"/>
+      <c r="C3" s="349"/>
+      <c r="D3" s="349"/>
+      <c r="E3" s="349"/>
+      <c r="F3" s="349"/>
+      <c r="G3" s="349"/>
+      <c r="H3" s="349"/>
+      <c r="I3" s="349"/>
+      <c r="J3" s="349"/>
+      <c r="K3" s="349"/>
+      <c r="L3" s="349"/>
+      <c r="M3" s="349"/>
     </row>
     <row r="4" spans="2:13" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="2:13" ht="19" customHeight="1" x14ac:dyDescent="0.2">
@@ -29907,10 +29988,10 @@
     </row>
     <row r="6" spans="2:13" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="13"/>
-      <c r="C6" s="351" t="s">
+      <c r="C6" s="350" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="351" t="s">
+      <c r="D6" s="350" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="120" t="s">
@@ -29920,8 +30001,8 @@
       <c r="G6" s="13"/>
     </row>
     <row r="7" spans="2:13" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C7" s="351"/>
-      <c r="D7" s="351"/>
+      <c r="C7" s="350"/>
+      <c r="D7" s="350"/>
       <c r="E7" s="120" t="s">
         <v>100</v>
       </c>
@@ -30489,41 +30570,41 @@
       </c>
     </row>
     <row r="2" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="350" t="s">
+      <c r="B2" s="349" t="s">
         <v>1665</v>
       </c>
-      <c r="C2" s="350"/>
-      <c r="D2" s="350"/>
-      <c r="E2" s="350"/>
-      <c r="F2" s="350"/>
-      <c r="G2" s="350"/>
-      <c r="H2" s="350"/>
-      <c r="I2" s="350"/>
-      <c r="J2" s="350"/>
-      <c r="K2" s="350"/>
-      <c r="L2" s="350"/>
+      <c r="C2" s="349"/>
+      <c r="D2" s="349"/>
+      <c r="E2" s="349"/>
+      <c r="F2" s="349"/>
+      <c r="G2" s="349"/>
+      <c r="H2" s="349"/>
+      <c r="I2" s="349"/>
+      <c r="J2" s="349"/>
+      <c r="K2" s="349"/>
+      <c r="L2" s="349"/>
     </row>
     <row r="3" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="350"/>
-      <c r="C3" s="350"/>
-      <c r="D3" s="350"/>
-      <c r="E3" s="350"/>
-      <c r="F3" s="350"/>
-      <c r="G3" s="350"/>
-      <c r="H3" s="350"/>
-      <c r="I3" s="350"/>
-      <c r="J3" s="350"/>
-      <c r="K3" s="350"/>
-      <c r="L3" s="350"/>
+      <c r="B3" s="349"/>
+      <c r="C3" s="349"/>
+      <c r="D3" s="349"/>
+      <c r="E3" s="349"/>
+      <c r="F3" s="349"/>
+      <c r="G3" s="349"/>
+      <c r="H3" s="349"/>
+      <c r="I3" s="349"/>
+      <c r="J3" s="349"/>
+      <c r="K3" s="349"/>
+      <c r="L3" s="349"/>
     </row>
     <row r="4" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="6" spans="2:12" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="13"/>
-      <c r="C6" s="351" t="s">
+      <c r="C6" s="350" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="351" t="s">
+      <c r="D6" s="350" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="120" t="s">
@@ -30534,8 +30615,8 @@
     </row>
     <row r="7" spans="2:12" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="13"/>
-      <c r="C7" s="351"/>
-      <c r="D7" s="351"/>
+      <c r="C7" s="350"/>
+      <c r="D7" s="350"/>
       <c r="E7" s="120" t="s">
         <v>100</v>
       </c>
@@ -30916,32 +30997,32 @@
   <sheetData>
     <row r="1" spans="2:12" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="350" t="s">
+      <c r="B2" s="349" t="s">
         <v>1663</v>
       </c>
-      <c r="C2" s="350"/>
-      <c r="D2" s="350"/>
-      <c r="E2" s="350"/>
-      <c r="F2" s="350"/>
-      <c r="G2" s="350"/>
-      <c r="H2" s="350"/>
-      <c r="I2" s="350"/>
-      <c r="J2" s="350"/>
-      <c r="K2" s="350"/>
-      <c r="L2" s="350"/>
+      <c r="C2" s="349"/>
+      <c r="D2" s="349"/>
+      <c r="E2" s="349"/>
+      <c r="F2" s="349"/>
+      <c r="G2" s="349"/>
+      <c r="H2" s="349"/>
+      <c r="I2" s="349"/>
+      <c r="J2" s="349"/>
+      <c r="K2" s="349"/>
+      <c r="L2" s="349"/>
     </row>
     <row r="3" spans="2:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="350"/>
-      <c r="C3" s="350"/>
-      <c r="D3" s="350"/>
-      <c r="E3" s="350"/>
-      <c r="F3" s="350"/>
-      <c r="G3" s="350"/>
-      <c r="H3" s="350"/>
-      <c r="I3" s="350"/>
-      <c r="J3" s="350"/>
-      <c r="K3" s="350"/>
-      <c r="L3" s="350"/>
+      <c r="B3" s="349"/>
+      <c r="C3" s="349"/>
+      <c r="D3" s="349"/>
+      <c r="E3" s="349"/>
+      <c r="F3" s="349"/>
+      <c r="G3" s="349"/>
+      <c r="H3" s="349"/>
+      <c r="I3" s="349"/>
+      <c r="J3" s="349"/>
+      <c r="K3" s="349"/>
+      <c r="L3" s="349"/>
     </row>
     <row r="4" spans="2:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
@@ -30951,10 +31032,10 @@
     <row r="5" spans="2:12" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="2:12" s="9" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="13"/>
-      <c r="C6" s="354" t="s">
+      <c r="C6" s="353" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="354" t="s">
+      <c r="D6" s="353" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="14" t="s">
@@ -30962,10 +31043,10 @@
       </c>
       <c r="F6" s="13"/>
       <c r="G6" s="13"/>
-      <c r="H6" s="354" t="s">
+      <c r="H6" s="353" t="s">
         <v>102</v>
       </c>
-      <c r="I6" s="354" t="s">
+      <c r="I6" s="353" t="s">
         <v>0</v>
       </c>
       <c r="J6" s="8" t="s">
@@ -30973,14 +31054,14 @@
       </c>
     </row>
     <row r="7" spans="2:12" s="9" customFormat="1" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C7" s="356"/>
-      <c r="D7" s="356"/>
+      <c r="C7" s="355"/>
+      <c r="D7" s="355"/>
       <c r="E7" s="15" t="s">
         <v>98</v>
       </c>
       <c r="G7" s="20"/>
-      <c r="H7" s="355"/>
-      <c r="I7" s="355"/>
+      <c r="H7" s="354"/>
+      <c r="I7" s="354"/>
       <c r="J7" s="16" t="s">
         <v>100</v>
       </c>
@@ -31415,38 +31496,38 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A2" s="350" t="s">
+      <c r="A2" s="349" t="s">
         <v>1593</v>
       </c>
-      <c r="B2" s="350"/>
-      <c r="C2" s="350"/>
-      <c r="D2" s="350"/>
-      <c r="E2" s="350"/>
-      <c r="F2" s="350"/>
-      <c r="G2" s="350"/>
-      <c r="H2" s="350"/>
-      <c r="I2" s="350"/>
-      <c r="J2" s="350"/>
-      <c r="K2" s="350"/>
-      <c r="L2" s="350"/>
-      <c r="M2" s="350"/>
-      <c r="N2" s="350"/>
+      <c r="B2" s="349"/>
+      <c r="C2" s="349"/>
+      <c r="D2" s="349"/>
+      <c r="E2" s="349"/>
+      <c r="F2" s="349"/>
+      <c r="G2" s="349"/>
+      <c r="H2" s="349"/>
+      <c r="I2" s="349"/>
+      <c r="J2" s="349"/>
+      <c r="K2" s="349"/>
+      <c r="L2" s="349"/>
+      <c r="M2" s="349"/>
+      <c r="N2" s="349"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A3" s="350"/>
-      <c r="B3" s="350"/>
-      <c r="C3" s="350"/>
-      <c r="D3" s="350"/>
-      <c r="E3" s="350"/>
-      <c r="F3" s="350"/>
-      <c r="G3" s="350"/>
-      <c r="H3" s="350"/>
-      <c r="I3" s="350"/>
-      <c r="J3" s="350"/>
-      <c r="K3" s="350"/>
-      <c r="L3" s="350"/>
-      <c r="M3" s="350"/>
-      <c r="N3" s="350"/>
+      <c r="A3" s="349"/>
+      <c r="B3" s="349"/>
+      <c r="C3" s="349"/>
+      <c r="D3" s="349"/>
+      <c r="E3" s="349"/>
+      <c r="F3" s="349"/>
+      <c r="G3" s="349"/>
+      <c r="H3" s="349"/>
+      <c r="I3" s="349"/>
+      <c r="J3" s="349"/>
+      <c r="K3" s="349"/>
+      <c r="L3" s="349"/>
+      <c r="M3" s="349"/>
+      <c r="N3" s="349"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
@@ -31455,35 +31536,35 @@
     </row>
     <row r="5" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="1:14" ht="20" x14ac:dyDescent="0.2">
-      <c r="A6" s="354" t="s">
+      <c r="A6" s="353" t="s">
         <v>99</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>101</v>
       </c>
       <c r="C6" s="9"/>
-      <c r="D6" s="354" t="s">
+      <c r="D6" s="353" t="s">
         <v>99</v>
       </c>
       <c r="E6" s="8" t="s">
         <v>101</v>
       </c>
       <c r="F6" s="101"/>
-      <c r="G6" s="354" t="s">
+      <c r="G6" s="353" t="s">
         <v>99</v>
       </c>
       <c r="H6" s="8" t="s">
         <v>101</v>
       </c>
       <c r="I6" s="9"/>
-      <c r="J6" s="354" t="s">
+      <c r="J6" s="353" t="s">
         <v>99</v>
       </c>
       <c r="K6" s="8" t="s">
         <v>101</v>
       </c>
       <c r="L6" s="9"/>
-      <c r="M6" s="354" t="s">
+      <c r="M6" s="353" t="s">
         <v>99</v>
       </c>
       <c r="N6" s="44" t="s">
@@ -31491,27 +31572,27 @@
       </c>
     </row>
     <row r="7" spans="1:14" ht="21" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="356"/>
+      <c r="A7" s="355"/>
       <c r="B7" s="10" t="s">
         <v>98</v>
       </c>
       <c r="C7" s="9"/>
-      <c r="D7" s="356"/>
+      <c r="D7" s="355"/>
       <c r="E7" s="10" t="s">
         <v>98</v>
       </c>
       <c r="F7" s="101"/>
-      <c r="G7" s="356"/>
+      <c r="G7" s="355"/>
       <c r="H7" s="10" t="s">
         <v>98</v>
       </c>
       <c r="I7" s="9"/>
-      <c r="J7" s="356"/>
+      <c r="J7" s="355"/>
       <c r="K7" s="10" t="s">
         <v>100</v>
       </c>
       <c r="L7" s="9"/>
-      <c r="M7" s="356"/>
+      <c r="M7" s="355"/>
       <c r="N7" s="45" t="s">
         <v>100</v>
       </c>
@@ -33779,13 +33860,13 @@
     <row r="78" spans="1:14" ht="21" x14ac:dyDescent="0.25">
       <c r="D78" s="144"/>
       <c r="E78" s="222"/>
-      <c r="J78" s="357" t="s">
+      <c r="J78" s="356" t="s">
         <v>771</v>
       </c>
-      <c r="K78" s="357"/>
-      <c r="L78" s="357"/>
-      <c r="M78" s="357"/>
-      <c r="N78" s="357"/>
+      <c r="K78" s="356"/>
+      <c r="L78" s="356"/>
+      <c r="M78" s="356"/>
+      <c r="N78" s="356"/>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D79" s="144"/>
@@ -33895,55 +33976,55 @@
   <sheetData>
     <row r="1" spans="2:25" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:25" ht="19" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="413" t="s">
+      <c r="B2" s="412" t="s">
         <v>1664</v>
       </c>
-      <c r="C2" s="413"/>
-      <c r="D2" s="413"/>
-      <c r="E2" s="413"/>
-      <c r="F2" s="413"/>
-      <c r="G2" s="413"/>
-      <c r="H2" s="413"/>
-      <c r="I2" s="413"/>
-      <c r="J2" s="413"/>
-      <c r="K2" s="413"/>
-      <c r="L2" s="413"/>
-      <c r="M2" s="413"/>
-      <c r="P2" s="417" t="s">
+      <c r="C2" s="412"/>
+      <c r="D2" s="412"/>
+      <c r="E2" s="412"/>
+      <c r="F2" s="412"/>
+      <c r="G2" s="412"/>
+      <c r="H2" s="412"/>
+      <c r="I2" s="412"/>
+      <c r="J2" s="412"/>
+      <c r="K2" s="412"/>
+      <c r="L2" s="412"/>
+      <c r="M2" s="412"/>
+      <c r="P2" s="416" t="s">
         <v>1664</v>
       </c>
-      <c r="Q2" s="417"/>
-      <c r="R2" s="417"/>
-      <c r="S2" s="417"/>
-      <c r="T2" s="417"/>
-      <c r="U2" s="417"/>
-      <c r="V2" s="417"/>
-      <c r="W2" s="417"/>
-      <c r="X2" s="417"/>
+      <c r="Q2" s="416"/>
+      <c r="R2" s="416"/>
+      <c r="S2" s="416"/>
+      <c r="T2" s="416"/>
+      <c r="U2" s="416"/>
+      <c r="V2" s="416"/>
+      <c r="W2" s="416"/>
+      <c r="X2" s="416"/>
       <c r="Y2" s="48"/>
     </row>
     <row r="3" spans="2:25" ht="19" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="413"/>
-      <c r="C3" s="413"/>
-      <c r="D3" s="413"/>
-      <c r="E3" s="413"/>
-      <c r="F3" s="413"/>
-      <c r="G3" s="413"/>
-      <c r="H3" s="413"/>
-      <c r="I3" s="413"/>
-      <c r="J3" s="413"/>
-      <c r="K3" s="413"/>
-      <c r="L3" s="413"/>
-      <c r="M3" s="413"/>
-      <c r="P3" s="417"/>
-      <c r="Q3" s="417"/>
-      <c r="R3" s="417"/>
-      <c r="S3" s="417"/>
-      <c r="T3" s="417"/>
-      <c r="U3" s="417"/>
-      <c r="V3" s="417"/>
-      <c r="W3" s="417"/>
-      <c r="X3" s="417"/>
+      <c r="B3" s="412"/>
+      <c r="C3" s="412"/>
+      <c r="D3" s="412"/>
+      <c r="E3" s="412"/>
+      <c r="F3" s="412"/>
+      <c r="G3" s="412"/>
+      <c r="H3" s="412"/>
+      <c r="I3" s="412"/>
+      <c r="J3" s="412"/>
+      <c r="K3" s="412"/>
+      <c r="L3" s="412"/>
+      <c r="M3" s="412"/>
+      <c r="P3" s="416"/>
+      <c r="Q3" s="416"/>
+      <c r="R3" s="416"/>
+      <c r="S3" s="416"/>
+      <c r="T3" s="416"/>
+      <c r="U3" s="416"/>
+      <c r="V3" s="416"/>
+      <c r="W3" s="416"/>
+      <c r="X3" s="416"/>
       <c r="Y3" s="48"/>
     </row>
     <row r="4" spans="2:25" ht="19" customHeight="1" x14ac:dyDescent="0.2">
@@ -33953,20 +34034,20 @@
     </row>
     <row r="5" spans="2:25" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="2:25" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="354" t="s">
+      <c r="B6" s="353" t="s">
         <v>99</v>
       </c>
       <c r="C6" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="E6" s="354" t="s">
+      <c r="E6" s="353" t="s">
         <v>99</v>
       </c>
       <c r="F6" s="14" t="s">
         <v>101</v>
       </c>
       <c r="G6" s="13"/>
-      <c r="H6" s="354" t="s">
+      <c r="H6" s="353" t="s">
         <v>99</v>
       </c>
       <c r="I6" s="44" t="s">
@@ -33974,16 +34055,16 @@
       </c>
     </row>
     <row r="7" spans="2:25" s="9" customFormat="1" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="356"/>
+      <c r="B7" s="355"/>
       <c r="C7" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E7" s="356"/>
+      <c r="E7" s="355"/>
       <c r="F7" s="15" t="s">
         <v>98</v>
       </c>
       <c r="G7" s="20"/>
-      <c r="H7" s="356"/>
+      <c r="H7" s="355"/>
       <c r="I7" s="45" t="s">
         <v>100</v>
       </c>
@@ -34008,11 +34089,11 @@
       <c r="I8" s="92">
         <v>4.8767983845059435</v>
       </c>
-      <c r="P8" s="403" t="s">
+      <c r="P8" s="402" t="s">
         <v>82</v>
       </c>
-      <c r="Q8" s="404"/>
-      <c r="R8" s="405"/>
+      <c r="Q8" s="403"/>
+      <c r="R8" s="404"/>
     </row>
     <row r="9" spans="2:25" s="7" customFormat="1" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="159">
@@ -34034,9 +34115,9 @@
       <c r="I9" s="92">
         <v>5.3561154711092742</v>
       </c>
-      <c r="P9" s="414"/>
-      <c r="Q9" s="415"/>
-      <c r="R9" s="416"/>
+      <c r="P9" s="413"/>
+      <c r="Q9" s="414"/>
+      <c r="R9" s="415"/>
     </row>
     <row r="10" spans="2:25" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="159">
@@ -34088,10 +34169,10 @@
       <c r="I11" s="92">
         <v>7.3820661801826617</v>
       </c>
-      <c r="P11" s="418" t="s">
+      <c r="P11" s="417" t="s">
         <v>480</v>
       </c>
-      <c r="Q11" s="418"/>
+      <c r="Q11" s="417"/>
       <c r="R11" s="202">
         <v>10.080053500127852</v>
       </c>
@@ -34116,10 +34197,10 @@
       <c r="I12" s="92">
         <v>5.4229969250539263</v>
       </c>
-      <c r="P12" s="418" t="s">
+      <c r="P12" s="417" t="s">
         <v>481</v>
       </c>
-      <c r="Q12" s="418"/>
+      <c r="Q12" s="417"/>
       <c r="R12" s="202">
         <v>8.0737987057689669</v>
       </c>
@@ -34144,10 +34225,10 @@
       <c r="I13" s="92">
         <v>5.6849492863371438</v>
       </c>
-      <c r="P13" s="418" t="s">
+      <c r="P13" s="417" t="s">
         <v>482</v>
       </c>
-      <c r="Q13" s="418"/>
+      <c r="Q13" s="417"/>
       <c r="R13" s="202">
         <v>7.9935485139946119</v>
       </c>
@@ -34172,10 +34253,10 @@
       <c r="I14" s="92">
         <v>5.7936316489972013</v>
       </c>
-      <c r="P14" s="418" t="s">
+      <c r="P14" s="417" t="s">
         <v>483</v>
       </c>
-      <c r="Q14" s="418"/>
+      <c r="Q14" s="417"/>
       <c r="R14" s="202">
         <v>7.3515469797997683</v>
       </c>
@@ -34970,45 +35051,45 @@
     </row>
     <row r="72" spans="2:13" s="7" customFormat="1" ht="20" x14ac:dyDescent="0.2"/>
     <row r="73" spans="2:13" s="7" customFormat="1" ht="20" x14ac:dyDescent="0.2">
-      <c r="B73" s="413" t="s">
+      <c r="B73" s="412" t="s">
         <v>785</v>
       </c>
-      <c r="C73" s="413"/>
-      <c r="D73" s="413"/>
-      <c r="E73" s="413"/>
-      <c r="F73" s="413"/>
-      <c r="G73" s="413"/>
-      <c r="H73" s="413"/>
-      <c r="I73" s="413"/>
-      <c r="J73" s="413"/>
-      <c r="K73" s="413"/>
-      <c r="L73" s="413"/>
-      <c r="M73" s="413"/>
+      <c r="C73" s="412"/>
+      <c r="D73" s="412"/>
+      <c r="E73" s="412"/>
+      <c r="F73" s="412"/>
+      <c r="G73" s="412"/>
+      <c r="H73" s="412"/>
+      <c r="I73" s="412"/>
+      <c r="J73" s="412"/>
+      <c r="K73" s="412"/>
+      <c r="L73" s="412"/>
+      <c r="M73" s="412"/>
     </row>
     <row r="74" spans="2:13" s="7" customFormat="1" ht="20" x14ac:dyDescent="0.2">
-      <c r="B74" s="413"/>
-      <c r="C74" s="413"/>
-      <c r="D74" s="413"/>
-      <c r="E74" s="413"/>
-      <c r="F74" s="413"/>
-      <c r="G74" s="413"/>
-      <c r="H74" s="413"/>
-      <c r="I74" s="413"/>
-      <c r="J74" s="413"/>
-      <c r="K74" s="413"/>
-      <c r="L74" s="413"/>
-      <c r="M74" s="413"/>
+      <c r="B74" s="412"/>
+      <c r="C74" s="412"/>
+      <c r="D74" s="412"/>
+      <c r="E74" s="412"/>
+      <c r="F74" s="412"/>
+      <c r="G74" s="412"/>
+      <c r="H74" s="412"/>
+      <c r="I74" s="412"/>
+      <c r="J74" s="412"/>
+      <c r="K74" s="412"/>
+      <c r="L74" s="412"/>
+      <c r="M74" s="412"/>
     </row>
     <row r="75" spans="2:13" s="7" customFormat="1" ht="21" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="76" spans="2:13" s="7" customFormat="1" ht="20" x14ac:dyDescent="0.2">
-      <c r="B76" s="354" t="s">
+      <c r="B76" s="353" t="s">
         <v>99</v>
       </c>
       <c r="C76" s="44" t="s">
         <v>84</v>
       </c>
       <c r="D76" s="9"/>
-      <c r="E76" s="354" t="s">
+      <c r="E76" s="353" t="s">
         <v>99</v>
       </c>
       <c r="F76" s="44" t="s">
@@ -35016,12 +35097,12 @@
       </c>
     </row>
     <row r="77" spans="2:13" s="7" customFormat="1" ht="21" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B77" s="356"/>
+      <c r="B77" s="355"/>
       <c r="C77" s="45" t="s">
         <v>100</v>
       </c>
       <c r="D77" s="9"/>
-      <c r="E77" s="356"/>
+      <c r="E77" s="355"/>
       <c r="F77" s="45" t="s">
         <v>100</v>
       </c>
@@ -35756,45 +35837,45 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="350" t="s">
+      <c r="A2" s="349" t="s">
         <v>1594</v>
       </c>
-      <c r="B2" s="350"/>
-      <c r="C2" s="350"/>
-      <c r="D2" s="350"/>
-      <c r="E2" s="350"/>
-      <c r="F2" s="350"/>
-      <c r="G2" s="350"/>
-      <c r="H2" s="350"/>
-      <c r="I2" s="350"/>
-      <c r="J2" s="350"/>
-      <c r="K2" s="350"/>
+      <c r="B2" s="349"/>
+      <c r="C2" s="349"/>
+      <c r="D2" s="349"/>
+      <c r="E2" s="349"/>
+      <c r="F2" s="349"/>
+      <c r="G2" s="349"/>
+      <c r="H2" s="349"/>
+      <c r="I2" s="349"/>
+      <c r="J2" s="349"/>
+      <c r="K2" s="349"/>
     </row>
     <row r="3" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="350"/>
-      <c r="B3" s="350"/>
-      <c r="C3" s="350"/>
-      <c r="D3" s="350"/>
-      <c r="E3" s="350"/>
-      <c r="F3" s="350"/>
-      <c r="G3" s="350"/>
-      <c r="H3" s="350"/>
-      <c r="I3" s="350"/>
-      <c r="J3" s="350"/>
-      <c r="K3" s="350"/>
+      <c r="A3" s="349"/>
+      <c r="B3" s="349"/>
+      <c r="C3" s="349"/>
+      <c r="D3" s="349"/>
+      <c r="E3" s="349"/>
+      <c r="F3" s="349"/>
+      <c r="G3" s="349"/>
+      <c r="H3" s="349"/>
+      <c r="I3" s="349"/>
+      <c r="J3" s="349"/>
+      <c r="K3" s="349"/>
     </row>
     <row r="4" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="350"/>
-      <c r="B4" s="350"/>
-      <c r="C4" s="350"/>
-      <c r="D4" s="350"/>
-      <c r="E4" s="350"/>
-      <c r="F4" s="350"/>
-      <c r="G4" s="350"/>
-      <c r="H4" s="350"/>
-      <c r="I4" s="350"/>
-      <c r="J4" s="350"/>
-      <c r="K4" s="350"/>
+      <c r="A4" s="349"/>
+      <c r="B4" s="349"/>
+      <c r="C4" s="349"/>
+      <c r="D4" s="349"/>
+      <c r="E4" s="349"/>
+      <c r="F4" s="349"/>
+      <c r="G4" s="349"/>
+      <c r="H4" s="349"/>
+      <c r="I4" s="349"/>
+      <c r="J4" s="349"/>
+      <c r="K4" s="349"/>
     </row>
     <row r="5" spans="1:11" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A5" s="119"/>
@@ -35811,10 +35892,10 @@
     </row>
     <row r="6" spans="1:11" ht="20" x14ac:dyDescent="0.2">
       <c r="A6" s="13"/>
-      <c r="B6" s="352" t="s">
+      <c r="B6" s="351" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="354" t="s">
+      <c r="C6" s="353" t="s">
         <v>0</v>
       </c>
       <c r="D6" s="14" t="s">
@@ -35830,8 +35911,8 @@
     </row>
     <row r="7" spans="1:11" ht="21" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="13"/>
-      <c r="B7" s="358"/>
-      <c r="C7" s="356"/>
+      <c r="B7" s="357"/>
+      <c r="C7" s="355"/>
       <c r="D7" s="15" t="s">
         <v>100</v>
       </c>
@@ -35926,30 +36007,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:17" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B1" s="312" t="s">
+      <c r="B1" s="309" t="s">
         <v>1589</v>
       </c>
     </row>
     <row r="2" spans="2:17" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="347" t="s">
+      <c r="B2" s="346" t="s">
         <v>1595</v>
       </c>
-      <c r="C2" s="347"/>
-      <c r="D2" s="347"/>
-      <c r="E2" s="347"/>
-      <c r="F2" s="347"/>
-      <c r="G2" s="347"/>
-      <c r="H2" s="347"/>
+      <c r="C2" s="346"/>
+      <c r="D2" s="346"/>
+      <c r="E2" s="346"/>
+      <c r="F2" s="346"/>
+      <c r="G2" s="346"/>
+      <c r="H2" s="346"/>
       <c r="I2" s="38"/>
     </row>
     <row r="3" spans="2:17" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="347"/>
-      <c r="C3" s="347"/>
-      <c r="D3" s="347"/>
-      <c r="E3" s="347"/>
-      <c r="F3" s="347"/>
-      <c r="G3" s="347"/>
-      <c r="H3" s="347"/>
+      <c r="B3" s="346"/>
+      <c r="C3" s="346"/>
+      <c r="D3" s="346"/>
+      <c r="E3" s="346"/>
+      <c r="F3" s="346"/>
+      <c r="G3" s="346"/>
+      <c r="H3" s="346"/>
       <c r="I3" s="38"/>
     </row>
     <row r="4" spans="2:17" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -35959,10 +36040,10 @@
       <c r="Q5" s="41"/>
     </row>
     <row r="6" spans="2:17" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="359" t="s">
+      <c r="B6" s="358" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="359" t="s">
+      <c r="C6" s="358" t="s">
         <v>0</v>
       </c>
       <c r="D6" s="34" t="s">
@@ -35980,8 +36061,8 @@
       <c r="Q6" s="41"/>
     </row>
     <row r="7" spans="2:17" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="360"/>
-      <c r="C7" s="360"/>
+      <c r="B7" s="359"/>
+      <c r="C7" s="359"/>
       <c r="D7" s="36" t="s">
         <v>104</v>
       </c>
@@ -36029,9 +36110,9 @@
       </c>
       <c r="E9" s="31"/>
       <c r="F9" s="32"/>
-      <c r="G9" s="349"/>
-      <c r="H9" s="349"/>
-      <c r="I9" s="349"/>
+      <c r="G9" s="348"/>
+      <c r="H9" s="348"/>
+      <c r="I9" s="348"/>
       <c r="J9" s="32"/>
       <c r="L9" s="31"/>
       <c r="M9" s="32"/>
@@ -36045,9 +36126,9 @@
       <c r="D10" s="54"/>
       <c r="E10" s="31"/>
       <c r="F10" s="32"/>
-      <c r="G10" s="349"/>
-      <c r="H10" s="349"/>
-      <c r="I10" s="349"/>
+      <c r="G10" s="348"/>
+      <c r="H10" s="348"/>
+      <c r="I10" s="348"/>
       <c r="J10" s="32"/>
       <c r="L10" s="31"/>
       <c r="M10" s="32"/>
@@ -36467,28 +36548,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="30" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="343" t="s">
+      <c r="A1" s="340" t="s">
+        <v>1699</v>
+      </c>
+      <c r="B1" s="346" t="s">
         <v>1700</v>
       </c>
-      <c r="B1" s="347" t="s">
-        <v>1701</v>
-      </c>
-      <c r="C1" s="347"/>
-      <c r="D1" s="347"/>
-      <c r="E1" s="347"/>
-      <c r="F1" s="347"/>
-      <c r="G1" s="347"/>
-      <c r="H1" s="347"/>
+      <c r="C1" s="346"/>
+      <c r="D1" s="346"/>
+      <c r="E1" s="346"/>
+      <c r="F1" s="346"/>
+      <c r="G1" s="346"/>
+      <c r="H1" s="346"/>
       <c r="I1" s="38"/>
     </row>
     <row r="2" spans="1:17" s="30" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="347"/>
-      <c r="C2" s="347"/>
-      <c r="D2" s="347"/>
-      <c r="E2" s="347"/>
-      <c r="F2" s="347"/>
-      <c r="G2" s="347"/>
-      <c r="H2" s="347"/>
+      <c r="B2" s="346"/>
+      <c r="C2" s="346"/>
+      <c r="D2" s="346"/>
+      <c r="E2" s="346"/>
+      <c r="F2" s="346"/>
+      <c r="G2" s="346"/>
+      <c r="H2" s="346"/>
       <c r="I2" s="38"/>
     </row>
     <row r="3" spans="1:17" s="30" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -36498,10 +36579,10 @@
       <c r="Q4" s="41"/>
     </row>
     <row r="5" spans="1:17" s="30" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="348" t="s">
+      <c r="B5" s="347" t="s">
         <v>102</v>
       </c>
-      <c r="C5" s="348" t="s">
+      <c r="C5" s="347" t="s">
         <v>0</v>
       </c>
       <c r="D5" s="114" t="s">
@@ -36519,8 +36600,8 @@
       <c r="Q5" s="41"/>
     </row>
     <row r="6" spans="1:17" s="30" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="348"/>
-      <c r="C6" s="348"/>
+      <c r="B6" s="347"/>
+      <c r="C6" s="347"/>
       <c r="D6" s="114" t="s">
         <v>104</v>
       </c>
@@ -36568,9 +36649,9 @@
       </c>
       <c r="E8" s="31"/>
       <c r="F8" s="32"/>
-      <c r="G8" s="349"/>
-      <c r="H8" s="349"/>
-      <c r="I8" s="349"/>
+      <c r="G8" s="348"/>
+      <c r="H8" s="348"/>
+      <c r="I8" s="348"/>
       <c r="J8" s="32"/>
       <c r="L8" s="31"/>
       <c r="M8" s="32"/>
@@ -36590,9 +36671,9 @@
       </c>
       <c r="E9" s="31"/>
       <c r="F9" s="32"/>
-      <c r="G9" s="349"/>
-      <c r="H9" s="349"/>
-      <c r="I9" s="349"/>
+      <c r="G9" s="348"/>
+      <c r="H9" s="348"/>
+      <c r="I9" s="348"/>
       <c r="J9" s="32"/>
       <c r="L9" s="31"/>
       <c r="M9" s="32"/>
@@ -36733,7 +36814,7 @@
     </row>
     <row r="20" spans="2:4" ht="21" x14ac:dyDescent="0.25">
       <c r="B20" s="113" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="C20" s="113" t="s">
         <v>105</v>
@@ -36744,7 +36825,7 @@
     </row>
     <row r="21" spans="2:4" ht="21" x14ac:dyDescent="0.25">
       <c r="B21" s="113" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="C21" s="113" t="s">
         <v>83</v>
@@ -36820,10 +36901,10 @@
       </c>
     </row>
     <row r="28" spans="2:4" ht="21" x14ac:dyDescent="0.25">
-      <c r="B28" s="268" t="s">
+      <c r="B28" s="265" t="s">
         <v>1221</v>
       </c>
-      <c r="C28" s="268" t="s">
+      <c r="C28" s="265" t="s">
         <v>83</v>
       </c>
       <c r="D28" s="153">
@@ -36866,49 +36947,49 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>1702</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="350" t="s">
+      <c r="A2" s="349" t="s">
         <v>1591</v>
       </c>
-      <c r="B2" s="350"/>
-      <c r="C2" s="350"/>
-      <c r="D2" s="350"/>
-      <c r="E2" s="350"/>
-      <c r="F2" s="350"/>
-      <c r="G2" s="350"/>
-      <c r="H2" s="350"/>
-      <c r="I2" s="350"/>
-      <c r="J2" s="350"/>
-      <c r="K2" s="350"/>
+      <c r="B2" s="349"/>
+      <c r="C2" s="349"/>
+      <c r="D2" s="349"/>
+      <c r="E2" s="349"/>
+      <c r="F2" s="349"/>
+      <c r="G2" s="349"/>
+      <c r="H2" s="349"/>
+      <c r="I2" s="349"/>
+      <c r="J2" s="349"/>
+      <c r="K2" s="349"/>
     </row>
     <row r="3" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="350"/>
-      <c r="B3" s="350"/>
-      <c r="C3" s="350"/>
-      <c r="D3" s="350"/>
-      <c r="E3" s="350"/>
-      <c r="F3" s="350"/>
-      <c r="G3" s="350"/>
-      <c r="H3" s="350"/>
-      <c r="I3" s="350"/>
-      <c r="J3" s="350"/>
-      <c r="K3" s="350"/>
+      <c r="A3" s="349"/>
+      <c r="B3" s="349"/>
+      <c r="C3" s="349"/>
+      <c r="D3" s="349"/>
+      <c r="E3" s="349"/>
+      <c r="F3" s="349"/>
+      <c r="G3" s="349"/>
+      <c r="H3" s="349"/>
+      <c r="I3" s="349"/>
+      <c r="J3" s="349"/>
+      <c r="K3" s="349"/>
     </row>
     <row r="4" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="350"/>
-      <c r="B4" s="350"/>
-      <c r="C4" s="350"/>
-      <c r="D4" s="350"/>
-      <c r="E4" s="350"/>
-      <c r="F4" s="350"/>
-      <c r="G4" s="350"/>
-      <c r="H4" s="350"/>
-      <c r="I4" s="350"/>
-      <c r="J4" s="350"/>
-      <c r="K4" s="350"/>
+      <c r="A4" s="349"/>
+      <c r="B4" s="349"/>
+      <c r="C4" s="349"/>
+      <c r="D4" s="349"/>
+      <c r="E4" s="349"/>
+      <c r="F4" s="349"/>
+      <c r="G4" s="349"/>
+      <c r="H4" s="349"/>
+      <c r="I4" s="349"/>
+      <c r="J4" s="349"/>
+      <c r="K4" s="349"/>
     </row>
     <row r="5" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="119"/>
@@ -36925,10 +37006,10 @@
     </row>
     <row r="6" spans="1:11" ht="20" x14ac:dyDescent="0.2">
       <c r="A6" s="13"/>
-      <c r="B6" s="351" t="s">
+      <c r="B6" s="350" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="351" t="s">
+      <c r="C6" s="350" t="s">
         <v>0</v>
       </c>
       <c r="D6" s="120" t="s">
@@ -36946,8 +37027,8 @@
     </row>
     <row r="7" spans="1:11" ht="20" x14ac:dyDescent="0.2">
       <c r="A7" s="13"/>
-      <c r="B7" s="351"/>
-      <c r="C7" s="351"/>
+      <c r="B7" s="350"/>
+      <c r="C7" s="350"/>
       <c r="D7" s="120" t="s">
         <v>100</v>
       </c>
@@ -36964,7 +37045,7 @@
     <row r="8" spans="1:11" ht="21" x14ac:dyDescent="0.25">
       <c r="A8" s="7"/>
       <c r="B8" s="113" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
       <c r="C8" s="113" t="s">
         <v>83</v>
@@ -36983,7 +37064,7 @@
     <row r="9" spans="1:11" ht="21" x14ac:dyDescent="0.25">
       <c r="A9" s="7"/>
       <c r="B9" s="113" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="C9" s="113" t="s">
         <v>404</v>
@@ -37002,7 +37083,7 @@
     <row r="10" spans="1:11" ht="21" x14ac:dyDescent="0.25">
       <c r="A10" s="7"/>
       <c r="B10" s="113" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="C10" s="113" t="s">
         <v>1034</v>
@@ -37020,7 +37101,7 @@
     </row>
     <row r="11" spans="1:11" ht="21" x14ac:dyDescent="0.25">
       <c r="B11" s="113" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="C11" s="113" t="s">
         <v>1034</v>

--- a/public/docs/tarifa-italgres.xlsx
+++ b/public/docs/tarifa-italgres.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/carlos/Dropbox/TODO/TODO/USA/Todo USA/PAJARITO/Tarifas Miami tile/Tarifas nuevas USA 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{642CE9A0-CD50-2E4E-9B8E-6AA98B40B320}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74761C0F-46EB-9C4F-BD7B-E36A6795007C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1900" yWindow="480" windowWidth="38400" windowHeight="19460" tabRatio="500" firstSheet="24" activeTab="26" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="460" windowWidth="38400" windowHeight="19420" tabRatio="500" firstSheet="20" activeTab="32" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ALAPLANA" sheetId="116" r:id="rId1"/>
@@ -64,7 +64,7 @@
     <sheet name="VENATTO" sheetId="45" r:id="rId49"/>
     <sheet name="VIVES" sheetId="47" r:id="rId50"/>
   </sheets>
-  <calcPr calcId="191029" concurrentCalc="0"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2591" uniqueCount="1715">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2603" uniqueCount="1721">
   <si>
     <t>SIZE</t>
   </si>
@@ -4977,12 +4977,6 @@
     <t>BARCELONA , all colours decor</t>
   </si>
   <si>
-    <t>GREENBOOK , all the colours plain</t>
-  </si>
-  <si>
-    <t>GREENBOOK , all the colours relief</t>
-  </si>
-  <si>
     <t>JAIPUR , all the colours except burgundi</t>
   </si>
   <si>
@@ -5458,6 +5452,30 @@
   </si>
   <si>
     <t>05.04.26</t>
+  </si>
+  <si>
+    <t>20.04.26</t>
+  </si>
+  <si>
+    <t>Vitrubius Ivory and cream</t>
+  </si>
+  <si>
+    <t>Vitrubius Ivory and cream grip</t>
+  </si>
+  <si>
+    <t>Tears all the colours</t>
+  </si>
+  <si>
+    <t>23.04.26</t>
+  </si>
+  <si>
+    <t>GLENBROOK , all the colours plain</t>
+  </si>
+  <si>
+    <t>GLENBROOK , all the colours relief</t>
+  </si>
+  <si>
+    <t>SHALLOW, all the colours</t>
   </si>
 </sst>
 </file>
@@ -7266,7 +7284,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="435">
+  <cellXfs count="437">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="42" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
@@ -7759,8 +7777,6 @@
     <xf numFmtId="168" fontId="81" fillId="0" borderId="29" xfId="280" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="81" fillId="0" borderId="29" xfId="280" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="101" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="67" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="67" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="85" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7848,6 +7864,36 @@
     </xf>
     <xf numFmtId="167" fontId="70" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="21" xfId="246" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="99" fillId="0" borderId="21" xfId="246" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="99" fillId="0" borderId="19" xfId="246" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="246" applyFont="1"/>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="246" applyFont="1"/>
+    <xf numFmtId="0" fontId="54" fillId="2" borderId="32" xfId="246" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="102" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="101" fillId="0" borderId="28" xfId="246" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="27" xfId="246" applyBorder="1"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="26" xfId="246" applyBorder="1"/>
+    <xf numFmtId="4" fontId="102" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="101" fillId="0" borderId="30" xfId="246" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="8" xfId="246" applyBorder="1"/>
+    <xf numFmtId="169" fontId="67" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="67" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="67" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="54" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="51" fillId="4" borderId="0" xfId="246" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -7996,6 +8042,9 @@
     <xf numFmtId="0" fontId="51" fillId="4" borderId="0" xfId="246" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="52" fillId="4" borderId="0" xfId="246" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="53" fillId="4" borderId="0" xfId="246" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="54" fillId="2" borderId="32" xfId="246" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="49" fillId="3" borderId="1" xfId="246" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -8057,33 +8106,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="67" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="100" fillId="0" borderId="21" xfId="246" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="99" fillId="0" borderId="21" xfId="246" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="99" fillId="0" borderId="19" xfId="246" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="246" applyFont="1"/>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="246" applyFont="1"/>
-    <xf numFmtId="0" fontId="54" fillId="2" borderId="32" xfId="246" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="2" borderId="32" xfId="246" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="102" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="101" fillId="0" borderId="28" xfId="246" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="27" xfId="246" applyBorder="1"/>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="26" xfId="246" applyBorder="1"/>
-    <xf numFmtId="4" fontId="102" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="101" fillId="0" borderId="30" xfId="246" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="8" xfId="246" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="313">
     <cellStyle name="Comma [0] 2" xfId="248" xr:uid="{00000000-0005-0000-0000-000025010000}"/>
@@ -8748,28 +8770,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="30" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="339" t="s">
-        <v>1696</v>
-      </c>
-      <c r="B1" s="346" t="s">
-        <v>1697</v>
-      </c>
-      <c r="C1" s="346"/>
-      <c r="D1" s="346"/>
-      <c r="E1" s="346"/>
-      <c r="F1" s="346"/>
-      <c r="G1" s="346"/>
-      <c r="H1" s="346"/>
+      <c r="A1" s="337" t="s">
+        <v>1694</v>
+      </c>
+      <c r="B1" s="364" t="s">
+        <v>1695</v>
+      </c>
+      <c r="C1" s="364"/>
+      <c r="D1" s="364"/>
+      <c r="E1" s="364"/>
+      <c r="F1" s="364"/>
+      <c r="G1" s="364"/>
+      <c r="H1" s="364"/>
       <c r="I1" s="38"/>
     </row>
     <row r="2" spans="1:17" s="30" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="346"/>
-      <c r="C2" s="346"/>
-      <c r="D2" s="346"/>
-      <c r="E2" s="346"/>
-      <c r="F2" s="346"/>
-      <c r="G2" s="346"/>
-      <c r="H2" s="346"/>
+      <c r="B2" s="364"/>
+      <c r="C2" s="364"/>
+      <c r="D2" s="364"/>
+      <c r="E2" s="364"/>
+      <c r="F2" s="364"/>
+      <c r="G2" s="364"/>
+      <c r="H2" s="364"/>
       <c r="I2" s="38"/>
     </row>
     <row r="3" spans="1:17" s="30" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -8779,10 +8801,10 @@
       <c r="Q4" s="41"/>
     </row>
     <row r="5" spans="1:17" s="30" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="347" t="s">
+      <c r="B5" s="365" t="s">
         <v>102</v>
       </c>
-      <c r="C5" s="347" t="s">
+      <c r="C5" s="365" t="s">
         <v>0</v>
       </c>
       <c r="D5" s="114" t="s">
@@ -8800,8 +8822,8 @@
       <c r="Q5" s="41"/>
     </row>
     <row r="6" spans="1:17" s="30" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="347"/>
-      <c r="C6" s="347"/>
+      <c r="B6" s="365"/>
+      <c r="C6" s="365"/>
       <c r="D6" s="114" t="s">
         <v>104</v>
       </c>
@@ -8818,7 +8840,7 @@
     </row>
     <row r="7" spans="1:17" s="30" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="121" t="s">
-        <v>1695</v>
+        <v>1693</v>
       </c>
       <c r="C7" s="121" t="s">
         <v>105</v>
@@ -8839,7 +8861,7 @@
     </row>
     <row r="8" spans="1:17" s="30" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="121" t="s">
-        <v>1695</v>
+        <v>1693</v>
       </c>
       <c r="C8" s="121" t="s">
         <v>83</v>
@@ -8849,9 +8871,9 @@
       </c>
       <c r="E8" s="31"/>
       <c r="F8" s="32"/>
-      <c r="G8" s="348"/>
-      <c r="H8" s="348"/>
-      <c r="I8" s="348"/>
+      <c r="G8" s="366"/>
+      <c r="H8" s="366"/>
+      <c r="I8" s="366"/>
       <c r="J8" s="32"/>
       <c r="L8" s="31"/>
       <c r="M8" s="32"/>
@@ -8865,9 +8887,9 @@
       <c r="D9" s="202"/>
       <c r="E9" s="31"/>
       <c r="F9" s="32"/>
-      <c r="G9" s="348"/>
-      <c r="H9" s="348"/>
-      <c r="I9" s="348"/>
+      <c r="G9" s="366"/>
+      <c r="H9" s="366"/>
+      <c r="I9" s="366"/>
       <c r="J9" s="32"/>
       <c r="L9" s="31"/>
       <c r="M9" s="32"/>
@@ -8900,45 +8922,45 @@
   <sheetData>
     <row r="1" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="349" t="s">
-        <v>1599</v>
-      </c>
-      <c r="C2" s="349"/>
-      <c r="D2" s="349"/>
-      <c r="E2" s="349"/>
-      <c r="F2" s="349"/>
-      <c r="G2" s="349"/>
-      <c r="H2" s="349"/>
-      <c r="I2" s="349"/>
-      <c r="J2" s="349"/>
-      <c r="K2" s="349"/>
-      <c r="L2" s="349"/>
+      <c r="B2" s="367" t="s">
+        <v>1597</v>
+      </c>
+      <c r="C2" s="367"/>
+      <c r="D2" s="367"/>
+      <c r="E2" s="367"/>
+      <c r="F2" s="367"/>
+      <c r="G2" s="367"/>
+      <c r="H2" s="367"/>
+      <c r="I2" s="367"/>
+      <c r="J2" s="367"/>
+      <c r="K2" s="367"/>
+      <c r="L2" s="367"/>
     </row>
     <row r="3" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="349"/>
-      <c r="C3" s="349"/>
-      <c r="D3" s="349"/>
-      <c r="E3" s="349"/>
-      <c r="F3" s="349"/>
-      <c r="G3" s="349"/>
-      <c r="H3" s="349"/>
-      <c r="I3" s="349"/>
-      <c r="J3" s="349"/>
-      <c r="K3" s="349"/>
-      <c r="L3" s="349"/>
+      <c r="B3" s="367"/>
+      <c r="C3" s="367"/>
+      <c r="D3" s="367"/>
+      <c r="E3" s="367"/>
+      <c r="F3" s="367"/>
+      <c r="G3" s="367"/>
+      <c r="H3" s="367"/>
+      <c r="I3" s="367"/>
+      <c r="J3" s="367"/>
+      <c r="K3" s="367"/>
+      <c r="L3" s="367"/>
     </row>
     <row r="4" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
-        <v>1589</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="5" spans="2:12" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="2:12" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="13"/>
-      <c r="C6" s="360" t="s">
+      <c r="C6" s="378" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="362" t="s">
+      <c r="D6" s="380" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="138" t="s">
@@ -8949,8 +8971,8 @@
     </row>
     <row r="7" spans="2:12" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="13"/>
-      <c r="C7" s="361"/>
-      <c r="D7" s="363"/>
+      <c r="C7" s="379"/>
+      <c r="D7" s="381"/>
       <c r="E7" s="236" t="s">
         <v>100</v>
       </c>
@@ -8959,7 +8981,7 @@
     </row>
     <row r="8" spans="2:12" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C8" s="113" t="s">
-        <v>1600</v>
+        <v>1598</v>
       </c>
       <c r="D8" s="113" t="s">
         <v>105</v>
@@ -8971,7 +8993,7 @@
     </row>
     <row r="9" spans="2:12" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C9" s="113" t="s">
-        <v>1601</v>
+        <v>1599</v>
       </c>
       <c r="D9" s="113" t="s">
         <v>105</v>
@@ -8983,7 +9005,7 @@
     </row>
     <row r="10" spans="2:12" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C10" s="113" t="s">
-        <v>1601</v>
+        <v>1599</v>
       </c>
       <c r="D10" s="113" t="s">
         <v>83</v>
@@ -8995,7 +9017,7 @@
     </row>
     <row r="11" spans="2:12" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C11" s="113" t="s">
-        <v>1602</v>
+        <v>1600</v>
       </c>
       <c r="D11" s="113" t="s">
         <v>105</v>
@@ -9007,7 +9029,7 @@
     </row>
     <row r="12" spans="2:12" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C12" s="113" t="s">
-        <v>1602</v>
+        <v>1600</v>
       </c>
       <c r="D12" s="113" t="s">
         <v>83</v>
@@ -9019,7 +9041,7 @@
     </row>
     <row r="13" spans="2:12" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C13" s="113" t="s">
-        <v>1603</v>
+        <v>1601</v>
       </c>
       <c r="D13" s="113" t="s">
         <v>83</v>
@@ -9457,36 +9479,36 @@
       <c r="K1" s="177"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" s="364" t="s">
-        <v>1604</v>
-      </c>
-      <c r="B2" s="364"/>
-      <c r="C2" s="364"/>
-      <c r="D2" s="364"/>
-      <c r="E2" s="364"/>
-      <c r="F2" s="364"/>
-      <c r="G2" s="364"/>
-      <c r="H2" s="364"/>
-      <c r="I2" s="364"/>
-      <c r="J2" s="364"/>
-      <c r="K2" s="364"/>
+      <c r="A2" s="382" t="s">
+        <v>1602</v>
+      </c>
+      <c r="B2" s="382"/>
+      <c r="C2" s="382"/>
+      <c r="D2" s="382"/>
+      <c r="E2" s="382"/>
+      <c r="F2" s="382"/>
+      <c r="G2" s="382"/>
+      <c r="H2" s="382"/>
+      <c r="I2" s="382"/>
+      <c r="J2" s="382"/>
+      <c r="K2" s="382"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A3" s="364"/>
-      <c r="B3" s="364"/>
-      <c r="C3" s="364"/>
-      <c r="D3" s="364"/>
-      <c r="E3" s="364"/>
-      <c r="F3" s="364"/>
-      <c r="G3" s="364"/>
-      <c r="H3" s="364"/>
-      <c r="I3" s="364"/>
-      <c r="J3" s="364"/>
-      <c r="K3" s="364"/>
+      <c r="A3" s="382"/>
+      <c r="B3" s="382"/>
+      <c r="C3" s="382"/>
+      <c r="D3" s="382"/>
+      <c r="E3" s="382"/>
+      <c r="F3" s="382"/>
+      <c r="G3" s="382"/>
+      <c r="H3" s="382"/>
+      <c r="I3" s="382"/>
+      <c r="J3" s="382"/>
+      <c r="K3" s="382"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="177" t="s">
-        <v>1589</v>
+        <v>1587</v>
       </c>
       <c r="B4" s="177"/>
       <c r="C4" s="177"/>
@@ -9514,10 +9536,10 @@
     </row>
     <row r="6" spans="1:11" ht="20" x14ac:dyDescent="0.2">
       <c r="A6" s="13"/>
-      <c r="B6" s="360" t="s">
+      <c r="B6" s="378" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="362" t="s">
+      <c r="C6" s="380" t="s">
         <v>0</v>
       </c>
       <c r="D6" s="180" t="s">
@@ -9533,8 +9555,8 @@
     </row>
     <row r="7" spans="1:11" ht="21" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="13"/>
-      <c r="B7" s="361"/>
-      <c r="C7" s="363"/>
+      <c r="B7" s="379"/>
+      <c r="C7" s="381"/>
       <c r="D7" s="191" t="s">
         <v>100</v>
       </c>
@@ -9709,7 +9731,9 @@
       <c r="D16" s="207">
         <v>7.8222841800908691</v>
       </c>
-      <c r="E16" s="179"/>
+      <c r="E16" s="179" t="s">
+        <v>1589</v>
+      </c>
       <c r="F16" s="6"/>
       <c r="G16" s="177"/>
       <c r="H16" s="177"/>
@@ -9829,24 +9853,24 @@
   <sheetData>
     <row r="1" spans="2:10" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:10" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="346" t="s">
-        <v>1605</v>
-      </c>
-      <c r="C2" s="346"/>
-      <c r="D2" s="346"/>
-      <c r="E2" s="346"/>
-      <c r="F2" s="346"/>
+      <c r="B2" s="364" t="s">
+        <v>1603</v>
+      </c>
+      <c r="C2" s="364"/>
+      <c r="D2" s="364"/>
+      <c r="E2" s="364"/>
+      <c r="F2" s="364"/>
       <c r="G2" s="38"/>
       <c r="H2" s="38"/>
       <c r="I2" s="38"/>
       <c r="J2" s="38"/>
     </row>
     <row r="3" spans="2:10" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="346"/>
-      <c r="C3" s="346"/>
-      <c r="D3" s="346"/>
-      <c r="E3" s="346"/>
-      <c r="F3" s="346"/>
+      <c r="B3" s="364"/>
+      <c r="C3" s="364"/>
+      <c r="D3" s="364"/>
+      <c r="E3" s="364"/>
+      <c r="F3" s="364"/>
       <c r="G3" s="38"/>
       <c r="H3" s="38"/>
       <c r="I3" s="38"/>
@@ -9864,13 +9888,13 @@
       <c r="J4" s="38"/>
     </row>
     <row r="5" spans="2:10" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="316" t="s">
-        <v>1589</v>
+      <c r="B5" s="314" t="s">
+        <v>1587</v>
       </c>
     </row>
     <row r="6" spans="2:10" s="35" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="33"/>
-      <c r="C6" s="365" t="s">
+      <c r="C6" s="383" t="s">
         <v>99</v>
       </c>
       <c r="D6" s="192" t="s">
@@ -9878,7 +9902,7 @@
       </c>
       <c r="E6" s="193"/>
       <c r="F6" s="194"/>
-      <c r="G6" s="365" t="s">
+      <c r="G6" s="383" t="s">
         <v>99</v>
       </c>
       <c r="H6" s="192" t="s">
@@ -9887,13 +9911,13 @@
     </row>
     <row r="7" spans="2:10" s="35" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="33"/>
-      <c r="C7" s="365"/>
+      <c r="C7" s="383"/>
       <c r="D7" s="192" t="s">
         <v>98</v>
       </c>
       <c r="E7" s="193"/>
       <c r="F7" s="194"/>
-      <c r="G7" s="365"/>
+      <c r="G7" s="383"/>
       <c r="H7" s="192" t="s">
         <v>100</v>
       </c>
@@ -10207,7 +10231,7 @@
       </c>
       <c r="E27" s="195"/>
       <c r="F27" s="195"/>
-      <c r="G27" s="312" t="s">
+      <c r="G27" s="310" t="s">
         <v>70</v>
       </c>
       <c r="H27" s="234">
@@ -10223,7 +10247,7 @@
       </c>
       <c r="E28" s="195"/>
       <c r="F28" s="195"/>
-      <c r="G28" s="313" t="s">
+      <c r="G28" s="311" t="s">
         <v>71</v>
       </c>
       <c r="H28" s="234">
@@ -10239,7 +10263,7 @@
       </c>
       <c r="E29" s="195"/>
       <c r="F29" s="195"/>
-      <c r="G29" s="313" t="s">
+      <c r="G29" s="311" t="s">
         <v>72</v>
       </c>
       <c r="H29" s="234">
@@ -10255,7 +10279,7 @@
       </c>
       <c r="E30" s="195"/>
       <c r="F30" s="195"/>
-      <c r="G30" s="313" t="s">
+      <c r="G30" s="311" t="s">
         <v>73</v>
       </c>
       <c r="H30" s="234">
@@ -10271,7 +10295,7 @@
       </c>
       <c r="E31" s="195"/>
       <c r="F31" s="195"/>
-      <c r="G31" s="313" t="s">
+      <c r="G31" s="311" t="s">
         <v>74</v>
       </c>
       <c r="H31" s="234">
@@ -10287,7 +10311,7 @@
       </c>
       <c r="E32" s="195"/>
       <c r="F32" s="195"/>
-      <c r="G32" s="313" t="s">
+      <c r="G32" s="311" t="s">
         <v>75</v>
       </c>
       <c r="H32" s="234">
@@ -10303,7 +10327,7 @@
       </c>
       <c r="E33" s="195"/>
       <c r="F33" s="195"/>
-      <c r="G33" s="313" t="s">
+      <c r="G33" s="311" t="s">
         <v>76</v>
       </c>
       <c r="H33" s="234">
@@ -10319,7 +10343,7 @@
       </c>
       <c r="E34" s="195"/>
       <c r="F34" s="195"/>
-      <c r="G34" s="313" t="s">
+      <c r="G34" s="311" t="s">
         <v>77</v>
       </c>
       <c r="H34" s="234">
@@ -10335,7 +10359,7 @@
       </c>
       <c r="E35" s="195"/>
       <c r="F35" s="195"/>
-      <c r="G35" s="313" t="s">
+      <c r="G35" s="311" t="s">
         <v>78</v>
       </c>
       <c r="H35" s="234">
@@ -10343,7 +10367,7 @@
       </c>
     </row>
     <row r="36" spans="3:8" s="37" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C36" s="310" t="s">
+      <c r="C36" s="308" t="s">
         <v>32</v>
       </c>
       <c r="D36" s="228">
@@ -10351,7 +10375,7 @@
       </c>
       <c r="E36" s="195"/>
       <c r="F36" s="195"/>
-      <c r="G36" s="313" t="s">
+      <c r="G36" s="311" t="s">
         <v>79</v>
       </c>
       <c r="H36" s="234">
@@ -10367,7 +10391,7 @@
       </c>
       <c r="E37" s="195"/>
       <c r="F37" s="195"/>
-      <c r="G37" s="313" t="s">
+      <c r="G37" s="311" t="s">
         <v>80</v>
       </c>
       <c r="H37" s="234">
@@ -10383,7 +10407,7 @@
       </c>
       <c r="E38" s="195"/>
       <c r="F38" s="195"/>
-      <c r="G38" s="313" t="s">
+      <c r="G38" s="311" t="s">
         <v>81</v>
       </c>
       <c r="H38" s="234">
@@ -10399,7 +10423,7 @@
       </c>
       <c r="E39" s="195"/>
       <c r="F39" s="195"/>
-      <c r="G39" s="314" t="s">
+      <c r="G39" s="312" t="s">
         <v>1223</v>
       </c>
       <c r="H39" s="234">
@@ -10415,7 +10439,7 @@
       </c>
       <c r="E40" s="195"/>
       <c r="F40" s="195"/>
-      <c r="G40" s="314" t="s">
+      <c r="G40" s="312" t="s">
         <v>1224</v>
       </c>
       <c r="H40" s="234">
@@ -10431,7 +10455,7 @@
       </c>
       <c r="E41" s="195"/>
       <c r="F41" s="195"/>
-      <c r="G41" s="314" t="s">
+      <c r="G41" s="312" t="s">
         <v>1225</v>
       </c>
       <c r="H41" s="234">
@@ -10443,7 +10467,7 @@
       <c r="D42" s="229"/>
       <c r="E42" s="195"/>
       <c r="F42" s="195"/>
-      <c r="G42" s="314" t="s">
+      <c r="G42" s="312" t="s">
         <v>1226</v>
       </c>
       <c r="H42" s="235">
@@ -10451,7 +10475,7 @@
       </c>
     </row>
     <row r="43" spans="3:8" s="37" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C43" s="311" t="s">
+      <c r="C43" s="309" t="s">
         <v>38</v>
       </c>
       <c r="D43" s="225">
@@ -10459,7 +10483,7 @@
       </c>
       <c r="E43" s="195"/>
       <c r="F43" s="195"/>
-      <c r="G43" s="314" t="s">
+      <c r="G43" s="312" t="s">
         <v>1227</v>
       </c>
       <c r="H43" s="234">
@@ -10467,7 +10491,7 @@
       </c>
     </row>
     <row r="44" spans="3:8" s="37" customFormat="1" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C44" s="311" t="s">
+      <c r="C44" s="309" t="s">
         <v>39</v>
       </c>
       <c r="D44" s="225">
@@ -10475,7 +10499,7 @@
       </c>
       <c r="E44" s="195"/>
       <c r="F44" s="195"/>
-      <c r="G44" s="315" t="s">
+      <c r="G44" s="313" t="s">
         <v>1228</v>
       </c>
       <c r="H44" s="234">
@@ -10483,7 +10507,7 @@
       </c>
     </row>
     <row r="45" spans="3:8" s="37" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C45" s="311" t="s">
+      <c r="C45" s="309" t="s">
         <v>40</v>
       </c>
       <c r="D45" s="231">
@@ -10495,7 +10519,7 @@
       <c r="H45" s="196"/>
     </row>
     <row r="46" spans="3:8" s="37" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C46" s="311" t="s">
+      <c r="C46" s="309" t="s">
         <v>41</v>
       </c>
       <c r="D46" s="231">
@@ -10507,7 +10531,7 @@
       <c r="H46" s="198"/>
     </row>
     <row r="47" spans="3:8" s="37" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C47" s="311" t="s">
+      <c r="C47" s="309" t="s">
         <v>42</v>
       </c>
       <c r="D47" s="231">
@@ -10519,7 +10543,7 @@
       <c r="H47" s="199"/>
     </row>
     <row r="48" spans="3:8" s="37" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C48" s="311" t="s">
+      <c r="C48" s="309" t="s">
         <v>43</v>
       </c>
       <c r="D48" s="231">
@@ -10531,7 +10555,7 @@
       <c r="H48" s="195"/>
     </row>
     <row r="49" spans="3:8" s="37" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C49" s="311" t="s">
+      <c r="C49" s="309" t="s">
         <v>44</v>
       </c>
       <c r="D49" s="231">
@@ -10543,7 +10567,7 @@
       <c r="H49" s="195"/>
     </row>
     <row r="50" spans="3:8" s="37" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C50" s="311" t="s">
+      <c r="C50" s="309" t="s">
         <v>45</v>
       </c>
       <c r="D50" s="231">
@@ -10555,7 +10579,7 @@
       <c r="H50" s="195"/>
     </row>
     <row r="51" spans="3:8" s="37" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C51" s="311" t="s">
+      <c r="C51" s="309" t="s">
         <v>46</v>
       </c>
       <c r="D51" s="231">
@@ -10567,7 +10591,7 @@
       <c r="H51" s="195"/>
     </row>
     <row r="52" spans="3:8" s="37" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C52" s="311" t="s">
+      <c r="C52" s="309" t="s">
         <v>47</v>
       </c>
       <c r="D52" s="231">
@@ -10579,7 +10603,7 @@
       <c r="H52" s="195"/>
     </row>
     <row r="53" spans="3:8" s="37" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C53" s="311" t="s">
+      <c r="C53" s="309" t="s">
         <v>48</v>
       </c>
       <c r="D53" s="231">
@@ -10591,7 +10615,7 @@
       <c r="H53" s="195"/>
     </row>
     <row r="54" spans="3:8" s="37" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C54" s="311" t="s">
+      <c r="C54" s="309" t="s">
         <v>1222</v>
       </c>
       <c r="D54" s="231">
@@ -10603,7 +10627,7 @@
       <c r="H54" s="195"/>
     </row>
     <row r="55" spans="3:8" s="37" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C55" s="311" t="s">
+      <c r="C55" s="309" t="s">
         <v>49</v>
       </c>
       <c r="D55" s="231">
@@ -10615,7 +10639,7 @@
       <c r="H55" s="195"/>
     </row>
     <row r="56" spans="3:8" s="37" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C56" s="311" t="s">
+      <c r="C56" s="309" t="s">
         <v>50</v>
       </c>
       <c r="D56" s="231">
@@ -10627,7 +10651,7 @@
       <c r="H56" s="195"/>
     </row>
     <row r="57" spans="3:8" s="37" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C57" s="311" t="s">
+      <c r="C57" s="309" t="s">
         <v>51</v>
       </c>
       <c r="D57" s="231">
@@ -10639,7 +10663,7 @@
       <c r="H57" s="195"/>
     </row>
     <row r="58" spans="3:8" s="37" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C58" s="311" t="s">
+      <c r="C58" s="309" t="s">
         <v>52</v>
       </c>
       <c r="D58" s="231">
@@ -10651,7 +10675,7 @@
       <c r="H58" s="195"/>
     </row>
     <row r="59" spans="3:8" s="37" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C59" s="311" t="s">
+      <c r="C59" s="309" t="s">
         <v>53</v>
       </c>
       <c r="D59" s="231">
@@ -10824,36 +10848,36 @@
       <c r="K1" s="177"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" s="364" t="s">
-        <v>1606</v>
-      </c>
-      <c r="B2" s="364"/>
-      <c r="C2" s="364"/>
-      <c r="D2" s="364"/>
-      <c r="E2" s="364"/>
-      <c r="F2" s="364"/>
-      <c r="G2" s="364"/>
-      <c r="H2" s="364"/>
-      <c r="I2" s="364"/>
-      <c r="J2" s="364"/>
-      <c r="K2" s="364"/>
+      <c r="A2" s="382" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B2" s="382"/>
+      <c r="C2" s="382"/>
+      <c r="D2" s="382"/>
+      <c r="E2" s="382"/>
+      <c r="F2" s="382"/>
+      <c r="G2" s="382"/>
+      <c r="H2" s="382"/>
+      <c r="I2" s="382"/>
+      <c r="J2" s="382"/>
+      <c r="K2" s="382"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A3" s="364"/>
-      <c r="B3" s="364"/>
-      <c r="C3" s="364"/>
-      <c r="D3" s="364"/>
-      <c r="E3" s="364"/>
-      <c r="F3" s="364"/>
-      <c r="G3" s="364"/>
-      <c r="H3" s="364"/>
-      <c r="I3" s="364"/>
-      <c r="J3" s="364"/>
-      <c r="K3" s="364"/>
+      <c r="A3" s="382"/>
+      <c r="B3" s="382"/>
+      <c r="C3" s="382"/>
+      <c r="D3" s="382"/>
+      <c r="E3" s="382"/>
+      <c r="F3" s="382"/>
+      <c r="G3" s="382"/>
+      <c r="H3" s="382"/>
+      <c r="I3" s="382"/>
+      <c r="J3" s="382"/>
+      <c r="K3" s="382"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="177" t="s">
-        <v>1589</v>
+        <v>1587</v>
       </c>
       <c r="B4" s="177"/>
       <c r="C4" s="177"/>
@@ -10881,13 +10905,13 @@
     </row>
     <row r="6" spans="1:11" ht="20" x14ac:dyDescent="0.2">
       <c r="A6" s="13"/>
-      <c r="B6" s="350" t="s">
+      <c r="B6" s="368" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="350" t="s">
+      <c r="C6" s="368" t="s">
         <v>0</v>
       </c>
-      <c r="D6" s="290" t="s">
+      <c r="D6" s="288" t="s">
         <v>101</v>
       </c>
       <c r="E6" s="13"/>
@@ -10900,9 +10924,9 @@
     </row>
     <row r="7" spans="1:11" ht="21" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="13"/>
-      <c r="B7" s="363"/>
-      <c r="C7" s="363"/>
-      <c r="D7" s="291" t="s">
+      <c r="B7" s="381"/>
+      <c r="C7" s="381"/>
+      <c r="D7" s="289" t="s">
         <v>100</v>
       </c>
       <c r="E7" s="13"/>
@@ -10915,13 +10939,13 @@
     </row>
     <row r="8" spans="1:11" ht="21" x14ac:dyDescent="0.25">
       <c r="A8" s="28"/>
-      <c r="B8" s="288" t="s">
+      <c r="B8" s="286" t="s">
         <v>1150</v>
       </c>
-      <c r="C8" s="288" t="s">
+      <c r="C8" s="286" t="s">
         <v>874</v>
       </c>
-      <c r="D8" s="292">
+      <c r="D8" s="290">
         <v>10.591679287713985</v>
       </c>
       <c r="E8" s="28"/>
@@ -10934,10 +10958,10 @@
     </row>
     <row r="9" spans="1:11" ht="21" x14ac:dyDescent="0.25">
       <c r="A9" s="28"/>
-      <c r="B9" s="289" t="s">
+      <c r="B9" s="287" t="s">
         <v>1151</v>
       </c>
-      <c r="C9" s="289" t="s">
+      <c r="C9" s="287" t="s">
         <v>874</v>
       </c>
       <c r="D9" s="202">
@@ -11162,7 +11186,7 @@
       <c r="C22" s="130" t="s">
         <v>871</v>
       </c>
-      <c r="D22" s="293">
+      <c r="D22" s="291">
         <v>6.6240763688099493</v>
       </c>
     </row>
@@ -11173,7 +11197,7 @@
       <c r="C23" s="130" t="s">
         <v>893</v>
       </c>
-      <c r="D23" s="294">
+      <c r="D23" s="292">
         <v>7.8850704483913923</v>
       </c>
     </row>
@@ -11184,7 +11208,7 @@
       <c r="C24" s="130" t="s">
         <v>1116</v>
       </c>
-      <c r="D24" s="295">
+      <c r="D24" s="293">
         <v>8.6096195327917755</v>
       </c>
     </row>
@@ -11211,45 +11235,45 @@
   <sheetData>
     <row r="1" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="349" t="s">
-        <v>1607</v>
-      </c>
-      <c r="C2" s="349"/>
-      <c r="D2" s="349"/>
-      <c r="E2" s="349"/>
-      <c r="F2" s="349"/>
-      <c r="G2" s="349"/>
-      <c r="H2" s="349"/>
-      <c r="I2" s="349"/>
-      <c r="J2" s="349"/>
-      <c r="K2" s="349"/>
-      <c r="L2" s="349"/>
+      <c r="B2" s="367" t="s">
+        <v>1605</v>
+      </c>
+      <c r="C2" s="367"/>
+      <c r="D2" s="367"/>
+      <c r="E2" s="367"/>
+      <c r="F2" s="367"/>
+      <c r="G2" s="367"/>
+      <c r="H2" s="367"/>
+      <c r="I2" s="367"/>
+      <c r="J2" s="367"/>
+      <c r="K2" s="367"/>
+      <c r="L2" s="367"/>
     </row>
     <row r="3" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="349"/>
-      <c r="C3" s="349"/>
-      <c r="D3" s="349"/>
-      <c r="E3" s="349"/>
-      <c r="F3" s="349"/>
-      <c r="G3" s="349"/>
-      <c r="H3" s="349"/>
-      <c r="I3" s="349"/>
-      <c r="J3" s="349"/>
-      <c r="K3" s="349"/>
-      <c r="L3" s="349"/>
+      <c r="B3" s="367"/>
+      <c r="C3" s="367"/>
+      <c r="D3" s="367"/>
+      <c r="E3" s="367"/>
+      <c r="F3" s="367"/>
+      <c r="G3" s="367"/>
+      <c r="H3" s="367"/>
+      <c r="I3" s="367"/>
+      <c r="J3" s="367"/>
+      <c r="K3" s="367"/>
+      <c r="L3" s="367"/>
     </row>
     <row r="4" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
-        <v>1589</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="5" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="6" spans="2:12" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="13"/>
-      <c r="C6" s="350" t="s">
+      <c r="C6" s="368" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="350" t="s">
+      <c r="D6" s="368" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="120" t="s">
@@ -11260,8 +11284,8 @@
     </row>
     <row r="7" spans="2:12" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="13"/>
-      <c r="C7" s="350"/>
-      <c r="D7" s="350"/>
+      <c r="C7" s="368"/>
+      <c r="D7" s="368"/>
       <c r="E7" s="120" t="s">
         <v>100</v>
       </c>
@@ -11318,7 +11342,7 @@
     </row>
     <row r="12" spans="2:12" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C12" s="130" t="s">
-        <v>1610</v>
+        <v>1608</v>
       </c>
       <c r="D12" s="130" t="s">
         <v>108</v>
@@ -11330,7 +11354,7 @@
     </row>
     <row r="13" spans="2:12" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C13" s="130" t="s">
-        <v>1611</v>
+        <v>1609</v>
       </c>
       <c r="D13" s="130" t="s">
         <v>108</v>
@@ -11343,7 +11367,7 @@
     <row r="14" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="1"/>
       <c r="C14" s="130" t="s">
-        <v>1612</v>
+        <v>1610</v>
       </c>
       <c r="D14" s="130" t="s">
         <v>108</v>
@@ -11357,7 +11381,7 @@
     <row r="15" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="1"/>
       <c r="C15" s="130" t="s">
-        <v>1611</v>
+        <v>1609</v>
       </c>
       <c r="D15" s="130" t="s">
         <v>83</v>
@@ -11371,7 +11395,7 @@
     <row r="16" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="1"/>
       <c r="C16" s="130" t="s">
-        <v>1610</v>
+        <v>1608</v>
       </c>
       <c r="D16" s="130" t="s">
         <v>83</v>
@@ -11385,7 +11409,7 @@
     <row r="17" spans="2:7" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="1"/>
       <c r="C17" s="130" t="s">
-        <v>1613</v>
+        <v>1611</v>
       </c>
       <c r="D17" s="130" t="s">
         <v>108</v>
@@ -11399,7 +11423,7 @@
     <row r="18" spans="2:7" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="1"/>
       <c r="C18" s="130" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D18" s="130" t="s">
         <v>108</v>
@@ -11413,7 +11437,7 @@
     <row r="19" spans="2:7" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="1"/>
       <c r="C19" s="130" t="s">
-        <v>1613</v>
+        <v>1611</v>
       </c>
       <c r="D19" s="130" t="s">
         <v>83</v>
@@ -11425,7 +11449,7 @@
     <row r="20" spans="2:7" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="1"/>
       <c r="C20" s="130" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D20" s="130" t="s">
         <v>83</v>
@@ -11465,7 +11489,7 @@
     <row r="23" spans="2:7" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="1"/>
       <c r="C23" s="130" t="s">
-        <v>1615</v>
+        <v>1613</v>
       </c>
       <c r="D23" s="130" t="s">
         <v>108</v>
@@ -11479,7 +11503,7 @@
     <row r="24" spans="2:7" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="1"/>
       <c r="C24" s="130" t="s">
-        <v>1616</v>
+        <v>1614</v>
       </c>
       <c r="D24" s="130" t="s">
         <v>108</v>
@@ -11493,7 +11517,7 @@
     <row r="25" spans="2:7" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="1"/>
       <c r="C25" s="130" t="s">
-        <v>1615</v>
+        <v>1613</v>
       </c>
       <c r="D25" s="130" t="s">
         <v>83</v>
@@ -11507,7 +11531,7 @@
     <row r="26" spans="2:7" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="1"/>
       <c r="C26" s="130" t="s">
-        <v>1616</v>
+        <v>1614</v>
       </c>
       <c r="D26" s="130" t="s">
         <v>83</v>
@@ -11787,45 +11811,45 @@
   <sheetData>
     <row r="1" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="349" t="s">
-        <v>1608</v>
-      </c>
-      <c r="C2" s="349"/>
-      <c r="D2" s="349"/>
-      <c r="E2" s="349"/>
-      <c r="F2" s="349"/>
-      <c r="G2" s="349"/>
-      <c r="H2" s="349"/>
-      <c r="I2" s="349"/>
-      <c r="J2" s="349"/>
-      <c r="K2" s="349"/>
-      <c r="L2" s="349"/>
+      <c r="B2" s="367" t="s">
+        <v>1606</v>
+      </c>
+      <c r="C2" s="367"/>
+      <c r="D2" s="367"/>
+      <c r="E2" s="367"/>
+      <c r="F2" s="367"/>
+      <c r="G2" s="367"/>
+      <c r="H2" s="367"/>
+      <c r="I2" s="367"/>
+      <c r="J2" s="367"/>
+      <c r="K2" s="367"/>
+      <c r="L2" s="367"/>
     </row>
     <row r="3" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="349"/>
-      <c r="C3" s="349"/>
-      <c r="D3" s="349"/>
-      <c r="E3" s="349"/>
-      <c r="F3" s="349"/>
-      <c r="G3" s="349"/>
-      <c r="H3" s="349"/>
-      <c r="I3" s="349"/>
-      <c r="J3" s="349"/>
-      <c r="K3" s="349"/>
-      <c r="L3" s="349"/>
+      <c r="B3" s="367"/>
+      <c r="C3" s="367"/>
+      <c r="D3" s="367"/>
+      <c r="E3" s="367"/>
+      <c r="F3" s="367"/>
+      <c r="G3" s="367"/>
+      <c r="H3" s="367"/>
+      <c r="I3" s="367"/>
+      <c r="J3" s="367"/>
+      <c r="K3" s="367"/>
+      <c r="L3" s="367"/>
     </row>
     <row r="4" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
-        <v>1589</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="5" spans="2:12" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="2:12" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="13"/>
-      <c r="C6" s="360" t="s">
+      <c r="C6" s="378" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="362" t="s">
+      <c r="D6" s="380" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="138" t="s">
@@ -11838,8 +11862,8 @@
     </row>
     <row r="7" spans="2:12" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="13"/>
-      <c r="C7" s="361"/>
-      <c r="D7" s="363"/>
+      <c r="C7" s="379"/>
+      <c r="D7" s="381"/>
       <c r="E7" s="236" t="s">
         <v>100</v>
       </c>
@@ -12354,25 +12378,25 @@
   <sheetData>
     <row r="1" spans="1:12" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>1589</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="367" t="s">
-        <v>1609</v>
-      </c>
-      <c r="C2" s="367"/>
+      <c r="B2" s="385" t="s">
+        <v>1607</v>
+      </c>
+      <c r="C2" s="385"/>
     </row>
     <row r="3" spans="1:12" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="367"/>
-      <c r="C3" s="367"/>
+      <c r="B3" s="385"/>
+      <c r="C3" s="385"/>
     </row>
     <row r="6" spans="1:12" ht="20" x14ac:dyDescent="0.2">
       <c r="A6" s="13"/>
-      <c r="B6" s="350" t="s">
+      <c r="B6" s="368" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="350" t="s">
+      <c r="C6" s="368" t="s">
         <v>0</v>
       </c>
       <c r="D6" s="157" t="s">
@@ -12391,8 +12415,8 @@
     </row>
     <row r="7" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="13"/>
-      <c r="B7" s="363"/>
-      <c r="C7" s="363"/>
+      <c r="B7" s="381"/>
+      <c r="C7" s="381"/>
       <c r="D7" s="185" t="s">
         <v>1052</v>
       </c>
@@ -12957,21 +12981,21 @@
       <c r="E43" s="175"/>
     </row>
     <row r="44" spans="2:5" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B44" s="366" t="s">
+      <c r="B44" s="384" t="s">
         <v>1020</v>
       </c>
-      <c r="C44" s="366"/>
-      <c r="D44" s="366"/>
-      <c r="E44" s="366"/>
+      <c r="C44" s="384"/>
+      <c r="D44" s="384"/>
+      <c r="E44" s="384"/>
     </row>
     <row r="45" spans="2:5" ht="21" x14ac:dyDescent="0.25">
-      <c r="B45" s="298" t="s">
-        <v>1566</v>
-      </c>
-      <c r="C45" s="299" t="s">
-        <v>1567</v>
-      </c>
-      <c r="D45" s="300">
+      <c r="B45" s="296" t="s">
+        <v>1564</v>
+      </c>
+      <c r="C45" s="297" t="s">
+        <v>1565</v>
+      </c>
+      <c r="D45" s="298">
         <v>14</v>
       </c>
       <c r="E45" s="206">
@@ -12980,12 +13004,12 @@
     </row>
     <row r="46" spans="2:5" ht="21" x14ac:dyDescent="0.25">
       <c r="B46" s="261" t="s">
-        <v>1568</v>
+        <v>1566</v>
       </c>
       <c r="C46" s="160" t="s">
-        <v>1569</v>
-      </c>
-      <c r="D46" s="301">
+        <v>1567</v>
+      </c>
+      <c r="D46" s="299">
         <v>14</v>
       </c>
       <c r="E46" s="207">
@@ -12994,12 +13018,12 @@
     </row>
     <row r="47" spans="2:5" ht="21" x14ac:dyDescent="0.25">
       <c r="B47" s="261" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="C47" s="160" t="s">
-        <v>1571</v>
-      </c>
-      <c r="D47" s="301">
+        <v>1569</v>
+      </c>
+      <c r="D47" s="299">
         <v>10</v>
       </c>
       <c r="E47" s="207">
@@ -13008,12 +13032,12 @@
     </row>
     <row r="48" spans="2:5" ht="21" x14ac:dyDescent="0.25">
       <c r="B48" s="261" t="s">
-        <v>1572</v>
+        <v>1570</v>
       </c>
       <c r="C48" s="160" t="s">
-        <v>1573</v>
-      </c>
-      <c r="D48" s="301">
+        <v>1571</v>
+      </c>
+      <c r="D48" s="299">
         <v>10</v>
       </c>
       <c r="E48" s="207">
@@ -13022,12 +13046,12 @@
     </row>
     <row r="49" spans="2:5" ht="21" x14ac:dyDescent="0.25">
       <c r="B49" s="261" t="s">
-        <v>1574</v>
+        <v>1572</v>
       </c>
       <c r="C49" s="160" t="s">
-        <v>1575</v>
-      </c>
-      <c r="D49" s="301">
+        <v>1573</v>
+      </c>
+      <c r="D49" s="299">
         <v>10</v>
       </c>
       <c r="E49" s="207">
@@ -13036,12 +13060,12 @@
     </row>
     <row r="50" spans="2:5" ht="21" x14ac:dyDescent="0.25">
       <c r="B50" s="261" t="s">
-        <v>1576</v>
+        <v>1574</v>
       </c>
       <c r="C50" s="160" t="s">
         <v>1019</v>
       </c>
-      <c r="D50" s="301">
+      <c r="D50" s="299">
         <v>15</v>
       </c>
       <c r="E50" s="207">
@@ -13078,45 +13102,45 @@
   <sheetData>
     <row r="1" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="349" t="s">
-        <v>1666</v>
-      </c>
-      <c r="C2" s="349"/>
-      <c r="D2" s="349"/>
-      <c r="E2" s="349"/>
-      <c r="F2" s="349"/>
-      <c r="G2" s="349"/>
-      <c r="H2" s="349"/>
-      <c r="I2" s="349"/>
-      <c r="J2" s="349"/>
-      <c r="K2" s="349"/>
-      <c r="L2" s="349"/>
+      <c r="B2" s="367" t="s">
+        <v>1664</v>
+      </c>
+      <c r="C2" s="367"/>
+      <c r="D2" s="367"/>
+      <c r="E2" s="367"/>
+      <c r="F2" s="367"/>
+      <c r="G2" s="367"/>
+      <c r="H2" s="367"/>
+      <c r="I2" s="367"/>
+      <c r="J2" s="367"/>
+      <c r="K2" s="367"/>
+      <c r="L2" s="367"/>
     </row>
     <row r="3" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="349"/>
-      <c r="C3" s="349"/>
-      <c r="D3" s="349"/>
-      <c r="E3" s="349"/>
-      <c r="F3" s="349"/>
-      <c r="G3" s="349"/>
-      <c r="H3" s="349"/>
-      <c r="I3" s="349"/>
-      <c r="J3" s="349"/>
-      <c r="K3" s="349"/>
-      <c r="L3" s="349"/>
+      <c r="B3" s="367"/>
+      <c r="C3" s="367"/>
+      <c r="D3" s="367"/>
+      <c r="E3" s="367"/>
+      <c r="F3" s="367"/>
+      <c r="G3" s="367"/>
+      <c r="H3" s="367"/>
+      <c r="I3" s="367"/>
+      <c r="J3" s="367"/>
+      <c r="K3" s="367"/>
+      <c r="L3" s="367"/>
     </row>
     <row r="4" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
-        <v>1589</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="5" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="6" spans="2:12" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="13"/>
-      <c r="C6" s="350" t="s">
+      <c r="C6" s="368" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="350" t="s">
+      <c r="D6" s="368" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="120" t="s">
@@ -13127,8 +13151,8 @@
     </row>
     <row r="7" spans="2:12" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="13"/>
-      <c r="C7" s="350"/>
-      <c r="D7" s="350"/>
+      <c r="C7" s="368"/>
+      <c r="D7" s="368"/>
       <c r="E7" s="120" t="s">
         <v>100</v>
       </c>
@@ -13595,11 +13619,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="3:7" ht="34" x14ac:dyDescent="0.4">
-      <c r="D1" s="368" t="s">
+      <c r="D1" s="386" t="s">
         <v>1179</v>
       </c>
-      <c r="E1" s="368"/>
-      <c r="F1" s="368"/>
+      <c r="E1" s="386"/>
+      <c r="F1" s="386"/>
     </row>
     <row r="2" spans="3:7" ht="29" x14ac:dyDescent="0.35">
       <c r="D2" s="216"/>
@@ -13618,10 +13642,10 @@
     </row>
     <row r="5" spans="3:7" ht="20" x14ac:dyDescent="0.2">
       <c r="C5" s="13"/>
-      <c r="D5" s="353" t="s">
+      <c r="D5" s="371" t="s">
         <v>102</v>
       </c>
-      <c r="E5" s="353" t="s">
+      <c r="E5" s="371" t="s">
         <v>0</v>
       </c>
       <c r="F5" s="8" t="s">
@@ -13631,8 +13655,8 @@
     </row>
     <row r="6" spans="3:7" ht="20" x14ac:dyDescent="0.2">
       <c r="C6" s="13"/>
-      <c r="D6" s="354"/>
-      <c r="E6" s="354"/>
+      <c r="D6" s="372"/>
+      <c r="E6" s="372"/>
       <c r="F6" s="16" t="s">
         <v>100</v>
       </c>
@@ -13640,18 +13664,18 @@
     </row>
     <row r="7" spans="3:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C7" s="13"/>
-      <c r="D7" s="381" t="s">
+      <c r="D7" s="399" t="s">
         <v>965</v>
       </c>
-      <c r="E7" s="382"/>
-      <c r="F7" s="383"/>
+      <c r="E7" s="400"/>
+      <c r="F7" s="401"/>
       <c r="G7" s="13"/>
     </row>
     <row r="8" spans="3:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C8" s="13"/>
-      <c r="D8" s="384"/>
-      <c r="E8" s="385"/>
-      <c r="F8" s="386"/>
+      <c r="D8" s="402"/>
+      <c r="E8" s="403"/>
+      <c r="F8" s="404"/>
       <c r="G8" s="13"/>
     </row>
     <row r="9" spans="3:7" ht="21" x14ac:dyDescent="0.25">
@@ -13982,16 +14006,16 @@
       </c>
     </row>
     <row r="38" spans="4:6" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D38" s="369" t="s">
+      <c r="D38" s="387" t="s">
         <v>966</v>
       </c>
-      <c r="E38" s="387"/>
-      <c r="F38" s="388"/>
+      <c r="E38" s="405"/>
+      <c r="F38" s="406"/>
     </row>
     <row r="39" spans="4:6" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D39" s="389"/>
-      <c r="E39" s="390"/>
-      <c r="F39" s="391"/>
+      <c r="D39" s="407"/>
+      <c r="E39" s="408"/>
+      <c r="F39" s="409"/>
     </row>
     <row r="40" spans="4:6" ht="19" x14ac:dyDescent="0.25">
       <c r="D40" s="169" t="s">
@@ -14082,16 +14106,16 @@
       </c>
     </row>
     <row r="48" spans="4:6" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D48" s="375" t="s">
+      <c r="D48" s="393" t="s">
         <v>967</v>
       </c>
-      <c r="E48" s="376"/>
-      <c r="F48" s="377"/>
+      <c r="E48" s="394"/>
+      <c r="F48" s="395"/>
     </row>
     <row r="49" spans="4:6" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D49" s="378"/>
-      <c r="E49" s="379"/>
-      <c r="F49" s="380"/>
+      <c r="D49" s="396"/>
+      <c r="E49" s="397"/>
+      <c r="F49" s="398"/>
     </row>
     <row r="50" spans="4:6" ht="19" x14ac:dyDescent="0.25">
       <c r="D50" s="169" t="s">
@@ -14237,16 +14261,16 @@
       </c>
     </row>
     <row r="63" spans="4:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D63" s="369" t="s">
+      <c r="D63" s="387" t="s">
         <v>968</v>
       </c>
-      <c r="E63" s="370"/>
-      <c r="F63" s="371"/>
+      <c r="E63" s="388"/>
+      <c r="F63" s="389"/>
     </row>
     <row r="64" spans="4:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D64" s="372"/>
-      <c r="E64" s="373"/>
-      <c r="F64" s="374"/>
+      <c r="D64" s="390"/>
+      <c r="E64" s="391"/>
+      <c r="F64" s="392"/>
     </row>
     <row r="65" spans="4:6" ht="19" x14ac:dyDescent="0.25">
       <c r="D65" s="169" t="s">
@@ -14304,16 +14328,16 @@
       </c>
     </row>
     <row r="70" spans="4:6" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D70" s="375" t="s">
+      <c r="D70" s="393" t="s">
         <v>969</v>
       </c>
-      <c r="E70" s="376"/>
-      <c r="F70" s="377"/>
+      <c r="E70" s="394"/>
+      <c r="F70" s="395"/>
     </row>
     <row r="71" spans="4:6" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D71" s="378"/>
-      <c r="E71" s="379"/>
-      <c r="F71" s="380"/>
+      <c r="D71" s="396"/>
+      <c r="E71" s="397"/>
+      <c r="F71" s="398"/>
     </row>
     <row r="72" spans="4:6" ht="19" x14ac:dyDescent="0.25">
       <c r="D72" s="169" t="s">
@@ -14426,16 +14450,16 @@
       </c>
     </row>
     <row r="82" spans="4:6" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D82" s="375" t="s">
+      <c r="D82" s="393" t="s">
         <v>970</v>
       </c>
-      <c r="E82" s="376"/>
-      <c r="F82" s="377"/>
+      <c r="E82" s="394"/>
+      <c r="F82" s="395"/>
     </row>
     <row r="83" spans="4:6" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D83" s="378"/>
-      <c r="E83" s="379"/>
-      <c r="F83" s="380"/>
+      <c r="D83" s="396"/>
+      <c r="E83" s="397"/>
+      <c r="F83" s="398"/>
     </row>
     <row r="84" spans="4:6" ht="19" x14ac:dyDescent="0.25">
       <c r="D84" s="169" t="s">
@@ -14603,16 +14627,16 @@
       </c>
     </row>
     <row r="99" spans="4:6" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D99" s="375" t="s">
+      <c r="D99" s="393" t="s">
         <v>971</v>
       </c>
-      <c r="E99" s="376"/>
-      <c r="F99" s="377"/>
+      <c r="E99" s="394"/>
+      <c r="F99" s="395"/>
     </row>
     <row r="100" spans="4:6" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D100" s="378"/>
-      <c r="E100" s="379"/>
-      <c r="F100" s="380"/>
+      <c r="D100" s="396"/>
+      <c r="E100" s="397"/>
+      <c r="F100" s="398"/>
     </row>
     <row r="101" spans="4:6" ht="19" x14ac:dyDescent="0.25">
       <c r="D101" s="169" t="s">
@@ -14681,41 +14705,41 @@
       </c>
     </row>
     <row r="2" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="349" t="s">
+      <c r="B2" s="367" t="s">
         <v>1177</v>
       </c>
-      <c r="C2" s="349"/>
-      <c r="D2" s="349"/>
-      <c r="E2" s="349"/>
-      <c r="F2" s="349"/>
-      <c r="G2" s="349"/>
-      <c r="H2" s="349"/>
-      <c r="I2" s="349"/>
-      <c r="J2" s="349"/>
-      <c r="K2" s="349"/>
-      <c r="L2" s="349"/>
+      <c r="C2" s="367"/>
+      <c r="D2" s="367"/>
+      <c r="E2" s="367"/>
+      <c r="F2" s="367"/>
+      <c r="G2" s="367"/>
+      <c r="H2" s="367"/>
+      <c r="I2" s="367"/>
+      <c r="J2" s="367"/>
+      <c r="K2" s="367"/>
+      <c r="L2" s="367"/>
     </row>
     <row r="3" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="349"/>
-      <c r="C3" s="349"/>
-      <c r="D3" s="349"/>
-      <c r="E3" s="349"/>
-      <c r="F3" s="349"/>
-      <c r="G3" s="349"/>
-      <c r="H3" s="349"/>
-      <c r="I3" s="349"/>
-      <c r="J3" s="349"/>
-      <c r="K3" s="349"/>
-      <c r="L3" s="349"/>
+      <c r="B3" s="367"/>
+      <c r="C3" s="367"/>
+      <c r="D3" s="367"/>
+      <c r="E3" s="367"/>
+      <c r="F3" s="367"/>
+      <c r="G3" s="367"/>
+      <c r="H3" s="367"/>
+      <c r="I3" s="367"/>
+      <c r="J3" s="367"/>
+      <c r="K3" s="367"/>
+      <c r="L3" s="367"/>
     </row>
     <row r="4" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="6" spans="2:12" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="13"/>
-      <c r="C6" s="350" t="s">
+      <c r="C6" s="368" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="350" t="s">
+      <c r="D6" s="368" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="120" t="s">
@@ -14726,8 +14750,8 @@
     </row>
     <row r="7" spans="2:12" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="13"/>
-      <c r="C7" s="363"/>
-      <c r="D7" s="363"/>
+      <c r="C7" s="381"/>
+      <c r="D7" s="381"/>
       <c r="E7" s="157" t="s">
         <v>100</v>
       </c>
@@ -15175,49 +15199,49 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>1589</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="349" t="s">
-        <v>1590</v>
-      </c>
-      <c r="B2" s="349"/>
-      <c r="C2" s="349"/>
-      <c r="D2" s="349"/>
-      <c r="E2" s="349"/>
-      <c r="F2" s="349"/>
-      <c r="G2" s="349"/>
-      <c r="H2" s="349"/>
-      <c r="I2" s="349"/>
-      <c r="J2" s="349"/>
-      <c r="K2" s="349"/>
+      <c r="A2" s="367" t="s">
+        <v>1588</v>
+      </c>
+      <c r="B2" s="367"/>
+      <c r="C2" s="367"/>
+      <c r="D2" s="367"/>
+      <c r="E2" s="367"/>
+      <c r="F2" s="367"/>
+      <c r="G2" s="367"/>
+      <c r="H2" s="367"/>
+      <c r="I2" s="367"/>
+      <c r="J2" s="367"/>
+      <c r="K2" s="367"/>
     </row>
     <row r="3" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="349"/>
-      <c r="B3" s="349"/>
-      <c r="C3" s="349"/>
-      <c r="D3" s="349"/>
-      <c r="E3" s="349"/>
-      <c r="F3" s="349"/>
-      <c r="G3" s="349"/>
-      <c r="H3" s="349"/>
-      <c r="I3" s="349"/>
-      <c r="J3" s="349"/>
-      <c r="K3" s="349"/>
+      <c r="A3" s="367"/>
+      <c r="B3" s="367"/>
+      <c r="C3" s="367"/>
+      <c r="D3" s="367"/>
+      <c r="E3" s="367"/>
+      <c r="F3" s="367"/>
+      <c r="G3" s="367"/>
+      <c r="H3" s="367"/>
+      <c r="I3" s="367"/>
+      <c r="J3" s="367"/>
+      <c r="K3" s="367"/>
     </row>
     <row r="4" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="349"/>
-      <c r="B4" s="349"/>
-      <c r="C4" s="349"/>
-      <c r="D4" s="349"/>
-      <c r="E4" s="349"/>
-      <c r="F4" s="349"/>
-      <c r="G4" s="349"/>
-      <c r="H4" s="349"/>
-      <c r="I4" s="349"/>
-      <c r="J4" s="349"/>
-      <c r="K4" s="349"/>
+      <c r="A4" s="367"/>
+      <c r="B4" s="367"/>
+      <c r="C4" s="367"/>
+      <c r="D4" s="367"/>
+      <c r="E4" s="367"/>
+      <c r="F4" s="367"/>
+      <c r="G4" s="367"/>
+      <c r="H4" s="367"/>
+      <c r="I4" s="367"/>
+      <c r="J4" s="367"/>
+      <c r="K4" s="367"/>
     </row>
     <row r="5" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="119"/>
@@ -15234,10 +15258,10 @@
     </row>
     <row r="6" spans="1:11" ht="20" x14ac:dyDescent="0.2">
       <c r="A6" s="13"/>
-      <c r="B6" s="350" t="s">
+      <c r="B6" s="368" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="350" t="s">
+      <c r="C6" s="368" t="s">
         <v>0</v>
       </c>
       <c r="D6" s="120" t="s">
@@ -15255,8 +15279,8 @@
     </row>
     <row r="7" spans="1:11" ht="20" x14ac:dyDescent="0.2">
       <c r="A7" s="13"/>
-      <c r="B7" s="350"/>
-      <c r="C7" s="350"/>
+      <c r="B7" s="368"/>
+      <c r="C7" s="368"/>
       <c r="D7" s="120" t="s">
         <v>100</v>
       </c>
@@ -15588,44 +15612,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A1" s="392" t="s">
-        <v>1617</v>
-      </c>
-      <c r="B1" s="392"/>
-      <c r="C1" s="392"/>
-      <c r="D1" s="392"/>
-      <c r="E1" s="392"/>
-      <c r="F1" s="392"/>
-      <c r="G1" s="392"/>
-      <c r="H1" s="392"/>
-      <c r="I1" s="392"/>
-      <c r="J1" s="392"/>
-      <c r="K1" s="392"/>
+      <c r="A1" s="410" t="s">
+        <v>1615</v>
+      </c>
+      <c r="B1" s="410"/>
+      <c r="C1" s="410"/>
+      <c r="D1" s="410"/>
+      <c r="E1" s="410"/>
+      <c r="F1" s="410"/>
+      <c r="G1" s="410"/>
+      <c r="H1" s="410"/>
+      <c r="I1" s="410"/>
+      <c r="J1" s="410"/>
+      <c r="K1" s="410"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" s="392"/>
-      <c r="B2" s="392"/>
-      <c r="C2" s="392"/>
-      <c r="D2" s="392"/>
-      <c r="E2" s="392"/>
-      <c r="F2" s="392"/>
-      <c r="G2" s="392"/>
-      <c r="H2" s="392"/>
-      <c r="I2" s="392"/>
-      <c r="J2" s="392"/>
-      <c r="K2" s="392"/>
+      <c r="A2" s="410"/>
+      <c r="B2" s="410"/>
+      <c r="C2" s="410"/>
+      <c r="D2" s="410"/>
+      <c r="E2" s="410"/>
+      <c r="F2" s="410"/>
+      <c r="G2" s="410"/>
+      <c r="H2" s="410"/>
+      <c r="I2" s="410"/>
+      <c r="J2" s="410"/>
+      <c r="K2" s="410"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>1589</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="20" x14ac:dyDescent="0.2">
       <c r="A5" s="13"/>
-      <c r="B5" s="350" t="s">
+      <c r="B5" s="368" t="s">
         <v>102</v>
       </c>
-      <c r="C5" s="350" t="s">
+      <c r="C5" s="368" t="s">
         <v>0</v>
       </c>
       <c r="D5" s="120" t="s">
@@ -15641,8 +15665,8 @@
     </row>
     <row r="6" spans="1:11" ht="20" x14ac:dyDescent="0.2">
       <c r="A6" s="13"/>
-      <c r="B6" s="350"/>
-      <c r="C6" s="350"/>
+      <c r="B6" s="368"/>
+      <c r="C6" s="368"/>
       <c r="D6" s="120" t="s">
         <v>100</v>
       </c>
@@ -15797,43 +15821,43 @@
   <sheetData>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>1701</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="392" t="s">
-        <v>1706</v>
-      </c>
-      <c r="B3" s="392"/>
-      <c r="C3" s="392"/>
-      <c r="D3" s="392"/>
-      <c r="E3" s="392"/>
-      <c r="F3" s="392"/>
-      <c r="G3" s="392"/>
-      <c r="H3" s="392"/>
-      <c r="I3" s="392"/>
-      <c r="J3" s="392"/>
-      <c r="K3" s="392"/>
+      <c r="A3" s="410" t="s">
+        <v>1704</v>
+      </c>
+      <c r="B3" s="410"/>
+      <c r="C3" s="410"/>
+      <c r="D3" s="410"/>
+      <c r="E3" s="410"/>
+      <c r="F3" s="410"/>
+      <c r="G3" s="410"/>
+      <c r="H3" s="410"/>
+      <c r="I3" s="410"/>
+      <c r="J3" s="410"/>
+      <c r="K3" s="410"/>
     </row>
     <row r="4" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="392"/>
-      <c r="B4" s="392"/>
-      <c r="C4" s="392"/>
-      <c r="D4" s="392"/>
-      <c r="E4" s="392"/>
-      <c r="F4" s="392"/>
-      <c r="G4" s="392"/>
-      <c r="H4" s="392"/>
-      <c r="I4" s="392"/>
-      <c r="J4" s="392"/>
-      <c r="K4" s="392"/>
+      <c r="A4" s="410"/>
+      <c r="B4" s="410"/>
+      <c r="C4" s="410"/>
+      <c r="D4" s="410"/>
+      <c r="E4" s="410"/>
+      <c r="F4" s="410"/>
+      <c r="G4" s="410"/>
+      <c r="H4" s="410"/>
+      <c r="I4" s="410"/>
+      <c r="J4" s="410"/>
+      <c r="K4" s="410"/>
     </row>
     <row r="7" spans="1:11" ht="20" x14ac:dyDescent="0.2">
       <c r="A7" s="13"/>
-      <c r="B7" s="350" t="s">
+      <c r="B7" s="368" t="s">
         <v>102</v>
       </c>
-      <c r="C7" s="350" t="s">
+      <c r="C7" s="368" t="s">
         <v>0</v>
       </c>
       <c r="D7" s="120" t="s">
@@ -15849,8 +15873,8 @@
     </row>
     <row r="8" spans="1:11" ht="20" x14ac:dyDescent="0.2">
       <c r="A8" s="13"/>
-      <c r="B8" s="363"/>
-      <c r="C8" s="363"/>
+      <c r="B8" s="381"/>
+      <c r="C8" s="381"/>
       <c r="D8" s="157" t="s">
         <v>100</v>
       </c>
@@ -15865,7 +15889,7 @@
     <row r="9" spans="1:11" ht="21" x14ac:dyDescent="0.25">
       <c r="A9" s="7"/>
       <c r="B9" s="113" t="s">
-        <v>1618</v>
+        <v>1616</v>
       </c>
       <c r="C9" s="113" t="s">
         <v>83</v>
@@ -15884,7 +15908,7 @@
     <row r="10" spans="1:11" ht="21" x14ac:dyDescent="0.25">
       <c r="A10" s="7"/>
       <c r="B10" s="113" t="s">
-        <v>1707</v>
+        <v>1705</v>
       </c>
       <c r="C10" s="113" t="s">
         <v>83</v>
@@ -15959,7 +15983,7 @@
     </row>
     <row r="14" spans="1:11" ht="21" x14ac:dyDescent="0.25">
       <c r="B14" s="113" t="s">
-        <v>1619</v>
+        <v>1617</v>
       </c>
       <c r="C14" s="113" t="s">
         <v>105</v>
@@ -15970,7 +15994,7 @@
     </row>
     <row r="15" spans="1:11" ht="21" x14ac:dyDescent="0.25">
       <c r="B15" s="113" t="s">
-        <v>1619</v>
+        <v>1617</v>
       </c>
       <c r="C15" s="113" t="s">
         <v>83</v>
@@ -15981,7 +16005,7 @@
     </row>
     <row r="16" spans="1:11" ht="21" x14ac:dyDescent="0.25">
       <c r="B16" s="113" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="C16" s="113" t="s">
         <v>83</v>
@@ -15992,7 +16016,7 @@
     </row>
     <row r="17" spans="2:4" ht="21" x14ac:dyDescent="0.25">
       <c r="B17" s="113" t="s">
-        <v>1621</v>
+        <v>1619</v>
       </c>
       <c r="C17" s="113" t="s">
         <v>105</v>
@@ -16003,7 +16027,7 @@
     </row>
     <row r="18" spans="2:4" ht="21" x14ac:dyDescent="0.25">
       <c r="B18" s="113" t="s">
-        <v>1621</v>
+        <v>1619</v>
       </c>
       <c r="C18" s="113" t="s">
         <v>83</v>
@@ -16047,7 +16071,7 @@
     </row>
     <row r="22" spans="2:4" ht="21" x14ac:dyDescent="0.25">
       <c r="B22" s="113" t="s">
-        <v>1622</v>
+        <v>1620</v>
       </c>
       <c r="C22" s="113" t="s">
         <v>105</v>
@@ -16058,7 +16082,7 @@
     </row>
     <row r="23" spans="2:4" ht="21" x14ac:dyDescent="0.25">
       <c r="B23" s="113" t="s">
-        <v>1622</v>
+        <v>1620</v>
       </c>
       <c r="C23" s="113" t="s">
         <v>83</v>
@@ -16069,7 +16093,7 @@
     </row>
     <row r="24" spans="2:4" ht="21" x14ac:dyDescent="0.25">
       <c r="B24" s="113" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="C24" s="113" t="s">
         <v>83</v>
@@ -16080,7 +16104,7 @@
     </row>
     <row r="25" spans="2:4" ht="21" x14ac:dyDescent="0.25">
       <c r="B25" s="113" t="s">
-        <v>1624</v>
+        <v>1622</v>
       </c>
       <c r="C25" s="113" t="s">
         <v>83</v>
@@ -16112,7 +16136,7 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF36772E-8323-854E-852F-CE9D4991E3BF}">
-  <dimension ref="A2:K19"/>
+  <dimension ref="A2:K24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="48.33203125" customWidth="1"/>
@@ -16121,43 +16145,43 @@
   <sheetData>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>1672</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="392" t="s">
-        <v>1671</v>
-      </c>
-      <c r="B3" s="392"/>
-      <c r="C3" s="392"/>
-      <c r="D3" s="392"/>
-      <c r="E3" s="392"/>
-      <c r="F3" s="392"/>
-      <c r="G3" s="392"/>
-      <c r="H3" s="392"/>
-      <c r="I3" s="392"/>
-      <c r="J3" s="392"/>
-      <c r="K3" s="392"/>
+      <c r="A3" s="410" t="s">
+        <v>1669</v>
+      </c>
+      <c r="B3" s="410"/>
+      <c r="C3" s="410"/>
+      <c r="D3" s="410"/>
+      <c r="E3" s="410"/>
+      <c r="F3" s="410"/>
+      <c r="G3" s="410"/>
+      <c r="H3" s="410"/>
+      <c r="I3" s="410"/>
+      <c r="J3" s="410"/>
+      <c r="K3" s="410"/>
     </row>
     <row r="4" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="392"/>
-      <c r="B4" s="392"/>
-      <c r="C4" s="392"/>
-      <c r="D4" s="392"/>
-      <c r="E4" s="392"/>
-      <c r="F4" s="392"/>
-      <c r="G4" s="392"/>
-      <c r="H4" s="392"/>
-      <c r="I4" s="392"/>
-      <c r="J4" s="392"/>
-      <c r="K4" s="392"/>
+      <c r="A4" s="410"/>
+      <c r="B4" s="410"/>
+      <c r="C4" s="410"/>
+      <c r="D4" s="410"/>
+      <c r="E4" s="410"/>
+      <c r="F4" s="410"/>
+      <c r="G4" s="410"/>
+      <c r="H4" s="410"/>
+      <c r="I4" s="410"/>
+      <c r="J4" s="410"/>
+      <c r="K4" s="410"/>
     </row>
     <row r="7" spans="1:11" ht="20" x14ac:dyDescent="0.2">
       <c r="A7" s="13"/>
-      <c r="B7" s="350" t="s">
+      <c r="B7" s="368" t="s">
         <v>102</v>
       </c>
-      <c r="C7" s="350" t="s">
+      <c r="C7" s="368" t="s">
         <v>0</v>
       </c>
       <c r="D7" s="120" t="s">
@@ -16173,9 +16197,9 @@
     </row>
     <row r="8" spans="1:11" ht="20" x14ac:dyDescent="0.2">
       <c r="A8" s="13"/>
-      <c r="B8" s="363"/>
-      <c r="C8" s="363"/>
-      <c r="D8" s="157" t="s">
+      <c r="B8" s="368"/>
+      <c r="C8" s="368"/>
+      <c r="D8" s="120" t="s">
         <v>100</v>
       </c>
       <c r="E8" s="13"/>
@@ -16195,7 +16219,7 @@
         <v>1548</v>
       </c>
       <c r="D9" s="202">
-        <v>10.295589517646517</v>
+        <v>9.4931387397310569</v>
       </c>
       <c r="E9" s="7"/>
       <c r="F9" s="12"/>
@@ -16214,7 +16238,7 @@
         <v>1548</v>
       </c>
       <c r="D10" s="202">
-        <v>10.877318830602599</v>
+        <v>10.021983569691129</v>
       </c>
       <c r="E10" s="7"/>
       <c r="F10" s="12"/>
@@ -16233,7 +16257,7 @@
         <v>1551</v>
       </c>
       <c r="D11" s="202">
-        <v>10.065684519711782</v>
+        <v>9.2841341961540227</v>
       </c>
       <c r="E11" s="7"/>
       <c r="F11" s="12"/>
@@ -16252,7 +16276,7 @@
         <v>936</v>
       </c>
       <c r="D12" s="202">
-        <v>9.4874386158153214</v>
+        <v>8.7584561017026932</v>
       </c>
       <c r="E12" s="7"/>
       <c r="F12" s="12"/>
@@ -16271,7 +16295,7 @@
         <v>936</v>
       </c>
       <c r="D13" s="212">
-        <v>9.9507320207444145</v>
+        <v>9.1796319243655038</v>
       </c>
       <c r="E13" s="7"/>
       <c r="F13" s="12"/>
@@ -16283,69 +16307,100 @@
     </row>
     <row r="14" spans="1:11" ht="21" x14ac:dyDescent="0.25">
       <c r="B14" s="113" t="s">
-        <v>1554</v>
+        <v>1718</v>
       </c>
       <c r="C14" s="113" t="s">
         <v>901</v>
       </c>
       <c r="D14" s="202">
-        <v>10.055234292532926</v>
+        <v>9.2746339896277927</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="21" x14ac:dyDescent="0.25">
       <c r="B15" s="113" t="s">
-        <v>1555</v>
+        <v>1719</v>
       </c>
       <c r="C15" s="113" t="s">
         <v>901</v>
       </c>
       <c r="D15" s="220">
-        <v>10.616063151131303</v>
+        <v>9.784478406535408</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="21" x14ac:dyDescent="0.25">
       <c r="B16" s="113" t="s">
-        <v>1556</v>
+        <v>1554</v>
       </c>
       <c r="C16" s="113" t="s">
         <v>1551</v>
       </c>
       <c r="D16" s="220">
-        <v>10.358290880719631</v>
+        <v>9.5501399788884278</v>
       </c>
     </row>
     <row r="17" spans="2:4" ht="21" x14ac:dyDescent="0.25">
       <c r="B17" s="113" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="C17" s="113" t="s">
         <v>1551</v>
       </c>
       <c r="D17" s="220">
-        <v>10.912152921198768</v>
+        <v>10.053650924778557</v>
       </c>
     </row>
     <row r="18" spans="2:4" ht="21" x14ac:dyDescent="0.25">
       <c r="B18" s="113" t="s">
-        <v>1558</v>
+        <v>1556</v>
       </c>
       <c r="C18" s="113" t="s">
         <v>1551</v>
       </c>
       <c r="D18" s="220">
-        <v>12.664307678186242</v>
+        <v>11.646518885676256</v>
       </c>
     </row>
     <row r="19" spans="2:4" ht="21" x14ac:dyDescent="0.25">
       <c r="B19" s="113" t="s">
-        <v>1559</v>
+        <v>1557</v>
       </c>
       <c r="C19" s="113" t="s">
         <v>1551</v>
       </c>
       <c r="D19" s="220">
-        <v>10.755399513515995</v>
-      </c>
+        <v>9.9111478268851254</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" ht="21" x14ac:dyDescent="0.25">
+      <c r="B20" s="113" t="s">
+        <v>1720</v>
+      </c>
+      <c r="C20" s="113" t="s">
+        <v>874</v>
+      </c>
+      <c r="D20" s="220">
+        <v>9.1099637431731608</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" ht="21" x14ac:dyDescent="0.25">
+      <c r="B21" s="113" t="s">
+        <v>1720</v>
+      </c>
+      <c r="C21" s="113" t="s">
+        <v>936</v>
+      </c>
+      <c r="D21" s="220">
+        <v>11.646518885676256</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="D22" s="147"/>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="D23" s="147"/>
+    </row>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="D24" s="147"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -16369,45 +16424,45 @@
   <sheetData>
     <row r="1" spans="2:16" ht="19" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:16" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="349" t="s">
-        <v>1628</v>
-      </c>
-      <c r="C2" s="349"/>
-      <c r="D2" s="349"/>
-      <c r="E2" s="349"/>
-      <c r="F2" s="349"/>
-      <c r="G2" s="349"/>
-      <c r="H2" s="349"/>
-      <c r="I2" s="349"/>
-      <c r="J2" s="349"/>
-      <c r="K2" s="349"/>
-      <c r="L2" s="349"/>
+      <c r="B2" s="367" t="s">
+        <v>1626</v>
+      </c>
+      <c r="C2" s="367"/>
+      <c r="D2" s="367"/>
+      <c r="E2" s="367"/>
+      <c r="F2" s="367"/>
+      <c r="G2" s="367"/>
+      <c r="H2" s="367"/>
+      <c r="I2" s="367"/>
+      <c r="J2" s="367"/>
+      <c r="K2" s="367"/>
+      <c r="L2" s="367"/>
     </row>
     <row r="3" spans="2:16" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="349"/>
-      <c r="C3" s="349"/>
-      <c r="D3" s="349"/>
-      <c r="E3" s="349"/>
-      <c r="F3" s="349"/>
-      <c r="G3" s="349"/>
-      <c r="H3" s="349"/>
-      <c r="I3" s="349"/>
-      <c r="J3" s="349"/>
-      <c r="K3" s="349"/>
-      <c r="L3" s="349"/>
+      <c r="B3" s="367"/>
+      <c r="C3" s="367"/>
+      <c r="D3" s="367"/>
+      <c r="E3" s="367"/>
+      <c r="F3" s="367"/>
+      <c r="G3" s="367"/>
+      <c r="H3" s="367"/>
+      <c r="I3" s="367"/>
+      <c r="J3" s="367"/>
+      <c r="K3" s="367"/>
+      <c r="L3" s="367"/>
     </row>
     <row r="4" spans="2:16" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>1589</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="5" spans="2:16" ht="19" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="2:16" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="13"/>
-      <c r="C6" s="350" t="s">
+      <c r="C6" s="368" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="350" t="s">
+      <c r="D6" s="368" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="128" t="s">
@@ -16417,8 +16472,8 @@
     </row>
     <row r="7" spans="2:16" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="13"/>
-      <c r="C7" s="363"/>
-      <c r="D7" s="363"/>
+      <c r="C7" s="381"/>
+      <c r="D7" s="381"/>
       <c r="E7" s="131" t="s">
         <v>100</v>
       </c>
@@ -16565,7 +16620,7 @@
     <row r="18" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="1"/>
       <c r="C18" s="130" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
       <c r="D18" s="130" t="s">
         <v>105</v>
@@ -16578,7 +16633,7 @@
     <row r="19" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="1"/>
       <c r="C19" s="130" t="s">
-        <v>1625</v>
+        <v>1623</v>
       </c>
       <c r="D19" s="130" t="s">
         <v>83</v>
@@ -16591,7 +16646,7 @@
     <row r="20" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="1"/>
       <c r="C20" s="130" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
       <c r="D20" s="130" t="s">
         <v>113</v>
@@ -16604,7 +16659,7 @@
     <row r="21" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="1"/>
       <c r="C21" s="130" t="s">
-        <v>1626</v>
+        <v>1624</v>
       </c>
       <c r="D21" s="130" t="s">
         <v>83</v>
@@ -16617,7 +16672,7 @@
     <row r="22" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="1"/>
       <c r="C22" s="130" t="s">
-        <v>1627</v>
+        <v>1625</v>
       </c>
       <c r="D22" s="130" t="s">
         <v>83</v>
@@ -16630,7 +16685,7 @@
     <row r="23" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="1"/>
       <c r="C23" s="130" t="s">
-        <v>1561</v>
+        <v>1559</v>
       </c>
       <c r="D23" s="130" t="s">
         <v>105</v>
@@ -16643,7 +16698,7 @@
     <row r="24" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="1"/>
       <c r="C24" s="130" t="s">
-        <v>1561</v>
+        <v>1559</v>
       </c>
       <c r="D24" s="130" t="s">
         <v>83</v>
@@ -16724,9 +16779,9 @@
         <v>786</v>
       </c>
       <c r="D30" s="130" t="s">
-        <v>1562</v>
-      </c>
-      <c r="E30" s="317">
+        <v>1560</v>
+      </c>
+      <c r="E30" s="315">
         <v>7.510670521822937</v>
       </c>
       <c r="F30" s="2"/>
@@ -16941,45 +16996,45 @@
   <sheetData>
     <row r="1" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B1" t="s">
-        <v>1589</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="2" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="349" t="s">
-        <v>1632</v>
-      </c>
-      <c r="C2" s="349"/>
-      <c r="D2" s="349"/>
-      <c r="E2" s="349"/>
-      <c r="F2" s="349"/>
-      <c r="G2" s="349"/>
-      <c r="H2" s="349"/>
-      <c r="I2" s="349"/>
-      <c r="J2" s="349"/>
-      <c r="K2" s="349"/>
-      <c r="L2" s="349"/>
+      <c r="B2" s="367" t="s">
+        <v>1630</v>
+      </c>
+      <c r="C2" s="367"/>
+      <c r="D2" s="367"/>
+      <c r="E2" s="367"/>
+      <c r="F2" s="367"/>
+      <c r="G2" s="367"/>
+      <c r="H2" s="367"/>
+      <c r="I2" s="367"/>
+      <c r="J2" s="367"/>
+      <c r="K2" s="367"/>
+      <c r="L2" s="367"/>
     </row>
     <row r="3" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="349"/>
-      <c r="C3" s="349"/>
-      <c r="D3" s="349"/>
-      <c r="E3" s="349"/>
-      <c r="F3" s="349"/>
-      <c r="G3" s="349"/>
-      <c r="H3" s="349"/>
-      <c r="I3" s="349"/>
-      <c r="J3" s="349"/>
-      <c r="K3" s="349"/>
-      <c r="L3" s="349"/>
+      <c r="B3" s="367"/>
+      <c r="C3" s="367"/>
+      <c r="D3" s="367"/>
+      <c r="E3" s="367"/>
+      <c r="F3" s="367"/>
+      <c r="G3" s="367"/>
+      <c r="H3" s="367"/>
+      <c r="I3" s="367"/>
+      <c r="J3" s="367"/>
+      <c r="K3" s="367"/>
+      <c r="L3" s="367"/>
     </row>
     <row r="4" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="6" spans="2:12" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="13"/>
-      <c r="C6" s="350" t="s">
+      <c r="C6" s="368" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="350" t="s">
+      <c r="D6" s="368" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="120" t="s">
@@ -16990,8 +17045,8 @@
     </row>
     <row r="7" spans="2:12" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="13"/>
-      <c r="C7" s="363"/>
-      <c r="D7" s="363"/>
+      <c r="C7" s="381"/>
+      <c r="D7" s="381"/>
       <c r="E7" s="157" t="s">
         <v>100</v>
       </c>
@@ -17000,7 +17055,7 @@
     </row>
     <row r="8" spans="2:12" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C8" s="113" t="s">
-        <v>1629</v>
+        <v>1627</v>
       </c>
       <c r="D8" s="113" t="s">
         <v>404</v>
@@ -17013,7 +17068,7 @@
     <row r="9" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="1"/>
       <c r="C9" s="113" t="s">
-        <v>1629</v>
+        <v>1627</v>
       </c>
       <c r="D9" s="113" t="s">
         <v>83</v>
@@ -17055,7 +17110,7 @@
     <row r="12" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="1"/>
       <c r="C12" s="113" t="s">
-        <v>1630</v>
+        <v>1628</v>
       </c>
       <c r="D12" s="113" t="s">
         <v>83</v>
@@ -17069,7 +17124,7 @@
     <row r="13" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="1"/>
       <c r="C13" s="113" t="s">
-        <v>1631</v>
+        <v>1629</v>
       </c>
       <c r="D13" s="113" t="s">
         <v>83</v>
@@ -17386,45 +17441,45 @@
   <sheetData>
     <row r="1" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B1" t="s">
-        <v>1589</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="2" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="349" t="s">
-        <v>1633</v>
-      </c>
-      <c r="C2" s="349"/>
-      <c r="D2" s="349"/>
-      <c r="E2" s="349"/>
-      <c r="F2" s="349"/>
-      <c r="G2" s="349"/>
-      <c r="H2" s="349"/>
-      <c r="I2" s="349"/>
-      <c r="J2" s="349"/>
-      <c r="K2" s="349"/>
-      <c r="L2" s="349"/>
+      <c r="B2" s="367" t="s">
+        <v>1631</v>
+      </c>
+      <c r="C2" s="367"/>
+      <c r="D2" s="367"/>
+      <c r="E2" s="367"/>
+      <c r="F2" s="367"/>
+      <c r="G2" s="367"/>
+      <c r="H2" s="367"/>
+      <c r="I2" s="367"/>
+      <c r="J2" s="367"/>
+      <c r="K2" s="367"/>
+      <c r="L2" s="367"/>
     </row>
     <row r="3" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="349"/>
-      <c r="C3" s="349"/>
-      <c r="D3" s="349"/>
-      <c r="E3" s="349"/>
-      <c r="F3" s="349"/>
-      <c r="G3" s="349"/>
-      <c r="H3" s="349"/>
-      <c r="I3" s="349"/>
-      <c r="J3" s="349"/>
-      <c r="K3" s="349"/>
-      <c r="L3" s="349"/>
+      <c r="B3" s="367"/>
+      <c r="C3" s="367"/>
+      <c r="D3" s="367"/>
+      <c r="E3" s="367"/>
+      <c r="F3" s="367"/>
+      <c r="G3" s="367"/>
+      <c r="H3" s="367"/>
+      <c r="I3" s="367"/>
+      <c r="J3" s="367"/>
+      <c r="K3" s="367"/>
+      <c r="L3" s="367"/>
     </row>
     <row r="4" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="6" spans="2:12" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="13"/>
-      <c r="C6" s="350" t="s">
+      <c r="C6" s="368" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="350" t="s">
+      <c r="D6" s="368" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="120" t="s">
@@ -17435,8 +17490,8 @@
     </row>
     <row r="7" spans="2:12" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="13"/>
-      <c r="C7" s="350"/>
-      <c r="D7" s="350"/>
+      <c r="C7" s="368"/>
+      <c r="D7" s="368"/>
       <c r="E7" s="120" t="s">
         <v>100</v>
       </c>
@@ -17785,44 +17840,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A1" s="392" t="s">
-        <v>1634</v>
-      </c>
-      <c r="B1" s="392"/>
-      <c r="C1" s="392"/>
-      <c r="D1" s="392"/>
-      <c r="E1" s="392"/>
-      <c r="F1" s="392"/>
-      <c r="G1" s="392"/>
-      <c r="H1" s="392"/>
-      <c r="I1" s="392"/>
-      <c r="J1" s="392"/>
-      <c r="K1" s="392"/>
+      <c r="A1" s="410" t="s">
+        <v>1632</v>
+      </c>
+      <c r="B1" s="410"/>
+      <c r="C1" s="410"/>
+      <c r="D1" s="410"/>
+      <c r="E1" s="410"/>
+      <c r="F1" s="410"/>
+      <c r="G1" s="410"/>
+      <c r="H1" s="410"/>
+      <c r="I1" s="410"/>
+      <c r="J1" s="410"/>
+      <c r="K1" s="410"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" s="392"/>
-      <c r="B2" s="392"/>
-      <c r="C2" s="392"/>
-      <c r="D2" s="392"/>
-      <c r="E2" s="392"/>
-      <c r="F2" s="392"/>
-      <c r="G2" s="392"/>
-      <c r="H2" s="392"/>
-      <c r="I2" s="392"/>
-      <c r="J2" s="392"/>
-      <c r="K2" s="392"/>
+      <c r="A2" s="410"/>
+      <c r="B2" s="410"/>
+      <c r="C2" s="410"/>
+      <c r="D2" s="410"/>
+      <c r="E2" s="410"/>
+      <c r="F2" s="410"/>
+      <c r="G2" s="410"/>
+      <c r="H2" s="410"/>
+      <c r="I2" s="410"/>
+      <c r="J2" s="410"/>
+      <c r="K2" s="410"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>1589</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="20" x14ac:dyDescent="0.2">
       <c r="A5" s="13"/>
-      <c r="B5" s="350" t="s">
+      <c r="B5" s="368" t="s">
         <v>102</v>
       </c>
-      <c r="C5" s="350" t="s">
+      <c r="C5" s="368" t="s">
         <v>0</v>
       </c>
       <c r="D5" s="120" t="s">
@@ -17840,8 +17895,8 @@
     </row>
     <row r="6" spans="1:11" ht="20" x14ac:dyDescent="0.2">
       <c r="A6" s="13"/>
-      <c r="B6" s="350"/>
-      <c r="C6" s="350"/>
+      <c r="B6" s="368"/>
+      <c r="C6" s="368"/>
       <c r="D6" s="120" t="s">
         <v>100</v>
       </c>
@@ -18006,32 +18061,32 @@
       <c r="B1" s="189"/>
     </row>
     <row r="2" spans="2:10" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="394" t="s">
-        <v>1640</v>
-      </c>
-      <c r="C2" s="394"/>
-      <c r="D2" s="395"/>
-      <c r="E2" s="395"/>
-      <c r="F2" s="395"/>
-      <c r="G2" s="396"/>
+      <c r="B2" s="412" t="s">
+        <v>1638</v>
+      </c>
+      <c r="C2" s="412"/>
+      <c r="D2" s="413"/>
+      <c r="E2" s="413"/>
+      <c r="F2" s="413"/>
+      <c r="G2" s="414"/>
       <c r="H2" s="38"/>
       <c r="I2" s="38"/>
       <c r="J2" s="38"/>
     </row>
     <row r="3" spans="2:10" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="395"/>
-      <c r="C3" s="395"/>
-      <c r="D3" s="395"/>
-      <c r="E3" s="395"/>
-      <c r="F3" s="395"/>
-      <c r="G3" s="396"/>
+      <c r="B3" s="413"/>
+      <c r="C3" s="413"/>
+      <c r="D3" s="413"/>
+      <c r="E3" s="413"/>
+      <c r="F3" s="413"/>
+      <c r="G3" s="414"/>
       <c r="H3" s="38"/>
       <c r="I3" s="38"/>
       <c r="J3" s="38"/>
     </row>
     <row r="4" spans="2:10" ht="19" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="142" t="s">
-        <v>1714</v>
+        <v>1712</v>
       </c>
       <c r="C4" s="255"/>
       <c r="D4" s="255"/>
@@ -18039,19 +18094,19 @@
       <c r="F4" s="42"/>
     </row>
     <row r="5" spans="2:10" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="321"/>
-      <c r="C5" s="323"/>
-      <c r="D5" s="323"/>
-      <c r="E5" s="321"/>
+      <c r="B5" s="319"/>
+      <c r="C5" s="321"/>
+      <c r="D5" s="321"/>
+      <c r="E5" s="319"/>
     </row>
     <row r="6" spans="2:10" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="347" t="s">
+      <c r="B6" s="365" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="347" t="s">
+      <c r="C6" s="365" t="s">
         <v>106</v>
       </c>
-      <c r="D6" s="347" t="s">
+      <c r="D6" s="365" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="114" t="s">
@@ -18062,10 +18117,10 @@
       </c>
     </row>
     <row r="7" spans="2:10" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="426"/>
-      <c r="C7" s="426"/>
-      <c r="D7" s="426"/>
-      <c r="E7" s="427" t="s">
+      <c r="B7" s="415"/>
+      <c r="C7" s="415"/>
+      <c r="D7" s="415"/>
+      <c r="E7" s="352" t="s">
         <v>100</v>
       </c>
       <c r="F7" s="260" t="s">
@@ -18085,7 +18140,7 @@
       <c r="E8" s="251">
         <v>17.872320895864885</v>
       </c>
-      <c r="F8" s="421"/>
+      <c r="F8" s="347"/>
     </row>
     <row r="9" spans="2:10" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="113" t="s">
@@ -18100,7 +18155,7 @@
       <c r="E9" s="251">
         <v>16.273119463949694</v>
       </c>
-      <c r="F9" s="422"/>
+      <c r="F9" s="348"/>
     </row>
     <row r="10" spans="2:10" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="113" t="s">
@@ -18115,7 +18170,7 @@
       <c r="E10" s="251">
         <v>15.839276699251913</v>
       </c>
-      <c r="F10" s="422"/>
+      <c r="F10" s="348"/>
     </row>
     <row r="11" spans="2:10" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="113" t="s">
@@ -18130,7 +18185,7 @@
       <c r="E11" s="251">
         <v>10.87383542154298</v>
       </c>
-      <c r="F11" s="422"/>
+      <c r="F11" s="348"/>
     </row>
     <row r="12" spans="2:10" ht="19" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="113" t="s">
@@ -18143,11 +18198,11 @@
       <c r="E12" s="251">
         <v>5.2022121253843681</v>
       </c>
-      <c r="F12" s="422"/>
-      <c r="G12" s="393"/>
-      <c r="H12" s="393"/>
-      <c r="I12" s="393"/>
-      <c r="J12" s="393"/>
+      <c r="F12" s="348"/>
+      <c r="G12" s="411"/>
+      <c r="H12" s="411"/>
+      <c r="I12" s="411"/>
+      <c r="J12" s="411"/>
     </row>
     <row r="13" spans="2:10" ht="19" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="113" t="s">
@@ -18162,15 +18217,15 @@
       <c r="E13" s="251">
         <v>13.685896553306712</v>
       </c>
-      <c r="F13" s="422"/>
-      <c r="G13" s="393"/>
-      <c r="H13" s="393"/>
-      <c r="I13" s="393"/>
-      <c r="J13" s="393"/>
+      <c r="F13" s="348"/>
+      <c r="G13" s="411"/>
+      <c r="H13" s="411"/>
+      <c r="I13" s="411"/>
+      <c r="J13" s="411"/>
     </row>
     <row r="14" spans="2:10" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="113" t="s">
-        <v>1710</v>
+        <v>1708</v>
       </c>
       <c r="C14" s="113">
         <v>5.6</v>
@@ -18181,7 +18236,7 @@
       <c r="E14" s="251">
         <v>14.515581256597367</v>
       </c>
-      <c r="F14" s="422"/>
+      <c r="F14" s="348"/>
     </row>
     <row r="15" spans="2:10" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="113" t="s">
@@ -18196,7 +18251,7 @@
       <c r="E15" s="251">
         <v>28.702556335765752</v>
       </c>
-      <c r="F15" s="422"/>
+      <c r="F15" s="348"/>
     </row>
     <row r="16" spans="2:10" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="113" t="s">
@@ -18211,7 +18266,7 @@
       <c r="E16" s="251">
         <v>20.611547110927528</v>
       </c>
-      <c r="F16" s="422"/>
+      <c r="F16" s="348"/>
     </row>
     <row r="17" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="113" t="s">
@@ -18226,7 +18281,7 @@
       <c r="E17" s="251">
         <v>20.564046078296389</v>
       </c>
-      <c r="F17" s="422"/>
+      <c r="F17" s="348"/>
     </row>
     <row r="18" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="113" t="s">
@@ -18241,7 +18296,7 @@
       <c r="E18" s="251">
         <v>20.089035751984948</v>
       </c>
-      <c r="F18" s="422"/>
+      <c r="F18" s="348"/>
     </row>
     <row r="19" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="113" t="s">
@@ -18256,7 +18311,7 @@
       <c r="E19" s="251">
         <v>10.424158979301483</v>
       </c>
-      <c r="F19" s="422"/>
+      <c r="F19" s="348"/>
     </row>
     <row r="20" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="113" t="s">
@@ -18271,11 +18326,11 @@
       <c r="E20" s="251">
         <v>13.685896553306712</v>
       </c>
-      <c r="F20" s="422"/>
+      <c r="F20" s="348"/>
     </row>
     <row r="21" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="113" t="s">
-        <v>1635</v>
+        <v>1633</v>
       </c>
       <c r="C21" s="113">
         <v>5.6</v>
@@ -18286,7 +18341,7 @@
       <c r="E21" s="251">
         <v>13.685896553306712</v>
       </c>
-      <c r="F21" s="422"/>
+      <c r="F21" s="348"/>
     </row>
     <row r="22" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="113" t="s">
@@ -18301,7 +18356,7 @@
       <c r="E22" s="251">
         <v>16.076781862407636</v>
       </c>
-      <c r="F22" s="422"/>
+      <c r="F22" s="348"/>
     </row>
     <row r="23" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="113" t="s">
@@ -18316,7 +18371,7 @@
       <c r="E23" s="251">
         <v>8.5114507320207426</v>
       </c>
-      <c r="F23" s="422"/>
+      <c r="F23" s="348"/>
     </row>
     <row r="24" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="113" t="s">
@@ -18331,7 +18386,7 @@
       <c r="E24" s="251">
         <v>6.7729129377208688</v>
       </c>
-      <c r="F24" s="422"/>
+      <c r="F24" s="348"/>
     </row>
     <row r="25" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="113" t="s">
@@ -18346,7 +18401,7 @@
       <c r="E25" s="251">
         <v>10.424158979301483</v>
       </c>
-      <c r="F25" s="422"/>
+      <c r="F25" s="348"/>
     </row>
     <row r="26" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="113" t="s">
@@ -18361,7 +18416,7 @@
       <c r="E26" s="251">
         <v>10.424158979301483</v>
       </c>
-      <c r="F26" s="422"/>
+      <c r="F26" s="348"/>
     </row>
     <row r="27" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="113" t="s">
@@ -18376,7 +18431,7 @@
       <c r="E27" s="251">
         <v>15.877277525356831</v>
       </c>
-      <c r="F27" s="422"/>
+      <c r="F27" s="348"/>
     </row>
     <row r="28" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="113" t="s">
@@ -18389,7 +18444,7 @@
       <c r="E28" s="251">
         <v>5.5188856762586633</v>
       </c>
-      <c r="F28" s="422"/>
+      <c r="F28" s="348"/>
     </row>
     <row r="29" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="113" t="s">
@@ -18402,7 +18457,7 @@
       <c r="E29" s="251">
         <v>6.4150718252329142</v>
       </c>
-      <c r="F29" s="422"/>
+      <c r="F29" s="348"/>
     </row>
     <row r="30" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="113" t="s">
@@ -18415,7 +18470,7 @@
       <c r="E30" s="251">
         <v>6.3770709991280006</v>
       </c>
-      <c r="F30" s="422"/>
+      <c r="F30" s="348"/>
     </row>
     <row r="31" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="113" t="s">
@@ -18428,7 +18483,7 @@
       <c r="E31" s="251">
         <v>6.9407499196842437</v>
       </c>
-      <c r="F31" s="422"/>
+      <c r="F31" s="348"/>
     </row>
     <row r="32" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="113" t="s">
@@ -18443,7 +18498,7 @@
       <c r="E32" s="251">
         <v>16.064114920372663</v>
       </c>
-      <c r="F32" s="422"/>
+      <c r="F32" s="348"/>
     </row>
     <row r="33" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="113" t="s">
@@ -18456,11 +18511,11 @@
       <c r="E33" s="251">
         <v>5.2022121253843681</v>
       </c>
-      <c r="F33" s="422"/>
+      <c r="F33" s="348"/>
     </row>
     <row r="34" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="113" t="s">
-        <v>1686</v>
+        <v>1684</v>
       </c>
       <c r="C34" s="113">
         <v>9</v>
@@ -18471,11 +18526,11 @@
       <c r="E34" s="251">
         <v>7.168754876313737</v>
       </c>
-      <c r="F34" s="422"/>
+      <c r="F34" s="348"/>
     </row>
     <row r="35" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="113" t="s">
-        <v>1686</v>
+        <v>1684</v>
       </c>
       <c r="C35" s="113"/>
       <c r="D35" s="113" t="s">
@@ -18484,11 +18539,11 @@
       <c r="E35" s="251">
         <v>5.7437238973794118</v>
       </c>
-      <c r="F35" s="422"/>
+      <c r="F35" s="348"/>
     </row>
     <row r="36" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="113" t="s">
-        <v>1711</v>
+        <v>1709</v>
       </c>
       <c r="C36" s="113"/>
       <c r="D36" s="113" t="s">
@@ -18497,7 +18552,7 @@
       <c r="E36" s="251">
         <v>5.9020606728165594</v>
       </c>
-      <c r="F36" s="422"/>
+      <c r="F36" s="348"/>
     </row>
     <row r="37" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="113" t="s">
@@ -18510,7 +18565,7 @@
       <c r="E37" s="251">
         <v>6.8520813254394417</v>
       </c>
-      <c r="F37" s="422"/>
+      <c r="F37" s="348"/>
     </row>
     <row r="38" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="113" t="s">
@@ -18523,7 +18578,7 @@
       <c r="E38" s="251">
         <v>5.9400614989214739</v>
       </c>
-      <c r="F38" s="422"/>
+      <c r="F38" s="348"/>
     </row>
     <row r="39" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="113" t="s">
@@ -18538,7 +18593,7 @@
       <c r="E39" s="251">
         <v>8.8534581669649821</v>
       </c>
-      <c r="F39" s="422"/>
+      <c r="F39" s="348"/>
     </row>
     <row r="40" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="113" t="s">
@@ -18551,7 +18606,7 @@
       <c r="E40" s="251">
         <v>5.2022121253843681</v>
       </c>
-      <c r="F40" s="422"/>
+      <c r="F40" s="348"/>
     </row>
     <row r="41" spans="2:6" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B41" s="113" t="s">
@@ -18564,11 +18619,11 @@
       <c r="E41" s="251">
         <v>7.8971040433246138</v>
       </c>
-      <c r="F41" s="423"/>
+      <c r="F41" s="349"/>
     </row>
     <row r="42" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="113" t="s">
-        <v>1636</v>
+        <v>1634</v>
       </c>
       <c r="C42" s="113">
         <v>9</v>
@@ -18576,14 +18631,14 @@
       <c r="D42" s="113" t="s">
         <v>105</v>
       </c>
-      <c r="E42" s="319">
+      <c r="E42" s="317">
         <v>7.4854284271880305</v>
       </c>
-      <c r="F42" s="424"/>
+      <c r="F42" s="350"/>
     </row>
     <row r="43" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="113" t="s">
-        <v>1636</v>
+        <v>1634</v>
       </c>
       <c r="C43" s="113">
         <v>9</v>
@@ -18591,14 +18646,14 @@
       <c r="D43" s="113" t="s">
         <v>83</v>
       </c>
-      <c r="E43" s="319">
+      <c r="E43" s="317">
         <v>6.0603974482537062</v>
       </c>
-      <c r="F43" s="322"/>
+      <c r="F43" s="320"/>
     </row>
     <row r="44" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="113" t="s">
-        <v>1637</v>
+        <v>1635</v>
       </c>
       <c r="C44" s="113">
         <v>9</v>
@@ -18606,14 +18661,14 @@
       <c r="D44" s="113" t="s">
         <v>83</v>
       </c>
-      <c r="E44" s="319">
+      <c r="E44" s="317">
         <v>6.2187342236908529</v>
       </c>
-      <c r="F44" s="322"/>
+      <c r="F44" s="320"/>
     </row>
     <row r="45" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="113" t="s">
-        <v>1712</v>
+        <v>1710</v>
       </c>
       <c r="C45" s="113">
         <v>6.5</v>
@@ -18621,14 +18676,14 @@
       <c r="D45" s="113" t="s">
         <v>113</v>
       </c>
-      <c r="E45" s="319">
+      <c r="E45" s="317">
         <v>13.69</v>
       </c>
-      <c r="F45" s="322"/>
+      <c r="F45" s="320"/>
     </row>
     <row r="46" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="113" t="s">
-        <v>1638</v>
+        <v>1636</v>
       </c>
       <c r="C46" s="113">
         <v>9</v>
@@ -18636,14 +18691,14 @@
       <c r="D46" s="113" t="s">
         <v>105</v>
       </c>
-      <c r="E46" s="319">
+      <c r="E46" s="317">
         <v>7.4854284271880305</v>
       </c>
-      <c r="F46" s="424"/>
+      <c r="F46" s="350"/>
     </row>
     <row r="47" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="113" t="s">
-        <v>1638</v>
+        <v>1636</v>
       </c>
       <c r="C47" s="113">
         <v>9</v>
@@ -18651,14 +18706,14 @@
       <c r="D47" s="113" t="s">
         <v>83</v>
       </c>
-      <c r="E47" s="319">
+      <c r="E47" s="317">
         <v>6.0603974482537062</v>
       </c>
-      <c r="F47" s="425"/>
+      <c r="F47" s="351"/>
     </row>
     <row r="48" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B48" s="113" t="s">
-        <v>1639</v>
+        <v>1637</v>
       </c>
       <c r="C48" s="113">
         <v>9</v>
@@ -18666,10 +18721,10 @@
       <c r="D48" s="113" t="s">
         <v>83</v>
       </c>
-      <c r="E48" s="319">
+      <c r="E48" s="317">
         <v>6.2187342236908529</v>
       </c>
-      <c r="F48" s="425"/>
+      <c r="F48" s="351"/>
     </row>
     <row r="49" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="113" t="s">
@@ -18681,10 +18736,10 @@
       <c r="D49" s="113" t="s">
         <v>129</v>
       </c>
-      <c r="E49" s="319">
+      <c r="E49" s="317">
         <v>20.611547110927528</v>
       </c>
-      <c r="F49" s="425"/>
+      <c r="F49" s="351"/>
     </row>
     <row r="50" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B50" s="113" t="s">
@@ -18696,14 +18751,14 @@
       <c r="D50" s="113" t="s">
         <v>83</v>
       </c>
-      <c r="E50" s="319">
+      <c r="E50" s="317">
         <v>7.7862683005186106</v>
       </c>
-      <c r="F50" s="425"/>
+      <c r="F50" s="351"/>
     </row>
     <row r="51" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="113" t="s">
-        <v>1713</v>
+        <v>1711</v>
       </c>
       <c r="C51" s="113">
         <v>6.5</v>
@@ -18711,27 +18766,27 @@
       <c r="D51" s="113" t="s">
         <v>113</v>
       </c>
-      <c r="E51" s="319">
+      <c r="E51" s="317">
         <v>13.685896553306712</v>
       </c>
-      <c r="F51" s="425"/>
+      <c r="F51" s="351"/>
     </row>
     <row r="52" spans="2:6" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B52" s="252"/>
       <c r="C52" s="257"/>
       <c r="D52" s="256"/>
-      <c r="E52" s="318"/>
+      <c r="E52" s="316"/>
     </row>
     <row r="53" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="418" t="s">
+      <c r="B53" s="344" t="s">
         <v>1247</v>
       </c>
-      <c r="C53" s="428"/>
-      <c r="D53" s="419" t="s">
+      <c r="C53" s="353"/>
+      <c r="D53" s="345" t="s">
         <v>237</v>
       </c>
-      <c r="E53" s="429"/>
-      <c r="F53" s="430">
+      <c r="E53" s="354"/>
+      <c r="F53" s="355">
         <v>51.24</v>
       </c>
     </row>
@@ -18739,12 +18794,12 @@
       <c r="B54" s="115" t="s">
         <v>1248</v>
       </c>
-      <c r="C54" s="320"/>
+      <c r="C54" s="318"/>
       <c r="D54" s="121" t="s">
         <v>237</v>
       </c>
-      <c r="E54" s="319"/>
-      <c r="F54" s="431">
+      <c r="E54" s="317"/>
+      <c r="F54" s="356">
         <v>70.28</v>
       </c>
     </row>
@@ -18752,12 +18807,12 @@
       <c r="B55" s="116" t="s">
         <v>1249</v>
       </c>
-      <c r="C55" s="432"/>
-      <c r="D55" s="420" t="s">
+      <c r="C55" s="357"/>
+      <c r="D55" s="346" t="s">
         <v>2</v>
       </c>
-      <c r="E55" s="433"/>
-      <c r="F55" s="434">
+      <c r="E55" s="358"/>
+      <c r="F55" s="359">
         <v>16</v>
       </c>
     </row>
@@ -18838,11 +18893,11 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="349" t="s">
-        <v>1641</v>
-      </c>
-      <c r="C2" s="349"/>
-      <c r="D2" s="349"/>
+      <c r="B2" s="367" t="s">
+        <v>1639</v>
+      </c>
+      <c r="C2" s="367"/>
+      <c r="D2" s="367"/>
       <c r="E2" s="49"/>
       <c r="F2" s="49"/>
       <c r="G2" s="49"/>
@@ -18853,9 +18908,9 @@
       <c r="L2" s="49"/>
     </row>
     <row r="3" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="349"/>
-      <c r="C3" s="349"/>
-      <c r="D3" s="349"/>
+      <c r="B3" s="367"/>
+      <c r="C3" s="367"/>
+      <c r="D3" s="367"/>
       <c r="E3" s="49"/>
       <c r="F3" s="49"/>
       <c r="G3" s="49"/>
@@ -18867,15 +18922,15 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>1642</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="1:12" ht="20" x14ac:dyDescent="0.2">
-      <c r="B6" s="397" t="s">
+      <c r="B6" s="416" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="399" t="s">
+      <c r="C6" s="418" t="s">
         <v>0</v>
       </c>
       <c r="D6" s="50" t="s">
@@ -18883,8 +18938,8 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="20" x14ac:dyDescent="0.2">
-      <c r="B7" s="398"/>
-      <c r="C7" s="400"/>
+      <c r="B7" s="417"/>
+      <c r="C7" s="419"/>
       <c r="D7" s="132" t="s">
         <v>100</v>
       </c>
@@ -19022,36 +19077,36 @@
       <c r="K1" s="177"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" s="364" t="s">
-        <v>1643</v>
-      </c>
-      <c r="B2" s="364"/>
-      <c r="C2" s="364"/>
-      <c r="D2" s="364"/>
-      <c r="E2" s="364"/>
-      <c r="F2" s="364"/>
-      <c r="G2" s="364"/>
-      <c r="H2" s="364"/>
-      <c r="I2" s="364"/>
-      <c r="J2" s="364"/>
-      <c r="K2" s="364"/>
+      <c r="A2" s="382" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B2" s="382"/>
+      <c r="C2" s="382"/>
+      <c r="D2" s="382"/>
+      <c r="E2" s="382"/>
+      <c r="F2" s="382"/>
+      <c r="G2" s="382"/>
+      <c r="H2" s="382"/>
+      <c r="I2" s="382"/>
+      <c r="J2" s="382"/>
+      <c r="K2" s="382"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A3" s="364"/>
-      <c r="B3" s="364"/>
-      <c r="C3" s="364"/>
-      <c r="D3" s="364"/>
-      <c r="E3" s="364"/>
-      <c r="F3" s="364"/>
-      <c r="G3" s="364"/>
-      <c r="H3" s="364"/>
-      <c r="I3" s="364"/>
-      <c r="J3" s="364"/>
-      <c r="K3" s="364"/>
+      <c r="A3" s="382"/>
+      <c r="B3" s="382"/>
+      <c r="C3" s="382"/>
+      <c r="D3" s="382"/>
+      <c r="E3" s="382"/>
+      <c r="F3" s="382"/>
+      <c r="G3" s="382"/>
+      <c r="H3" s="382"/>
+      <c r="I3" s="382"/>
+      <c r="J3" s="382"/>
+      <c r="K3" s="382"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="177" t="s">
-        <v>1642</v>
+        <v>1640</v>
       </c>
       <c r="B4" s="177"/>
       <c r="C4" s="177"/>
@@ -19079,10 +19134,10 @@
     </row>
     <row r="6" spans="1:11" ht="20" x14ac:dyDescent="0.2">
       <c r="A6" s="13"/>
-      <c r="B6" s="360" t="s">
+      <c r="B6" s="378" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="362" t="s">
+      <c r="C6" s="380" t="s">
         <v>0</v>
       </c>
       <c r="D6" s="180" t="s">
@@ -19098,8 +19153,8 @@
     </row>
     <row r="7" spans="1:11" ht="20" x14ac:dyDescent="0.2">
       <c r="A7" s="13"/>
-      <c r="B7" s="361"/>
-      <c r="C7" s="363"/>
+      <c r="B7" s="379"/>
+      <c r="C7" s="381"/>
       <c r="D7" s="191" t="s">
         <v>100</v>
       </c>
@@ -19339,7 +19394,7 @@
     </row>
     <row r="22" spans="2:4" ht="21" x14ac:dyDescent="0.25">
       <c r="B22" s="130" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="C22" s="130" t="s">
         <v>105</v>
@@ -19350,7 +19405,7 @@
     </row>
     <row r="23" spans="2:4" ht="21" x14ac:dyDescent="0.25">
       <c r="B23" s="130" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="C23" s="130" t="s">
         <v>1191</v>
@@ -19361,7 +19416,7 @@
     </row>
     <row r="24" spans="2:4" ht="21" x14ac:dyDescent="0.25">
       <c r="B24" s="130" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="C24" s="130" t="s">
         <v>1191</v>
@@ -19372,7 +19427,7 @@
     </row>
     <row r="25" spans="2:4" ht="21" x14ac:dyDescent="0.25">
       <c r="B25" s="130" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="C25" s="130" t="s">
         <v>1195</v>
@@ -19402,49 +19457,49 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>1589</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="349" t="s">
-        <v>1592</v>
-      </c>
-      <c r="B2" s="349"/>
-      <c r="C2" s="349"/>
-      <c r="D2" s="349"/>
-      <c r="E2" s="349"/>
-      <c r="F2" s="349"/>
-      <c r="G2" s="349"/>
-      <c r="H2" s="349"/>
-      <c r="I2" s="349"/>
-      <c r="J2" s="349"/>
-      <c r="K2" s="349"/>
+      <c r="A2" s="367" t="s">
+        <v>1590</v>
+      </c>
+      <c r="B2" s="367"/>
+      <c r="C2" s="367"/>
+      <c r="D2" s="367"/>
+      <c r="E2" s="367"/>
+      <c r="F2" s="367"/>
+      <c r="G2" s="367"/>
+      <c r="H2" s="367"/>
+      <c r="I2" s="367"/>
+      <c r="J2" s="367"/>
+      <c r="K2" s="367"/>
     </row>
     <row r="3" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="349"/>
-      <c r="B3" s="349"/>
-      <c r="C3" s="349"/>
-      <c r="D3" s="349"/>
-      <c r="E3" s="349"/>
-      <c r="F3" s="349"/>
-      <c r="G3" s="349"/>
-      <c r="H3" s="349"/>
-      <c r="I3" s="349"/>
-      <c r="J3" s="349"/>
-      <c r="K3" s="349"/>
+      <c r="A3" s="367"/>
+      <c r="B3" s="367"/>
+      <c r="C3" s="367"/>
+      <c r="D3" s="367"/>
+      <c r="E3" s="367"/>
+      <c r="F3" s="367"/>
+      <c r="G3" s="367"/>
+      <c r="H3" s="367"/>
+      <c r="I3" s="367"/>
+      <c r="J3" s="367"/>
+      <c r="K3" s="367"/>
     </row>
     <row r="4" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="349"/>
-      <c r="B4" s="349"/>
-      <c r="C4" s="349"/>
-      <c r="D4" s="349"/>
-      <c r="E4" s="349"/>
-      <c r="F4" s="349"/>
-      <c r="G4" s="349"/>
-      <c r="H4" s="349"/>
-      <c r="I4" s="349"/>
-      <c r="J4" s="349"/>
-      <c r="K4" s="349"/>
+      <c r="A4" s="367"/>
+      <c r="B4" s="367"/>
+      <c r="C4" s="367"/>
+      <c r="D4" s="367"/>
+      <c r="E4" s="367"/>
+      <c r="F4" s="367"/>
+      <c r="G4" s="367"/>
+      <c r="H4" s="367"/>
+      <c r="I4" s="367"/>
+      <c r="J4" s="367"/>
+      <c r="K4" s="367"/>
     </row>
     <row r="5" spans="1:11" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A5" s="119"/>
@@ -19461,10 +19516,10 @@
     </row>
     <row r="6" spans="1:11" ht="20" x14ac:dyDescent="0.2">
       <c r="A6" s="13"/>
-      <c r="B6" s="351" t="s">
+      <c r="B6" s="369" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="353" t="s">
+      <c r="C6" s="371" t="s">
         <v>0</v>
       </c>
       <c r="D6" s="14" t="s">
@@ -19480,8 +19535,8 @@
     </row>
     <row r="7" spans="1:11" ht="20" x14ac:dyDescent="0.2">
       <c r="A7" s="13"/>
-      <c r="B7" s="352"/>
-      <c r="C7" s="354"/>
+      <c r="B7" s="370"/>
+      <c r="C7" s="372"/>
       <c r="D7" s="190" t="s">
         <v>100</v>
       </c>
@@ -19592,7 +19647,7 @@
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B20" t="s">
-        <v>1591</v>
+        <v>1589</v>
       </c>
     </row>
   </sheetData>
@@ -19627,32 +19682,32 @@
       <c r="K1" s="177"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" s="364" t="s">
+      <c r="A2" s="382" t="s">
         <v>1178</v>
       </c>
-      <c r="B2" s="364"/>
-      <c r="C2" s="364"/>
-      <c r="D2" s="364"/>
-      <c r="E2" s="364"/>
-      <c r="F2" s="364"/>
-      <c r="G2" s="364"/>
-      <c r="H2" s="364"/>
-      <c r="I2" s="364"/>
-      <c r="J2" s="364"/>
-      <c r="K2" s="364"/>
+      <c r="B2" s="382"/>
+      <c r="C2" s="382"/>
+      <c r="D2" s="382"/>
+      <c r="E2" s="382"/>
+      <c r="F2" s="382"/>
+      <c r="G2" s="382"/>
+      <c r="H2" s="382"/>
+      <c r="I2" s="382"/>
+      <c r="J2" s="382"/>
+      <c r="K2" s="382"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A3" s="364"/>
-      <c r="B3" s="364"/>
-      <c r="C3" s="364"/>
-      <c r="D3" s="364"/>
-      <c r="E3" s="364"/>
-      <c r="F3" s="364"/>
-      <c r="G3" s="364"/>
-      <c r="H3" s="364"/>
-      <c r="I3" s="364"/>
-      <c r="J3" s="364"/>
-      <c r="K3" s="364"/>
+      <c r="A3" s="382"/>
+      <c r="B3" s="382"/>
+      <c r="C3" s="382"/>
+      <c r="D3" s="382"/>
+      <c r="E3" s="382"/>
+      <c r="F3" s="382"/>
+      <c r="G3" s="382"/>
+      <c r="H3" s="382"/>
+      <c r="I3" s="382"/>
+      <c r="J3" s="382"/>
+      <c r="K3" s="382"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="177" t="s">
@@ -19684,10 +19739,10 @@
     </row>
     <row r="6" spans="1:11" ht="20" x14ac:dyDescent="0.2">
       <c r="A6" s="13"/>
-      <c r="B6" s="360" t="s">
+      <c r="B6" s="378" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="362" t="s">
+      <c r="C6" s="380" t="s">
         <v>0</v>
       </c>
       <c r="D6" s="180" t="s">
@@ -19703,8 +19758,8 @@
     </row>
     <row r="7" spans="1:11" ht="20" x14ac:dyDescent="0.2">
       <c r="A7" s="13"/>
-      <c r="B7" s="401"/>
-      <c r="C7" s="350"/>
+      <c r="B7" s="420"/>
+      <c r="C7" s="368"/>
       <c r="D7" s="181" t="s">
         <v>100</v>
       </c>
@@ -19902,7 +19957,7 @@
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60523296-FECD-B847-9FCE-E5185E1EC6B1}">
-  <dimension ref="A2:L11"/>
+  <dimension ref="A2:L12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="7.83203125" customWidth="1"/>
@@ -19911,45 +19966,45 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B2" s="392" t="s">
-        <v>1644</v>
-      </c>
-      <c r="C2" s="392"/>
-      <c r="D2" s="392"/>
-      <c r="E2" s="392"/>
-      <c r="F2" s="392"/>
-      <c r="G2" s="392"/>
-      <c r="H2" s="392"/>
-      <c r="I2" s="392"/>
-      <c r="J2" s="392"/>
-      <c r="K2" s="392"/>
-      <c r="L2" s="392"/>
+      <c r="B2" s="410" t="s">
+        <v>1642</v>
+      </c>
+      <c r="C2" s="410"/>
+      <c r="D2" s="410"/>
+      <c r="E2" s="410"/>
+      <c r="F2" s="410"/>
+      <c r="G2" s="410"/>
+      <c r="H2" s="410"/>
+      <c r="I2" s="410"/>
+      <c r="J2" s="410"/>
+      <c r="K2" s="410"/>
+      <c r="L2" s="410"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B3" s="392"/>
-      <c r="C3" s="392"/>
-      <c r="D3" s="392"/>
-      <c r="E3" s="392"/>
-      <c r="F3" s="392"/>
-      <c r="G3" s="392"/>
-      <c r="H3" s="392"/>
-      <c r="I3" s="392"/>
-      <c r="J3" s="392"/>
-      <c r="K3" s="392"/>
-      <c r="L3" s="392"/>
+      <c r="B3" s="410"/>
+      <c r="C3" s="410"/>
+      <c r="D3" s="410"/>
+      <c r="E3" s="410"/>
+      <c r="F3" s="410"/>
+      <c r="G3" s="410"/>
+      <c r="H3" s="410"/>
+      <c r="I3" s="410"/>
+      <c r="J3" s="410"/>
+      <c r="K3" s="410"/>
+      <c r="L3" s="410"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
-        <v>1589</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="20" x14ac:dyDescent="0.2">
       <c r="A6" s="9"/>
       <c r="B6" s="13"/>
-      <c r="C6" s="350" t="s">
+      <c r="C6" s="368" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="350" t="s">
+      <c r="D6" s="368" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="120" t="s">
@@ -19966,8 +20021,8 @@
     <row r="7" spans="1:12" ht="20" x14ac:dyDescent="0.2">
       <c r="A7" s="9"/>
       <c r="B7" s="13"/>
-      <c r="C7" s="350"/>
-      <c r="D7" s="350"/>
+      <c r="C7" s="368"/>
+      <c r="D7" s="368"/>
       <c r="E7" s="120" t="s">
         <v>100</v>
       </c>
@@ -20042,9 +20097,15 @@
     <row r="11" spans="1:12" ht="21" x14ac:dyDescent="0.25">
       <c r="A11" s="7"/>
       <c r="B11" s="7"/>
-      <c r="C11" s="121"/>
-      <c r="D11" s="121"/>
-      <c r="E11" s="130"/>
+      <c r="C11" s="121" t="s">
+        <v>1714</v>
+      </c>
+      <c r="D11" s="121" t="s">
+        <v>105</v>
+      </c>
+      <c r="E11" s="130">
+        <v>8.01</v>
+      </c>
       <c r="F11" s="7"/>
       <c r="G11" s="12"/>
       <c r="H11" s="7"/>
@@ -20052,6 +20113,17 @@
       <c r="J11" s="7"/>
       <c r="K11" s="7"/>
       <c r="L11" s="7"/>
+    </row>
+    <row r="12" spans="1:12" ht="21" x14ac:dyDescent="0.25">
+      <c r="C12" s="121" t="s">
+        <v>1715</v>
+      </c>
+      <c r="D12" s="121" t="s">
+        <v>105</v>
+      </c>
+      <c r="E12" s="130">
+        <v>8.33</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -20074,44 +20146,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A1" s="349" t="s">
-        <v>1684</v>
-      </c>
-      <c r="B1" s="349"/>
-      <c r="C1" s="349"/>
-      <c r="D1" s="349"/>
-      <c r="E1" s="349"/>
-      <c r="F1" s="349"/>
-      <c r="G1" s="349"/>
-      <c r="H1" s="349"/>
-      <c r="I1" s="349"/>
-      <c r="J1" s="349"/>
-      <c r="K1" s="349"/>
+      <c r="A1" s="367" t="s">
+        <v>1682</v>
+      </c>
+      <c r="B1" s="367"/>
+      <c r="C1" s="367"/>
+      <c r="D1" s="367"/>
+      <c r="E1" s="367"/>
+      <c r="F1" s="367"/>
+      <c r="G1" s="367"/>
+      <c r="H1" s="367"/>
+      <c r="I1" s="367"/>
+      <c r="J1" s="367"/>
+      <c r="K1" s="367"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" s="349"/>
-      <c r="B2" s="349"/>
-      <c r="C2" s="349"/>
-      <c r="D2" s="349"/>
-      <c r="E2" s="349"/>
-      <c r="F2" s="349"/>
-      <c r="G2" s="349"/>
-      <c r="H2" s="349"/>
-      <c r="I2" s="349"/>
-      <c r="J2" s="349"/>
-      <c r="K2" s="349"/>
+      <c r="A2" s="367"/>
+      <c r="B2" s="367"/>
+      <c r="C2" s="367"/>
+      <c r="D2" s="367"/>
+      <c r="E2" s="367"/>
+      <c r="F2" s="367"/>
+      <c r="G2" s="367"/>
+      <c r="H2" s="367"/>
+      <c r="I2" s="367"/>
+      <c r="J2" s="367"/>
+      <c r="K2" s="367"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>1672</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="20" x14ac:dyDescent="0.2">
       <c r="A5" s="13"/>
-      <c r="B5" s="350" t="s">
+      <c r="B5" s="368" t="s">
         <v>102</v>
       </c>
-      <c r="C5" s="350" t="s">
+      <c r="C5" s="368" t="s">
         <v>0</v>
       </c>
       <c r="D5" s="120" t="s">
@@ -20127,8 +20199,8 @@
     </row>
     <row r="6" spans="1:11" ht="20" x14ac:dyDescent="0.2">
       <c r="A6" s="13"/>
-      <c r="B6" s="350"/>
-      <c r="C6" s="350"/>
+      <c r="B6" s="368"/>
+      <c r="C6" s="368"/>
       <c r="D6" s="120" t="s">
         <v>100</v>
       </c>
@@ -20143,12 +20215,12 @@
     <row r="7" spans="1:11" ht="21" x14ac:dyDescent="0.25">
       <c r="A7" s="7"/>
       <c r="B7" s="285" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="C7" s="285" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="329">
+      <c r="D7" s="327">
         <v>5.949561705447703</v>
       </c>
       <c r="E7" s="7"/>
@@ -20162,12 +20234,12 @@
     <row r="8" spans="1:11" ht="21" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" s="285" t="s">
-        <v>1674</v>
+        <v>1672</v>
       </c>
       <c r="C8" s="285" t="s">
         <v>105</v>
       </c>
-      <c r="D8" s="329">
+      <c r="D8" s="327">
         <v>8.7521226306852071</v>
       </c>
       <c r="E8" s="1"/>
@@ -20176,12 +20248,12 @@
     <row r="9" spans="1:11" ht="21" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="285" t="s">
-        <v>1674</v>
+        <v>1672</v>
       </c>
       <c r="C9" s="285" t="s">
         <v>83</v>
       </c>
-      <c r="D9" s="329">
+      <c r="D9" s="327">
         <v>6.6145761622837211</v>
       </c>
       <c r="E9" s="1"/>
@@ -20189,122 +20261,122 @@
     </row>
     <row r="10" spans="1:11" ht="21" x14ac:dyDescent="0.25">
       <c r="B10" s="285" t="s">
-        <v>1675</v>
+        <v>1673</v>
       </c>
       <c r="C10" s="285" t="s">
         <v>1</v>
       </c>
-      <c r="D10" s="328">
+      <c r="D10" s="326">
         <v>5.7437238973794118</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="21" x14ac:dyDescent="0.25">
       <c r="B11" s="285" t="s">
-        <v>1676</v>
+        <v>1674</v>
       </c>
       <c r="C11" s="285" t="s">
         <v>1</v>
       </c>
-      <c r="D11" s="328">
+      <c r="D11" s="326">
         <v>5.7437238973794118</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="21" x14ac:dyDescent="0.25">
       <c r="B12" s="285" t="s">
-        <v>1677</v>
+        <v>1675</v>
       </c>
       <c r="C12" s="285" t="s">
         <v>105</v>
       </c>
-      <c r="D12" s="328">
+      <c r="D12" s="326">
         <v>7.0895864885951623</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="21" x14ac:dyDescent="0.25">
       <c r="B13" s="285" t="s">
-        <v>1677</v>
+        <v>1675</v>
       </c>
       <c r="C13" s="285" t="s">
         <v>83</v>
       </c>
-      <c r="D13" s="328">
+      <c r="D13" s="326">
         <v>5.5695534443985499</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="21" x14ac:dyDescent="0.25">
       <c r="B14" s="285" t="s">
-        <v>1678</v>
+        <v>1676</v>
       </c>
       <c r="C14" s="285" t="s">
         <v>105</v>
       </c>
-      <c r="D14" s="328">
+      <c r="D14" s="326">
         <v>8.5304511450732008</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="21" x14ac:dyDescent="0.25">
       <c r="B15" s="285" t="s">
-        <v>1678</v>
+        <v>1676</v>
       </c>
       <c r="C15" s="285" t="s">
         <v>83</v>
       </c>
-      <c r="D15" s="328">
+      <c r="D15" s="326">
         <v>6.6145761622837211</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="21" x14ac:dyDescent="0.25">
       <c r="B16" s="285" t="s">
-        <v>1679</v>
+        <v>1677</v>
       </c>
       <c r="C16" s="285" t="s">
         <v>83</v>
       </c>
-      <c r="D16" s="328">
+      <c r="D16" s="326">
         <v>6.6145761622837211</v>
       </c>
     </row>
     <row r="17" spans="2:4" ht="21" x14ac:dyDescent="0.25">
       <c r="B17" s="285" t="s">
-        <v>1680</v>
+        <v>1678</v>
       </c>
       <c r="C17" s="285" t="s">
         <v>1</v>
       </c>
-      <c r="D17" s="328">
+      <c r="D17" s="326">
         <v>5.7437238973794118</v>
       </c>
     </row>
     <row r="18" spans="2:4" ht="21" x14ac:dyDescent="0.25">
       <c r="B18" s="285" t="s">
-        <v>1681</v>
+        <v>1679</v>
       </c>
       <c r="C18" s="285" t="s">
         <v>83</v>
       </c>
-      <c r="D18" s="328">
+      <c r="D18" s="326">
         <v>6.6145761622837211</v>
       </c>
     </row>
     <row r="19" spans="2:4" ht="21" x14ac:dyDescent="0.25">
       <c r="B19" s="285" t="s">
-        <v>1682</v>
+        <v>1680</v>
       </c>
       <c r="C19" s="285" t="s">
         <v>83</v>
       </c>
-      <c r="D19" s="328">
+      <c r="D19" s="326">
         <v>5.5695534443985499</v>
       </c>
     </row>
     <row r="20" spans="2:4" ht="21" x14ac:dyDescent="0.25">
       <c r="B20" s="285" t="s">
-        <v>1683</v>
+        <v>1681</v>
       </c>
       <c r="C20" s="285" t="s">
         <v>83</v>
       </c>
-      <c r="D20" s="328">
+      <c r="D20" s="326">
         <v>5.5695534443985499</v>
       </c>
     </row>
@@ -20357,36 +20429,36 @@
       <c r="K1" s="177"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" s="364" t="s">
-        <v>1645</v>
-      </c>
-      <c r="B2" s="364"/>
-      <c r="C2" s="364"/>
-      <c r="D2" s="364"/>
-      <c r="E2" s="364"/>
-      <c r="F2" s="364"/>
-      <c r="G2" s="364"/>
-      <c r="H2" s="364"/>
-      <c r="I2" s="364"/>
-      <c r="J2" s="364"/>
-      <c r="K2" s="364"/>
+      <c r="A2" s="382" t="s">
+        <v>1643</v>
+      </c>
+      <c r="B2" s="382"/>
+      <c r="C2" s="382"/>
+      <c r="D2" s="382"/>
+      <c r="E2" s="382"/>
+      <c r="F2" s="382"/>
+      <c r="G2" s="382"/>
+      <c r="H2" s="382"/>
+      <c r="I2" s="382"/>
+      <c r="J2" s="382"/>
+      <c r="K2" s="382"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A3" s="364"/>
-      <c r="B3" s="364"/>
-      <c r="C3" s="364"/>
-      <c r="D3" s="364"/>
-      <c r="E3" s="364"/>
-      <c r="F3" s="364"/>
-      <c r="G3" s="364"/>
-      <c r="H3" s="364"/>
-      <c r="I3" s="364"/>
-      <c r="J3" s="364"/>
-      <c r="K3" s="364"/>
+      <c r="A3" s="382"/>
+      <c r="B3" s="382"/>
+      <c r="C3" s="382"/>
+      <c r="D3" s="382"/>
+      <c r="E3" s="382"/>
+      <c r="F3" s="382"/>
+      <c r="G3" s="382"/>
+      <c r="H3" s="382"/>
+      <c r="I3" s="382"/>
+      <c r="J3" s="382"/>
+      <c r="K3" s="382"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="177" t="s">
-        <v>1701</v>
+        <v>1699</v>
       </c>
       <c r="B4" s="177"/>
       <c r="C4" s="177"/>
@@ -20414,16 +20486,16 @@
     </row>
     <row r="6" spans="1:11" ht="20" x14ac:dyDescent="0.2">
       <c r="A6" s="13"/>
-      <c r="B6" s="350" t="s">
+      <c r="B6" s="368" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="350" t="s">
+      <c r="C6" s="368" t="s">
         <v>0</v>
       </c>
-      <c r="D6" s="290" t="s">
+      <c r="D6" s="288" t="s">
         <v>101</v>
       </c>
-      <c r="E6" s="341" t="s">
+      <c r="E6" s="339" t="s">
         <v>84</v>
       </c>
       <c r="F6" s="13"/>
@@ -20435,12 +20507,12 @@
     </row>
     <row r="7" spans="1:11" ht="20" x14ac:dyDescent="0.2">
       <c r="A7" s="13"/>
-      <c r="B7" s="350"/>
-      <c r="C7" s="350"/>
-      <c r="D7" s="290" t="s">
+      <c r="B7" s="368"/>
+      <c r="C7" s="368"/>
+      <c r="D7" s="288" t="s">
         <v>100</v>
       </c>
-      <c r="E7" s="341" t="s">
+      <c r="E7" s="339" t="s">
         <v>98</v>
       </c>
       <c r="F7" s="13"/>
@@ -20461,7 +20533,7 @@
       <c r="D8" s="202">
         <v>10.788241773371887</v>
       </c>
-      <c r="E8" s="342"/>
+      <c r="E8" s="340"/>
       <c r="F8" s="29"/>
       <c r="G8" s="28"/>
       <c r="H8" s="28"/>
@@ -20480,7 +20552,7 @@
       <c r="D9" s="202">
         <v>9.1098719537381267</v>
       </c>
-      <c r="E9" s="342"/>
+      <c r="E9" s="340"/>
       <c r="F9" s="29"/>
       <c r="G9" s="28"/>
       <c r="H9" s="28"/>
@@ -20499,7 +20571,7 @@
       <c r="D10" s="202">
         <v>10.202395704254439</v>
       </c>
-      <c r="E10" s="342"/>
+      <c r="E10" s="340"/>
       <c r="F10" s="29"/>
       <c r="G10" s="28"/>
       <c r="H10" s="28"/>
@@ -20518,7 +20590,7 @@
       <c r="D11" s="202">
         <v>20.46261875258158</v>
       </c>
-      <c r="E11" s="342"/>
+      <c r="E11" s="340"/>
       <c r="F11" s="29"/>
       <c r="G11" s="28"/>
       <c r="H11" s="28"/>
@@ -20537,7 +20609,7 @@
       <c r="D12" s="202">
         <v>14.477488641057414</v>
       </c>
-      <c r="E12" s="342"/>
+      <c r="E12" s="340"/>
       <c r="F12" s="29"/>
       <c r="G12" s="28"/>
       <c r="H12" s="28"/>
@@ -20556,7 +20628,7 @@
       <c r="D13" s="202">
         <v>12.102437009500207</v>
       </c>
-      <c r="E13" s="342"/>
+      <c r="E13" s="340"/>
       <c r="F13" s="29"/>
       <c r="G13" s="28"/>
       <c r="H13" s="28"/>
@@ -20575,7 +20647,7 @@
       <c r="D14" s="202">
         <v>10.202395704254439</v>
       </c>
-      <c r="E14" s="343"/>
+      <c r="E14" s="341"/>
       <c r="F14" s="6"/>
       <c r="G14" s="177"/>
       <c r="H14" s="177"/>
@@ -20586,7 +20658,7 @@
     <row r="15" spans="1:11" ht="21" x14ac:dyDescent="0.25">
       <c r="A15" s="179"/>
       <c r="B15" s="113" t="s">
-        <v>1685</v>
+        <v>1683</v>
       </c>
       <c r="C15" s="113" t="s">
         <v>113</v>
@@ -20594,7 +20666,7 @@
       <c r="D15" s="202">
         <v>14.477488641057414</v>
       </c>
-      <c r="E15" s="343"/>
+      <c r="E15" s="341"/>
       <c r="F15" s="6"/>
       <c r="G15" s="177"/>
       <c r="H15" s="177"/>
@@ -20604,7 +20676,7 @@
     </row>
     <row r="16" spans="1:11" ht="21" x14ac:dyDescent="0.25">
       <c r="B16" s="113" t="s">
-        <v>1693</v>
+        <v>1691</v>
       </c>
       <c r="C16" s="113" t="s">
         <v>105</v>
@@ -20616,7 +20688,7 @@
     </row>
     <row r="17" spans="2:5" ht="21" x14ac:dyDescent="0.25">
       <c r="B17" s="113" t="s">
-        <v>1693</v>
+        <v>1691</v>
       </c>
       <c r="C17" s="113" t="s">
         <v>83</v>
@@ -20628,7 +20700,7 @@
     </row>
     <row r="18" spans="2:5" ht="21" x14ac:dyDescent="0.25">
       <c r="B18" s="113" t="s">
-        <v>1694</v>
+        <v>1692</v>
       </c>
       <c r="C18" s="113" t="s">
         <v>83</v>
@@ -20700,7 +20772,7 @@
     </row>
     <row r="24" spans="2:5" ht="21" x14ac:dyDescent="0.25">
       <c r="B24" s="130" t="s">
-        <v>1708</v>
+        <v>1706</v>
       </c>
       <c r="C24" s="130" t="s">
         <v>83</v>
@@ -20712,7 +20784,7 @@
     </row>
     <row r="25" spans="2:5" ht="21" x14ac:dyDescent="0.25">
       <c r="B25" s="130" t="s">
-        <v>1709</v>
+        <v>1707</v>
       </c>
       <c r="C25" s="130" t="s">
         <v>1195</v>
@@ -20755,49 +20827,49 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>1589</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="349" t="s">
-        <v>1646</v>
-      </c>
-      <c r="B2" s="349"/>
-      <c r="C2" s="349"/>
-      <c r="D2" s="349"/>
-      <c r="E2" s="349"/>
-      <c r="F2" s="349"/>
-      <c r="G2" s="349"/>
-      <c r="H2" s="349"/>
-      <c r="I2" s="349"/>
-      <c r="J2" s="349"/>
-      <c r="K2" s="349"/>
+      <c r="A2" s="367" t="s">
+        <v>1644</v>
+      </c>
+      <c r="B2" s="367"/>
+      <c r="C2" s="367"/>
+      <c r="D2" s="367"/>
+      <c r="E2" s="367"/>
+      <c r="F2" s="367"/>
+      <c r="G2" s="367"/>
+      <c r="H2" s="367"/>
+      <c r="I2" s="367"/>
+      <c r="J2" s="367"/>
+      <c r="K2" s="367"/>
     </row>
     <row r="3" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="349"/>
-      <c r="B3" s="349"/>
-      <c r="C3" s="349"/>
-      <c r="D3" s="349"/>
-      <c r="E3" s="349"/>
-      <c r="F3" s="349"/>
-      <c r="G3" s="349"/>
-      <c r="H3" s="349"/>
-      <c r="I3" s="349"/>
-      <c r="J3" s="349"/>
-      <c r="K3" s="349"/>
+      <c r="A3" s="367"/>
+      <c r="B3" s="367"/>
+      <c r="C3" s="367"/>
+      <c r="D3" s="367"/>
+      <c r="E3" s="367"/>
+      <c r="F3" s="367"/>
+      <c r="G3" s="367"/>
+      <c r="H3" s="367"/>
+      <c r="I3" s="367"/>
+      <c r="J3" s="367"/>
+      <c r="K3" s="367"/>
     </row>
     <row r="4" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="349"/>
-      <c r="B4" s="349"/>
-      <c r="C4" s="349"/>
-      <c r="D4" s="349"/>
-      <c r="E4" s="349"/>
-      <c r="F4" s="349"/>
-      <c r="G4" s="349"/>
-      <c r="H4" s="349"/>
-      <c r="I4" s="349"/>
-      <c r="J4" s="349"/>
-      <c r="K4" s="349"/>
+      <c r="A4" s="367"/>
+      <c r="B4" s="367"/>
+      <c r="C4" s="367"/>
+      <c r="D4" s="367"/>
+      <c r="E4" s="367"/>
+      <c r="F4" s="367"/>
+      <c r="G4" s="367"/>
+      <c r="H4" s="367"/>
+      <c r="I4" s="367"/>
+      <c r="J4" s="367"/>
+      <c r="K4" s="367"/>
     </row>
     <row r="5" spans="1:11" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A5" s="119"/>
@@ -20814,13 +20886,13 @@
     </row>
     <row r="6" spans="1:11" ht="20" x14ac:dyDescent="0.2">
       <c r="A6" s="13"/>
-      <c r="B6" s="351" t="s">
+      <c r="B6" s="378" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="353" t="s">
+      <c r="C6" s="380" t="s">
         <v>0</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="138" t="s">
         <v>84</v>
       </c>
       <c r="E6" s="13"/>
@@ -20833,9 +20905,9 @@
     </row>
     <row r="7" spans="1:11" ht="20" x14ac:dyDescent="0.2">
       <c r="A7" s="13"/>
-      <c r="B7" s="352"/>
-      <c r="C7" s="354"/>
-      <c r="D7" s="190" t="s">
+      <c r="B7" s="420"/>
+      <c r="C7" s="368"/>
+      <c r="D7" s="363" t="s">
         <v>100</v>
       </c>
       <c r="E7" s="13"/>
@@ -20848,13 +20920,13 @@
     </row>
     <row r="8" spans="1:11" ht="21" x14ac:dyDescent="0.25">
       <c r="A8" s="7"/>
-      <c r="B8" s="113" t="s">
+      <c r="B8" s="261" t="s">
         <v>1084</v>
       </c>
-      <c r="C8" s="113" t="s">
+      <c r="C8" s="130" t="s">
         <v>899</v>
       </c>
-      <c r="D8" s="202">
+      <c r="D8" s="207">
         <v>10.091091835329749</v>
       </c>
       <c r="E8" s="7"/>
@@ -20867,14 +20939,14 @@
     </row>
     <row r="9" spans="1:11" ht="21" x14ac:dyDescent="0.25">
       <c r="A9" s="7"/>
-      <c r="B9" s="113" t="s">
-        <v>1085</v>
-      </c>
-      <c r="C9" s="113" t="s">
-        <v>876</v>
-      </c>
-      <c r="D9" s="202">
-        <v>12.327123778053142</v>
+      <c r="B9" s="261" t="s">
+        <v>1255</v>
+      </c>
+      <c r="C9" s="130" t="s">
+        <v>895</v>
+      </c>
+      <c r="D9" s="207">
+        <v>18.11021616411951</v>
       </c>
       <c r="E9" s="7"/>
       <c r="F9" s="12"/>
@@ -20886,14 +20958,14 @@
     </row>
     <row r="10" spans="1:11" ht="21" x14ac:dyDescent="0.25">
       <c r="A10" s="7"/>
-      <c r="B10" s="113" t="s">
-        <v>1086</v>
-      </c>
-      <c r="C10" s="113" t="s">
-        <v>1087</v>
-      </c>
-      <c r="D10" s="202">
-        <v>9.3408921933085498</v>
+      <c r="B10" s="261" t="s">
+        <v>1251</v>
+      </c>
+      <c r="C10" s="130" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D10" s="207">
+        <v>12.283422828032494</v>
       </c>
       <c r="E10" s="7"/>
       <c r="F10" s="12"/>
@@ -20904,117 +20976,125 @@
       <c r="K10" s="7"/>
     </row>
     <row r="11" spans="1:11" ht="21" x14ac:dyDescent="0.25">
-      <c r="B11" s="113" t="s">
+      <c r="B11" s="261" t="s">
+        <v>1250</v>
+      </c>
+      <c r="C11" s="130" t="s">
+        <v>1137</v>
+      </c>
+      <c r="D11" s="207">
+        <v>14.04966955803387</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="21" x14ac:dyDescent="0.25">
+      <c r="B12" s="261" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C12" s="130" t="s">
+        <v>876</v>
+      </c>
+      <c r="D12" s="207">
+        <v>12.327123778053142</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="21" x14ac:dyDescent="0.25">
+      <c r="B13" s="261" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C13" s="130" t="s">
+        <v>1087</v>
+      </c>
+      <c r="D13" s="207">
+        <v>9.3408921933085498</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="21" x14ac:dyDescent="0.25">
+      <c r="B14" s="261" t="s">
         <v>1088</v>
       </c>
-      <c r="C11" s="113" t="s">
+      <c r="C14" s="130" t="s">
         <v>871</v>
       </c>
-      <c r="D11" s="202">
+      <c r="D14" s="207">
         <v>9.9927646977832829</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="21" x14ac:dyDescent="0.25">
-      <c r="B12" s="113" t="s">
+    <row r="15" spans="1:11" ht="21" x14ac:dyDescent="0.25">
+      <c r="B15" s="261" t="s">
         <v>1089</v>
       </c>
-      <c r="C12" s="113" t="s">
+      <c r="C15" s="130" t="s">
         <v>871</v>
       </c>
-      <c r="D12" s="202">
+      <c r="D15" s="207">
         <v>11.431254302629767</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="21" x14ac:dyDescent="0.25">
-      <c r="B13" s="113" t="s">
+    <row r="16" spans="1:11" ht="21" x14ac:dyDescent="0.25">
+      <c r="B16" s="261" t="s">
         <v>1090</v>
       </c>
-      <c r="C13" s="113" t="s">
+      <c r="C16" s="130" t="s">
         <v>1087</v>
       </c>
-      <c r="D13" s="202">
+      <c r="D16" s="207">
         <v>12.429092661434664</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="21" x14ac:dyDescent="0.25">
-      <c r="B14" s="113" t="s">
+    <row r="17" spans="2:4" ht="21" x14ac:dyDescent="0.25">
+      <c r="B17" s="261" t="s">
         <v>1091</v>
       </c>
-      <c r="C14" s="113" t="s">
+      <c r="C17" s="130" t="s">
         <v>899</v>
       </c>
-      <c r="D14" s="202">
+      <c r="D17" s="207">
         <v>12.429092661434664</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="21" x14ac:dyDescent="0.25">
-      <c r="B15" s="113" t="s">
+    <row r="18" spans="2:4" ht="21" x14ac:dyDescent="0.25">
+      <c r="B18" s="261" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C18" s="130" t="s">
+        <v>895</v>
+      </c>
+      <c r="D18" s="207">
+        <v>13.885790995456425</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" ht="21" x14ac:dyDescent="0.25">
+      <c r="B19" s="261" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C19" s="130" t="s">
+        <v>895</v>
+      </c>
+      <c r="D19" s="207">
+        <v>15.37890678782872</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" ht="21" x14ac:dyDescent="0.25">
+      <c r="B20" s="261" t="s">
         <v>1092</v>
       </c>
-      <c r="C15" s="113" t="s">
+      <c r="C20" s="130" t="s">
         <v>1093</v>
       </c>
-      <c r="D15" s="202">
+      <c r="D20" s="207">
         <v>18.314153930882551</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="21" x14ac:dyDescent="0.25">
-      <c r="B16" s="113" t="s">
-        <v>1250</v>
-      </c>
-      <c r="C16" s="113" t="s">
-        <v>1137</v>
-      </c>
-      <c r="D16" s="220">
-        <v>14.04966955803387</v>
-      </c>
-    </row>
-    <row r="17" spans="2:4" ht="21" x14ac:dyDescent="0.25">
-      <c r="B17" s="113" t="s">
-        <v>1251</v>
-      </c>
-      <c r="C17" s="113" t="s">
-        <v>1252</v>
-      </c>
-      <c r="D17" s="220">
-        <v>12.283422828032494</v>
-      </c>
-    </row>
-    <row r="18" spans="2:4" ht="21" x14ac:dyDescent="0.25">
-      <c r="B18" s="113" t="s">
-        <v>1253</v>
-      </c>
-      <c r="C18" s="113" t="s">
-        <v>895</v>
-      </c>
-      <c r="D18" s="220">
-        <v>13.885790995456425</v>
-      </c>
-    </row>
-    <row r="19" spans="2:4" ht="21" x14ac:dyDescent="0.25">
-      <c r="B19" s="113" t="s">
-        <v>1254</v>
-      </c>
-      <c r="C19" s="113" t="s">
-        <v>895</v>
-      </c>
-      <c r="D19" s="220">
-        <v>15.37890678782872</v>
-      </c>
-    </row>
-    <row r="20" spans="2:4" ht="21" x14ac:dyDescent="0.25">
-      <c r="B20" s="113" t="s">
-        <v>1255</v>
-      </c>
-      <c r="C20" s="113" t="s">
-        <v>895</v>
-      </c>
-      <c r="D20" s="220">
-        <v>18.11021616411951</v>
-      </c>
-    </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="D21" s="147"/>
+    <row r="21" spans="2:4" ht="22" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="262" t="s">
+        <v>1716</v>
+      </c>
+      <c r="C21" s="224" t="s">
+        <v>906</v>
+      </c>
+      <c r="D21" s="208">
+        <v>18.314153930882551</v>
+      </c>
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.2">
       <c r="D22" s="147"/>
@@ -21050,43 +21130,43 @@
   <sheetData>
     <row r="1" spans="2:11" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:11" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="349" t="s">
-        <v>1647</v>
-      </c>
-      <c r="C2" s="349"/>
-      <c r="D2" s="349"/>
-      <c r="E2" s="349"/>
-      <c r="F2" s="349"/>
-      <c r="G2" s="349"/>
-      <c r="H2" s="349"/>
-      <c r="I2" s="349"/>
-      <c r="J2" s="349"/>
-      <c r="K2" s="349"/>
+      <c r="B2" s="367" t="s">
+        <v>1645</v>
+      </c>
+      <c r="C2" s="367"/>
+      <c r="D2" s="367"/>
+      <c r="E2" s="367"/>
+      <c r="F2" s="367"/>
+      <c r="G2" s="367"/>
+      <c r="H2" s="367"/>
+      <c r="I2" s="367"/>
+      <c r="J2" s="367"/>
+      <c r="K2" s="367"/>
     </row>
     <row r="3" spans="2:11" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="349"/>
-      <c r="C3" s="349"/>
-      <c r="D3" s="349"/>
-      <c r="E3" s="349"/>
-      <c r="F3" s="349"/>
-      <c r="G3" s="349"/>
-      <c r="H3" s="349"/>
-      <c r="I3" s="349"/>
-      <c r="J3" s="349"/>
-      <c r="K3" s="349"/>
+      <c r="B3" s="367"/>
+      <c r="C3" s="367"/>
+      <c r="D3" s="367"/>
+      <c r="E3" s="367"/>
+      <c r="F3" s="367"/>
+      <c r="G3" s="367"/>
+      <c r="H3" s="367"/>
+      <c r="I3" s="367"/>
+      <c r="J3" s="367"/>
+      <c r="K3" s="367"/>
     </row>
     <row r="4" spans="2:11" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
-        <v>1642</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="5" spans="2:11" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="2:11" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="13"/>
-      <c r="C6" s="353" t="s">
+      <c r="C6" s="371" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="353" t="s">
+      <c r="D6" s="371" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="8" t="s">
@@ -21097,8 +21177,8 @@
     </row>
     <row r="7" spans="2:11" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="13"/>
-      <c r="C7" s="354"/>
-      <c r="D7" s="354"/>
+      <c r="C7" s="372"/>
+      <c r="D7" s="372"/>
       <c r="E7" s="16" t="s">
         <v>100</v>
       </c>
@@ -21489,46 +21569,46 @@
   <sheetData>
     <row r="1" spans="2:11" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:11" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="349" t="s">
-        <v>1588</v>
-      </c>
-      <c r="C2" s="349"/>
-      <c r="D2" s="349"/>
-      <c r="E2" s="349"/>
-      <c r="F2" s="349"/>
-      <c r="G2" s="349"/>
-      <c r="H2" s="349"/>
-      <c r="I2" s="349"/>
-      <c r="J2" s="349"/>
-      <c r="K2" s="349"/>
+      <c r="B2" s="367" t="s">
+        <v>1586</v>
+      </c>
+      <c r="C2" s="367"/>
+      <c r="D2" s="367"/>
+      <c r="E2" s="367"/>
+      <c r="F2" s="367"/>
+      <c r="G2" s="367"/>
+      <c r="H2" s="367"/>
+      <c r="I2" s="367"/>
+      <c r="J2" s="367"/>
+      <c r="K2" s="367"/>
     </row>
     <row r="3" spans="2:11" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="349"/>
-      <c r="C3" s="349"/>
-      <c r="D3" s="349"/>
-      <c r="E3" s="349"/>
-      <c r="F3" s="349"/>
-      <c r="G3" s="349"/>
-      <c r="H3" s="349"/>
-      <c r="I3" s="349"/>
-      <c r="J3" s="349"/>
-      <c r="K3" s="349"/>
+      <c r="B3" s="367"/>
+      <c r="C3" s="367"/>
+      <c r="D3" s="367"/>
+      <c r="E3" s="367"/>
+      <c r="F3" s="367"/>
+      <c r="G3" s="367"/>
+      <c r="H3" s="367"/>
+      <c r="I3" s="367"/>
+      <c r="J3" s="367"/>
+      <c r="K3" s="367"/>
     </row>
     <row r="4" spans="2:11" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="2:11" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>1589</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="6" spans="2:11" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="13"/>
-      <c r="C6" s="353" t="s">
+      <c r="C6" s="371" t="s">
         <v>102</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>412</v>
       </c>
-      <c r="E6" s="353" t="s">
+      <c r="E6" s="371" t="s">
         <v>0</v>
       </c>
       <c r="F6" s="8" t="s">
@@ -21539,11 +21619,11 @@
     </row>
     <row r="7" spans="2:11" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="13"/>
-      <c r="C7" s="354"/>
+      <c r="C7" s="372"/>
       <c r="D7" s="16" t="s">
-        <v>1581</v>
-      </c>
-      <c r="E7" s="354"/>
+        <v>1579</v>
+      </c>
+      <c r="E7" s="372"/>
       <c r="F7" s="16" t="s">
         <v>100</v>
       </c>
@@ -21551,46 +21631,46 @@
       <c r="H7" s="13"/>
     </row>
     <row r="8" spans="2:11" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C8" s="307" t="s">
+      <c r="C8" s="305" t="s">
+        <v>1580</v>
+      </c>
+      <c r="D8" s="305" t="s">
+        <v>1581</v>
+      </c>
+      <c r="E8" s="121" t="s">
         <v>1582</v>
       </c>
-      <c r="D8" s="307" t="s">
+      <c r="F8" s="306">
+        <v>13.05</v>
+      </c>
+      <c r="H8" s="12"/>
+    </row>
+    <row r="9" spans="2:11" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C9" s="305" t="s">
+        <v>1580</v>
+      </c>
+      <c r="D9" s="305" t="s">
+        <v>1581</v>
+      </c>
+      <c r="E9" s="121" t="s">
         <v>1583</v>
       </c>
-      <c r="E8" s="121" t="s">
-        <v>1584</v>
-      </c>
-      <c r="F8" s="308">
-        <v>13.05</v>
-      </c>
-      <c r="H8" s="12"/>
-    </row>
-    <row r="9" spans="2:11" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C9" s="307" t="s">
-        <v>1582</v>
-      </c>
-      <c r="D9" s="307" t="s">
-        <v>1583</v>
-      </c>
-      <c r="E9" s="121" t="s">
-        <v>1585</v>
-      </c>
-      <c r="F9" s="308">
+      <c r="F9" s="306">
         <v>15.25</v>
       </c>
       <c r="H9" s="12"/>
     </row>
     <row r="10" spans="2:11" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C10" s="121" t="s">
-        <v>1582</v>
+        <v>1580</v>
       </c>
       <c r="D10" s="121" t="s">
-        <v>1586</v>
+        <v>1584</v>
       </c>
       <c r="E10" s="121" t="s">
-        <v>1587</v>
-      </c>
-      <c r="F10" s="308">
+        <v>1585</v>
+      </c>
+      <c r="F10" s="306">
         <v>26.79</v>
       </c>
       <c r="H10" s="12"/>
@@ -21600,7 +21680,7 @@
       <c r="D11" s="113"/>
       <c r="E11" s="113"/>
       <c r="F11" s="264" t="s">
-        <v>1591</v>
+        <v>1589</v>
       </c>
       <c r="H11" s="12"/>
     </row>
@@ -21759,41 +21839,41 @@
   <sheetData>
     <row r="1" spans="2:10" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:10" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="349" t="s">
-        <v>1670</v>
-      </c>
-      <c r="C2" s="349"/>
-      <c r="D2" s="349"/>
-      <c r="E2" s="349"/>
-      <c r="F2" s="349"/>
-      <c r="G2" s="349"/>
-      <c r="H2" s="349"/>
-      <c r="I2" s="349"/>
-      <c r="J2" s="349"/>
+      <c r="B2" s="367" t="s">
+        <v>1668</v>
+      </c>
+      <c r="C2" s="367"/>
+      <c r="D2" s="367"/>
+      <c r="E2" s="367"/>
+      <c r="F2" s="367"/>
+      <c r="G2" s="367"/>
+      <c r="H2" s="367"/>
+      <c r="I2" s="367"/>
+      <c r="J2" s="367"/>
     </row>
     <row r="3" spans="2:10" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="349"/>
-      <c r="C3" s="349"/>
-      <c r="D3" s="349"/>
-      <c r="E3" s="349"/>
-      <c r="F3" s="349"/>
-      <c r="G3" s="349"/>
-      <c r="H3" s="349"/>
-      <c r="I3" s="349"/>
-      <c r="J3" s="349"/>
+      <c r="B3" s="367"/>
+      <c r="C3" s="367"/>
+      <c r="D3" s="367"/>
+      <c r="E3" s="367"/>
+      <c r="F3" s="367"/>
+      <c r="G3" s="367"/>
+      <c r="H3" s="367"/>
+      <c r="I3" s="367"/>
+      <c r="J3" s="367"/>
     </row>
     <row r="4" spans="2:10" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="2:10" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>1589</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="6" spans="2:10" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="13"/>
-      <c r="C6" s="353" t="s">
+      <c r="C6" s="371" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="353" t="s">
+      <c r="D6" s="371" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="8" t="s">
@@ -21804,8 +21884,8 @@
     </row>
     <row r="7" spans="2:10" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="13"/>
-      <c r="C7" s="354"/>
-      <c r="D7" s="354"/>
+      <c r="C7" s="372"/>
+      <c r="D7" s="372"/>
       <c r="E7" s="16" t="s">
         <v>100</v>
       </c>
@@ -22117,7 +22197,7 @@
     <row r="32" spans="2:7" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="1"/>
       <c r="C32" s="113" t="s">
-        <v>1667</v>
+        <v>1665</v>
       </c>
       <c r="D32" s="113" t="s">
         <v>105</v>
@@ -22131,7 +22211,7 @@
     <row r="33" spans="2:7" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="1"/>
       <c r="C33" s="113" t="s">
-        <v>1667</v>
+        <v>1665</v>
       </c>
       <c r="D33" s="113" t="s">
         <v>83</v>
@@ -22159,7 +22239,7 @@
     <row r="35" spans="2:7" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="1"/>
       <c r="C35" s="113" t="s">
-        <v>1668</v>
+        <v>1666</v>
       </c>
       <c r="D35" s="113" t="s">
         <v>114</v>
@@ -22187,7 +22267,7 @@
     <row r="37" spans="2:7" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="1"/>
       <c r="C37" s="113" t="s">
-        <v>1669</v>
+        <v>1667</v>
       </c>
       <c r="D37" s="113" t="s">
         <v>83</v>
@@ -22332,41 +22412,41 @@
   <sheetData>
     <row r="1" spans="2:10" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:10" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="349" t="s">
-        <v>1648</v>
-      </c>
-      <c r="C2" s="349"/>
-      <c r="D2" s="349"/>
-      <c r="E2" s="349"/>
-      <c r="F2" s="349"/>
-      <c r="G2" s="349"/>
-      <c r="H2" s="349"/>
-      <c r="I2" s="349"/>
-      <c r="J2" s="349"/>
+      <c r="B2" s="367" t="s">
+        <v>1646</v>
+      </c>
+      <c r="C2" s="367"/>
+      <c r="D2" s="367"/>
+      <c r="E2" s="367"/>
+      <c r="F2" s="367"/>
+      <c r="G2" s="367"/>
+      <c r="H2" s="367"/>
+      <c r="I2" s="367"/>
+      <c r="J2" s="367"/>
     </row>
     <row r="3" spans="2:10" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="349"/>
-      <c r="C3" s="349"/>
-      <c r="D3" s="349"/>
-      <c r="E3" s="349"/>
-      <c r="F3" s="349"/>
-      <c r="G3" s="349"/>
-      <c r="H3" s="349"/>
-      <c r="I3" s="349"/>
-      <c r="J3" s="349"/>
+      <c r="B3" s="367"/>
+      <c r="C3" s="367"/>
+      <c r="D3" s="367"/>
+      <c r="E3" s="367"/>
+      <c r="F3" s="367"/>
+      <c r="G3" s="367"/>
+      <c r="H3" s="367"/>
+      <c r="I3" s="367"/>
+      <c r="J3" s="367"/>
     </row>
     <row r="4" spans="2:10" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="2:10" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
-        <v>1589</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="6" spans="2:10" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="13"/>
-      <c r="C6" s="350" t="s">
+      <c r="C6" s="368" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="350" t="s">
+      <c r="D6" s="368" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="120" t="s">
@@ -22379,8 +22459,8 @@
     </row>
     <row r="7" spans="2:10" s="9" customFormat="1" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B7" s="13"/>
-      <c r="C7" s="363"/>
-      <c r="D7" s="363"/>
+      <c r="C7" s="381"/>
+      <c r="D7" s="381"/>
       <c r="E7" s="157" t="s">
         <v>100</v>
       </c>
@@ -22396,7 +22476,7 @@
       <c r="D8" s="240" t="s">
         <v>1087</v>
       </c>
-      <c r="E8" s="286">
+      <c r="E8" s="362">
         <v>13.939235394006149</v>
       </c>
       <c r="F8" s="266"/>
@@ -22409,7 +22489,7 @@
       <c r="D9" s="113" t="s">
         <v>1258</v>
       </c>
-      <c r="E9" s="287">
+      <c r="E9" s="360">
         <v>23.695947496443154</v>
       </c>
       <c r="F9" s="245"/>
@@ -22422,7 +22502,7 @@
       <c r="D10" s="113" t="s">
         <v>906</v>
       </c>
-      <c r="E10" s="287">
+      <c r="E10" s="360">
         <v>16.377621735738217</v>
       </c>
       <c r="F10" s="245"/>
@@ -22435,7 +22515,7 @@
       <c r="D11" s="113" t="s">
         <v>906</v>
       </c>
-      <c r="E11" s="287">
+      <c r="E11" s="360">
         <v>20.953554545871764</v>
       </c>
       <c r="F11" s="245"/>
@@ -22448,7 +22528,7 @@
       <c r="D12" s="113" t="s">
         <v>936</v>
       </c>
-      <c r="E12" s="287">
+      <c r="E12" s="360">
         <v>17.055303134609204</v>
       </c>
       <c r="F12" s="245"/>
@@ -22461,7 +22541,7 @@
       <c r="D13" s="113" t="s">
         <v>906</v>
       </c>
-      <c r="E13" s="287">
+      <c r="E13" s="360">
         <v>17.055303134609204</v>
       </c>
       <c r="F13" s="245"/>
@@ -22474,7 +22554,7 @@
       <c r="D14" s="113" t="s">
         <v>906</v>
       </c>
-      <c r="E14" s="287">
+      <c r="E14" s="360">
         <v>20.36770847675432</v>
       </c>
       <c r="F14" s="245"/>
@@ -22487,7 +22567,7 @@
       <c r="D15" s="113" t="s">
         <v>1087</v>
       </c>
-      <c r="E15" s="287">
+      <c r="E15" s="360">
         <v>13.939235394006149</v>
       </c>
       <c r="F15" s="245"/>
@@ -22500,7 +22580,7 @@
       <c r="D16" s="113" t="s">
         <v>895</v>
       </c>
-      <c r="E16" s="287">
+      <c r="E16" s="360">
         <v>17.055303134609204</v>
       </c>
       <c r="F16" s="245"/>
@@ -22513,7 +22593,7 @@
       <c r="D17" s="113" t="s">
         <v>1265</v>
       </c>
-      <c r="E17" s="287">
+      <c r="E17" s="360">
         <v>17.055303134609204</v>
       </c>
       <c r="F17" s="245"/>
@@ -22526,7 +22606,7 @@
       <c r="D18" s="113" t="s">
         <v>1203</v>
       </c>
-      <c r="E18" s="225">
+      <c r="E18" s="360">
         <v>20.36770847675432</v>
       </c>
       <c r="F18" s="245"/>
@@ -22539,7 +22619,7 @@
       <c r="D19" s="141" t="s">
         <v>1203</v>
       </c>
-      <c r="E19" s="267">
+      <c r="E19" s="361">
         <v>23.189269815044288</v>
       </c>
       <c r="F19" s="268"/>
@@ -22552,8 +22632,8 @@
       <c r="D20" s="265" t="s">
         <v>895</v>
       </c>
-      <c r="E20" s="296"/>
-      <c r="F20" s="297">
+      <c r="E20" s="294"/>
+      <c r="F20" s="295">
         <v>6.13</v>
       </c>
       <c r="G20" s="12"/>
@@ -22578,6 +22658,9 @@
     <row r="23" spans="2:7" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="1"/>
       <c r="C23" s="2"/>
+      <c r="E23" t="s">
+        <v>1589</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -22605,50 +22688,50 @@
   <sheetData>
     <row r="1" spans="2:13" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:13" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="349" t="s">
-        <v>1649</v>
-      </c>
-      <c r="C2" s="349"/>
-      <c r="D2" s="349"/>
-      <c r="E2" s="349"/>
-      <c r="F2" s="349"/>
-      <c r="G2" s="349"/>
-      <c r="H2" s="349"/>
-      <c r="I2" s="349"/>
-      <c r="J2" s="349"/>
-      <c r="K2" s="349"/>
-      <c r="L2" s="349"/>
-      <c r="M2" s="349"/>
+      <c r="B2" s="367" t="s">
+        <v>1647</v>
+      </c>
+      <c r="C2" s="367"/>
+      <c r="D2" s="367"/>
+      <c r="E2" s="367"/>
+      <c r="F2" s="367"/>
+      <c r="G2" s="367"/>
+      <c r="H2" s="367"/>
+      <c r="I2" s="367"/>
+      <c r="J2" s="367"/>
+      <c r="K2" s="367"/>
+      <c r="L2" s="367"/>
+      <c r="M2" s="367"/>
     </row>
     <row r="3" spans="2:13" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="349"/>
-      <c r="C3" s="349"/>
-      <c r="D3" s="349"/>
-      <c r="E3" s="349"/>
-      <c r="F3" s="349"/>
-      <c r="G3" s="349"/>
-      <c r="H3" s="349"/>
-      <c r="I3" s="349"/>
-      <c r="J3" s="349"/>
-      <c r="K3" s="349"/>
-      <c r="L3" s="349"/>
-      <c r="M3" s="349"/>
+      <c r="B3" s="367"/>
+      <c r="C3" s="367"/>
+      <c r="D3" s="367"/>
+      <c r="E3" s="367"/>
+      <c r="F3" s="367"/>
+      <c r="G3" s="367"/>
+      <c r="H3" s="367"/>
+      <c r="I3" s="367"/>
+      <c r="J3" s="367"/>
+      <c r="K3" s="367"/>
+      <c r="L3" s="367"/>
+      <c r="M3" s="367"/>
     </row>
     <row r="4" spans="2:13" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
-        <v>1589</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="5" spans="2:13" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="2:13" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="353" t="s">
+      <c r="B6" s="371" t="s">
         <v>99</v>
       </c>
       <c r="C6" s="21" t="s">
         <v>101</v>
       </c>
       <c r="D6" s="9"/>
-      <c r="E6" s="353" t="s">
+      <c r="E6" s="371" t="s">
         <v>99</v>
       </c>
       <c r="F6" s="21" t="s">
@@ -22657,12 +22740,12 @@
       <c r="G6" s="11"/>
     </row>
     <row r="7" spans="2:13" s="7" customFormat="1" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="355"/>
+      <c r="B7" s="373"/>
       <c r="C7" s="22" t="s">
         <v>100</v>
       </c>
       <c r="D7" s="9"/>
-      <c r="E7" s="355"/>
+      <c r="E7" s="373"/>
       <c r="F7" s="22" t="s">
         <v>100</v>
       </c>
@@ -22712,11 +22795,11 @@
         <v>38.655814860709533</v>
       </c>
       <c r="G10" s="12"/>
-      <c r="I10" s="402" t="s">
+      <c r="I10" s="421" t="s">
         <v>97</v>
       </c>
-      <c r="J10" s="403"/>
-      <c r="K10" s="404"/>
+      <c r="J10" s="422"/>
+      <c r="K10" s="423"/>
       <c r="L10" s="23"/>
     </row>
     <row r="11" spans="2:13" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
@@ -22733,10 +22816,10 @@
         <v>41.563020560833436</v>
       </c>
       <c r="G11" s="12"/>
-      <c r="I11" s="402" t="s">
+      <c r="I11" s="421" t="s">
         <v>103</v>
       </c>
-      <c r="J11" s="406" t="s">
+      <c r="J11" s="425" t="s">
         <v>0</v>
       </c>
       <c r="K11" s="24" t="s">
@@ -22757,8 +22840,8 @@
         <v>41.56957570333654</v>
       </c>
       <c r="G12" s="12"/>
-      <c r="I12" s="405"/>
-      <c r="J12" s="407"/>
+      <c r="I12" s="424"/>
+      <c r="J12" s="426"/>
       <c r="K12" s="25" t="s">
         <v>100</v>
       </c>
@@ -23710,38 +23793,38 @@
   <sheetData>
     <row r="1" spans="2:15" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:15" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="349" t="s">
+      <c r="B2" s="367" t="s">
         <v>1166</v>
       </c>
-      <c r="C2" s="349"/>
-      <c r="D2" s="349"/>
-      <c r="E2" s="349"/>
-      <c r="F2" s="349"/>
-      <c r="G2" s="349"/>
-      <c r="H2" s="349"/>
-      <c r="I2" s="349"/>
-      <c r="J2" s="349"/>
-      <c r="K2" s="349"/>
-      <c r="L2" s="349"/>
-      <c r="M2" s="349"/>
-      <c r="N2" s="349"/>
-      <c r="O2" s="349"/>
+      <c r="C2" s="367"/>
+      <c r="D2" s="367"/>
+      <c r="E2" s="367"/>
+      <c r="F2" s="367"/>
+      <c r="G2" s="367"/>
+      <c r="H2" s="367"/>
+      <c r="I2" s="367"/>
+      <c r="J2" s="367"/>
+      <c r="K2" s="367"/>
+      <c r="L2" s="367"/>
+      <c r="M2" s="367"/>
+      <c r="N2" s="367"/>
+      <c r="O2" s="367"/>
     </row>
     <row r="3" spans="2:15" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="349"/>
-      <c r="C3" s="349"/>
-      <c r="D3" s="349"/>
-      <c r="E3" s="349"/>
-      <c r="F3" s="349"/>
-      <c r="G3" s="349"/>
-      <c r="H3" s="349"/>
-      <c r="I3" s="349"/>
-      <c r="J3" s="349"/>
-      <c r="K3" s="349"/>
-      <c r="L3" s="349"/>
-      <c r="M3" s="349"/>
-      <c r="N3" s="349"/>
-      <c r="O3" s="349"/>
+      <c r="B3" s="367"/>
+      <c r="C3" s="367"/>
+      <c r="D3" s="367"/>
+      <c r="E3" s="367"/>
+      <c r="F3" s="367"/>
+      <c r="G3" s="367"/>
+      <c r="H3" s="367"/>
+      <c r="I3" s="367"/>
+      <c r="J3" s="367"/>
+      <c r="K3" s="367"/>
+      <c r="L3" s="367"/>
+      <c r="M3" s="367"/>
+      <c r="N3" s="367"/>
+      <c r="O3" s="367"/>
     </row>
     <row r="4" spans="2:15" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
@@ -23750,32 +23833,32 @@
     </row>
     <row r="5" spans="2:15" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="2:15" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="353" t="s">
+      <c r="B6" s="371" t="s">
         <v>99</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="E6" s="353" t="s">
+      <c r="E6" s="371" t="s">
         <v>99</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>101</v>
       </c>
       <c r="G6" s="101"/>
-      <c r="H6" s="353" t="s">
+      <c r="H6" s="371" t="s">
         <v>99</v>
       </c>
       <c r="I6" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="K6" s="353" t="s">
+      <c r="K6" s="371" t="s">
         <v>99</v>
       </c>
       <c r="L6" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="N6" s="353" t="s">
+      <c r="N6" s="371" t="s">
         <v>99</v>
       </c>
       <c r="O6" s="8" t="s">
@@ -23783,24 +23866,24 @@
       </c>
     </row>
     <row r="7" spans="2:15" s="9" customFormat="1" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="355"/>
+      <c r="B7" s="373"/>
       <c r="C7" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="E7" s="355"/>
+      <c r="E7" s="373"/>
       <c r="F7" s="10" t="s">
         <v>98</v>
       </c>
       <c r="G7" s="101"/>
-      <c r="H7" s="354"/>
+      <c r="H7" s="372"/>
       <c r="I7" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="K7" s="355"/>
+      <c r="K7" s="373"/>
       <c r="L7" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="N7" s="355"/>
+      <c r="N7" s="373"/>
       <c r="O7" s="10" t="s">
         <v>100</v>
       </c>
@@ -23834,7 +23917,7 @@
       <c r="N8" s="144" t="s">
         <v>363</v>
       </c>
-      <c r="O8" s="344">
+      <c r="O8" s="342">
         <v>13.252612624286945</v>
       </c>
     </row>
@@ -23842,7 +23925,7 @@
       <c r="B9" s="146" t="s">
         <v>240</v>
       </c>
-      <c r="C9" s="345">
+      <c r="C9" s="343">
         <v>16.648</v>
       </c>
       <c r="E9" s="146" t="s">
@@ -23861,13 +23944,13 @@
       <c r="K9" s="144" t="s">
         <v>332</v>
       </c>
-      <c r="L9" s="344">
+      <c r="L9" s="342">
         <v>10.950209630871486</v>
       </c>
       <c r="N9" s="144" t="s">
         <v>364</v>
       </c>
-      <c r="O9" s="344">
+      <c r="O9" s="342">
         <v>13.68105331076393</v>
       </c>
     </row>
@@ -23875,7 +23958,7 @@
       <c r="B10" s="146" t="s">
         <v>241</v>
       </c>
-      <c r="C10" s="345">
+      <c r="C10" s="343">
         <v>17.8</v>
       </c>
       <c r="E10" s="146" t="s">
@@ -23894,13 +23977,13 @@
       <c r="K10" s="144" t="s">
         <v>333</v>
       </c>
-      <c r="L10" s="344">
+      <c r="L10" s="342">
         <v>10.525494515581252</v>
       </c>
       <c r="N10" s="144" t="s">
         <v>365</v>
       </c>
-      <c r="O10" s="344">
+      <c r="O10" s="342">
         <v>14.128121853174697</v>
       </c>
     </row>
@@ -23908,7 +23991,7 @@
       <c r="B11" s="146" t="s">
         <v>242</v>
       </c>
-      <c r="C11" s="345">
+      <c r="C11" s="343">
         <v>18.952000000000002</v>
       </c>
       <c r="E11" s="146" t="s">
@@ -23927,13 +24010,13 @@
       <c r="K11" s="144" t="s">
         <v>334</v>
       </c>
-      <c r="L11" s="344">
+      <c r="L11" s="342">
         <v>11.348845747854421</v>
       </c>
       <c r="N11" s="144" t="s">
         <v>366</v>
       </c>
-      <c r="O11" s="344">
+      <c r="O11" s="342">
         <v>14.239888988777393</v>
       </c>
     </row>
@@ -23941,7 +24024,7 @@
       <c r="B12" s="146" t="s">
         <v>243</v>
       </c>
-      <c r="C12" s="345">
+      <c r="C12" s="343">
         <v>25.704000000000001</v>
       </c>
       <c r="E12" s="146" t="s">
@@ -23960,13 +24043,13 @@
       <c r="K12" s="144" t="s">
         <v>336</v>
       </c>
-      <c r="L12" s="344">
+      <c r="L12" s="342">
         <v>11.94121156654869</v>
       </c>
       <c r="N12" s="144" t="s">
         <v>367</v>
       </c>
-      <c r="O12" s="344">
+      <c r="O12" s="342">
         <v>14.571464824398715</v>
       </c>
     </row>
@@ -23974,7 +24057,7 @@
       <c r="B13" s="146" t="s">
         <v>244</v>
       </c>
-      <c r="C13" s="345">
+      <c r="C13" s="343">
         <v>24.552000000000003</v>
       </c>
       <c r="E13" s="146" t="s">
@@ -23993,13 +24076,13 @@
       <c r="K13" s="144" t="s">
         <v>337</v>
       </c>
-      <c r="L13" s="344">
+      <c r="L13" s="342">
         <v>10.514317802020985</v>
       </c>
       <c r="N13" s="144" t="s">
         <v>368</v>
       </c>
-      <c r="O13" s="344">
+      <c r="O13" s="342">
         <v>14.999905510875699</v>
       </c>
     </row>
@@ -24007,7 +24090,7 @@
       <c r="B14" s="146" t="s">
         <v>245</v>
       </c>
-      <c r="C14" s="345">
+      <c r="C14" s="343">
         <v>34.44</v>
       </c>
       <c r="E14" s="146" t="s">
@@ -24026,13 +24109,13 @@
       <c r="K14" s="144" t="s">
         <v>338</v>
       </c>
-      <c r="L14" s="344">
+      <c r="L14" s="342">
         <v>12.183373693687855</v>
       </c>
       <c r="N14" s="144" t="s">
         <v>369</v>
       </c>
-      <c r="O14" s="344">
+      <c r="O14" s="342">
         <v>15.860512455016428</v>
       </c>
     </row>
@@ -24040,7 +24123,7 @@
       <c r="B15" s="146" t="s">
         <v>246</v>
       </c>
-      <c r="C15" s="345">
+      <c r="C15" s="343">
         <v>35.176000000000002</v>
       </c>
       <c r="E15" s="146" t="s">
@@ -24059,13 +24142,13 @@
       <c r="K15" s="144" t="s">
         <v>339</v>
       </c>
-      <c r="L15" s="344">
+      <c r="L15" s="342">
         <v>11.00981876985959</v>
       </c>
       <c r="N15" s="144" t="s">
         <v>370</v>
       </c>
-      <c r="O15" s="344">
+      <c r="O15" s="342">
         <v>16.348562280481513</v>
       </c>
     </row>
@@ -24073,7 +24156,7 @@
       <c r="B16" s="146" t="s">
         <v>247</v>
       </c>
-      <c r="C16" s="345">
+      <c r="C16" s="343">
         <v>43.176000000000002</v>
       </c>
       <c r="E16" s="146" t="s">
@@ -24092,13 +24175,13 @@
       <c r="K16" s="144" t="s">
         <v>340</v>
       </c>
-      <c r="L16" s="344">
+      <c r="L16" s="342">
         <v>11.918858139428153</v>
       </c>
       <c r="N16" s="144" t="s">
         <v>371</v>
       </c>
-      <c r="O16" s="344">
+      <c r="O16" s="342">
         <v>16.460329416084207</v>
       </c>
     </row>
@@ -24106,7 +24189,7 @@
       <c r="B17" s="146" t="s">
         <v>248</v>
       </c>
-      <c r="C17" s="345">
+      <c r="C17" s="343">
         <v>47.751999999999995</v>
       </c>
       <c r="E17" s="146" t="s">
@@ -24125,13 +24208,13 @@
       <c r="K17" s="144" t="s">
         <v>341</v>
       </c>
-      <c r="L17" s="344">
+      <c r="L17" s="342">
         <v>11.762384149584383</v>
       </c>
       <c r="N17" s="144" t="s">
         <v>372</v>
       </c>
-      <c r="O17" s="344">
+      <c r="O17" s="342">
         <v>17.01543952291091</v>
       </c>
     </row>
@@ -24139,7 +24222,7 @@
       <c r="B18" s="146" t="s">
         <v>249</v>
       </c>
-      <c r="C18" s="345">
+      <c r="C18" s="343">
         <v>45.768000000000001</v>
       </c>
       <c r="E18" s="146" t="s">
@@ -24158,13 +24241,13 @@
       <c r="K18" s="144" t="s">
         <v>342</v>
       </c>
-      <c r="L18" s="344">
+      <c r="L18" s="342">
         <v>12.753386085261583</v>
       </c>
       <c r="N18" s="144" t="s">
         <v>373</v>
       </c>
-      <c r="O18" s="344">
+      <c r="O18" s="342">
         <v>17.235248222929538</v>
       </c>
     </row>
@@ -24172,7 +24255,7 @@
       <c r="B19" s="146" t="s">
         <v>250</v>
       </c>
-      <c r="C19" s="345">
+      <c r="C19" s="343">
         <v>66.055999999999997</v>
       </c>
       <c r="E19" s="146" t="s">
@@ -24191,13 +24274,13 @@
       <c r="K19" s="144" t="s">
         <v>343</v>
       </c>
-      <c r="L19" s="344">
+      <c r="L19" s="342">
         <v>12.451614819134319</v>
       </c>
       <c r="N19" s="144" t="s">
         <v>374</v>
       </c>
-      <c r="O19" s="344">
+      <c r="O19" s="342">
         <v>17.637609911099233</v>
       </c>
     </row>
@@ -24205,7 +24288,7 @@
       <c r="B20" s="146" t="s">
         <v>251</v>
       </c>
-      <c r="C20" s="345">
+      <c r="C20" s="343">
         <v>74.376000000000005</v>
       </c>
       <c r="E20" s="146" t="s">
@@ -24224,13 +24307,13 @@
       <c r="K20" s="144" t="s">
         <v>344</v>
       </c>
-      <c r="L20" s="344">
+      <c r="L20" s="342">
         <v>13.360654188702881</v>
       </c>
       <c r="N20" s="144" t="s">
         <v>375</v>
       </c>
-      <c r="O20" s="344">
+      <c r="O20" s="342">
         <v>18.121934165377567</v>
       </c>
     </row>
@@ -24238,7 +24321,7 @@
       <c r="B21" s="146" t="s">
         <v>253</v>
       </c>
-      <c r="C21" s="345">
+      <c r="C21" s="343">
         <v>205.73599999999999</v>
       </c>
       <c r="E21" s="146" t="s">
@@ -24257,13 +24340,13 @@
       <c r="K21" s="144" t="s">
         <v>345</v>
       </c>
-      <c r="L21" s="344">
+      <c r="L21" s="342">
         <v>14.727938814242478</v>
       </c>
       <c r="N21" s="144" t="s">
         <v>376</v>
       </c>
-      <c r="O21" s="344">
+      <c r="O21" s="342">
         <v>18.345468436582948</v>
       </c>
     </row>
@@ -24271,7 +24354,7 @@
       <c r="B22" s="146" t="s">
         <v>254</v>
       </c>
-      <c r="C22" s="345">
+      <c r="C22" s="343">
         <v>200.744</v>
       </c>
       <c r="E22" s="146" t="s">
@@ -24290,13 +24373,13 @@
       <c r="K22" s="144" t="s">
         <v>346</v>
       </c>
-      <c r="L22" s="344">
+      <c r="L22" s="342">
         <v>13.491049180239356</v>
       </c>
       <c r="N22" s="144" t="s">
         <v>377</v>
       </c>
-      <c r="O22" s="344">
+      <c r="O22" s="342">
         <v>18.565277136601576</v>
       </c>
     </row>
@@ -24304,7 +24387,7 @@
       <c r="B23" s="146" t="s">
         <v>255</v>
       </c>
-      <c r="C23" s="345">
+      <c r="C23" s="343">
         <v>76.64800000000001</v>
       </c>
       <c r="E23" s="146" t="s">
@@ -24323,13 +24406,13 @@
       <c r="K23" s="144" t="s">
         <v>347</v>
       </c>
-      <c r="L23" s="344">
+      <c r="L23" s="342">
         <v>15.357560344804313</v>
       </c>
       <c r="N23" s="144" t="s">
         <v>378</v>
       </c>
-      <c r="O23" s="344">
+      <c r="O23" s="342">
         <v>18.893127401036139</v>
       </c>
     </row>
@@ -24337,7 +24420,7 @@
       <c r="B24" s="146" t="s">
         <v>256</v>
       </c>
-      <c r="C24" s="345">
+      <c r="C24" s="343">
         <v>116.712</v>
       </c>
       <c r="E24" s="146" t="s">
@@ -24356,13 +24439,13 @@
       <c r="K24" s="144" t="s">
         <v>348</v>
       </c>
-      <c r="L24" s="344">
+      <c r="L24" s="342">
         <v>15.745019748226978</v>
       </c>
       <c r="N24" s="144" t="s">
         <v>379</v>
       </c>
-      <c r="O24" s="344">
+      <c r="O24" s="342">
         <v>19.112936101054768</v>
       </c>
     </row>
@@ -24370,7 +24453,7 @@
       <c r="B25" s="146" t="s">
         <v>257</v>
       </c>
-      <c r="C25" s="345">
+      <c r="C25" s="343">
         <v>9.3840000000000003</v>
       </c>
       <c r="E25" s="146" t="s">
@@ -24389,13 +24472,13 @@
       <c r="K25" s="144" t="s">
         <v>349</v>
       </c>
-      <c r="L25" s="344">
+      <c r="L25" s="342">
         <v>16.374641278788811</v>
       </c>
       <c r="N25" s="144" t="s">
         <v>380</v>
       </c>
-      <c r="O25" s="344">
+      <c r="O25" s="342">
         <v>19.44451193667609</v>
       </c>
     </row>
@@ -24403,7 +24486,7 @@
       <c r="B26" s="146" t="s">
         <v>258</v>
       </c>
-      <c r="C26" s="345">
+      <c r="C26" s="343">
         <v>18.727999999999998</v>
       </c>
       <c r="E26" s="146" t="s">
@@ -24422,13 +24505,13 @@
       <c r="K26" s="144" t="s">
         <v>350</v>
       </c>
-      <c r="L26" s="344">
+      <c r="L26" s="342">
         <v>18.602532848469142</v>
       </c>
       <c r="N26" s="144" t="s">
         <v>381</v>
       </c>
-      <c r="O26" s="344">
+      <c r="O26" s="342">
         <v>20.003347614689545</v>
       </c>
     </row>
@@ -24436,7 +24519,7 @@
       <c r="B27" s="146" t="s">
         <v>259</v>
       </c>
-      <c r="C27" s="345">
+      <c r="C27" s="343">
         <v>20.903999999999996</v>
       </c>
       <c r="E27" s="146" t="s">
@@ -24455,13 +24538,13 @@
       <c r="K27" s="144" t="s">
         <v>351</v>
       </c>
-      <c r="L27" s="344">
+      <c r="L27" s="342">
         <v>19.850599196032537</v>
       </c>
       <c r="N27" s="144" t="s">
         <v>382</v>
       </c>
-      <c r="O27" s="344">
+      <c r="O27" s="342">
         <v>20.11138917910548</v>
       </c>
     </row>
@@ -24469,7 +24552,7 @@
       <c r="B28" s="146" t="s">
         <v>260</v>
       </c>
-      <c r="C28" s="345">
+      <c r="C28" s="343">
         <v>51.400000000000006</v>
       </c>
       <c r="E28" s="146" t="s">
@@ -24488,13 +24571,13 @@
       <c r="K28" s="144" t="s">
         <v>352</v>
       </c>
-      <c r="L28" s="344">
+      <c r="L28" s="342">
         <v>24.500112037104529</v>
       </c>
       <c r="N28" s="144" t="s">
         <v>383</v>
       </c>
-      <c r="O28" s="344">
+      <c r="O28" s="342">
         <v>20.785717563908396</v>
       </c>
     </row>
@@ -24502,7 +24585,7 @@
       <c r="B29" s="146" t="s">
         <v>261</v>
       </c>
-      <c r="C29" s="345">
+      <c r="C29" s="343">
         <v>67.816000000000003</v>
       </c>
       <c r="E29" s="146" t="s">
@@ -24521,13 +24604,13 @@
       <c r="K29" s="144" t="s">
         <v>353</v>
       </c>
-      <c r="L29" s="344">
+      <c r="L29" s="342">
         <v>21.36318109785563</v>
       </c>
       <c r="N29" s="144" t="s">
         <v>384</v>
       </c>
-      <c r="O29" s="344">
+      <c r="O29" s="342">
         <v>21.668677935169658</v>
       </c>
     </row>
@@ -24535,7 +24618,7 @@
       <c r="B30" s="146" t="s">
         <v>262</v>
       </c>
-      <c r="C30" s="345">
+      <c r="C30" s="343">
         <v>82.376000000000005</v>
       </c>
       <c r="E30" s="146" t="s">
@@ -24554,13 +24637,13 @@
       <c r="K30" s="144" t="s">
         <v>354</v>
       </c>
-      <c r="L30" s="344">
+      <c r="L30" s="342">
         <v>67.616147381436406</v>
       </c>
       <c r="N30" s="144" t="s">
         <v>385</v>
       </c>
-      <c r="O30" s="344">
+      <c r="O30" s="342">
         <v>24.887571440527186</v>
       </c>
     </row>
@@ -24587,13 +24670,13 @@
       <c r="K31" s="144" t="s">
         <v>355</v>
       </c>
-      <c r="L31" s="344">
+      <c r="L31" s="342">
         <v>9.3258605934456948</v>
       </c>
       <c r="N31" s="144" t="s">
         <v>1164</v>
       </c>
-      <c r="O31" s="344">
+      <c r="O31" s="342">
         <v>25.662490247372528</v>
       </c>
     </row>
@@ -24620,13 +24703,13 @@
       <c r="K32" s="144" t="s">
         <v>356</v>
       </c>
-      <c r="L32" s="344">
+      <c r="L32" s="342">
         <v>10.566475798635578</v>
       </c>
       <c r="N32" s="144" t="s">
         <v>386</v>
       </c>
-      <c r="O32" s="344">
+      <c r="O32" s="342">
         <v>26.117009932156808</v>
       </c>
     </row>
@@ -24653,13 +24736,13 @@
       <c r="K33" s="144" t="s">
         <v>357</v>
       </c>
-      <c r="L33" s="344">
+      <c r="L33" s="342">
         <v>11.583556732620076</v>
       </c>
       <c r="N33" s="144" t="s">
         <v>387</v>
       </c>
-      <c r="O33" s="344">
+      <c r="O33" s="342">
         <v>28.765891045940617</v>
       </c>
     </row>
@@ -24686,13 +24769,13 @@
       <c r="K34" s="144" t="s">
         <v>358</v>
       </c>
-      <c r="L34" s="344">
+      <c r="L34" s="342">
         <v>11.918858139428153</v>
       </c>
       <c r="N34" s="144" t="s">
         <v>388</v>
       </c>
-      <c r="O34" s="344">
+      <c r="O34" s="342">
         <v>35.86682972789832</v>
       </c>
     </row>
@@ -24713,13 +24796,13 @@
       <c r="K35" s="144" t="s">
         <v>359</v>
       </c>
-      <c r="L35" s="344">
+      <c r="L35" s="342">
         <v>12.026899703844087</v>
       </c>
       <c r="N35" s="144" t="s">
         <v>1165</v>
       </c>
-      <c r="O35" s="344">
+      <c r="O35" s="342">
         <v>36.969598799178215</v>
       </c>
     </row>
@@ -24740,13 +24823,13 @@
       <c r="K36" s="144" t="s">
         <v>360</v>
       </c>
-      <c r="L36" s="344">
+      <c r="L36" s="342">
         <v>12.362201110652164</v>
       </c>
       <c r="N36" s="144" t="s">
         <v>389</v>
       </c>
-      <c r="O36" s="344">
+      <c r="O36" s="342">
         <v>41.630288353810478</v>
       </c>
     </row>
@@ -24767,13 +24850,13 @@
       <c r="K37" s="144" t="s">
         <v>361</v>
       </c>
-      <c r="L37" s="344">
+      <c r="L37" s="342">
         <v>12.798092939502661</v>
       </c>
       <c r="N37" s="144" t="s">
         <v>390</v>
       </c>
-      <c r="O37" s="344">
+      <c r="O37" s="342">
         <v>50.504598920664222</v>
       </c>
     </row>
@@ -24794,13 +24877,13 @@
       <c r="K38" s="144" t="s">
         <v>362</v>
       </c>
-      <c r="L38" s="344">
+      <c r="L38" s="342">
         <v>13.025352781894803</v>
       </c>
       <c r="N38" s="144" t="s">
         <v>391</v>
       </c>
-      <c r="O38" s="344">
+      <c r="O38" s="342">
         <v>56.271783117763142</v>
       </c>
     </row>
@@ -24821,7 +24904,7 @@
       <c r="N39" s="144" t="s">
         <v>392</v>
       </c>
-      <c r="O39" s="344">
+      <c r="O39" s="342">
         <v>76.233393536403966</v>
       </c>
     </row>
@@ -24842,7 +24925,7 @@
       <c r="N40" s="144" t="s">
         <v>393</v>
       </c>
-      <c r="O40" s="344">
+      <c r="O40" s="342">
         <v>92.208642785215417</v>
       </c>
     </row>
@@ -24851,7 +24934,7 @@
       <c r="N41" s="144" t="s">
         <v>750</v>
       </c>
-      <c r="O41" s="344">
+      <c r="O41" s="342">
         <v>18.98999225189181</v>
       </c>
     </row>
@@ -25004,49 +25087,49 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>1589</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" s="349" t="s">
-        <v>1650</v>
-      </c>
-      <c r="B2" s="349"/>
-      <c r="C2" s="349"/>
-      <c r="D2" s="349"/>
-      <c r="E2" s="349"/>
-      <c r="F2" s="349"/>
-      <c r="G2" s="349"/>
-      <c r="H2" s="349"/>
-      <c r="I2" s="349"/>
-      <c r="J2" s="349"/>
-      <c r="K2" s="349"/>
+      <c r="A2" s="367" t="s">
+        <v>1648</v>
+      </c>
+      <c r="B2" s="367"/>
+      <c r="C2" s="367"/>
+      <c r="D2" s="367"/>
+      <c r="E2" s="367"/>
+      <c r="F2" s="367"/>
+      <c r="G2" s="367"/>
+      <c r="H2" s="367"/>
+      <c r="I2" s="367"/>
+      <c r="J2" s="367"/>
+      <c r="K2" s="367"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A3" s="349"/>
-      <c r="B3" s="349"/>
-      <c r="C3" s="349"/>
-      <c r="D3" s="349"/>
-      <c r="E3" s="349"/>
-      <c r="F3" s="349"/>
-      <c r="G3" s="349"/>
-      <c r="H3" s="349"/>
-      <c r="I3" s="349"/>
-      <c r="J3" s="349"/>
-      <c r="K3" s="349"/>
+      <c r="A3" s="367"/>
+      <c r="B3" s="367"/>
+      <c r="C3" s="367"/>
+      <c r="D3" s="367"/>
+      <c r="E3" s="367"/>
+      <c r="F3" s="367"/>
+      <c r="G3" s="367"/>
+      <c r="H3" s="367"/>
+      <c r="I3" s="367"/>
+      <c r="J3" s="367"/>
+      <c r="K3" s="367"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A4" s="349"/>
-      <c r="B4" s="349"/>
-      <c r="C4" s="349"/>
-      <c r="D4" s="349"/>
-      <c r="E4" s="349"/>
-      <c r="F4" s="349"/>
-      <c r="G4" s="349"/>
-      <c r="H4" s="349"/>
-      <c r="I4" s="349"/>
-      <c r="J4" s="349"/>
-      <c r="K4" s="349"/>
+      <c r="A4" s="367"/>
+      <c r="B4" s="367"/>
+      <c r="C4" s="367"/>
+      <c r="D4" s="367"/>
+      <c r="E4" s="367"/>
+      <c r="F4" s="367"/>
+      <c r="G4" s="367"/>
+      <c r="H4" s="367"/>
+      <c r="I4" s="367"/>
+      <c r="J4" s="367"/>
+      <c r="K4" s="367"/>
     </row>
     <row r="5" spans="1:11" ht="46" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A5" s="119"/>
@@ -25063,13 +25146,13 @@
     </row>
     <row r="6" spans="1:11" ht="20" x14ac:dyDescent="0.2">
       <c r="A6" s="13"/>
-      <c r="B6" s="408" t="s">
+      <c r="B6" s="427" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="410" t="s">
+      <c r="C6" s="429" t="s">
         <v>0</v>
       </c>
-      <c r="D6" s="302" t="s">
+      <c r="D6" s="300" t="s">
         <v>84</v>
       </c>
       <c r="E6" s="13"/>
@@ -25082,9 +25165,9 @@
     </row>
     <row r="7" spans="1:11" ht="20" x14ac:dyDescent="0.2">
       <c r="A7" s="13"/>
-      <c r="B7" s="409"/>
-      <c r="C7" s="411"/>
-      <c r="D7" s="304" t="s">
+      <c r="B7" s="428"/>
+      <c r="C7" s="430"/>
+      <c r="D7" s="302" t="s">
         <v>100</v>
       </c>
       <c r="E7" s="13"/>
@@ -25098,12 +25181,12 @@
     <row r="8" spans="1:11" ht="21" x14ac:dyDescent="0.25">
       <c r="A8" s="7"/>
       <c r="B8" s="130" t="s">
-        <v>1577</v>
+        <v>1575</v>
       </c>
       <c r="C8" s="130" t="s">
         <v>83</v>
       </c>
-      <c r="D8" s="305">
+      <c r="D8" s="303">
         <v>12.143742255266419</v>
       </c>
       <c r="E8" s="7"/>
@@ -25117,12 +25200,12 @@
     <row r="9" spans="1:11" ht="21" x14ac:dyDescent="0.25">
       <c r="A9" s="7"/>
       <c r="B9" s="130" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
       <c r="C9" s="130" t="s">
         <v>83</v>
       </c>
-      <c r="D9" s="305">
+      <c r="D9" s="303">
         <v>16.260498416632242</v>
       </c>
       <c r="E9" s="7"/>
@@ -25136,12 +25219,12 @@
     <row r="10" spans="1:11" ht="21" x14ac:dyDescent="0.25">
       <c r="A10" s="7"/>
       <c r="B10" s="130" t="s">
-        <v>1577</v>
+        <v>1575</v>
       </c>
       <c r="C10" s="130" t="s">
         <v>404</v>
       </c>
-      <c r="D10" s="305">
+      <c r="D10" s="303">
         <v>12.143742255266419</v>
       </c>
       <c r="E10" s="7"/>
@@ -25154,76 +25237,76 @@
     </row>
     <row r="11" spans="1:11" ht="21" x14ac:dyDescent="0.25">
       <c r="B11" s="130" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
       <c r="C11" s="130" t="s">
         <v>404</v>
       </c>
-      <c r="D11" s="306">
+      <c r="D11" s="304">
         <v>16.260498416632242</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="21" x14ac:dyDescent="0.25">
       <c r="B12" s="130" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
       <c r="C12" s="130" t="s">
         <v>83</v>
       </c>
-      <c r="D12" s="306">
+      <c r="D12" s="304">
         <v>14.677130662260772</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="21" x14ac:dyDescent="0.25">
       <c r="B13" s="130" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="C13" s="130" t="s">
         <v>83</v>
       </c>
-      <c r="D13" s="306">
+      <c r="D13" s="304">
         <v>20.218917802560924</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="21" x14ac:dyDescent="0.25">
       <c r="B14" s="130" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
       <c r="C14" s="130" t="s">
         <v>404</v>
       </c>
-      <c r="D14" s="306">
+      <c r="D14" s="304">
         <v>14.677130662260772</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="21" x14ac:dyDescent="0.25">
       <c r="B15" s="130" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="C15" s="130" t="s">
         <v>404</v>
       </c>
-      <c r="D15" s="306">
+      <c r="D15" s="304">
         <v>20.218917802560924</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="19" x14ac:dyDescent="0.25">
-      <c r="D16" s="303"/>
+      <c r="D16" s="301"/>
     </row>
     <row r="17" spans="4:4" ht="19" x14ac:dyDescent="0.25">
-      <c r="D17" s="303"/>
+      <c r="D17" s="301"/>
     </row>
     <row r="18" spans="4:4" ht="19" x14ac:dyDescent="0.25">
-      <c r="D18" s="303"/>
+      <c r="D18" s="301"/>
     </row>
     <row r="19" spans="4:4" ht="19" x14ac:dyDescent="0.25">
-      <c r="D19" s="303"/>
+      <c r="D19" s="301"/>
     </row>
     <row r="20" spans="4:4" ht="19" x14ac:dyDescent="0.25">
-      <c r="D20" s="303"/>
+      <c r="D20" s="301"/>
     </row>
     <row r="21" spans="4:4" ht="19" x14ac:dyDescent="0.25">
-      <c r="D21" s="303"/>
+      <c r="D21" s="301"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -25251,42 +25334,42 @@
   <sheetData>
     <row r="1" spans="2:9" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="349" t="s">
-        <v>1651</v>
-      </c>
-      <c r="C2" s="349"/>
-      <c r="D2" s="349"/>
-      <c r="E2" s="349"/>
-      <c r="F2" s="349"/>
-      <c r="G2" s="349"/>
-      <c r="H2" s="349"/>
-      <c r="I2" s="349"/>
+      <c r="B2" s="367" t="s">
+        <v>1649</v>
+      </c>
+      <c r="C2" s="367"/>
+      <c r="D2" s="367"/>
+      <c r="E2" s="367"/>
+      <c r="F2" s="367"/>
+      <c r="G2" s="367"/>
+      <c r="H2" s="367"/>
+      <c r="I2" s="367"/>
     </row>
     <row r="3" spans="2:9" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="349"/>
-      <c r="C3" s="349"/>
-      <c r="D3" s="349"/>
-      <c r="E3" s="349"/>
-      <c r="F3" s="349"/>
-      <c r="G3" s="349"/>
-      <c r="H3" s="349"/>
-      <c r="I3" s="349"/>
+      <c r="B3" s="367"/>
+      <c r="C3" s="367"/>
+      <c r="D3" s="367"/>
+      <c r="E3" s="367"/>
+      <c r="F3" s="367"/>
+      <c r="G3" s="367"/>
+      <c r="H3" s="367"/>
+      <c r="I3" s="367"/>
     </row>
     <row r="4" spans="2:9" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
-        <v>1687</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="5" spans="2:9" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="2:9" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="353" t="s">
+      <c r="B6" s="371" t="s">
         <v>99</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>101</v>
       </c>
       <c r="E6" s="101"/>
-      <c r="G6" s="353" t="s">
+      <c r="G6" s="371" t="s">
         <v>99</v>
       </c>
       <c r="H6" s="8" t="s">
@@ -25294,12 +25377,12 @@
       </c>
     </row>
     <row r="7" spans="2:9" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="354"/>
+      <c r="B7" s="372"/>
       <c r="C7" s="16" t="s">
         <v>98</v>
       </c>
       <c r="E7" s="101"/>
-      <c r="G7" s="354"/>
+      <c r="G7" s="372"/>
       <c r="H7" s="16" t="s">
         <v>100</v>
       </c>
@@ -26065,42 +26148,42 @@
   <sheetData>
     <row r="1" spans="2:9" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="349" t="s">
-        <v>1658</v>
-      </c>
-      <c r="C2" s="349"/>
-      <c r="D2" s="349"/>
-      <c r="E2" s="349"/>
-      <c r="F2" s="349"/>
-      <c r="G2" s="349"/>
-      <c r="H2" s="349"/>
-      <c r="I2" s="349"/>
+      <c r="B2" s="367" t="s">
+        <v>1656</v>
+      </c>
+      <c r="C2" s="367"/>
+      <c r="D2" s="367"/>
+      <c r="E2" s="367"/>
+      <c r="F2" s="367"/>
+      <c r="G2" s="367"/>
+      <c r="H2" s="367"/>
+      <c r="I2" s="367"/>
     </row>
     <row r="3" spans="2:9" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="349"/>
-      <c r="C3" s="349"/>
-      <c r="D3" s="349"/>
-      <c r="E3" s="349"/>
-      <c r="F3" s="349"/>
-      <c r="G3" s="349"/>
-      <c r="H3" s="349"/>
-      <c r="I3" s="349"/>
+      <c r="B3" s="367"/>
+      <c r="C3" s="367"/>
+      <c r="D3" s="367"/>
+      <c r="E3" s="367"/>
+      <c r="F3" s="367"/>
+      <c r="G3" s="367"/>
+      <c r="H3" s="367"/>
+      <c r="I3" s="367"/>
     </row>
     <row r="4" spans="2:9" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
-        <v>1589</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="5" spans="2:9" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="2:9" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="353" t="s">
+      <c r="B6" s="371" t="s">
         <v>99</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>101</v>
       </c>
       <c r="E6" s="101"/>
-      <c r="G6" s="353" t="s">
+      <c r="G6" s="371" t="s">
         <v>99</v>
       </c>
       <c r="H6" s="8" t="s">
@@ -26108,12 +26191,12 @@
       </c>
     </row>
     <row r="7" spans="2:9" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="354"/>
+      <c r="B7" s="372"/>
       <c r="C7" s="16" t="s">
         <v>98</v>
       </c>
       <c r="E7" s="101"/>
-      <c r="G7" s="354"/>
+      <c r="G7" s="372"/>
       <c r="H7" s="16" t="s">
         <v>100</v>
       </c>
@@ -26886,93 +26969,93 @@
       </c>
     </row>
     <row r="65" spans="2:8" ht="19" x14ac:dyDescent="0.25">
-      <c r="G65" s="325"/>
-      <c r="H65" s="326"/>
+      <c r="G65" s="323"/>
+      <c r="H65" s="324"/>
     </row>
     <row r="66" spans="2:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="B66" s="327" t="s">
-        <v>1656</v>
-      </c>
-      <c r="C66" s="332"/>
-      <c r="D66" s="332"/>
-      <c r="E66" s="333"/>
-      <c r="F66" s="333"/>
-      <c r="G66" s="333"/>
-      <c r="H66" s="333"/>
+      <c r="B66" s="325" t="s">
+        <v>1654</v>
+      </c>
+      <c r="C66" s="330"/>
+      <c r="D66" s="330"/>
+      <c r="E66" s="331"/>
+      <c r="F66" s="331"/>
+      <c r="G66" s="331"/>
+      <c r="H66" s="331"/>
     </row>
     <row r="67" spans="2:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="B67" s="331"/>
+      <c r="B67" s="329"/>
       <c r="C67" s="130" t="s">
-        <v>1652</v>
+        <v>1650</v>
       </c>
       <c r="D67" s="121"/>
       <c r="E67" s="121"/>
       <c r="F67" s="121"/>
       <c r="G67" s="121"/>
-      <c r="H67" s="330">
+      <c r="H67" s="328">
         <v>7.3385653311303862</v>
       </c>
     </row>
     <row r="68" spans="2:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="B68" s="331"/>
+      <c r="B68" s="329"/>
       <c r="C68" s="130" t="s">
-        <v>1688</v>
+        <v>1686</v>
       </c>
       <c r="D68" s="121"/>
       <c r="E68" s="121"/>
       <c r="F68" s="121"/>
       <c r="G68" s="121"/>
-      <c r="H68" s="330">
+      <c r="H68" s="328">
         <v>9.8719537381247413</v>
       </c>
     </row>
     <row r="69" spans="2:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="B69" s="331"/>
+      <c r="B69" s="329"/>
       <c r="C69" s="130" t="s">
-        <v>1653</v>
+        <v>1651</v>
       </c>
       <c r="D69" s="121"/>
       <c r="E69" s="121"/>
       <c r="F69" s="121"/>
       <c r="G69" s="121"/>
-      <c r="H69" s="330">
+      <c r="H69" s="328">
         <v>7.9719124328789741</v>
       </c>
     </row>
     <row r="70" spans="2:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="B70" s="331"/>
+      <c r="B70" s="329"/>
       <c r="C70" s="130" t="s">
-        <v>1654</v>
+        <v>1652</v>
       </c>
       <c r="D70" s="121"/>
       <c r="E70" s="121"/>
       <c r="F70" s="121"/>
       <c r="G70" s="121"/>
-      <c r="H70" s="330">
+      <c r="H70" s="328">
         <v>9.8719537381247413</v>
       </c>
     </row>
     <row r="71" spans="2:8" ht="21" x14ac:dyDescent="0.25">
       <c r="C71" s="130" t="s">
-        <v>1689</v>
+        <v>1687</v>
       </c>
       <c r="D71" s="121"/>
       <c r="E71" s="121"/>
       <c r="F71" s="121"/>
       <c r="G71" s="121"/>
-      <c r="H71" s="330">
+      <c r="H71" s="328">
         <v>5.4385240258846208</v>
       </c>
     </row>
     <row r="72" spans="2:8" ht="21" x14ac:dyDescent="0.25">
       <c r="C72" s="130" t="s">
-        <v>1690</v>
+        <v>1688</v>
       </c>
       <c r="D72" s="121"/>
       <c r="E72" s="121"/>
       <c r="F72" s="121"/>
       <c r="G72" s="121"/>
-      <c r="H72" s="330">
+      <c r="H72" s="328">
         <v>8.6052595346275638</v>
       </c>
     </row>
@@ -27001,40 +27084,40 @@
   <sheetData>
     <row r="1" spans="2:8" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:8" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="349" t="s">
-        <v>1657</v>
-      </c>
-      <c r="C2" s="349"/>
-      <c r="D2" s="349"/>
-      <c r="E2" s="349"/>
-      <c r="F2" s="349"/>
-      <c r="G2" s="349"/>
-      <c r="H2" s="349"/>
+      <c r="B2" s="367" t="s">
+        <v>1655</v>
+      </c>
+      <c r="C2" s="367"/>
+      <c r="D2" s="367"/>
+      <c r="E2" s="367"/>
+      <c r="F2" s="367"/>
+      <c r="G2" s="367"/>
+      <c r="H2" s="367"/>
     </row>
     <row r="3" spans="2:8" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="349"/>
-      <c r="C3" s="349"/>
-      <c r="D3" s="349"/>
-      <c r="E3" s="349"/>
-      <c r="F3" s="349"/>
-      <c r="G3" s="349"/>
-      <c r="H3" s="349"/>
+      <c r="B3" s="367"/>
+      <c r="C3" s="367"/>
+      <c r="D3" s="367"/>
+      <c r="E3" s="367"/>
+      <c r="F3" s="367"/>
+      <c r="G3" s="367"/>
+      <c r="H3" s="367"/>
     </row>
     <row r="4" spans="2:8" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
-        <v>1687</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="5" spans="2:8" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="2:8" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="353" t="s">
+      <c r="B6" s="371" t="s">
         <v>99</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>101</v>
       </c>
       <c r="E6" s="101"/>
-      <c r="G6" s="353" t="s">
+      <c r="G6" s="371" t="s">
         <v>99</v>
       </c>
       <c r="H6" s="8" t="s">
@@ -27042,12 +27125,12 @@
       </c>
     </row>
     <row r="7" spans="2:8" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="354"/>
+      <c r="B7" s="372"/>
       <c r="C7" s="16" t="s">
         <v>98</v>
       </c>
       <c r="E7" s="101"/>
-      <c r="G7" s="354"/>
+      <c r="G7" s="372"/>
       <c r="H7" s="16" t="s">
         <v>100</v>
       </c>
@@ -28148,20 +28231,20 @@
     </row>
     <row r="98" spans="2:8" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="99" spans="2:8" ht="26" x14ac:dyDescent="0.3">
-      <c r="B99" s="334" t="s">
-        <v>1691</v>
-      </c>
-      <c r="C99" s="335"/>
-      <c r="D99" s="336"/>
-      <c r="E99" s="336"/>
-      <c r="F99" s="336"/>
-      <c r="G99" s="336"/>
-      <c r="H99" s="337"/>
+      <c r="B99" s="332" t="s">
+        <v>1689</v>
+      </c>
+      <c r="C99" s="333"/>
+      <c r="D99" s="334"/>
+      <c r="E99" s="334"/>
+      <c r="F99" s="334"/>
+      <c r="G99" s="334"/>
+      <c r="H99" s="335"/>
     </row>
     <row r="100" spans="2:8" ht="21" x14ac:dyDescent="0.25">
       <c r="B100" s="130"/>
       <c r="C100" s="130" t="s">
-        <v>1652</v>
+        <v>1650</v>
       </c>
       <c r="D100" s="121"/>
       <c r="E100" s="121"/>
@@ -28174,7 +28257,7 @@
     <row r="101" spans="2:8" ht="21" x14ac:dyDescent="0.25">
       <c r="B101" s="130"/>
       <c r="C101" s="130" t="s">
-        <v>1653</v>
+        <v>1651</v>
       </c>
       <c r="D101" s="121"/>
       <c r="E101" s="121"/>
@@ -28187,7 +28270,7 @@
     <row r="102" spans="2:8" ht="21" x14ac:dyDescent="0.25">
       <c r="B102" s="130"/>
       <c r="C102" s="130" t="s">
-        <v>1688</v>
+        <v>1686</v>
       </c>
       <c r="D102" s="121"/>
       <c r="E102" s="121"/>
@@ -28198,22 +28281,22 @@
       </c>
     </row>
     <row r="103" spans="2:8" ht="29" x14ac:dyDescent="0.35">
-      <c r="B103" s="324"/>
+      <c r="B103" s="322"/>
       <c r="C103" s="130" t="s">
-        <v>1654</v>
+        <v>1652</v>
       </c>
       <c r="D103" s="121"/>
-      <c r="E103" s="324"/>
-      <c r="F103" s="324"/>
-      <c r="G103" s="324"/>
-      <c r="H103" s="338">
+      <c r="E103" s="322"/>
+      <c r="F103" s="322"/>
+      <c r="G103" s="322"/>
+      <c r="H103" s="336">
         <v>10.02</v>
       </c>
     </row>
     <row r="104" spans="2:8" ht="21" x14ac:dyDescent="0.25">
       <c r="B104" s="130"/>
       <c r="C104" s="130" t="s">
-        <v>1692</v>
+        <v>1690</v>
       </c>
       <c r="D104" s="121"/>
       <c r="E104" s="121"/>
@@ -28226,7 +28309,7 @@
     <row r="105" spans="2:8" ht="21" x14ac:dyDescent="0.25">
       <c r="B105" s="121"/>
       <c r="C105" s="130" t="s">
-        <v>1655</v>
+        <v>1653</v>
       </c>
       <c r="D105" s="121"/>
       <c r="E105" s="121"/>
@@ -28258,44 +28341,44 @@
   <sheetData>
     <row r="2" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B3" s="349" t="s">
-        <v>1659</v>
-      </c>
-      <c r="C3" s="349"/>
-      <c r="D3" s="349"/>
-      <c r="E3" s="349"/>
-      <c r="F3" s="349"/>
-      <c r="G3" s="349"/>
-      <c r="H3" s="349"/>
-      <c r="I3" s="349"/>
-      <c r="J3" s="349"/>
-      <c r="K3" s="349"/>
+      <c r="B3" s="367" t="s">
+        <v>1657</v>
+      </c>
+      <c r="C3" s="367"/>
+      <c r="D3" s="367"/>
+      <c r="E3" s="367"/>
+      <c r="F3" s="367"/>
+      <c r="G3" s="367"/>
+      <c r="H3" s="367"/>
+      <c r="I3" s="367"/>
+      <c r="J3" s="367"/>
+      <c r="K3" s="367"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B4" s="349"/>
-      <c r="C4" s="349"/>
-      <c r="D4" s="349"/>
-      <c r="E4" s="349"/>
-      <c r="F4" s="349"/>
-      <c r="G4" s="349"/>
-      <c r="H4" s="349"/>
-      <c r="I4" s="349"/>
-      <c r="J4" s="349"/>
-      <c r="K4" s="349"/>
+      <c r="B4" s="367"/>
+      <c r="C4" s="367"/>
+      <c r="D4" s="367"/>
+      <c r="E4" s="367"/>
+      <c r="F4" s="367"/>
+      <c r="G4" s="367"/>
+      <c r="H4" s="367"/>
+      <c r="I4" s="367"/>
+      <c r="J4" s="367"/>
+      <c r="K4" s="367"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
-        <v>1589</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="1:11" ht="20" x14ac:dyDescent="0.2">
       <c r="A7" s="9"/>
       <c r="B7" s="13"/>
-      <c r="C7" s="353" t="s">
+      <c r="C7" s="371" t="s">
         <v>102</v>
       </c>
-      <c r="D7" s="353" t="s">
+      <c r="D7" s="371" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="8" t="s">
@@ -28311,8 +28394,8 @@
     <row r="8" spans="1:11" ht="21" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9"/>
       <c r="B8" s="13"/>
-      <c r="C8" s="355"/>
-      <c r="D8" s="354"/>
+      <c r="C8" s="373"/>
+      <c r="D8" s="372"/>
       <c r="E8" s="16" t="s">
         <v>100</v>
       </c>
@@ -28396,38 +28479,38 @@
   <sheetData>
     <row r="1" spans="2:13" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:13" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="349" t="s">
-        <v>1660</v>
-      </c>
-      <c r="C2" s="349"/>
-      <c r="D2" s="349"/>
-      <c r="E2" s="349"/>
-      <c r="F2" s="349"/>
-      <c r="G2" s="349"/>
-      <c r="H2" s="349"/>
-      <c r="I2" s="349"/>
-      <c r="J2" s="349"/>
-      <c r="K2" s="349"/>
-      <c r="L2" s="349"/>
-      <c r="M2" s="349"/>
+      <c r="B2" s="367" t="s">
+        <v>1658</v>
+      </c>
+      <c r="C2" s="367"/>
+      <c r="D2" s="367"/>
+      <c r="E2" s="367"/>
+      <c r="F2" s="367"/>
+      <c r="G2" s="367"/>
+      <c r="H2" s="367"/>
+      <c r="I2" s="367"/>
+      <c r="J2" s="367"/>
+      <c r="K2" s="367"/>
+      <c r="L2" s="367"/>
+      <c r="M2" s="367"/>
     </row>
     <row r="3" spans="2:13" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="349"/>
-      <c r="C3" s="349"/>
-      <c r="D3" s="349"/>
-      <c r="E3" s="349"/>
-      <c r="F3" s="349"/>
-      <c r="G3" s="349"/>
-      <c r="H3" s="349"/>
-      <c r="I3" s="349"/>
-      <c r="J3" s="349"/>
-      <c r="K3" s="349"/>
-      <c r="L3" s="349"/>
-      <c r="M3" s="349"/>
+      <c r="B3" s="367"/>
+      <c r="C3" s="367"/>
+      <c r="D3" s="367"/>
+      <c r="E3" s="367"/>
+      <c r="F3" s="367"/>
+      <c r="G3" s="367"/>
+      <c r="H3" s="367"/>
+      <c r="I3" s="367"/>
+      <c r="J3" s="367"/>
+      <c r="K3" s="367"/>
+      <c r="L3" s="367"/>
+      <c r="M3" s="367"/>
     </row>
     <row r="4" spans="2:13" ht="19" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>1589</v>
+        <v>1587</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
@@ -28446,7 +28529,7 @@
       <c r="H5" s="4"/>
     </row>
     <row r="6" spans="2:13" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="351" t="s">
+      <c r="B6" s="369" t="s">
         <v>99</v>
       </c>
       <c r="C6" s="8" t="s">
@@ -28454,7 +28537,7 @@
       </c>
       <c r="D6" s="18"/>
       <c r="E6" s="18"/>
-      <c r="F6" s="351" t="s">
+      <c r="F6" s="369" t="s">
         <v>99</v>
       </c>
       <c r="G6" s="8" t="s">
@@ -28463,13 +28546,13 @@
       <c r="H6" s="19"/>
     </row>
     <row r="7" spans="2:13" s="7" customFormat="1" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="357"/>
+      <c r="B7" s="375"/>
       <c r="C7" s="10" t="s">
         <v>100</v>
       </c>
       <c r="D7" s="18"/>
       <c r="E7" s="18"/>
-      <c r="F7" s="357"/>
+      <c r="F7" s="375"/>
       <c r="G7" s="10" t="s">
         <v>100</v>
       </c>
@@ -29473,47 +29556,47 @@
   <sheetData>
     <row r="1" spans="2:13" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:13" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="349" t="s">
-        <v>1661</v>
-      </c>
-      <c r="C2" s="349"/>
-      <c r="D2" s="349"/>
-      <c r="E2" s="349"/>
-      <c r="F2" s="349"/>
-      <c r="G2" s="349"/>
-      <c r="H2" s="349"/>
-      <c r="I2" s="349"/>
-      <c r="J2" s="349"/>
-      <c r="K2" s="349"/>
-      <c r="L2" s="349"/>
-      <c r="M2" s="349"/>
+      <c r="B2" s="367" t="s">
+        <v>1659</v>
+      </c>
+      <c r="C2" s="367"/>
+      <c r="D2" s="367"/>
+      <c r="E2" s="367"/>
+      <c r="F2" s="367"/>
+      <c r="G2" s="367"/>
+      <c r="H2" s="367"/>
+      <c r="I2" s="367"/>
+      <c r="J2" s="367"/>
+      <c r="K2" s="367"/>
+      <c r="L2" s="367"/>
+      <c r="M2" s="367"/>
     </row>
     <row r="3" spans="2:13" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="349"/>
-      <c r="C3" s="349"/>
-      <c r="D3" s="349"/>
-      <c r="E3" s="349"/>
-      <c r="F3" s="349"/>
-      <c r="G3" s="349"/>
-      <c r="H3" s="349"/>
-      <c r="I3" s="349"/>
-      <c r="J3" s="349"/>
-      <c r="K3" s="349"/>
-      <c r="L3" s="349"/>
-      <c r="M3" s="349"/>
+      <c r="B3" s="367"/>
+      <c r="C3" s="367"/>
+      <c r="D3" s="367"/>
+      <c r="E3" s="367"/>
+      <c r="F3" s="367"/>
+      <c r="G3" s="367"/>
+      <c r="H3" s="367"/>
+      <c r="I3" s="367"/>
+      <c r="J3" s="367"/>
+      <c r="K3" s="367"/>
+      <c r="L3" s="367"/>
+      <c r="M3" s="367"/>
     </row>
     <row r="4" spans="2:13" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
-        <v>1589</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="5" spans="2:13" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="2:13" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="13"/>
-      <c r="C6" s="353" t="s">
+      <c r="C6" s="371" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="353" t="s">
+      <c r="D6" s="371" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="8" t="s">
@@ -29523,8 +29606,8 @@
       <c r="G6" s="13"/>
     </row>
     <row r="7" spans="2:13" s="9" customFormat="1" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C7" s="354"/>
-      <c r="D7" s="354"/>
+      <c r="C7" s="372"/>
+      <c r="D7" s="372"/>
       <c r="E7" s="16" t="s">
         <v>100</v>
       </c>
@@ -29951,47 +30034,47 @@
   <sheetData>
     <row r="1" spans="2:13" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:13" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="349" t="s">
-        <v>1662</v>
-      </c>
-      <c r="C2" s="349"/>
-      <c r="D2" s="349"/>
-      <c r="E2" s="349"/>
-      <c r="F2" s="349"/>
-      <c r="G2" s="349"/>
-      <c r="H2" s="349"/>
-      <c r="I2" s="349"/>
-      <c r="J2" s="349"/>
-      <c r="K2" s="349"/>
-      <c r="L2" s="349"/>
-      <c r="M2" s="349"/>
+      <c r="B2" s="367" t="s">
+        <v>1660</v>
+      </c>
+      <c r="C2" s="367"/>
+      <c r="D2" s="367"/>
+      <c r="E2" s="367"/>
+      <c r="F2" s="367"/>
+      <c r="G2" s="367"/>
+      <c r="H2" s="367"/>
+      <c r="I2" s="367"/>
+      <c r="J2" s="367"/>
+      <c r="K2" s="367"/>
+      <c r="L2" s="367"/>
+      <c r="M2" s="367"/>
     </row>
     <row r="3" spans="2:13" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="349"/>
-      <c r="C3" s="349"/>
-      <c r="D3" s="349"/>
-      <c r="E3" s="349"/>
-      <c r="F3" s="349"/>
-      <c r="G3" s="349"/>
-      <c r="H3" s="349"/>
-      <c r="I3" s="349"/>
-      <c r="J3" s="349"/>
-      <c r="K3" s="349"/>
-      <c r="L3" s="349"/>
-      <c r="M3" s="349"/>
+      <c r="B3" s="367"/>
+      <c r="C3" s="367"/>
+      <c r="D3" s="367"/>
+      <c r="E3" s="367"/>
+      <c r="F3" s="367"/>
+      <c r="G3" s="367"/>
+      <c r="H3" s="367"/>
+      <c r="I3" s="367"/>
+      <c r="J3" s="367"/>
+      <c r="K3" s="367"/>
+      <c r="L3" s="367"/>
+      <c r="M3" s="367"/>
     </row>
     <row r="4" spans="2:13" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="2:13" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
-        <v>1589</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="6" spans="2:13" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="13"/>
-      <c r="C6" s="350" t="s">
+      <c r="C6" s="368" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="350" t="s">
+      <c r="D6" s="368" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="120" t="s">
@@ -30001,8 +30084,8 @@
       <c r="G6" s="13"/>
     </row>
     <row r="7" spans="2:13" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C7" s="350"/>
-      <c r="D7" s="350"/>
+      <c r="C7" s="368"/>
+      <c r="D7" s="368"/>
       <c r="E7" s="120" t="s">
         <v>100</v>
       </c>
@@ -30566,45 +30649,45 @@
   <sheetData>
     <row r="1" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B1" t="s">
-        <v>1589</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="2" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="349" t="s">
-        <v>1665</v>
-      </c>
-      <c r="C2" s="349"/>
-      <c r="D2" s="349"/>
-      <c r="E2" s="349"/>
-      <c r="F2" s="349"/>
-      <c r="G2" s="349"/>
-      <c r="H2" s="349"/>
-      <c r="I2" s="349"/>
-      <c r="J2" s="349"/>
-      <c r="K2" s="349"/>
-      <c r="L2" s="349"/>
+      <c r="B2" s="367" t="s">
+        <v>1663</v>
+      </c>
+      <c r="C2" s="367"/>
+      <c r="D2" s="367"/>
+      <c r="E2" s="367"/>
+      <c r="F2" s="367"/>
+      <c r="G2" s="367"/>
+      <c r="H2" s="367"/>
+      <c r="I2" s="367"/>
+      <c r="J2" s="367"/>
+      <c r="K2" s="367"/>
+      <c r="L2" s="367"/>
     </row>
     <row r="3" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="349"/>
-      <c r="C3" s="349"/>
-      <c r="D3" s="349"/>
-      <c r="E3" s="349"/>
-      <c r="F3" s="349"/>
-      <c r="G3" s="349"/>
-      <c r="H3" s="349"/>
-      <c r="I3" s="349"/>
-      <c r="J3" s="349"/>
-      <c r="K3" s="349"/>
-      <c r="L3" s="349"/>
+      <c r="B3" s="367"/>
+      <c r="C3" s="367"/>
+      <c r="D3" s="367"/>
+      <c r="E3" s="367"/>
+      <c r="F3" s="367"/>
+      <c r="G3" s="367"/>
+      <c r="H3" s="367"/>
+      <c r="I3" s="367"/>
+      <c r="J3" s="367"/>
+      <c r="K3" s="367"/>
+      <c r="L3" s="367"/>
     </row>
     <row r="4" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="6" spans="2:12" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="13"/>
-      <c r="C6" s="350" t="s">
+      <c r="C6" s="368" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="350" t="s">
+      <c r="D6" s="368" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="120" t="s">
@@ -30615,8 +30698,8 @@
     </row>
     <row r="7" spans="2:12" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="13"/>
-      <c r="C7" s="350"/>
-      <c r="D7" s="350"/>
+      <c r="C7" s="368"/>
+      <c r="D7" s="368"/>
       <c r="E7" s="120" t="s">
         <v>100</v>
       </c>
@@ -30997,45 +31080,45 @@
   <sheetData>
     <row r="1" spans="2:12" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="349" t="s">
-        <v>1663</v>
-      </c>
-      <c r="C2" s="349"/>
-      <c r="D2" s="349"/>
-      <c r="E2" s="349"/>
-      <c r="F2" s="349"/>
-      <c r="G2" s="349"/>
-      <c r="H2" s="349"/>
-      <c r="I2" s="349"/>
-      <c r="J2" s="349"/>
-      <c r="K2" s="349"/>
-      <c r="L2" s="349"/>
+      <c r="B2" s="367" t="s">
+        <v>1661</v>
+      </c>
+      <c r="C2" s="367"/>
+      <c r="D2" s="367"/>
+      <c r="E2" s="367"/>
+      <c r="F2" s="367"/>
+      <c r="G2" s="367"/>
+      <c r="H2" s="367"/>
+      <c r="I2" s="367"/>
+      <c r="J2" s="367"/>
+      <c r="K2" s="367"/>
+      <c r="L2" s="367"/>
     </row>
     <row r="3" spans="2:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="349"/>
-      <c r="C3" s="349"/>
-      <c r="D3" s="349"/>
-      <c r="E3" s="349"/>
-      <c r="F3" s="349"/>
-      <c r="G3" s="349"/>
-      <c r="H3" s="349"/>
-      <c r="I3" s="349"/>
-      <c r="J3" s="349"/>
-      <c r="K3" s="349"/>
-      <c r="L3" s="349"/>
+      <c r="B3" s="367"/>
+      <c r="C3" s="367"/>
+      <c r="D3" s="367"/>
+      <c r="E3" s="367"/>
+      <c r="F3" s="367"/>
+      <c r="G3" s="367"/>
+      <c r="H3" s="367"/>
+      <c r="I3" s="367"/>
+      <c r="J3" s="367"/>
+      <c r="K3" s="367"/>
+      <c r="L3" s="367"/>
     </row>
     <row r="4" spans="2:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
-        <v>1589</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="5" spans="2:12" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="2:12" s="9" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="13"/>
-      <c r="C6" s="353" t="s">
+      <c r="C6" s="371" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="353" t="s">
+      <c r="D6" s="371" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="14" t="s">
@@ -31043,10 +31126,10 @@
       </c>
       <c r="F6" s="13"/>
       <c r="G6" s="13"/>
-      <c r="H6" s="353" t="s">
+      <c r="H6" s="371" t="s">
         <v>102</v>
       </c>
-      <c r="I6" s="353" t="s">
+      <c r="I6" s="371" t="s">
         <v>0</v>
       </c>
       <c r="J6" s="8" t="s">
@@ -31054,14 +31137,14 @@
       </c>
     </row>
     <row r="7" spans="2:12" s="9" customFormat="1" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C7" s="355"/>
-      <c r="D7" s="355"/>
+      <c r="C7" s="373"/>
+      <c r="D7" s="373"/>
       <c r="E7" s="15" t="s">
         <v>98</v>
       </c>
       <c r="G7" s="20"/>
-      <c r="H7" s="354"/>
-      <c r="I7" s="354"/>
+      <c r="H7" s="372"/>
+      <c r="I7" s="372"/>
       <c r="J7" s="16" t="s">
         <v>100</v>
       </c>
@@ -31496,75 +31579,75 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A2" s="349" t="s">
-        <v>1593</v>
-      </c>
-      <c r="B2" s="349"/>
-      <c r="C2" s="349"/>
-      <c r="D2" s="349"/>
-      <c r="E2" s="349"/>
-      <c r="F2" s="349"/>
-      <c r="G2" s="349"/>
-      <c r="H2" s="349"/>
-      <c r="I2" s="349"/>
-      <c r="J2" s="349"/>
-      <c r="K2" s="349"/>
-      <c r="L2" s="349"/>
-      <c r="M2" s="349"/>
-      <c r="N2" s="349"/>
+      <c r="A2" s="367" t="s">
+        <v>1591</v>
+      </c>
+      <c r="B2" s="367"/>
+      <c r="C2" s="367"/>
+      <c r="D2" s="367"/>
+      <c r="E2" s="367"/>
+      <c r="F2" s="367"/>
+      <c r="G2" s="367"/>
+      <c r="H2" s="367"/>
+      <c r="I2" s="367"/>
+      <c r="J2" s="367"/>
+      <c r="K2" s="367"/>
+      <c r="L2" s="367"/>
+      <c r="M2" s="367"/>
+      <c r="N2" s="367"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A3" s="349"/>
-      <c r="B3" s="349"/>
-      <c r="C3" s="349"/>
-      <c r="D3" s="349"/>
-      <c r="E3" s="349"/>
-      <c r="F3" s="349"/>
-      <c r="G3" s="349"/>
-      <c r="H3" s="349"/>
-      <c r="I3" s="349"/>
-      <c r="J3" s="349"/>
-      <c r="K3" s="349"/>
-      <c r="L3" s="349"/>
-      <c r="M3" s="349"/>
-      <c r="N3" s="349"/>
+      <c r="A3" s="367"/>
+      <c r="B3" s="367"/>
+      <c r="C3" s="367"/>
+      <c r="D3" s="367"/>
+      <c r="E3" s="367"/>
+      <c r="F3" s="367"/>
+      <c r="G3" s="367"/>
+      <c r="H3" s="367"/>
+      <c r="I3" s="367"/>
+      <c r="J3" s="367"/>
+      <c r="K3" s="367"/>
+      <c r="L3" s="367"/>
+      <c r="M3" s="367"/>
+      <c r="N3" s="367"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>1589</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="1:14" ht="20" x14ac:dyDescent="0.2">
-      <c r="A6" s="353" t="s">
+      <c r="A6" s="371" t="s">
         <v>99</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>101</v>
       </c>
       <c r="C6" s="9"/>
-      <c r="D6" s="353" t="s">
+      <c r="D6" s="371" t="s">
         <v>99</v>
       </c>
       <c r="E6" s="8" t="s">
         <v>101</v>
       </c>
       <c r="F6" s="101"/>
-      <c r="G6" s="353" t="s">
+      <c r="G6" s="371" t="s">
         <v>99</v>
       </c>
       <c r="H6" s="8" t="s">
         <v>101</v>
       </c>
       <c r="I6" s="9"/>
-      <c r="J6" s="353" t="s">
+      <c r="J6" s="371" t="s">
         <v>99</v>
       </c>
       <c r="K6" s="8" t="s">
         <v>101</v>
       </c>
       <c r="L6" s="9"/>
-      <c r="M6" s="353" t="s">
+      <c r="M6" s="371" t="s">
         <v>99</v>
       </c>
       <c r="N6" s="44" t="s">
@@ -31572,27 +31655,27 @@
       </c>
     </row>
     <row r="7" spans="1:14" ht="21" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="355"/>
+      <c r="A7" s="373"/>
       <c r="B7" s="10" t="s">
         <v>98</v>
       </c>
       <c r="C7" s="9"/>
-      <c r="D7" s="355"/>
+      <c r="D7" s="373"/>
       <c r="E7" s="10" t="s">
         <v>98</v>
       </c>
       <c r="F7" s="101"/>
-      <c r="G7" s="355"/>
+      <c r="G7" s="373"/>
       <c r="H7" s="10" t="s">
         <v>98</v>
       </c>
       <c r="I7" s="9"/>
-      <c r="J7" s="355"/>
+      <c r="J7" s="373"/>
       <c r="K7" s="10" t="s">
         <v>100</v>
       </c>
       <c r="L7" s="9"/>
-      <c r="M7" s="355"/>
+      <c r="M7" s="373"/>
       <c r="N7" s="45" t="s">
         <v>100</v>
       </c>
@@ -33860,13 +33943,13 @@
     <row r="78" spans="1:14" ht="21" x14ac:dyDescent="0.25">
       <c r="D78" s="144"/>
       <c r="E78" s="222"/>
-      <c r="J78" s="356" t="s">
+      <c r="J78" s="374" t="s">
         <v>771</v>
       </c>
-      <c r="K78" s="356"/>
-      <c r="L78" s="356"/>
-      <c r="M78" s="356"/>
-      <c r="N78" s="356"/>
+      <c r="K78" s="374"/>
+      <c r="L78" s="374"/>
+      <c r="M78" s="374"/>
+      <c r="N78" s="374"/>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D79" s="144"/>
@@ -33976,78 +34059,78 @@
   <sheetData>
     <row r="1" spans="2:25" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:25" ht="19" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="412" t="s">
-        <v>1664</v>
-      </c>
-      <c r="C2" s="412"/>
-      <c r="D2" s="412"/>
-      <c r="E2" s="412"/>
-      <c r="F2" s="412"/>
-      <c r="G2" s="412"/>
-      <c r="H2" s="412"/>
-      <c r="I2" s="412"/>
-      <c r="J2" s="412"/>
-      <c r="K2" s="412"/>
-      <c r="L2" s="412"/>
-      <c r="M2" s="412"/>
-      <c r="P2" s="416" t="s">
-        <v>1664</v>
-      </c>
-      <c r="Q2" s="416"/>
-      <c r="R2" s="416"/>
-      <c r="S2" s="416"/>
-      <c r="T2" s="416"/>
-      <c r="U2" s="416"/>
-      <c r="V2" s="416"/>
-      <c r="W2" s="416"/>
-      <c r="X2" s="416"/>
+      <c r="B2" s="431" t="s">
+        <v>1662</v>
+      </c>
+      <c r="C2" s="431"/>
+      <c r="D2" s="431"/>
+      <c r="E2" s="431"/>
+      <c r="F2" s="431"/>
+      <c r="G2" s="431"/>
+      <c r="H2" s="431"/>
+      <c r="I2" s="431"/>
+      <c r="J2" s="431"/>
+      <c r="K2" s="431"/>
+      <c r="L2" s="431"/>
+      <c r="M2" s="431"/>
+      <c r="P2" s="435" t="s">
+        <v>1662</v>
+      </c>
+      <c r="Q2" s="435"/>
+      <c r="R2" s="435"/>
+      <c r="S2" s="435"/>
+      <c r="T2" s="435"/>
+      <c r="U2" s="435"/>
+      <c r="V2" s="435"/>
+      <c r="W2" s="435"/>
+      <c r="X2" s="435"/>
       <c r="Y2" s="48"/>
     </row>
     <row r="3" spans="2:25" ht="19" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="412"/>
-      <c r="C3" s="412"/>
-      <c r="D3" s="412"/>
-      <c r="E3" s="412"/>
-      <c r="F3" s="412"/>
-      <c r="G3" s="412"/>
-      <c r="H3" s="412"/>
-      <c r="I3" s="412"/>
-      <c r="J3" s="412"/>
-      <c r="K3" s="412"/>
-      <c r="L3" s="412"/>
-      <c r="M3" s="412"/>
-      <c r="P3" s="416"/>
-      <c r="Q3" s="416"/>
-      <c r="R3" s="416"/>
-      <c r="S3" s="416"/>
-      <c r="T3" s="416"/>
-      <c r="U3" s="416"/>
-      <c r="V3" s="416"/>
-      <c r="W3" s="416"/>
-      <c r="X3" s="416"/>
+      <c r="B3" s="431"/>
+      <c r="C3" s="431"/>
+      <c r="D3" s="431"/>
+      <c r="E3" s="431"/>
+      <c r="F3" s="431"/>
+      <c r="G3" s="431"/>
+      <c r="H3" s="431"/>
+      <c r="I3" s="431"/>
+      <c r="J3" s="431"/>
+      <c r="K3" s="431"/>
+      <c r="L3" s="431"/>
+      <c r="M3" s="431"/>
+      <c r="P3" s="435"/>
+      <c r="Q3" s="435"/>
+      <c r="R3" s="435"/>
+      <c r="S3" s="435"/>
+      <c r="T3" s="435"/>
+      <c r="U3" s="435"/>
+      <c r="V3" s="435"/>
+      <c r="W3" s="435"/>
+      <c r="X3" s="435"/>
       <c r="Y3" s="48"/>
     </row>
     <row r="4" spans="2:25" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
-        <v>1589</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="5" spans="2:25" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="2:25" s="9" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="353" t="s">
+      <c r="B6" s="371" t="s">
         <v>99</v>
       </c>
       <c r="C6" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="E6" s="353" t="s">
+      <c r="E6" s="371" t="s">
         <v>99</v>
       </c>
       <c r="F6" s="14" t="s">
         <v>101</v>
       </c>
       <c r="G6" s="13"/>
-      <c r="H6" s="353" t="s">
+      <c r="H6" s="371" t="s">
         <v>99</v>
       </c>
       <c r="I6" s="44" t="s">
@@ -34055,16 +34138,16 @@
       </c>
     </row>
     <row r="7" spans="2:25" s="9" customFormat="1" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="355"/>
+      <c r="B7" s="373"/>
       <c r="C7" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E7" s="355"/>
+      <c r="E7" s="373"/>
       <c r="F7" s="15" t="s">
         <v>98</v>
       </c>
       <c r="G7" s="20"/>
-      <c r="H7" s="355"/>
+      <c r="H7" s="373"/>
       <c r="I7" s="45" t="s">
         <v>100</v>
       </c>
@@ -34089,11 +34172,11 @@
       <c r="I8" s="92">
         <v>4.8767983845059435</v>
       </c>
-      <c r="P8" s="402" t="s">
+      <c r="P8" s="421" t="s">
         <v>82</v>
       </c>
-      <c r="Q8" s="403"/>
-      <c r="R8" s="404"/>
+      <c r="Q8" s="422"/>
+      <c r="R8" s="423"/>
     </row>
     <row r="9" spans="2:25" s="7" customFormat="1" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="159">
@@ -34115,9 +34198,9 @@
       <c r="I9" s="92">
         <v>5.3561154711092742</v>
       </c>
-      <c r="P9" s="413"/>
-      <c r="Q9" s="414"/>
-      <c r="R9" s="415"/>
+      <c r="P9" s="432"/>
+      <c r="Q9" s="433"/>
+      <c r="R9" s="434"/>
     </row>
     <row r="10" spans="2:25" s="7" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="159">
@@ -34169,10 +34252,10 @@
       <c r="I11" s="92">
         <v>7.3820661801826617</v>
       </c>
-      <c r="P11" s="417" t="s">
+      <c r="P11" s="436" t="s">
         <v>480</v>
       </c>
-      <c r="Q11" s="417"/>
+      <c r="Q11" s="436"/>
       <c r="R11" s="202">
         <v>10.080053500127852</v>
       </c>
@@ -34197,10 +34280,10 @@
       <c r="I12" s="92">
         <v>5.4229969250539263</v>
       </c>
-      <c r="P12" s="417" t="s">
+      <c r="P12" s="436" t="s">
         <v>481</v>
       </c>
-      <c r="Q12" s="417"/>
+      <c r="Q12" s="436"/>
       <c r="R12" s="202">
         <v>8.0737987057689669</v>
       </c>
@@ -34225,10 +34308,10 @@
       <c r="I13" s="92">
         <v>5.6849492863371438</v>
       </c>
-      <c r="P13" s="417" t="s">
+      <c r="P13" s="436" t="s">
         <v>482</v>
       </c>
-      <c r="Q13" s="417"/>
+      <c r="Q13" s="436"/>
       <c r="R13" s="202">
         <v>7.9935485139946119</v>
       </c>
@@ -34253,10 +34336,10 @@
       <c r="I14" s="92">
         <v>5.7936316489972013</v>
       </c>
-      <c r="P14" s="417" t="s">
+      <c r="P14" s="436" t="s">
         <v>483</v>
       </c>
-      <c r="Q14" s="417"/>
+      <c r="Q14" s="436"/>
       <c r="R14" s="202">
         <v>7.3515469797997683</v>
       </c>
@@ -35051,45 +35134,45 @@
     </row>
     <row r="72" spans="2:13" s="7" customFormat="1" ht="20" x14ac:dyDescent="0.2"/>
     <row r="73" spans="2:13" s="7" customFormat="1" ht="20" x14ac:dyDescent="0.2">
-      <c r="B73" s="412" t="s">
+      <c r="B73" s="431" t="s">
         <v>785</v>
       </c>
-      <c r="C73" s="412"/>
-      <c r="D73" s="412"/>
-      <c r="E73" s="412"/>
-      <c r="F73" s="412"/>
-      <c r="G73" s="412"/>
-      <c r="H73" s="412"/>
-      <c r="I73" s="412"/>
-      <c r="J73" s="412"/>
-      <c r="K73" s="412"/>
-      <c r="L73" s="412"/>
-      <c r="M73" s="412"/>
+      <c r="C73" s="431"/>
+      <c r="D73" s="431"/>
+      <c r="E73" s="431"/>
+      <c r="F73" s="431"/>
+      <c r="G73" s="431"/>
+      <c r="H73" s="431"/>
+      <c r="I73" s="431"/>
+      <c r="J73" s="431"/>
+      <c r="K73" s="431"/>
+      <c r="L73" s="431"/>
+      <c r="M73" s="431"/>
     </row>
     <row r="74" spans="2:13" s="7" customFormat="1" ht="20" x14ac:dyDescent="0.2">
-      <c r="B74" s="412"/>
-      <c r="C74" s="412"/>
-      <c r="D74" s="412"/>
-      <c r="E74" s="412"/>
-      <c r="F74" s="412"/>
-      <c r="G74" s="412"/>
-      <c r="H74" s="412"/>
-      <c r="I74" s="412"/>
-      <c r="J74" s="412"/>
-      <c r="K74" s="412"/>
-      <c r="L74" s="412"/>
-      <c r="M74" s="412"/>
+      <c r="B74" s="431"/>
+      <c r="C74" s="431"/>
+      <c r="D74" s="431"/>
+      <c r="E74" s="431"/>
+      <c r="F74" s="431"/>
+      <c r="G74" s="431"/>
+      <c r="H74" s="431"/>
+      <c r="I74" s="431"/>
+      <c r="J74" s="431"/>
+      <c r="K74" s="431"/>
+      <c r="L74" s="431"/>
+      <c r="M74" s="431"/>
     </row>
     <row r="75" spans="2:13" s="7" customFormat="1" ht="21" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="76" spans="2:13" s="7" customFormat="1" ht="20" x14ac:dyDescent="0.2">
-      <c r="B76" s="353" t="s">
+      <c r="B76" s="371" t="s">
         <v>99</v>
       </c>
       <c r="C76" s="44" t="s">
         <v>84</v>
       </c>
       <c r="D76" s="9"/>
-      <c r="E76" s="353" t="s">
+      <c r="E76" s="371" t="s">
         <v>99</v>
       </c>
       <c r="F76" s="44" t="s">
@@ -35097,12 +35180,12 @@
       </c>
     </row>
     <row r="77" spans="2:13" s="7" customFormat="1" ht="21" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B77" s="355"/>
+      <c r="B77" s="373"/>
       <c r="C77" s="45" t="s">
         <v>100</v>
       </c>
       <c r="D77" s="9"/>
-      <c r="E77" s="355"/>
+      <c r="E77" s="373"/>
       <c r="F77" s="45" t="s">
         <v>100</v>
       </c>
@@ -35833,49 +35916,49 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>1589</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="349" t="s">
-        <v>1594</v>
-      </c>
-      <c r="B2" s="349"/>
-      <c r="C2" s="349"/>
-      <c r="D2" s="349"/>
-      <c r="E2" s="349"/>
-      <c r="F2" s="349"/>
-      <c r="G2" s="349"/>
-      <c r="H2" s="349"/>
-      <c r="I2" s="349"/>
-      <c r="J2" s="349"/>
-      <c r="K2" s="349"/>
+      <c r="A2" s="367" t="s">
+        <v>1592</v>
+      </c>
+      <c r="B2" s="367"/>
+      <c r="C2" s="367"/>
+      <c r="D2" s="367"/>
+      <c r="E2" s="367"/>
+      <c r="F2" s="367"/>
+      <c r="G2" s="367"/>
+      <c r="H2" s="367"/>
+      <c r="I2" s="367"/>
+      <c r="J2" s="367"/>
+      <c r="K2" s="367"/>
     </row>
     <row r="3" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="349"/>
-      <c r="B3" s="349"/>
-      <c r="C3" s="349"/>
-      <c r="D3" s="349"/>
-      <c r="E3" s="349"/>
-      <c r="F3" s="349"/>
-      <c r="G3" s="349"/>
-      <c r="H3" s="349"/>
-      <c r="I3" s="349"/>
-      <c r="J3" s="349"/>
-      <c r="K3" s="349"/>
+      <c r="A3" s="367"/>
+      <c r="B3" s="367"/>
+      <c r="C3" s="367"/>
+      <c r="D3" s="367"/>
+      <c r="E3" s="367"/>
+      <c r="F3" s="367"/>
+      <c r="G3" s="367"/>
+      <c r="H3" s="367"/>
+      <c r="I3" s="367"/>
+      <c r="J3" s="367"/>
+      <c r="K3" s="367"/>
     </row>
     <row r="4" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="349"/>
-      <c r="B4" s="349"/>
-      <c r="C4" s="349"/>
-      <c r="D4" s="349"/>
-      <c r="E4" s="349"/>
-      <c r="F4" s="349"/>
-      <c r="G4" s="349"/>
-      <c r="H4" s="349"/>
-      <c r="I4" s="349"/>
-      <c r="J4" s="349"/>
-      <c r="K4" s="349"/>
+      <c r="A4" s="367"/>
+      <c r="B4" s="367"/>
+      <c r="C4" s="367"/>
+      <c r="D4" s="367"/>
+      <c r="E4" s="367"/>
+      <c r="F4" s="367"/>
+      <c r="G4" s="367"/>
+      <c r="H4" s="367"/>
+      <c r="I4" s="367"/>
+      <c r="J4" s="367"/>
+      <c r="K4" s="367"/>
     </row>
     <row r="5" spans="1:11" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A5" s="119"/>
@@ -35892,10 +35975,10 @@
     </row>
     <row r="6" spans="1:11" ht="20" x14ac:dyDescent="0.2">
       <c r="A6" s="13"/>
-      <c r="B6" s="351" t="s">
+      <c r="B6" s="369" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="353" t="s">
+      <c r="C6" s="371" t="s">
         <v>0</v>
       </c>
       <c r="D6" s="14" t="s">
@@ -35911,8 +35994,8 @@
     </row>
     <row r="7" spans="1:11" ht="21" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="13"/>
-      <c r="B7" s="357"/>
-      <c r="C7" s="355"/>
+      <c r="B7" s="375"/>
+      <c r="C7" s="373"/>
       <c r="D7" s="15" t="s">
         <v>100</v>
       </c>
@@ -36007,30 +36090,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:17" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B1" s="309" t="s">
-        <v>1589</v>
+      <c r="B1" s="307" t="s">
+        <v>1587</v>
       </c>
     </row>
     <row r="2" spans="2:17" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="346" t="s">
-        <v>1595</v>
-      </c>
-      <c r="C2" s="346"/>
-      <c r="D2" s="346"/>
-      <c r="E2" s="346"/>
-      <c r="F2" s="346"/>
-      <c r="G2" s="346"/>
-      <c r="H2" s="346"/>
+      <c r="B2" s="364" t="s">
+        <v>1593</v>
+      </c>
+      <c r="C2" s="364"/>
+      <c r="D2" s="364"/>
+      <c r="E2" s="364"/>
+      <c r="F2" s="364"/>
+      <c r="G2" s="364"/>
+      <c r="H2" s="364"/>
       <c r="I2" s="38"/>
     </row>
     <row r="3" spans="2:17" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="346"/>
-      <c r="C3" s="346"/>
-      <c r="D3" s="346"/>
-      <c r="E3" s="346"/>
-      <c r="F3" s="346"/>
-      <c r="G3" s="346"/>
-      <c r="H3" s="346"/>
+      <c r="B3" s="364"/>
+      <c r="C3" s="364"/>
+      <c r="D3" s="364"/>
+      <c r="E3" s="364"/>
+      <c r="F3" s="364"/>
+      <c r="G3" s="364"/>
+      <c r="H3" s="364"/>
       <c r="I3" s="38"/>
     </row>
     <row r="4" spans="2:17" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -36040,10 +36123,10 @@
       <c r="Q5" s="41"/>
     </row>
     <row r="6" spans="2:17" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="358" t="s">
+      <c r="B6" s="376" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="358" t="s">
+      <c r="C6" s="376" t="s">
         <v>0</v>
       </c>
       <c r="D6" s="34" t="s">
@@ -36061,8 +36144,8 @@
       <c r="Q6" s="41"/>
     </row>
     <row r="7" spans="2:17" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="359"/>
-      <c r="C7" s="359"/>
+      <c r="B7" s="377"/>
+      <c r="C7" s="377"/>
       <c r="D7" s="36" t="s">
         <v>104</v>
       </c>
@@ -36110,9 +36193,9 @@
       </c>
       <c r="E9" s="31"/>
       <c r="F9" s="32"/>
-      <c r="G9" s="348"/>
-      <c r="H9" s="348"/>
-      <c r="I9" s="348"/>
+      <c r="G9" s="366"/>
+      <c r="H9" s="366"/>
+      <c r="I9" s="366"/>
       <c r="J9" s="32"/>
       <c r="L9" s="31"/>
       <c r="M9" s="32"/>
@@ -36126,9 +36209,9 @@
       <c r="D10" s="54"/>
       <c r="E10" s="31"/>
       <c r="F10" s="32"/>
-      <c r="G10" s="348"/>
-      <c r="H10" s="348"/>
-      <c r="I10" s="348"/>
+      <c r="G10" s="366"/>
+      <c r="H10" s="366"/>
+      <c r="I10" s="366"/>
       <c r="J10" s="32"/>
       <c r="L10" s="31"/>
       <c r="M10" s="32"/>
@@ -36548,28 +36631,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="30" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="340" t="s">
-        <v>1699</v>
-      </c>
-      <c r="B1" s="346" t="s">
-        <v>1700</v>
-      </c>
-      <c r="C1" s="346"/>
-      <c r="D1" s="346"/>
-      <c r="E1" s="346"/>
-      <c r="F1" s="346"/>
-      <c r="G1" s="346"/>
-      <c r="H1" s="346"/>
+      <c r="A1" s="338" t="s">
+        <v>1697</v>
+      </c>
+      <c r="B1" s="364" t="s">
+        <v>1698</v>
+      </c>
+      <c r="C1" s="364"/>
+      <c r="D1" s="364"/>
+      <c r="E1" s="364"/>
+      <c r="F1" s="364"/>
+      <c r="G1" s="364"/>
+      <c r="H1" s="364"/>
       <c r="I1" s="38"/>
     </row>
     <row r="2" spans="1:17" s="30" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="346"/>
-      <c r="C2" s="346"/>
-      <c r="D2" s="346"/>
-      <c r="E2" s="346"/>
-      <c r="F2" s="346"/>
-      <c r="G2" s="346"/>
-      <c r="H2" s="346"/>
+      <c r="B2" s="364"/>
+      <c r="C2" s="364"/>
+      <c r="D2" s="364"/>
+      <c r="E2" s="364"/>
+      <c r="F2" s="364"/>
+      <c r="G2" s="364"/>
+      <c r="H2" s="364"/>
       <c r="I2" s="38"/>
     </row>
     <row r="3" spans="1:17" s="30" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -36579,10 +36662,10 @@
       <c r="Q4" s="41"/>
     </row>
     <row r="5" spans="1:17" s="30" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="347" t="s">
+      <c r="B5" s="365" t="s">
         <v>102</v>
       </c>
-      <c r="C5" s="347" t="s">
+      <c r="C5" s="365" t="s">
         <v>0</v>
       </c>
       <c r="D5" s="114" t="s">
@@ -36600,8 +36683,8 @@
       <c r="Q5" s="41"/>
     </row>
     <row r="6" spans="1:17" s="30" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="347"/>
-      <c r="C6" s="347"/>
+      <c r="B6" s="365"/>
+      <c r="C6" s="365"/>
       <c r="D6" s="114" t="s">
         <v>104</v>
       </c>
@@ -36649,9 +36732,9 @@
       </c>
       <c r="E8" s="31"/>
       <c r="F8" s="32"/>
-      <c r="G8" s="348"/>
-      <c r="H8" s="348"/>
-      <c r="I8" s="348"/>
+      <c r="G8" s="366"/>
+      <c r="H8" s="366"/>
+      <c r="I8" s="366"/>
       <c r="J8" s="32"/>
       <c r="L8" s="31"/>
       <c r="M8" s="32"/>
@@ -36671,9 +36754,9 @@
       </c>
       <c r="E9" s="31"/>
       <c r="F9" s="32"/>
-      <c r="G9" s="348"/>
-      <c r="H9" s="348"/>
-      <c r="I9" s="348"/>
+      <c r="G9" s="366"/>
+      <c r="H9" s="366"/>
+      <c r="I9" s="366"/>
       <c r="J9" s="32"/>
       <c r="L9" s="31"/>
       <c r="M9" s="32"/>
@@ -36770,7 +36853,7 @@
     </row>
     <row r="16" spans="1:17" ht="21" x14ac:dyDescent="0.25">
       <c r="B16" s="113" t="s">
-        <v>1596</v>
+        <v>1594</v>
       </c>
       <c r="C16" s="113" t="s">
         <v>105</v>
@@ -36781,7 +36864,7 @@
     </row>
     <row r="17" spans="2:4" ht="21" x14ac:dyDescent="0.25">
       <c r="B17" s="113" t="s">
-        <v>1596</v>
+        <v>1594</v>
       </c>
       <c r="C17" s="113" t="s">
         <v>83</v>
@@ -36814,7 +36897,7 @@
     </row>
     <row r="20" spans="2:4" ht="21" x14ac:dyDescent="0.25">
       <c r="B20" s="113" t="s">
-        <v>1698</v>
+        <v>1696</v>
       </c>
       <c r="C20" s="113" t="s">
         <v>105</v>
@@ -36825,7 +36908,7 @@
     </row>
     <row r="21" spans="2:4" ht="21" x14ac:dyDescent="0.25">
       <c r="B21" s="113" t="s">
-        <v>1698</v>
+        <v>1696</v>
       </c>
       <c r="C21" s="113" t="s">
         <v>83</v>
@@ -36869,7 +36952,7 @@
     </row>
     <row r="25" spans="2:4" ht="21" x14ac:dyDescent="0.25">
       <c r="B25" s="113" t="s">
-        <v>1597</v>
+        <v>1595</v>
       </c>
       <c r="C25" s="113" t="s">
         <v>83</v>
@@ -36880,7 +36963,7 @@
     </row>
     <row r="26" spans="2:4" ht="21" x14ac:dyDescent="0.25">
       <c r="B26" s="113" t="s">
-        <v>1598</v>
+        <v>1596</v>
       </c>
       <c r="C26" s="113" t="s">
         <v>83</v>
@@ -36947,49 +37030,49 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>1701</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="349" t="s">
-        <v>1591</v>
-      </c>
-      <c r="B2" s="349"/>
-      <c r="C2" s="349"/>
-      <c r="D2" s="349"/>
-      <c r="E2" s="349"/>
-      <c r="F2" s="349"/>
-      <c r="G2" s="349"/>
-      <c r="H2" s="349"/>
-      <c r="I2" s="349"/>
-      <c r="J2" s="349"/>
-      <c r="K2" s="349"/>
+      <c r="A2" s="367" t="s">
+        <v>1589</v>
+      </c>
+      <c r="B2" s="367"/>
+      <c r="C2" s="367"/>
+      <c r="D2" s="367"/>
+      <c r="E2" s="367"/>
+      <c r="F2" s="367"/>
+      <c r="G2" s="367"/>
+      <c r="H2" s="367"/>
+      <c r="I2" s="367"/>
+      <c r="J2" s="367"/>
+      <c r="K2" s="367"/>
     </row>
     <row r="3" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="349"/>
-      <c r="B3" s="349"/>
-      <c r="C3" s="349"/>
-      <c r="D3" s="349"/>
-      <c r="E3" s="349"/>
-      <c r="F3" s="349"/>
-      <c r="G3" s="349"/>
-      <c r="H3" s="349"/>
-      <c r="I3" s="349"/>
-      <c r="J3" s="349"/>
-      <c r="K3" s="349"/>
+      <c r="A3" s="367"/>
+      <c r="B3" s="367"/>
+      <c r="C3" s="367"/>
+      <c r="D3" s="367"/>
+      <c r="E3" s="367"/>
+      <c r="F3" s="367"/>
+      <c r="G3" s="367"/>
+      <c r="H3" s="367"/>
+      <c r="I3" s="367"/>
+      <c r="J3" s="367"/>
+      <c r="K3" s="367"/>
     </row>
     <row r="4" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="349"/>
-      <c r="B4" s="349"/>
-      <c r="C4" s="349"/>
-      <c r="D4" s="349"/>
-      <c r="E4" s="349"/>
-      <c r="F4" s="349"/>
-      <c r="G4" s="349"/>
-      <c r="H4" s="349"/>
-      <c r="I4" s="349"/>
-      <c r="J4" s="349"/>
-      <c r="K4" s="349"/>
+      <c r="A4" s="367"/>
+      <c r="B4" s="367"/>
+      <c r="C4" s="367"/>
+      <c r="D4" s="367"/>
+      <c r="E4" s="367"/>
+      <c r="F4" s="367"/>
+      <c r="G4" s="367"/>
+      <c r="H4" s="367"/>
+      <c r="I4" s="367"/>
+      <c r="J4" s="367"/>
+      <c r="K4" s="367"/>
     </row>
     <row r="5" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="119"/>
@@ -37006,10 +37089,10 @@
     </row>
     <row r="6" spans="1:11" ht="20" x14ac:dyDescent="0.2">
       <c r="A6" s="13"/>
-      <c r="B6" s="350" t="s">
+      <c r="B6" s="368" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="350" t="s">
+      <c r="C6" s="368" t="s">
         <v>0</v>
       </c>
       <c r="D6" s="120" t="s">
@@ -37027,8 +37110,8 @@
     </row>
     <row r="7" spans="1:11" ht="20" x14ac:dyDescent="0.2">
       <c r="A7" s="13"/>
-      <c r="B7" s="350"/>
-      <c r="C7" s="350"/>
+      <c r="B7" s="368"/>
+      <c r="C7" s="368"/>
       <c r="D7" s="120" t="s">
         <v>100</v>
       </c>
@@ -37045,7 +37128,7 @@
     <row r="8" spans="1:11" ht="21" x14ac:dyDescent="0.25">
       <c r="A8" s="7"/>
       <c r="B8" s="113" t="s">
-        <v>1702</v>
+        <v>1700</v>
       </c>
       <c r="C8" s="113" t="s">
         <v>83</v>
@@ -37064,7 +37147,7 @@
     <row r="9" spans="1:11" ht="21" x14ac:dyDescent="0.25">
       <c r="A9" s="7"/>
       <c r="B9" s="113" t="s">
-        <v>1703</v>
+        <v>1701</v>
       </c>
       <c r="C9" s="113" t="s">
         <v>404</v>
@@ -37083,7 +37166,7 @@
     <row r="10" spans="1:11" ht="21" x14ac:dyDescent="0.25">
       <c r="A10" s="7"/>
       <c r="B10" s="113" t="s">
-        <v>1704</v>
+        <v>1702</v>
       </c>
       <c r="C10" s="113" t="s">
         <v>1034</v>
@@ -37101,7 +37184,7 @@
     </row>
     <row r="11" spans="1:11" ht="21" x14ac:dyDescent="0.25">
       <c r="B11" s="113" t="s">
-        <v>1705</v>
+        <v>1703</v>
       </c>
       <c r="C11" s="113" t="s">
         <v>1034</v>

--- a/public/docs/tarifa-italgres.xlsx
+++ b/public/docs/tarifa-italgres.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amont\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5285D00-2698-4322-B568-2F3E01BEB72D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E0D3525-3B93-44B0-8960-91EF9F315CD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,32 +44,33 @@
     <sheet name="IMOLA" sheetId="106" r:id="rId29"/>
     <sheet name="INTERMATEX SPAIN" sheetId="98" r:id="rId30"/>
     <sheet name="ITALCRAFT" sheetId="91" r:id="rId31"/>
-    <sheet name="KTL" sheetId="73" r:id="rId32"/>
-    <sheet name="KRONOS" sheetId="111" r:id="rId33"/>
-    <sheet name="LIFE" sheetId="97" r:id="rId34"/>
-    <sheet name="LIVING" sheetId="65" r:id="rId35"/>
-    <sheet name="MH PARQUETS" sheetId="115" r:id="rId36"/>
-    <sheet name="MIRAGE" sheetId="30" r:id="rId37"/>
-    <sheet name="NATUCER" sheetId="110" r:id="rId38"/>
-    <sheet name="ONIX" sheetId="33" r:id="rId39"/>
-    <sheet name="PAVIGRES" sheetId="114" r:id="rId40"/>
-    <sheet name="PERONDA HARMONY" sheetId="80" r:id="rId41"/>
-    <sheet name="PERONDA-MUSEUM" sheetId="87" r:id="rId42"/>
-    <sheet name="PERONDA" sheetId="81" r:id="rId43"/>
-    <sheet name="PORTOBELLO" sheetId="78" r:id="rId44"/>
-    <sheet name="REALONDA" sheetId="61" r:id="rId45"/>
-    <sheet name="SANT AGOSTINO" sheetId="43" r:id="rId46"/>
-    <sheet name="STN" sheetId="55" r:id="rId47"/>
-    <sheet name="VALLELUNGA" sheetId="82" r:id="rId48"/>
-    <sheet name="VENATTO" sheetId="45" r:id="rId49"/>
-    <sheet name="VIVES" sheetId="47" r:id="rId50"/>
+    <sheet name="KERLUX" sheetId="119" r:id="rId32"/>
+    <sheet name="KTL" sheetId="73" r:id="rId33"/>
+    <sheet name="KRONOS" sheetId="111" r:id="rId34"/>
+    <sheet name="LIFE" sheetId="97" r:id="rId35"/>
+    <sheet name="LIVING" sheetId="65" r:id="rId36"/>
+    <sheet name="MH PARQUETS" sheetId="115" r:id="rId37"/>
+    <sheet name="MIRAGE" sheetId="30" r:id="rId38"/>
+    <sheet name="NATUCER" sheetId="110" r:id="rId39"/>
+    <sheet name="ONIX" sheetId="33" r:id="rId40"/>
+    <sheet name="PAVIGRES" sheetId="114" r:id="rId41"/>
+    <sheet name="PERONDA HARMONY" sheetId="80" r:id="rId42"/>
+    <sheet name="PERONDA-MUSEUM" sheetId="87" r:id="rId43"/>
+    <sheet name="PERONDA" sheetId="81" r:id="rId44"/>
+    <sheet name="PORTOBELLO" sheetId="78" r:id="rId45"/>
+    <sheet name="REALONDA" sheetId="61" r:id="rId46"/>
+    <sheet name="SANT AGOSTINO" sheetId="43" r:id="rId47"/>
+    <sheet name="STN" sheetId="55" r:id="rId48"/>
+    <sheet name="VALLELUNGA" sheetId="82" r:id="rId49"/>
+    <sheet name="VENATTO" sheetId="45" r:id="rId50"/>
+    <sheet name="VIVES" sheetId="47" r:id="rId51"/>
   </sheets>
-  <calcPr calcId="181029" concurrentCalc="0"/>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2611" uniqueCount="1726">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2645" uniqueCount="1739">
   <si>
     <t>SIZE</t>
   </si>
@@ -5481,7 +5482,46 @@
     <t>27.05.26</t>
   </si>
   <si>
-    <t>27-05</t>
+    <t>KERLUX 2026</t>
+  </si>
+  <si>
+    <t>Aneto</t>
+  </si>
+  <si>
+    <t>Devon: Fresno , Haya , Pino and Roble</t>
+  </si>
+  <si>
+    <t>Dorset: Fresno , gris and Roble</t>
+  </si>
+  <si>
+    <t>Ebro, Nervión , Ordesa and Teide</t>
+  </si>
+  <si>
+    <t>Avón: Abeto , Haya and Nogal</t>
+  </si>
+  <si>
+    <t>Baza</t>
+  </si>
+  <si>
+    <t>Clyde: Haya , humo and Nogal</t>
+  </si>
+  <si>
+    <t>Gredos</t>
+  </si>
+  <si>
+    <t>Pirineos</t>
+  </si>
+  <si>
+    <t>Severn: Fresno , haya and roble</t>
+  </si>
+  <si>
+    <t>Trent : Abeto and Roble</t>
+  </si>
+  <si>
+    <t>9"x60"</t>
+  </si>
+  <si>
+    <t>7"x48"</t>
   </si>
 </sst>
 </file>
@@ -7322,7 +7362,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="452">
+  <cellXfs count="458">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="42" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
@@ -7960,16 +8000,16 @@
     </xf>
     <xf numFmtId="2" fontId="112" fillId="0" borderId="30" xfId="246" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="114" fillId="0" borderId="8" xfId="246" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="275" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="2" fontId="112" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="4" borderId="0" xfId="246" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="52" fillId="4" borderId="0" xfId="246" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="53" fillId="4" borderId="0" xfId="246" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="99" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="29" xfId="246" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="52" fillId="4" borderId="29" xfId="246" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="54" fillId="2" borderId="29" xfId="246" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="2" borderId="32" xfId="246" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="51" fillId="4" borderId="0" xfId="246" applyFont="1" applyFill="1" applyAlignment="1">
@@ -8110,6 +8150,15 @@
     <xf numFmtId="0" fontId="78" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="275" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="0" xfId="246" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="52" fillId="4" borderId="0" xfId="246" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="53" fillId="4" borderId="0" xfId="246" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="54" fillId="2" borderId="32" xfId="246" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="49" fillId="3" borderId="1" xfId="246" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -8155,12 +8204,6 @@
     <xf numFmtId="0" fontId="83" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="62" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="67" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="56" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -8171,6 +8214,13 @@
     <xf numFmtId="0" fontId="56" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="62" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="16" fontId="57" fillId="0" borderId="0" xfId="246" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="313">
     <cellStyle name="Comma [0] 2" xfId="248" xr:uid="{00000000-0005-0000-0000-000025010000}"/>
@@ -8858,8 +8908,8 @@
       <c r="G2" s="385"/>
       <c r="H2" s="385"/>
       <c r="I2" s="38"/>
-      <c r="N2" s="325" t="s">
-        <v>1725</v>
+      <c r="M2" s="457">
+        <v>46177</v>
       </c>
     </row>
     <row r="3" spans="1:17" s="30" customFormat="1" ht="19.05" customHeight="1"/>
@@ -8869,10 +8919,10 @@
       <c r="Q4" s="41"/>
     </row>
     <row r="5" spans="1:17" s="30" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B5" s="383" t="s">
+      <c r="B5" s="384" t="s">
         <v>102</v>
       </c>
-      <c r="C5" s="383" t="s">
+      <c r="C5" s="384" t="s">
         <v>0</v>
       </c>
       <c r="D5" s="110" t="s">
@@ -8890,8 +8940,8 @@
       <c r="Q5" s="41"/>
     </row>
     <row r="6" spans="1:17" s="30" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B6" s="383"/>
-      <c r="C6" s="383"/>
+      <c r="B6" s="384"/>
+      <c r="C6" s="384"/>
       <c r="D6" s="110" t="s">
         <v>104</v>
       </c>
@@ -18129,25 +18179,25 @@
       <c r="B1" s="180"/>
     </row>
     <row r="2" spans="2:10" ht="19.05" customHeight="1">
-      <c r="B2" s="380" t="s">
+      <c r="B2" s="432" t="s">
         <v>1636</v>
       </c>
-      <c r="C2" s="380"/>
-      <c r="D2" s="381"/>
-      <c r="E2" s="381"/>
-      <c r="F2" s="381"/>
-      <c r="G2" s="382"/>
+      <c r="C2" s="432"/>
+      <c r="D2" s="433"/>
+      <c r="E2" s="433"/>
+      <c r="F2" s="433"/>
+      <c r="G2" s="434"/>
       <c r="H2" s="38"/>
       <c r="I2" s="38"/>
       <c r="J2" s="38"/>
     </row>
     <row r="3" spans="2:10" ht="19.05" customHeight="1">
-      <c r="B3" s="381"/>
-      <c r="C3" s="381"/>
-      <c r="D3" s="381"/>
-      <c r="E3" s="381"/>
-      <c r="F3" s="381"/>
-      <c r="G3" s="382"/>
+      <c r="B3" s="433"/>
+      <c r="C3" s="433"/>
+      <c r="D3" s="433"/>
+      <c r="E3" s="433"/>
+      <c r="F3" s="433"/>
+      <c r="G3" s="434"/>
       <c r="H3" s="38"/>
       <c r="I3" s="38"/>
       <c r="J3" s="38"/>
@@ -18168,13 +18218,13 @@
       <c r="E5" s="306"/>
     </row>
     <row r="6" spans="2:10" ht="19.05" customHeight="1">
-      <c r="B6" s="383" t="s">
+      <c r="B6" s="384" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="383" t="s">
+      <c r="C6" s="384" t="s">
         <v>106</v>
       </c>
-      <c r="D6" s="383" t="s">
+      <c r="D6" s="384" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="110" t="s">
@@ -18185,9 +18235,9 @@
       </c>
     </row>
     <row r="7" spans="2:10" ht="19.05" customHeight="1" thickBot="1">
-      <c r="B7" s="384"/>
-      <c r="C7" s="384"/>
-      <c r="D7" s="384"/>
+      <c r="B7" s="435"/>
+      <c r="C7" s="435"/>
+      <c r="D7" s="435"/>
       <c r="E7" s="336" t="s">
         <v>100</v>
       </c>
@@ -18267,10 +18317,10 @@
         <v>5.2022121253843681</v>
       </c>
       <c r="F12" s="332"/>
-      <c r="G12" s="379"/>
-      <c r="H12" s="379"/>
-      <c r="I12" s="379"/>
-      <c r="J12" s="379"/>
+      <c r="G12" s="431"/>
+      <c r="H12" s="431"/>
+      <c r="I12" s="431"/>
+      <c r="J12" s="431"/>
     </row>
     <row r="13" spans="2:10" ht="19.05" customHeight="1">
       <c r="B13" s="359" t="s">
@@ -18286,10 +18336,10 @@
         <v>13.685896553306712</v>
       </c>
       <c r="F13" s="332"/>
-      <c r="G13" s="379"/>
-      <c r="H13" s="379"/>
-      <c r="I13" s="379"/>
-      <c r="J13" s="379"/>
+      <c r="G13" s="431"/>
+      <c r="H13" s="431"/>
+      <c r="I13" s="431"/>
+      <c r="J13" s="431"/>
     </row>
     <row r="14" spans="2:10" ht="19.05" customHeight="1">
       <c r="B14" s="359" t="s">
@@ -19091,10 +19141,10 @@
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1"/>
     <row r="6" spans="1:12" ht="21">
-      <c r="B6" s="431" t="s">
+      <c r="B6" s="436" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="433" t="s">
+      <c r="C6" s="438" t="s">
         <v>0</v>
       </c>
       <c r="D6" s="49" t="s">
@@ -19102,8 +19152,8 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="21">
-      <c r="B7" s="432"/>
-      <c r="C7" s="434"/>
+      <c r="B7" s="437"/>
+      <c r="C7" s="439"/>
       <c r="D7" s="128" t="s">
         <v>100</v>
       </c>
@@ -19922,7 +19972,7 @@
     </row>
     <row r="7" spans="1:11" ht="21">
       <c r="A7" s="13"/>
-      <c r="B7" s="435"/>
+      <c r="B7" s="440"/>
       <c r="C7" s="388"/>
       <c r="D7" s="172" t="s">
         <v>100</v>
@@ -20300,6 +20350,285 @@
 </file>
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4BE72FA-D1A2-124C-A05E-3076162811BA}">
+  <dimension ref="B1:E22"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.6"/>
+  <cols>
+    <col min="1" max="1" width="3.5" style="30" customWidth="1"/>
+    <col min="2" max="2" width="43.19921875" style="30" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22" style="244" customWidth="1"/>
+    <col min="4" max="4" width="15.19921875" style="244" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.296875" style="30" customWidth="1"/>
+    <col min="6" max="16384" width="11" style="30"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:5" ht="19.05" customHeight="1">
+      <c r="B1" s="180"/>
+    </row>
+    <row r="2" spans="2:5" ht="19.05" customHeight="1">
+      <c r="B2" s="382" t="s">
+        <v>1725</v>
+      </c>
+      <c r="C2" s="382"/>
+      <c r="D2" s="383"/>
+      <c r="E2" s="383"/>
+    </row>
+    <row r="3" spans="2:5" ht="19.05" customHeight="1">
+      <c r="B3" s="383"/>
+      <c r="C3" s="383"/>
+      <c r="D3" s="383"/>
+      <c r="E3" s="383"/>
+    </row>
+    <row r="4" spans="2:5" ht="19.05" customHeight="1">
+      <c r="B4" s="138" t="s">
+        <v>1724</v>
+      </c>
+      <c r="C4" s="245"/>
+      <c r="D4" s="245"/>
+      <c r="E4" s="138"/>
+    </row>
+    <row r="5" spans="2:5" ht="19.05" customHeight="1">
+      <c r="B5" s="306"/>
+      <c r="C5" s="308"/>
+      <c r="D5" s="308"/>
+      <c r="E5" s="306"/>
+    </row>
+    <row r="6" spans="2:5" ht="19.05" customHeight="1">
+      <c r="B6" s="384" t="s">
+        <v>102</v>
+      </c>
+      <c r="C6" s="384" t="s">
+        <v>106</v>
+      </c>
+      <c r="D6" s="384" t="s">
+        <v>0</v>
+      </c>
+      <c r="E6" s="110" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" ht="19.05" customHeight="1">
+      <c r="B7" s="384"/>
+      <c r="C7" s="384"/>
+      <c r="D7" s="384"/>
+      <c r="E7" s="110" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" ht="19.05" customHeight="1">
+      <c r="B8" s="109" t="s">
+        <v>1726</v>
+      </c>
+      <c r="C8" s="380">
+        <v>5.5</v>
+      </c>
+      <c r="D8" s="380" t="s">
+        <v>1737</v>
+      </c>
+      <c r="E8" s="381">
+        <v>5.0349217077841599</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" ht="19.05" customHeight="1">
+      <c r="B9" s="109" t="s">
+        <v>1727</v>
+      </c>
+      <c r="C9" s="380">
+        <v>5.5</v>
+      </c>
+      <c r="D9" s="380" t="s">
+        <v>1737</v>
+      </c>
+      <c r="E9" s="381">
+        <v>5.0349217077841599</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" ht="19.05" customHeight="1">
+      <c r="B10" s="109" t="s">
+        <v>1727</v>
+      </c>
+      <c r="C10" s="380">
+        <v>6.5</v>
+      </c>
+      <c r="D10" s="380" t="s">
+        <v>1737</v>
+      </c>
+      <c r="E10" s="381">
+        <v>5.3847020389771316</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" ht="19.05" customHeight="1">
+      <c r="B11" s="109" t="s">
+        <v>1728</v>
+      </c>
+      <c r="C11" s="380">
+        <v>5.5</v>
+      </c>
+      <c r="D11" s="380" t="s">
+        <v>1737</v>
+      </c>
+      <c r="E11" s="381">
+        <v>5.0349217077841599</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" ht="19.05" customHeight="1">
+      <c r="B12" s="109" t="s">
+        <v>1729</v>
+      </c>
+      <c r="C12" s="380">
+        <v>5.5</v>
+      </c>
+      <c r="D12" s="380" t="s">
+        <v>1737</v>
+      </c>
+      <c r="E12" s="381">
+        <v>5.0349217077841599</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" ht="19.05" customHeight="1">
+      <c r="B13" s="109" t="s">
+        <v>1730</v>
+      </c>
+      <c r="C13" s="380">
+        <v>5.5</v>
+      </c>
+      <c r="D13" s="380" t="s">
+        <v>1738</v>
+      </c>
+      <c r="E13" s="381">
+        <v>5.0349217077841599</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" ht="19.05" customHeight="1">
+      <c r="B14" s="109" t="s">
+        <v>1731</v>
+      </c>
+      <c r="C14" s="380">
+        <v>5.5</v>
+      </c>
+      <c r="D14" s="380" t="s">
+        <v>1738</v>
+      </c>
+      <c r="E14" s="381">
+        <v>5.0349217077841599</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" ht="19.05" customHeight="1">
+      <c r="B15" s="109" t="s">
+        <v>1732</v>
+      </c>
+      <c r="C15" s="380">
+        <v>5.5</v>
+      </c>
+      <c r="D15" s="380" t="s">
+        <v>1738</v>
+      </c>
+      <c r="E15" s="381">
+        <v>5.0349217077841599</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" ht="19.05" customHeight="1">
+      <c r="B16" s="109" t="s">
+        <v>1733</v>
+      </c>
+      <c r="C16" s="380">
+        <v>5.5</v>
+      </c>
+      <c r="D16" s="380" t="s">
+        <v>1738</v>
+      </c>
+      <c r="E16" s="381">
+        <v>5.0349217077841599</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" ht="19.05" customHeight="1">
+      <c r="B17" s="109" t="s">
+        <v>1733</v>
+      </c>
+      <c r="C17" s="380">
+        <v>5</v>
+      </c>
+      <c r="D17" s="380" t="s">
+        <v>1738</v>
+      </c>
+      <c r="E17" s="381">
+        <v>4.5167286245353155</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" ht="19.05" customHeight="1">
+      <c r="B18" s="109" t="s">
+        <v>1734</v>
+      </c>
+      <c r="C18" s="380">
+        <v>5.5</v>
+      </c>
+      <c r="D18" s="380" t="s">
+        <v>1738</v>
+      </c>
+      <c r="E18" s="381">
+        <v>5.0349217077841599</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" ht="19.05" customHeight="1">
+      <c r="B19" s="109" t="s">
+        <v>1734</v>
+      </c>
+      <c r="C19" s="380">
+        <v>5</v>
+      </c>
+      <c r="D19" s="380" t="s">
+        <v>1738</v>
+      </c>
+      <c r="E19" s="381">
+        <v>4.5167286245353155</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" ht="19.05" customHeight="1">
+      <c r="B20" s="109" t="s">
+        <v>1735</v>
+      </c>
+      <c r="C20" s="380">
+        <v>5.5</v>
+      </c>
+      <c r="D20" s="380" t="s">
+        <v>1738</v>
+      </c>
+      <c r="E20" s="381">
+        <v>5.0349217077841599</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" ht="19.05" customHeight="1">
+      <c r="B21" s="109" t="s">
+        <v>1736</v>
+      </c>
+      <c r="C21" s="380">
+        <v>5.5</v>
+      </c>
+      <c r="D21" s="380" t="s">
+        <v>1738</v>
+      </c>
+      <c r="E21" s="381">
+        <v>5.0349217077841599</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" ht="19.05" customHeight="1">
+      <c r="B22" s="360"/>
+      <c r="C22" s="360"/>
+      <c r="D22" s="360"/>
+      <c r="E22" s="379"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="B2:E3"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:D7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4ED139C6-C002-5A4B-80D8-3E01ADF7143F}">
   <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.6"/>
@@ -20570,7 +20899,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{389CCED4-30D7-EC40-A544-B5ACBC93A9B9}">
   <dimension ref="A1:K29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.6"/>
@@ -20980,7 +21309,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC53565C-0D4B-F642-9CFF-865ED2FE591E}">
   <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.6"/>
@@ -21069,7 +21398,7 @@
     </row>
     <row r="7" spans="1:11" ht="21">
       <c r="A7" s="13"/>
-      <c r="B7" s="435"/>
+      <c r="B7" s="440"/>
       <c r="C7" s="388"/>
       <c r="D7" s="340" t="s">
         <v>100</v>
@@ -21282,7 +21611,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AECF0B3-8484-4395-A4E9-AC5E8051C752}">
   <dimension ref="B1:K67"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.6"/>
@@ -21718,7 +22047,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{325547DD-C65B-B444-908A-9F3B67A97AD2}">
   <dimension ref="B1:K34"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.6"/>
@@ -21989,7 +22318,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1900-000000000000}">
   <dimension ref="B1:J59"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.6"/>
@@ -22562,7 +22891,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1990C61-06D6-BE49-B26D-A3A937C622B8}">
   <dimension ref="B1:J23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.6"/>
@@ -22833,1107 +23162,6 @@
     <mergeCell ref="D6:D7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1B00-000000000000}">
-  <dimension ref="B1:P128"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.6"/>
-  <cols>
-    <col min="1" max="1" width="3.5" customWidth="1"/>
-    <col min="3" max="3" width="12.796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.796875" customWidth="1"/>
-    <col min="8" max="8" width="13" customWidth="1"/>
-    <col min="9" max="9" width="30.796875" customWidth="1"/>
-    <col min="11" max="11" width="14.296875" customWidth="1"/>
-    <col min="16" max="16" width="12.796875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:13" ht="19.05" customHeight="1"/>
-    <row r="2" spans="2:13" ht="19.05" customHeight="1">
-      <c r="B2" s="387" t="s">
-        <v>1645</v>
-      </c>
-      <c r="C2" s="387"/>
-      <c r="D2" s="387"/>
-      <c r="E2" s="387"/>
-      <c r="F2" s="387"/>
-      <c r="G2" s="387"/>
-      <c r="H2" s="387"/>
-      <c r="I2" s="387"/>
-      <c r="J2" s="387"/>
-      <c r="K2" s="387"/>
-      <c r="L2" s="387"/>
-      <c r="M2" s="387"/>
-    </row>
-    <row r="3" spans="2:13" ht="19.05" customHeight="1">
-      <c r="B3" s="387"/>
-      <c r="C3" s="387"/>
-      <c r="D3" s="387"/>
-      <c r="E3" s="387"/>
-      <c r="F3" s="387"/>
-      <c r="G3" s="387"/>
-      <c r="H3" s="387"/>
-      <c r="I3" s="387"/>
-      <c r="J3" s="387"/>
-      <c r="K3" s="387"/>
-      <c r="L3" s="387"/>
-      <c r="M3" s="387"/>
-    </row>
-    <row r="4" spans="2:13" ht="19.05" customHeight="1">
-      <c r="B4" t="s">
-        <v>1586</v>
-      </c>
-    </row>
-    <row r="5" spans="2:13" ht="19.05" customHeight="1" thickBot="1"/>
-    <row r="6" spans="2:13" s="7" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B6" s="391" t="s">
-        <v>99</v>
-      </c>
-      <c r="C6" s="21" t="s">
-        <v>101</v>
-      </c>
-      <c r="D6" s="9"/>
-      <c r="E6" s="391" t="s">
-        <v>99</v>
-      </c>
-      <c r="F6" s="21" t="s">
-        <v>101</v>
-      </c>
-      <c r="G6" s="11"/>
-    </row>
-    <row r="7" spans="2:13" s="7" customFormat="1" ht="19.05" customHeight="1" thickBot="1">
-      <c r="B7" s="393"/>
-      <c r="C7" s="22" t="s">
-        <v>100</v>
-      </c>
-      <c r="D7" s="9"/>
-      <c r="E7" s="393"/>
-      <c r="F7" s="22" t="s">
-        <v>100</v>
-      </c>
-      <c r="G7" s="11"/>
-    </row>
-    <row r="8" spans="2:13" s="7" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B8" s="129">
-        <v>10</v>
-      </c>
-      <c r="C8" s="70">
-        <v>1.337388590573225</v>
-      </c>
-      <c r="E8" s="129">
-        <v>540</v>
-      </c>
-      <c r="F8" s="70">
-        <v>34.342531093671113</v>
-      </c>
-      <c r="G8" s="12"/>
-    </row>
-    <row r="9" spans="2:13" s="7" customFormat="1" ht="19.05" customHeight="1" thickBot="1">
-      <c r="B9" s="129">
-        <v>40</v>
-      </c>
-      <c r="C9" s="70">
-        <v>1.4389932993712422</v>
-      </c>
-      <c r="E9" s="129">
-        <v>560</v>
-      </c>
-      <c r="F9" s="70">
-        <v>37.357896645096147</v>
-      </c>
-      <c r="G9" s="12"/>
-    </row>
-    <row r="10" spans="2:13" s="7" customFormat="1" ht="19.05" customHeight="1" thickBot="1">
-      <c r="B10" s="129">
-        <v>51</v>
-      </c>
-      <c r="C10" s="70">
-        <v>1.5307652944146131</v>
-      </c>
-      <c r="E10" s="129">
-        <v>570</v>
-      </c>
-      <c r="F10" s="70">
-        <v>38.655814860709533</v>
-      </c>
-      <c r="G10" s="12"/>
-      <c r="I10" s="436" t="s">
-        <v>97</v>
-      </c>
-      <c r="J10" s="437"/>
-      <c r="K10" s="438"/>
-      <c r="L10" s="23"/>
-    </row>
-    <row r="11" spans="2:13" s="7" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B11" s="129">
-        <v>60</v>
-      </c>
-      <c r="C11" s="70">
-        <v>1.5963167194455916</v>
-      </c>
-      <c r="E11" s="129">
-        <v>590</v>
-      </c>
-      <c r="F11" s="70">
-        <v>41.563020560833436</v>
-      </c>
-      <c r="G11" s="12"/>
-      <c r="I11" s="436" t="s">
-        <v>103</v>
-      </c>
-      <c r="J11" s="440" t="s">
-        <v>0</v>
-      </c>
-      <c r="K11" s="24" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="12" spans="2:13" s="7" customFormat="1" ht="19.05" customHeight="1" thickBot="1">
-      <c r="B12" s="129">
-        <v>81</v>
-      </c>
-      <c r="C12" s="70">
-        <v>1.8585224195695076</v>
-      </c>
-      <c r="E12" s="129">
-        <v>594</v>
-      </c>
-      <c r="F12" s="70">
-        <v>41.56957570333654</v>
-      </c>
-      <c r="G12" s="12"/>
-      <c r="I12" s="439"/>
-      <c r="J12" s="441"/>
-      <c r="K12" s="25" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13" spans="2:13" s="7" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B13" s="129">
-        <v>100</v>
-      </c>
-      <c r="C13" s="70">
-        <v>1.6880887144889625</v>
-      </c>
-      <c r="E13" s="129">
-        <v>595</v>
-      </c>
-      <c r="F13" s="70">
-        <v>43.270635182890452</v>
-      </c>
-      <c r="G13" s="12"/>
-      <c r="I13" s="74" t="s">
-        <v>415</v>
-      </c>
-      <c r="J13" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="K13" s="73">
-        <v>16.614098231384478</v>
-      </c>
-    </row>
-    <row r="14" spans="2:13" s="7" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B14" s="129">
-        <v>140</v>
-      </c>
-      <c r="C14" s="70">
-        <v>1.9437392721097799</v>
-      </c>
-      <c r="E14" s="129">
-        <v>600</v>
-      </c>
-      <c r="F14" s="70">
-        <v>47.265994538528609</v>
-      </c>
-      <c r="G14" s="12"/>
-      <c r="I14" s="75" t="s">
-        <v>416</v>
-      </c>
-      <c r="J14" s="26" t="s">
-        <v>86</v>
-      </c>
-      <c r="K14" s="73">
-        <v>8.1654601779880576</v>
-      </c>
-    </row>
-    <row r="15" spans="2:13" s="7" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B15" s="129">
-        <v>150</v>
-      </c>
-      <c r="C15" s="70">
-        <v>2.0027355546376611</v>
-      </c>
-      <c r="E15" s="129">
-        <v>610</v>
-      </c>
-      <c r="F15" s="70">
-        <v>55.164941254761565</v>
-      </c>
-      <c r="G15" s="12"/>
-      <c r="I15" s="75" t="s">
-        <v>417</v>
-      </c>
-      <c r="J15" s="26" t="s">
-        <v>87</v>
-      </c>
-      <c r="K15" s="73">
-        <v>13.142628140137433</v>
-      </c>
-    </row>
-    <row r="16" spans="2:13" s="7" customFormat="1" ht="19.05" customHeight="1" thickBot="1">
-      <c r="B16" s="129">
-        <v>155</v>
-      </c>
-      <c r="C16" s="70">
-        <v>2.8581816512919365</v>
-      </c>
-      <c r="E16" s="129">
-        <v>611</v>
-      </c>
-      <c r="F16" s="70">
-        <v>71.057884253522403</v>
-      </c>
-      <c r="G16" s="12"/>
-      <c r="I16" s="75" t="s">
-        <v>418</v>
-      </c>
-      <c r="J16" s="27" t="s">
-        <v>88</v>
-      </c>
-      <c r="K16" s="73">
-        <v>11.051381097217529</v>
-      </c>
-    </row>
-    <row r="17" spans="2:11" s="7" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B17" s="129">
-        <v>160</v>
-      </c>
-      <c r="C17" s="70">
-        <v>5.8407714902014769</v>
-      </c>
-      <c r="E17" s="129">
-        <v>612</v>
-      </c>
-      <c r="F17" s="70">
-        <v>74.119135802469131</v>
-      </c>
-      <c r="G17" s="12"/>
-      <c r="I17" s="28"/>
-      <c r="J17" s="28"/>
-      <c r="K17" s="29"/>
-    </row>
-    <row r="18" spans="2:11" s="7" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B18" s="129">
-        <v>170</v>
-      </c>
-      <c r="C18" s="70">
-        <v>2.3206599660379088</v>
-      </c>
-      <c r="E18" s="129">
-        <v>620</v>
-      </c>
-      <c r="F18" s="70">
-        <v>83.309445591812377</v>
-      </c>
-      <c r="G18" s="12"/>
-    </row>
-    <row r="19" spans="2:11" s="7" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B19" s="129">
-        <v>180</v>
-      </c>
-      <c r="C19" s="70">
-        <v>5.6047863600899523</v>
-      </c>
-      <c r="E19" s="129">
-        <v>630</v>
-      </c>
-      <c r="F19" s="70">
-        <v>85.616855752902836</v>
-      </c>
-      <c r="G19" s="12"/>
-    </row>
-    <row r="20" spans="2:11" s="7" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B20" s="129">
-        <v>181</v>
-      </c>
-      <c r="C20" s="70">
-        <v>6.5847801643030879</v>
-      </c>
-      <c r="E20" s="129">
-        <v>631</v>
-      </c>
-      <c r="F20" s="70">
-        <v>119.9526921841296</v>
-      </c>
-      <c r="G20" s="12"/>
-    </row>
-    <row r="21" spans="2:11" s="7" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B21" s="129">
-        <v>200</v>
-      </c>
-      <c r="C21" s="70">
-        <v>6.3881258892101513</v>
-      </c>
-      <c r="E21" s="129">
-        <v>632</v>
-      </c>
-      <c r="F21" s="70">
-        <v>101.67695488549266</v>
-      </c>
-      <c r="G21" s="12"/>
-    </row>
-    <row r="22" spans="2:11" s="7" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B22" s="129">
-        <v>210</v>
-      </c>
-      <c r="C22" s="70">
-        <v>7.0633055670292331</v>
-      </c>
-      <c r="E22" s="129">
-        <v>633</v>
-      </c>
-      <c r="F22" s="70">
-        <v>111.30645922254347</v>
-      </c>
-      <c r="G22" s="12"/>
-    </row>
-    <row r="23" spans="2:11" s="7" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B23" s="129">
-        <v>220</v>
-      </c>
-      <c r="C23" s="70">
-        <v>7.2665149846252683</v>
-      </c>
-      <c r="E23" s="129">
-        <v>640</v>
-      </c>
-      <c r="F23" s="70">
-        <v>113.80724608747532</v>
-      </c>
-      <c r="G23" s="12"/>
-    </row>
-    <row r="24" spans="2:11" s="7" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B24" s="129">
-        <v>230</v>
-      </c>
-      <c r="C24" s="70">
-        <v>7.5877169672770641</v>
-      </c>
-      <c r="E24" s="129">
-        <v>641</v>
-      </c>
-      <c r="F24" s="70">
-        <v>141.09630432787182</v>
-      </c>
-      <c r="G24" s="12"/>
-    </row>
-    <row r="25" spans="2:11" s="7" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B25" s="129">
-        <v>240</v>
-      </c>
-      <c r="C25" s="70">
-        <v>8.2333985038322073</v>
-      </c>
-      <c r="E25" s="129">
-        <v>642</v>
-      </c>
-      <c r="F25" s="70">
-        <v>74.030641378677288</v>
-      </c>
-      <c r="G25" s="12"/>
-    </row>
-    <row r="26" spans="2:11" s="7" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B26" s="129">
-        <v>250</v>
-      </c>
-      <c r="C26" s="70">
-        <v>8.7250341915645517</v>
-      </c>
-      <c r="E26" s="129">
-        <v>660</v>
-      </c>
-      <c r="F26" s="70">
-        <v>224.52032539354718</v>
-      </c>
-      <c r="G26" s="12"/>
-    </row>
-    <row r="27" spans="2:11" s="7" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B27" s="129">
-        <v>270</v>
-      </c>
-      <c r="C27" s="70">
-        <v>9.3084418743402626</v>
-      </c>
-      <c r="E27" s="129">
-        <v>670</v>
-      </c>
-      <c r="F27" s="70">
-        <v>0</v>
-      </c>
-      <c r="G27" s="12"/>
-    </row>
-    <row r="28" spans="2:11" s="7" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B28" s="129">
-        <v>280</v>
-      </c>
-      <c r="C28" s="70">
-        <v>9.2396128780577342</v>
-      </c>
-      <c r="E28" s="129">
-        <v>671</v>
-      </c>
-      <c r="F28" s="70">
-        <v>240.40015810730185</v>
-      </c>
-      <c r="G28" s="12"/>
-    </row>
-    <row r="29" spans="2:11" s="7" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B29" s="129">
-        <v>300</v>
-      </c>
-      <c r="C29" s="70">
-        <v>10.730907797512502</v>
-      </c>
-      <c r="E29" s="129">
-        <v>680</v>
-      </c>
-      <c r="F29" s="70">
-        <v>448.2702820230391</v>
-      </c>
-      <c r="G29" s="12"/>
-    </row>
-    <row r="30" spans="2:11" s="7" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B30" s="129">
-        <v>330</v>
-      </c>
-      <c r="C30" s="70">
-        <v>11.625684749185366</v>
-      </c>
-      <c r="E30" s="129">
-        <v>800</v>
-      </c>
-      <c r="F30" s="70">
-        <v>7.4435038322089104</v>
-      </c>
-      <c r="G30" s="12"/>
-    </row>
-    <row r="31" spans="2:11" s="7" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B31" s="129">
-        <v>340</v>
-      </c>
-      <c r="C31" s="70">
-        <v>12.477853274588094</v>
-      </c>
-      <c r="E31" s="129">
-        <v>810</v>
-      </c>
-      <c r="F31" s="70">
-        <v>10.1278346872275</v>
-      </c>
-      <c r="G31" s="12"/>
-    </row>
-    <row r="32" spans="2:11" s="7" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B32" s="129">
-        <v>350</v>
-      </c>
-      <c r="C32" s="70">
-        <v>10.131112258479048</v>
-      </c>
-      <c r="E32" s="129">
-        <v>830</v>
-      </c>
-      <c r="F32" s="70">
-        <v>30.753590573225022</v>
-      </c>
-      <c r="G32" s="12"/>
-    </row>
-    <row r="33" spans="2:7" s="7" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B33" s="129">
-        <v>351</v>
-      </c>
-      <c r="C33" s="70">
-        <v>12.789222543485245</v>
-      </c>
-      <c r="E33" s="129">
-        <v>840</v>
-      </c>
-      <c r="F33" s="70">
-        <v>0</v>
-      </c>
-      <c r="G33" s="12"/>
-    </row>
-    <row r="34" spans="2:7" s="7" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B34" s="129">
-        <v>352</v>
-      </c>
-      <c r="C34" s="70">
-        <v>12.763001973472852</v>
-      </c>
-      <c r="E34" s="129">
-        <v>841</v>
-      </c>
-      <c r="F34" s="70">
-        <v>35.348745467896642</v>
-      </c>
-      <c r="G34" s="12"/>
-    </row>
-    <row r="35" spans="2:7" s="7" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B35" s="129">
-        <v>353</v>
-      </c>
-      <c r="C35" s="70">
-        <v>12.900659966037908</v>
-      </c>
-      <c r="E35" s="129">
-        <v>845</v>
-      </c>
-      <c r="F35" s="70">
-        <v>0</v>
-      </c>
-      <c r="G35" s="12"/>
-    </row>
-    <row r="36" spans="2:7" s="7" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B36" s="129">
-        <v>360</v>
-      </c>
-      <c r="C36" s="70">
-        <v>13.238249804947445</v>
-      </c>
-      <c r="E36" s="129">
-        <v>850</v>
-      </c>
-      <c r="F36" s="70">
-        <v>0</v>
-      </c>
-      <c r="G36" s="12"/>
-    </row>
-    <row r="37" spans="2:7" s="7" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B37" s="129">
-        <v>371</v>
-      </c>
-      <c r="C37" s="70">
-        <v>13.333299371242367</v>
-      </c>
-      <c r="E37" s="129">
-        <v>860</v>
-      </c>
-      <c r="F37" s="70">
-        <v>0</v>
-      </c>
-      <c r="G37" s="12"/>
-    </row>
-    <row r="38" spans="2:7" s="7" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B38" s="129">
-        <v>380</v>
-      </c>
-      <c r="C38" s="70">
-        <v>14.536168020560831</v>
-      </c>
-      <c r="E38" s="129">
-        <v>870</v>
-      </c>
-      <c r="F38" s="70">
-        <v>52.110244848317954</v>
-      </c>
-      <c r="G38" s="12"/>
-    </row>
-    <row r="39" spans="2:7" s="7" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B39" s="129">
-        <v>390</v>
-      </c>
-      <c r="C39" s="70">
-        <v>15.172016843361325</v>
-      </c>
-      <c r="E39" s="129">
-        <v>880</v>
-      </c>
-      <c r="F39" s="70">
-        <v>57.121651291936281</v>
-      </c>
-      <c r="G39" s="12"/>
-    </row>
-    <row r="40" spans="2:7" s="7" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B40" s="129">
-        <v>400</v>
-      </c>
-      <c r="C40" s="70">
-        <v>15.657097388590573</v>
-      </c>
-      <c r="E40" s="129">
-        <v>881</v>
-      </c>
-      <c r="F40" s="70">
-        <v>59.055418330350186</v>
-      </c>
-      <c r="G40" s="12"/>
-    </row>
-    <row r="41" spans="2:7" s="7" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B41" s="129">
-        <v>411</v>
-      </c>
-      <c r="C41" s="70">
-        <v>15.460443113497632</v>
-      </c>
-      <c r="E41" s="129">
-        <v>890</v>
-      </c>
-      <c r="F41" s="70">
-        <v>59.540498875579402</v>
-      </c>
-      <c r="G41" s="12"/>
-    </row>
-    <row r="42" spans="2:7" s="7" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B42" s="129">
-        <v>421</v>
-      </c>
-      <c r="C42" s="70">
-        <v>14.339513745467896</v>
-      </c>
-      <c r="E42" s="129">
-        <v>895</v>
-      </c>
-      <c r="F42" s="70">
-        <v>0</v>
-      </c>
-      <c r="G42" s="12"/>
-    </row>
-    <row r="43" spans="2:7" s="7" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B43" s="129">
-        <v>422</v>
-      </c>
-      <c r="C43" s="70">
-        <v>16.043850796273347</v>
-      </c>
-      <c r="E43" s="129">
-        <v>900</v>
-      </c>
-      <c r="F43" s="70">
-        <v>62.139612878057726</v>
-      </c>
-      <c r="G43" s="12"/>
-    </row>
-    <row r="44" spans="2:7" s="7" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B44" s="129">
-        <v>423</v>
-      </c>
-      <c r="C44" s="70">
-        <v>16.224117215108539</v>
-      </c>
-      <c r="E44" s="129">
-        <v>901</v>
-      </c>
-      <c r="F44" s="70">
-        <v>61.979011886731826</v>
-      </c>
-      <c r="G44" s="12"/>
-    </row>
-    <row r="45" spans="2:7" s="7" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B45" s="129">
-        <v>424</v>
-      </c>
-      <c r="C45" s="70">
-        <v>16.728863187847079</v>
-      </c>
-      <c r="E45" s="129">
-        <v>902</v>
-      </c>
-      <c r="F45" s="70">
-        <v>68.537431961081282</v>
-      </c>
-      <c r="G45" s="12"/>
-    </row>
-    <row r="46" spans="2:7" s="7" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B46" s="129">
-        <v>425</v>
-      </c>
-      <c r="C46" s="70">
-        <v>17.341769011886729</v>
-      </c>
-      <c r="E46" s="129">
-        <v>903</v>
-      </c>
-      <c r="F46" s="70">
-        <v>53.014854513745462</v>
-      </c>
-      <c r="G46" s="12"/>
-    </row>
-    <row r="47" spans="2:7" s="7" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B47" s="129">
-        <v>426</v>
-      </c>
-      <c r="C47" s="70">
-        <v>17.748187847078803</v>
-      </c>
-      <c r="E47" s="129">
-        <v>904</v>
-      </c>
-      <c r="F47" s="70">
-        <v>60.36644683096975</v>
-      </c>
-      <c r="G47" s="12"/>
-    </row>
-    <row r="48" spans="2:7" s="7" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B48" s="129">
-        <v>427</v>
-      </c>
-      <c r="C48" s="70">
-        <v>17.171335306806185</v>
-      </c>
-      <c r="E48" s="129">
-        <v>906</v>
-      </c>
-      <c r="F48" s="73">
-        <v>74.01753109367111</v>
-      </c>
-      <c r="G48" s="12"/>
-    </row>
-    <row r="49" spans="2:7" s="7" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B49" s="129">
-        <v>428</v>
-      </c>
-      <c r="C49" s="70">
-        <v>17.636750424526138</v>
-      </c>
-      <c r="E49" s="129">
-        <v>907</v>
-      </c>
-      <c r="F49" s="73">
-        <v>78.878169259718192</v>
-      </c>
-      <c r="G49" s="12"/>
-    </row>
-    <row r="50" spans="2:7" s="7" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B50" s="129">
-        <v>430</v>
-      </c>
-      <c r="C50" s="70">
-        <v>17.715412134563312</v>
-      </c>
-      <c r="E50" s="130">
-        <v>908</v>
-      </c>
-      <c r="F50" s="73">
-        <v>83.745362568268376</v>
-      </c>
-      <c r="G50" s="12"/>
-    </row>
-    <row r="51" spans="2:7" s="7" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B51" s="129">
-        <v>440</v>
-      </c>
-      <c r="C51" s="70">
-        <v>18.88222750011473</v>
-      </c>
-      <c r="E51" s="131">
-        <v>910</v>
-      </c>
-      <c r="F51" s="73">
-        <v>82.195071366285717</v>
-      </c>
-      <c r="G51" s="12"/>
-    </row>
-    <row r="52" spans="2:7" s="7" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B52" s="129">
-        <v>443</v>
-      </c>
-      <c r="C52" s="70">
-        <v>16.227394786360087</v>
-      </c>
-      <c r="E52" s="129">
-        <v>915</v>
-      </c>
-      <c r="F52" s="73">
-        <v>98.61242576529439</v>
-      </c>
-      <c r="G52" s="12"/>
-    </row>
-    <row r="53" spans="2:7" s="7" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B53" s="129">
-        <v>450</v>
-      </c>
-      <c r="C53" s="70">
-        <v>4.8476674009821474</v>
-      </c>
-      <c r="E53" s="129">
-        <v>918</v>
-      </c>
-      <c r="F53" s="73">
-        <v>128.06795860296481</v>
-      </c>
-      <c r="G53" s="12"/>
-    </row>
-    <row r="54" spans="2:7" s="7" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B54" s="129">
-        <v>452</v>
-      </c>
-      <c r="C54" s="70">
-        <v>18.236545963559593</v>
-      </c>
-      <c r="E54" s="129">
-        <v>919</v>
-      </c>
-      <c r="F54" s="73">
-        <v>221.13131671944555</v>
-      </c>
-      <c r="G54" s="12"/>
-    </row>
-    <row r="55" spans="2:7" s="7" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B55" s="129">
-        <v>459</v>
-      </c>
-      <c r="C55" s="70">
-        <v>19.652456744228733</v>
-      </c>
-      <c r="E55" s="129">
-        <v>920</v>
-      </c>
-      <c r="F55" s="73">
-        <v>185.89742576529443</v>
-      </c>
-      <c r="G55" s="12"/>
-    </row>
-    <row r="56" spans="2:7" s="7" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B56" s="129">
-        <v>460</v>
-      </c>
-      <c r="C56" s="70">
-        <v>17.56464385699206</v>
-      </c>
-      <c r="E56" s="117">
-        <v>921</v>
-      </c>
-      <c r="F56" s="73">
-        <v>256.12266740098215</v>
-      </c>
-      <c r="G56" s="12"/>
-    </row>
-    <row r="57" spans="2:7" s="7" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B57" s="129">
-        <v>464</v>
-      </c>
-      <c r="C57" s="70">
-        <v>17.99400569094497</v>
-      </c>
-      <c r="E57" s="129">
-        <v>922</v>
-      </c>
-      <c r="F57" s="73">
-        <v>258.06626715315059</v>
-      </c>
-    </row>
-    <row r="58" spans="2:7" s="7" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B58" s="129">
-        <v>466</v>
-      </c>
-      <c r="C58" s="70">
-        <v>19.940883014365042</v>
-      </c>
-      <c r="E58" s="129">
-        <v>923</v>
-      </c>
-      <c r="F58" s="73">
-        <v>326.34463146541827</v>
-      </c>
-    </row>
-    <row r="59" spans="2:7" s="7" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B59" s="129">
-        <v>467</v>
-      </c>
-      <c r="C59" s="70">
-        <v>20.927431961081272</v>
-      </c>
-      <c r="E59" s="129">
-        <v>924</v>
-      </c>
-      <c r="F59" s="73">
-        <v>363.51884460048637</v>
-      </c>
-    </row>
-    <row r="60" spans="2:7" s="7" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B60" s="129">
-        <v>470</v>
-      </c>
-      <c r="C60" s="70">
-        <v>21.622277066409652</v>
-      </c>
-      <c r="E60" s="129">
-        <v>999</v>
-      </c>
-      <c r="F60" s="73">
-        <v>555.12238239478631</v>
-      </c>
-    </row>
-    <row r="61" spans="2:7" s="7" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B61" s="129">
-        <v>471</v>
-      </c>
-      <c r="C61" s="70">
-        <v>16.237227500114731</v>
-      </c>
-      <c r="E61" s="129">
-        <v>1000</v>
-      </c>
-      <c r="F61" s="73">
-        <v>612.16523245674409</v>
-      </c>
-    </row>
-    <row r="62" spans="2:7" s="7" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B62" s="129">
-        <v>472</v>
-      </c>
-      <c r="C62" s="70">
-        <v>23.152902840883016</v>
-      </c>
-      <c r="E62" s="129">
-        <v>1200</v>
-      </c>
-      <c r="F62" s="73">
-        <v>696.67085203543081</v>
-      </c>
-    </row>
-    <row r="63" spans="2:7" s="7" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B63" s="129">
-        <v>473</v>
-      </c>
-      <c r="C63" s="70">
-        <v>24.073900362568267</v>
-      </c>
-      <c r="E63" s="129">
-        <v>1205</v>
-      </c>
-      <c r="F63" s="73">
-        <v>733.22888177520747</v>
-      </c>
-    </row>
-    <row r="64" spans="2:7" s="7" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B64" s="129">
-        <v>492</v>
-      </c>
-      <c r="C64" s="70">
-        <v>9.2953315893340669</v>
-      </c>
-      <c r="E64" s="129">
-        <v>1500</v>
-      </c>
-      <c r="F64" s="73">
-        <v>1179.214557115976</v>
-      </c>
-    </row>
-    <row r="65" spans="2:6" s="7" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B65" s="129">
-        <v>510</v>
-      </c>
-      <c r="C65" s="70">
-        <v>29.059086236174213</v>
-      </c>
-    </row>
-    <row r="66" spans="2:6" s="7" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B66" s="129">
-        <v>511</v>
-      </c>
-      <c r="C66" s="70">
-        <v>27.410467896645091</v>
-      </c>
-    </row>
-    <row r="67" spans="2:6" s="7" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B67" s="129">
-        <v>512</v>
-      </c>
-      <c r="C67" s="70">
-        <v>10.891508788838403</v>
-      </c>
-    </row>
-    <row r="68" spans="2:6" s="7" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B68" s="129">
-        <v>513</v>
-      </c>
-      <c r="C68" s="70">
-        <v>10.734185368764054</v>
-      </c>
-    </row>
-    <row r="69" spans="2:6" s="7" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B69" s="129">
-        <v>514</v>
-      </c>
-      <c r="C69" s="70">
-        <v>28.583838404699609</v>
-      </c>
-    </row>
-    <row r="70" spans="2:6" s="7" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B70" s="129">
-        <v>530</v>
-      </c>
-      <c r="C70" s="70">
-        <v>31.759804947450547</v>
-      </c>
-    </row>
-    <row r="71" spans="2:6" s="7" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B71" s="129">
-        <v>531</v>
-      </c>
-      <c r="C71" s="70">
-        <v>34.276979668640138</v>
-      </c>
-    </row>
-    <row r="72" spans="2:6" ht="20.399999999999999">
-      <c r="B72" s="7"/>
-      <c r="C72" s="7"/>
-      <c r="D72" s="7"/>
-      <c r="E72" s="7"/>
-      <c r="F72" s="7"/>
-    </row>
-    <row r="73" spans="2:6" ht="20.399999999999999">
-      <c r="B73" s="7"/>
-      <c r="C73" s="7"/>
-      <c r="D73" s="7"/>
-      <c r="E73" s="7"/>
-      <c r="F73" s="7"/>
-    </row>
-    <row r="74" spans="2:6" ht="20.399999999999999">
-      <c r="B74" s="7"/>
-      <c r="C74" s="7"/>
-      <c r="D74" s="7"/>
-      <c r="E74" s="7"/>
-      <c r="F74" s="7"/>
-    </row>
-    <row r="75" spans="2:6" ht="20.399999999999999">
-      <c r="B75" s="7"/>
-      <c r="C75" s="7"/>
-      <c r="D75" s="7"/>
-      <c r="E75" s="7"/>
-      <c r="F75" s="7"/>
-    </row>
-    <row r="76" spans="2:6" ht="20.399999999999999">
-      <c r="B76" s="7"/>
-      <c r="C76" s="7"/>
-      <c r="D76" s="7"/>
-      <c r="E76" s="7"/>
-      <c r="F76" s="7"/>
-    </row>
-    <row r="128" spans="15:16" ht="18">
-      <c r="O128" s="5"/>
-      <c r="P128" s="6"/>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="B2:M3"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="J11:J12"/>
-  </mergeCells>
-  <phoneticPr fontId="43" type="noConversion"/>
-  <pageMargins left="0.5" right="0.5" top="0.39000000000000007" bottom="0.39000000000000007" header="0" footer="0"/>
-  <pageSetup scale="52" orientation="portrait" r:id="rId1"/>
-  <rowBreaks count="1" manualBreakCount="1">
-    <brk id="71" max="16383" man="1"/>
-  </rowBreaks>
-  <colBreaks count="1" manualBreakCount="1">
-    <brk id="13" max="1048575" man="1"/>
-  </colBreaks>
 </worksheet>
 </file>
 
@@ -25240,6 +24468,1107 @@
 </file>
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1B00-000000000000}">
+  <dimension ref="B1:P128"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.6"/>
+  <cols>
+    <col min="1" max="1" width="3.5" customWidth="1"/>
+    <col min="3" max="3" width="12.796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.796875" customWidth="1"/>
+    <col min="8" max="8" width="13" customWidth="1"/>
+    <col min="9" max="9" width="30.796875" customWidth="1"/>
+    <col min="11" max="11" width="14.296875" customWidth="1"/>
+    <col min="16" max="16" width="12.796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:13" ht="19.05" customHeight="1"/>
+    <row r="2" spans="2:13" ht="19.05" customHeight="1">
+      <c r="B2" s="387" t="s">
+        <v>1645</v>
+      </c>
+      <c r="C2" s="387"/>
+      <c r="D2" s="387"/>
+      <c r="E2" s="387"/>
+      <c r="F2" s="387"/>
+      <c r="G2" s="387"/>
+      <c r="H2" s="387"/>
+      <c r="I2" s="387"/>
+      <c r="J2" s="387"/>
+      <c r="K2" s="387"/>
+      <c r="L2" s="387"/>
+      <c r="M2" s="387"/>
+    </row>
+    <row r="3" spans="2:13" ht="19.05" customHeight="1">
+      <c r="B3" s="387"/>
+      <c r="C3" s="387"/>
+      <c r="D3" s="387"/>
+      <c r="E3" s="387"/>
+      <c r="F3" s="387"/>
+      <c r="G3" s="387"/>
+      <c r="H3" s="387"/>
+      <c r="I3" s="387"/>
+      <c r="J3" s="387"/>
+      <c r="K3" s="387"/>
+      <c r="L3" s="387"/>
+      <c r="M3" s="387"/>
+    </row>
+    <row r="4" spans="2:13" ht="19.05" customHeight="1">
+      <c r="B4" t="s">
+        <v>1586</v>
+      </c>
+    </row>
+    <row r="5" spans="2:13" ht="19.05" customHeight="1" thickBot="1"/>
+    <row r="6" spans="2:13" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="B6" s="391" t="s">
+        <v>99</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="D6" s="9"/>
+      <c r="E6" s="391" t="s">
+        <v>99</v>
+      </c>
+      <c r="F6" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="G6" s="11"/>
+    </row>
+    <row r="7" spans="2:13" s="7" customFormat="1" ht="19.05" customHeight="1" thickBot="1">
+      <c r="B7" s="393"/>
+      <c r="C7" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="D7" s="9"/>
+      <c r="E7" s="393"/>
+      <c r="F7" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="G7" s="11"/>
+    </row>
+    <row r="8" spans="2:13" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="B8" s="129">
+        <v>10</v>
+      </c>
+      <c r="C8" s="70">
+        <v>1.337388590573225</v>
+      </c>
+      <c r="E8" s="129">
+        <v>540</v>
+      </c>
+      <c r="F8" s="70">
+        <v>34.342531093671113</v>
+      </c>
+      <c r="G8" s="12"/>
+    </row>
+    <row r="9" spans="2:13" s="7" customFormat="1" ht="19.05" customHeight="1" thickBot="1">
+      <c r="B9" s="129">
+        <v>40</v>
+      </c>
+      <c r="C9" s="70">
+        <v>1.4389932993712422</v>
+      </c>
+      <c r="E9" s="129">
+        <v>560</v>
+      </c>
+      <c r="F9" s="70">
+        <v>37.357896645096147</v>
+      </c>
+      <c r="G9" s="12"/>
+    </row>
+    <row r="10" spans="2:13" s="7" customFormat="1" ht="19.05" customHeight="1" thickBot="1">
+      <c r="B10" s="129">
+        <v>51</v>
+      </c>
+      <c r="C10" s="70">
+        <v>1.5307652944146131</v>
+      </c>
+      <c r="E10" s="129">
+        <v>570</v>
+      </c>
+      <c r="F10" s="70">
+        <v>38.655814860709533</v>
+      </c>
+      <c r="G10" s="12"/>
+      <c r="I10" s="441" t="s">
+        <v>97</v>
+      </c>
+      <c r="J10" s="442"/>
+      <c r="K10" s="443"/>
+      <c r="L10" s="23"/>
+    </row>
+    <row r="11" spans="2:13" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="B11" s="129">
+        <v>60</v>
+      </c>
+      <c r="C11" s="70">
+        <v>1.5963167194455916</v>
+      </c>
+      <c r="E11" s="129">
+        <v>590</v>
+      </c>
+      <c r="F11" s="70">
+        <v>41.563020560833436</v>
+      </c>
+      <c r="G11" s="12"/>
+      <c r="I11" s="441" t="s">
+        <v>103</v>
+      </c>
+      <c r="J11" s="445" t="s">
+        <v>0</v>
+      </c>
+      <c r="K11" s="24" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="12" spans="2:13" s="7" customFormat="1" ht="19.05" customHeight="1" thickBot="1">
+      <c r="B12" s="129">
+        <v>81</v>
+      </c>
+      <c r="C12" s="70">
+        <v>1.8585224195695076</v>
+      </c>
+      <c r="E12" s="129">
+        <v>594</v>
+      </c>
+      <c r="F12" s="70">
+        <v>41.56957570333654</v>
+      </c>
+      <c r="G12" s="12"/>
+      <c r="I12" s="444"/>
+      <c r="J12" s="446"/>
+      <c r="K12" s="25" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="2:13" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="B13" s="129">
+        <v>100</v>
+      </c>
+      <c r="C13" s="70">
+        <v>1.6880887144889625</v>
+      </c>
+      <c r="E13" s="129">
+        <v>595</v>
+      </c>
+      <c r="F13" s="70">
+        <v>43.270635182890452</v>
+      </c>
+      <c r="G13" s="12"/>
+      <c r="I13" s="74" t="s">
+        <v>415</v>
+      </c>
+      <c r="J13" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="K13" s="73">
+        <v>16.614098231384478</v>
+      </c>
+    </row>
+    <row r="14" spans="2:13" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="B14" s="129">
+        <v>140</v>
+      </c>
+      <c r="C14" s="70">
+        <v>1.9437392721097799</v>
+      </c>
+      <c r="E14" s="129">
+        <v>600</v>
+      </c>
+      <c r="F14" s="70">
+        <v>47.265994538528609</v>
+      </c>
+      <c r="G14" s="12"/>
+      <c r="I14" s="75" t="s">
+        <v>416</v>
+      </c>
+      <c r="J14" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="K14" s="73">
+        <v>8.1654601779880576</v>
+      </c>
+    </row>
+    <row r="15" spans="2:13" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="B15" s="129">
+        <v>150</v>
+      </c>
+      <c r="C15" s="70">
+        <v>2.0027355546376611</v>
+      </c>
+      <c r="E15" s="129">
+        <v>610</v>
+      </c>
+      <c r="F15" s="70">
+        <v>55.164941254761565</v>
+      </c>
+      <c r="G15" s="12"/>
+      <c r="I15" s="75" t="s">
+        <v>417</v>
+      </c>
+      <c r="J15" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="K15" s="73">
+        <v>13.142628140137433</v>
+      </c>
+    </row>
+    <row r="16" spans="2:13" s="7" customFormat="1" ht="19.05" customHeight="1" thickBot="1">
+      <c r="B16" s="129">
+        <v>155</v>
+      </c>
+      <c r="C16" s="70">
+        <v>2.8581816512919365</v>
+      </c>
+      <c r="E16" s="129">
+        <v>611</v>
+      </c>
+      <c r="F16" s="70">
+        <v>71.057884253522403</v>
+      </c>
+      <c r="G16" s="12"/>
+      <c r="I16" s="75" t="s">
+        <v>418</v>
+      </c>
+      <c r="J16" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="K16" s="73">
+        <v>11.051381097217529</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="B17" s="129">
+        <v>160</v>
+      </c>
+      <c r="C17" s="70">
+        <v>5.8407714902014769</v>
+      </c>
+      <c r="E17" s="129">
+        <v>612</v>
+      </c>
+      <c r="F17" s="70">
+        <v>74.119135802469131</v>
+      </c>
+      <c r="G17" s="12"/>
+      <c r="I17" s="28"/>
+      <c r="J17" s="28"/>
+      <c r="K17" s="29"/>
+    </row>
+    <row r="18" spans="2:11" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="B18" s="129">
+        <v>170</v>
+      </c>
+      <c r="C18" s="70">
+        <v>2.3206599660379088</v>
+      </c>
+      <c r="E18" s="129">
+        <v>620</v>
+      </c>
+      <c r="F18" s="70">
+        <v>83.309445591812377</v>
+      </c>
+      <c r="G18" s="12"/>
+    </row>
+    <row r="19" spans="2:11" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="B19" s="129">
+        <v>180</v>
+      </c>
+      <c r="C19" s="70">
+        <v>5.6047863600899523</v>
+      </c>
+      <c r="E19" s="129">
+        <v>630</v>
+      </c>
+      <c r="F19" s="70">
+        <v>85.616855752902836</v>
+      </c>
+      <c r="G19" s="12"/>
+    </row>
+    <row r="20" spans="2:11" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="B20" s="129">
+        <v>181</v>
+      </c>
+      <c r="C20" s="70">
+        <v>6.5847801643030879</v>
+      </c>
+      <c r="E20" s="129">
+        <v>631</v>
+      </c>
+      <c r="F20" s="70">
+        <v>119.9526921841296</v>
+      </c>
+      <c r="G20" s="12"/>
+    </row>
+    <row r="21" spans="2:11" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="B21" s="129">
+        <v>200</v>
+      </c>
+      <c r="C21" s="70">
+        <v>6.3881258892101513</v>
+      </c>
+      <c r="E21" s="129">
+        <v>632</v>
+      </c>
+      <c r="F21" s="70">
+        <v>101.67695488549266</v>
+      </c>
+      <c r="G21" s="12"/>
+    </row>
+    <row r="22" spans="2:11" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="B22" s="129">
+        <v>210</v>
+      </c>
+      <c r="C22" s="70">
+        <v>7.0633055670292331</v>
+      </c>
+      <c r="E22" s="129">
+        <v>633</v>
+      </c>
+      <c r="F22" s="70">
+        <v>111.30645922254347</v>
+      </c>
+      <c r="G22" s="12"/>
+    </row>
+    <row r="23" spans="2:11" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="B23" s="129">
+        <v>220</v>
+      </c>
+      <c r="C23" s="70">
+        <v>7.2665149846252683</v>
+      </c>
+      <c r="E23" s="129">
+        <v>640</v>
+      </c>
+      <c r="F23" s="70">
+        <v>113.80724608747532</v>
+      </c>
+      <c r="G23" s="12"/>
+    </row>
+    <row r="24" spans="2:11" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="B24" s="129">
+        <v>230</v>
+      </c>
+      <c r="C24" s="70">
+        <v>7.5877169672770641</v>
+      </c>
+      <c r="E24" s="129">
+        <v>641</v>
+      </c>
+      <c r="F24" s="70">
+        <v>141.09630432787182</v>
+      </c>
+      <c r="G24" s="12"/>
+    </row>
+    <row r="25" spans="2:11" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="B25" s="129">
+        <v>240</v>
+      </c>
+      <c r="C25" s="70">
+        <v>8.2333985038322073</v>
+      </c>
+      <c r="E25" s="129">
+        <v>642</v>
+      </c>
+      <c r="F25" s="70">
+        <v>74.030641378677288</v>
+      </c>
+      <c r="G25" s="12"/>
+    </row>
+    <row r="26" spans="2:11" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="B26" s="129">
+        <v>250</v>
+      </c>
+      <c r="C26" s="70">
+        <v>8.7250341915645517</v>
+      </c>
+      <c r="E26" s="129">
+        <v>660</v>
+      </c>
+      <c r="F26" s="70">
+        <v>224.52032539354718</v>
+      </c>
+      <c r="G26" s="12"/>
+    </row>
+    <row r="27" spans="2:11" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="B27" s="129">
+        <v>270</v>
+      </c>
+      <c r="C27" s="70">
+        <v>9.3084418743402626</v>
+      </c>
+      <c r="E27" s="129">
+        <v>670</v>
+      </c>
+      <c r="F27" s="70">
+        <v>0</v>
+      </c>
+      <c r="G27" s="12"/>
+    </row>
+    <row r="28" spans="2:11" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="B28" s="129">
+        <v>280</v>
+      </c>
+      <c r="C28" s="70">
+        <v>9.2396128780577342</v>
+      </c>
+      <c r="E28" s="129">
+        <v>671</v>
+      </c>
+      <c r="F28" s="70">
+        <v>240.40015810730185</v>
+      </c>
+      <c r="G28" s="12"/>
+    </row>
+    <row r="29" spans="2:11" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="B29" s="129">
+        <v>300</v>
+      </c>
+      <c r="C29" s="70">
+        <v>10.730907797512502</v>
+      </c>
+      <c r="E29" s="129">
+        <v>680</v>
+      </c>
+      <c r="F29" s="70">
+        <v>448.2702820230391</v>
+      </c>
+      <c r="G29" s="12"/>
+    </row>
+    <row r="30" spans="2:11" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="B30" s="129">
+        <v>330</v>
+      </c>
+      <c r="C30" s="70">
+        <v>11.625684749185366</v>
+      </c>
+      <c r="E30" s="129">
+        <v>800</v>
+      </c>
+      <c r="F30" s="70">
+        <v>7.4435038322089104</v>
+      </c>
+      <c r="G30" s="12"/>
+    </row>
+    <row r="31" spans="2:11" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="B31" s="129">
+        <v>340</v>
+      </c>
+      <c r="C31" s="70">
+        <v>12.477853274588094</v>
+      </c>
+      <c r="E31" s="129">
+        <v>810</v>
+      </c>
+      <c r="F31" s="70">
+        <v>10.1278346872275</v>
+      </c>
+      <c r="G31" s="12"/>
+    </row>
+    <row r="32" spans="2:11" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="B32" s="129">
+        <v>350</v>
+      </c>
+      <c r="C32" s="70">
+        <v>10.131112258479048</v>
+      </c>
+      <c r="E32" s="129">
+        <v>830</v>
+      </c>
+      <c r="F32" s="70">
+        <v>30.753590573225022</v>
+      </c>
+      <c r="G32" s="12"/>
+    </row>
+    <row r="33" spans="2:7" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="B33" s="129">
+        <v>351</v>
+      </c>
+      <c r="C33" s="70">
+        <v>12.789222543485245</v>
+      </c>
+      <c r="E33" s="129">
+        <v>840</v>
+      </c>
+      <c r="F33" s="70">
+        <v>0</v>
+      </c>
+      <c r="G33" s="12"/>
+    </row>
+    <row r="34" spans="2:7" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="B34" s="129">
+        <v>352</v>
+      </c>
+      <c r="C34" s="70">
+        <v>12.763001973472852</v>
+      </c>
+      <c r="E34" s="129">
+        <v>841</v>
+      </c>
+      <c r="F34" s="70">
+        <v>35.348745467896642</v>
+      </c>
+      <c r="G34" s="12"/>
+    </row>
+    <row r="35" spans="2:7" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="B35" s="129">
+        <v>353</v>
+      </c>
+      <c r="C35" s="70">
+        <v>12.900659966037908</v>
+      </c>
+      <c r="E35" s="129">
+        <v>845</v>
+      </c>
+      <c r="F35" s="70">
+        <v>0</v>
+      </c>
+      <c r="G35" s="12"/>
+    </row>
+    <row r="36" spans="2:7" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="B36" s="129">
+        <v>360</v>
+      </c>
+      <c r="C36" s="70">
+        <v>13.238249804947445</v>
+      </c>
+      <c r="E36" s="129">
+        <v>850</v>
+      </c>
+      <c r="F36" s="70">
+        <v>0</v>
+      </c>
+      <c r="G36" s="12"/>
+    </row>
+    <row r="37" spans="2:7" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="B37" s="129">
+        <v>371</v>
+      </c>
+      <c r="C37" s="70">
+        <v>13.333299371242367</v>
+      </c>
+      <c r="E37" s="129">
+        <v>860</v>
+      </c>
+      <c r="F37" s="70">
+        <v>0</v>
+      </c>
+      <c r="G37" s="12"/>
+    </row>
+    <row r="38" spans="2:7" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="B38" s="129">
+        <v>380</v>
+      </c>
+      <c r="C38" s="70">
+        <v>14.536168020560831</v>
+      </c>
+      <c r="E38" s="129">
+        <v>870</v>
+      </c>
+      <c r="F38" s="70">
+        <v>52.110244848317954</v>
+      </c>
+      <c r="G38" s="12"/>
+    </row>
+    <row r="39" spans="2:7" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="B39" s="129">
+        <v>390</v>
+      </c>
+      <c r="C39" s="70">
+        <v>15.172016843361325</v>
+      </c>
+      <c r="E39" s="129">
+        <v>880</v>
+      </c>
+      <c r="F39" s="70">
+        <v>57.121651291936281</v>
+      </c>
+      <c r="G39" s="12"/>
+    </row>
+    <row r="40" spans="2:7" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="B40" s="129">
+        <v>400</v>
+      </c>
+      <c r="C40" s="70">
+        <v>15.657097388590573</v>
+      </c>
+      <c r="E40" s="129">
+        <v>881</v>
+      </c>
+      <c r="F40" s="70">
+        <v>59.055418330350186</v>
+      </c>
+      <c r="G40" s="12"/>
+    </row>
+    <row r="41" spans="2:7" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="B41" s="129">
+        <v>411</v>
+      </c>
+      <c r="C41" s="70">
+        <v>15.460443113497632</v>
+      </c>
+      <c r="E41" s="129">
+        <v>890</v>
+      </c>
+      <c r="F41" s="70">
+        <v>59.540498875579402</v>
+      </c>
+      <c r="G41" s="12"/>
+    </row>
+    <row r="42" spans="2:7" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="B42" s="129">
+        <v>421</v>
+      </c>
+      <c r="C42" s="70">
+        <v>14.339513745467896</v>
+      </c>
+      <c r="E42" s="129">
+        <v>895</v>
+      </c>
+      <c r="F42" s="70">
+        <v>0</v>
+      </c>
+      <c r="G42" s="12"/>
+    </row>
+    <row r="43" spans="2:7" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="B43" s="129">
+        <v>422</v>
+      </c>
+      <c r="C43" s="70">
+        <v>16.043850796273347</v>
+      </c>
+      <c r="E43" s="129">
+        <v>900</v>
+      </c>
+      <c r="F43" s="70">
+        <v>62.139612878057726</v>
+      </c>
+      <c r="G43" s="12"/>
+    </row>
+    <row r="44" spans="2:7" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="B44" s="129">
+        <v>423</v>
+      </c>
+      <c r="C44" s="70">
+        <v>16.224117215108539</v>
+      </c>
+      <c r="E44" s="129">
+        <v>901</v>
+      </c>
+      <c r="F44" s="70">
+        <v>61.979011886731826</v>
+      </c>
+      <c r="G44" s="12"/>
+    </row>
+    <row r="45" spans="2:7" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="B45" s="129">
+        <v>424</v>
+      </c>
+      <c r="C45" s="70">
+        <v>16.728863187847079</v>
+      </c>
+      <c r="E45" s="129">
+        <v>902</v>
+      </c>
+      <c r="F45" s="70">
+        <v>68.537431961081282</v>
+      </c>
+      <c r="G45" s="12"/>
+    </row>
+    <row r="46" spans="2:7" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="B46" s="129">
+        <v>425</v>
+      </c>
+      <c r="C46" s="70">
+        <v>17.341769011886729</v>
+      </c>
+      <c r="E46" s="129">
+        <v>903</v>
+      </c>
+      <c r="F46" s="70">
+        <v>53.014854513745462</v>
+      </c>
+      <c r="G46" s="12"/>
+    </row>
+    <row r="47" spans="2:7" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="B47" s="129">
+        <v>426</v>
+      </c>
+      <c r="C47" s="70">
+        <v>17.748187847078803</v>
+      </c>
+      <c r="E47" s="129">
+        <v>904</v>
+      </c>
+      <c r="F47" s="70">
+        <v>60.36644683096975</v>
+      </c>
+      <c r="G47" s="12"/>
+    </row>
+    <row r="48" spans="2:7" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="B48" s="129">
+        <v>427</v>
+      </c>
+      <c r="C48" s="70">
+        <v>17.171335306806185</v>
+      </c>
+      <c r="E48" s="129">
+        <v>906</v>
+      </c>
+      <c r="F48" s="73">
+        <v>74.01753109367111</v>
+      </c>
+      <c r="G48" s="12"/>
+    </row>
+    <row r="49" spans="2:7" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="B49" s="129">
+        <v>428</v>
+      </c>
+      <c r="C49" s="70">
+        <v>17.636750424526138</v>
+      </c>
+      <c r="E49" s="129">
+        <v>907</v>
+      </c>
+      <c r="F49" s="73">
+        <v>78.878169259718192</v>
+      </c>
+      <c r="G49" s="12"/>
+    </row>
+    <row r="50" spans="2:7" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="B50" s="129">
+        <v>430</v>
+      </c>
+      <c r="C50" s="70">
+        <v>17.715412134563312</v>
+      </c>
+      <c r="E50" s="130">
+        <v>908</v>
+      </c>
+      <c r="F50" s="73">
+        <v>83.745362568268376</v>
+      </c>
+      <c r="G50" s="12"/>
+    </row>
+    <row r="51" spans="2:7" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="B51" s="129">
+        <v>440</v>
+      </c>
+      <c r="C51" s="70">
+        <v>18.88222750011473</v>
+      </c>
+      <c r="E51" s="131">
+        <v>910</v>
+      </c>
+      <c r="F51" s="73">
+        <v>82.195071366285717</v>
+      </c>
+      <c r="G51" s="12"/>
+    </row>
+    <row r="52" spans="2:7" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="B52" s="129">
+        <v>443</v>
+      </c>
+      <c r="C52" s="70">
+        <v>16.227394786360087</v>
+      </c>
+      <c r="E52" s="129">
+        <v>915</v>
+      </c>
+      <c r="F52" s="73">
+        <v>98.61242576529439</v>
+      </c>
+      <c r="G52" s="12"/>
+    </row>
+    <row r="53" spans="2:7" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="B53" s="129">
+        <v>450</v>
+      </c>
+      <c r="C53" s="70">
+        <v>4.8476674009821474</v>
+      </c>
+      <c r="E53" s="129">
+        <v>918</v>
+      </c>
+      <c r="F53" s="73">
+        <v>128.06795860296481</v>
+      </c>
+      <c r="G53" s="12"/>
+    </row>
+    <row r="54" spans="2:7" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="B54" s="129">
+        <v>452</v>
+      </c>
+      <c r="C54" s="70">
+        <v>18.236545963559593</v>
+      </c>
+      <c r="E54" s="129">
+        <v>919</v>
+      </c>
+      <c r="F54" s="73">
+        <v>221.13131671944555</v>
+      </c>
+      <c r="G54" s="12"/>
+    </row>
+    <row r="55" spans="2:7" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="B55" s="129">
+        <v>459</v>
+      </c>
+      <c r="C55" s="70">
+        <v>19.652456744228733</v>
+      </c>
+      <c r="E55" s="129">
+        <v>920</v>
+      </c>
+      <c r="F55" s="73">
+        <v>185.89742576529443</v>
+      </c>
+      <c r="G55" s="12"/>
+    </row>
+    <row r="56" spans="2:7" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="B56" s="129">
+        <v>460</v>
+      </c>
+      <c r="C56" s="70">
+        <v>17.56464385699206</v>
+      </c>
+      <c r="E56" s="117">
+        <v>921</v>
+      </c>
+      <c r="F56" s="73">
+        <v>256.12266740098215</v>
+      </c>
+      <c r="G56" s="12"/>
+    </row>
+    <row r="57" spans="2:7" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="B57" s="129">
+        <v>464</v>
+      </c>
+      <c r="C57" s="70">
+        <v>17.99400569094497</v>
+      </c>
+      <c r="E57" s="129">
+        <v>922</v>
+      </c>
+      <c r="F57" s="73">
+        <v>258.06626715315059</v>
+      </c>
+    </row>
+    <row r="58" spans="2:7" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="B58" s="129">
+        <v>466</v>
+      </c>
+      <c r="C58" s="70">
+        <v>19.940883014365042</v>
+      </c>
+      <c r="E58" s="129">
+        <v>923</v>
+      </c>
+      <c r="F58" s="73">
+        <v>326.34463146541827</v>
+      </c>
+    </row>
+    <row r="59" spans="2:7" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="B59" s="129">
+        <v>467</v>
+      </c>
+      <c r="C59" s="70">
+        <v>20.927431961081272</v>
+      </c>
+      <c r="E59" s="129">
+        <v>924</v>
+      </c>
+      <c r="F59" s="73">
+        <v>363.51884460048637</v>
+      </c>
+    </row>
+    <row r="60" spans="2:7" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="B60" s="129">
+        <v>470</v>
+      </c>
+      <c r="C60" s="70">
+        <v>21.622277066409652</v>
+      </c>
+      <c r="E60" s="129">
+        <v>999</v>
+      </c>
+      <c r="F60" s="73">
+        <v>555.12238239478631</v>
+      </c>
+    </row>
+    <row r="61" spans="2:7" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="B61" s="129">
+        <v>471</v>
+      </c>
+      <c r="C61" s="70">
+        <v>16.237227500114731</v>
+      </c>
+      <c r="E61" s="129">
+        <v>1000</v>
+      </c>
+      <c r="F61" s="73">
+        <v>612.16523245674409</v>
+      </c>
+    </row>
+    <row r="62" spans="2:7" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="B62" s="129">
+        <v>472</v>
+      </c>
+      <c r="C62" s="70">
+        <v>23.152902840883016</v>
+      </c>
+      <c r="E62" s="129">
+        <v>1200</v>
+      </c>
+      <c r="F62" s="73">
+        <v>696.67085203543081</v>
+      </c>
+    </row>
+    <row r="63" spans="2:7" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="B63" s="129">
+        <v>473</v>
+      </c>
+      <c r="C63" s="70">
+        <v>24.073900362568267</v>
+      </c>
+      <c r="E63" s="129">
+        <v>1205</v>
+      </c>
+      <c r="F63" s="73">
+        <v>733.22888177520747</v>
+      </c>
+    </row>
+    <row r="64" spans="2:7" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="B64" s="129">
+        <v>492</v>
+      </c>
+      <c r="C64" s="70">
+        <v>9.2953315893340669</v>
+      </c>
+      <c r="E64" s="129">
+        <v>1500</v>
+      </c>
+      <c r="F64" s="73">
+        <v>1179.214557115976</v>
+      </c>
+    </row>
+    <row r="65" spans="2:6" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="B65" s="129">
+        <v>510</v>
+      </c>
+      <c r="C65" s="70">
+        <v>29.059086236174213</v>
+      </c>
+    </row>
+    <row r="66" spans="2:6" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="B66" s="129">
+        <v>511</v>
+      </c>
+      <c r="C66" s="70">
+        <v>27.410467896645091</v>
+      </c>
+    </row>
+    <row r="67" spans="2:6" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="B67" s="129">
+        <v>512</v>
+      </c>
+      <c r="C67" s="70">
+        <v>10.891508788838403</v>
+      </c>
+    </row>
+    <row r="68" spans="2:6" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="B68" s="129">
+        <v>513</v>
+      </c>
+      <c r="C68" s="70">
+        <v>10.734185368764054</v>
+      </c>
+    </row>
+    <row r="69" spans="2:6" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="B69" s="129">
+        <v>514</v>
+      </c>
+      <c r="C69" s="70">
+        <v>28.583838404699609</v>
+      </c>
+    </row>
+    <row r="70" spans="2:6" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="B70" s="129">
+        <v>530</v>
+      </c>
+      <c r="C70" s="70">
+        <v>31.759804947450547</v>
+      </c>
+    </row>
+    <row r="71" spans="2:6" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="B71" s="129">
+        <v>531</v>
+      </c>
+      <c r="C71" s="70">
+        <v>34.276979668640138</v>
+      </c>
+    </row>
+    <row r="72" spans="2:6" ht="20.399999999999999">
+      <c r="B72" s="7"/>
+      <c r="C72" s="7"/>
+      <c r="D72" s="7"/>
+      <c r="E72" s="7"/>
+      <c r="F72" s="7"/>
+    </row>
+    <row r="73" spans="2:6" ht="20.399999999999999">
+      <c r="B73" s="7"/>
+      <c r="C73" s="7"/>
+      <c r="D73" s="7"/>
+      <c r="E73" s="7"/>
+      <c r="F73" s="7"/>
+    </row>
+    <row r="74" spans="2:6" ht="20.399999999999999">
+      <c r="B74" s="7"/>
+      <c r="C74" s="7"/>
+      <c r="D74" s="7"/>
+      <c r="E74" s="7"/>
+      <c r="F74" s="7"/>
+    </row>
+    <row r="75" spans="2:6" ht="20.399999999999999">
+      <c r="B75" s="7"/>
+      <c r="C75" s="7"/>
+      <c r="D75" s="7"/>
+      <c r="E75" s="7"/>
+      <c r="F75" s="7"/>
+    </row>
+    <row r="76" spans="2:6" ht="20.399999999999999">
+      <c r="B76" s="7"/>
+      <c r="C76" s="7"/>
+      <c r="D76" s="7"/>
+      <c r="E76" s="7"/>
+      <c r="F76" s="7"/>
+    </row>
+    <row r="128" spans="15:16" ht="18">
+      <c r="O128" s="5"/>
+      <c r="P128" s="6"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="B2:M3"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="J11:J12"/>
+  </mergeCells>
+  <phoneticPr fontId="43" type="noConversion"/>
+  <pageMargins left="0.5" right="0.5" top="0.39000000000000007" bottom="0.39000000000000007" header="0" footer="0"/>
+  <pageSetup scale="52" orientation="portrait" r:id="rId1"/>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="71" max="16383" man="1"/>
+  </rowBreaks>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="13" max="1048575" man="1"/>
+  </colBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1027015D-487D-DD4F-8ABF-780817ED8D59}">
   <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.6"/>
@@ -25310,10 +25639,10 @@
     </row>
     <row r="6" spans="1:11" ht="21">
       <c r="A6" s="13"/>
-      <c r="B6" s="442" t="s">
+      <c r="B6" s="447" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="444" t="s">
+      <c r="C6" s="449" t="s">
         <v>0</v>
       </c>
       <c r="D6" s="290" t="s">
@@ -25329,8 +25658,8 @@
     </row>
     <row r="7" spans="1:11" ht="21">
       <c r="A7" s="13"/>
-      <c r="B7" s="443"/>
-      <c r="C7" s="445"/>
+      <c r="B7" s="448"/>
+      <c r="C7" s="450"/>
       <c r="D7" s="292" t="s">
         <v>100</v>
       </c>
@@ -25482,7 +25811,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25506AED-C7DA-1E4E-801C-D8A7E27EA3F8}">
   <dimension ref="B1:I68"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.6"/>
@@ -26296,7 +26625,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9D7A3D9-D001-F74F-A815-3F376934A37D}">
   <dimension ref="B1:I72"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.6"/>
@@ -27233,7 +27562,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F69F168-0057-494C-B3B1-139AA2E7447A}">
   <dimension ref="B1:H105"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.6"/>
@@ -28493,7 +28822,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{342BD54F-5826-E245-8B48-014A4A3D6F1C}">
   <dimension ref="A2:K11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.6"/>
@@ -28631,7 +28960,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{736167A2-EDF5-41C9-A1FA-A4E74C9A4DE0}">
   <dimension ref="B1:M71"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.6"/>
@@ -29707,7 +30036,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2500-000000000000}">
   <dimension ref="B1:M71"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.6"/>
@@ -30185,7 +30514,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0C2C75B-4790-49ED-A41E-FB92946CE1CB}">
   <dimension ref="B1:M71"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.6"/>
@@ -30800,7 +31129,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7164E7E1-0C1D-DF47-AE8C-983858CE43BE}">
   <dimension ref="B1:L68"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.6"/>
@@ -31230,7 +31559,2472 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EED1ABC8-4161-BE4E-B620-33582EF339FF}">
+  <dimension ref="A2:N89"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.6"/>
+  <cols>
+    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="10" max="10" width="9.796875" customWidth="1"/>
+    <col min="14" max="14" width="10.796875" style="143"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:14">
+      <c r="A2" s="387" t="s">
+        <v>1590</v>
+      </c>
+      <c r="B2" s="387"/>
+      <c r="C2" s="387"/>
+      <c r="D2" s="387"/>
+      <c r="E2" s="387"/>
+      <c r="F2" s="387"/>
+      <c r="G2" s="387"/>
+      <c r="H2" s="387"/>
+      <c r="I2" s="387"/>
+      <c r="J2" s="387"/>
+      <c r="K2" s="387"/>
+      <c r="L2" s="387"/>
+      <c r="M2" s="387"/>
+      <c r="N2" s="387"/>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="387"/>
+      <c r="B3" s="387"/>
+      <c r="C3" s="387"/>
+      <c r="D3" s="387"/>
+      <c r="E3" s="387"/>
+      <c r="F3" s="387"/>
+      <c r="G3" s="387"/>
+      <c r="H3" s="387"/>
+      <c r="I3" s="387"/>
+      <c r="J3" s="387"/>
+      <c r="K3" s="387"/>
+      <c r="L3" s="387"/>
+      <c r="M3" s="387"/>
+      <c r="N3" s="387"/>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>1586</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="16.2" thickBot="1"/>
+    <row r="6" spans="1:14" ht="21">
+      <c r="A6" s="391" t="s">
+        <v>99</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="C6" s="9"/>
+      <c r="D6" s="391" t="s">
+        <v>99</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="F6" s="100"/>
+      <c r="G6" s="391" t="s">
+        <v>99</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="I6" s="9"/>
+      <c r="J6" s="391" t="s">
+        <v>99</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="L6" s="9"/>
+      <c r="M6" s="391" t="s">
+        <v>99</v>
+      </c>
+      <c r="N6" s="43" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="21.6" thickBot="1">
+      <c r="A7" s="393"/>
+      <c r="B7" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="C7" s="9"/>
+      <c r="D7" s="393"/>
+      <c r="E7" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="F7" s="100"/>
+      <c r="G7" s="393"/>
+      <c r="H7" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="I7" s="9"/>
+      <c r="J7" s="393"/>
+      <c r="K7" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="L7" s="9"/>
+      <c r="M7" s="393"/>
+      <c r="N7" s="44" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="21">
+      <c r="A8" s="117" t="s">
+        <v>1215</v>
+      </c>
+      <c r="B8" s="212">
+        <v>6.7203999999999997</v>
+      </c>
+      <c r="C8" s="7"/>
+      <c r="D8" s="140" t="s">
+        <v>246</v>
+      </c>
+      <c r="E8" s="213">
+        <v>111.07047999999999</v>
+      </c>
+      <c r="F8" s="101"/>
+      <c r="G8" s="140" t="s">
+        <v>604</v>
+      </c>
+      <c r="H8" s="213">
+        <v>76.068159999999992</v>
+      </c>
+      <c r="I8" s="7"/>
+      <c r="J8" t="s">
+        <v>1216</v>
+      </c>
+      <c r="K8" s="59">
+        <v>9.4476960851805938</v>
+      </c>
+      <c r="L8" s="7"/>
+      <c r="M8" s="140" t="s">
+        <v>702</v>
+      </c>
+      <c r="N8" s="144">
+        <v>44.561409426774979</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="21">
+      <c r="A9" s="139" t="s">
+        <v>487</v>
+      </c>
+      <c r="B9" s="213">
+        <v>7.0644799999999996</v>
+      </c>
+      <c r="C9" s="7"/>
+      <c r="D9" s="140" t="s">
+        <v>548</v>
+      </c>
+      <c r="E9" s="213">
+        <v>114.57384</v>
+      </c>
+      <c r="F9" s="101"/>
+      <c r="G9" s="140" t="s">
+        <v>605</v>
+      </c>
+      <c r="H9" s="213">
+        <v>76.881439999999998</v>
+      </c>
+      <c r="I9" s="7"/>
+      <c r="J9" s="140" t="s">
+        <v>646</v>
+      </c>
+      <c r="K9" s="60">
+        <v>11.570833907017301</v>
+      </c>
+      <c r="L9" s="7"/>
+      <c r="M9" s="140" t="s">
+        <v>703</v>
+      </c>
+      <c r="N9" s="145">
+        <v>46.86299279452934</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="21">
+      <c r="A10" s="139" t="s">
+        <v>488</v>
+      </c>
+      <c r="B10" s="213">
+        <v>8.1279999999999983</v>
+      </c>
+      <c r="C10" s="7"/>
+      <c r="D10" s="140" t="s">
+        <v>549</v>
+      </c>
+      <c r="E10" s="213">
+        <v>116.16911999999999</v>
+      </c>
+      <c r="F10" s="101"/>
+      <c r="G10" s="140" t="s">
+        <v>606</v>
+      </c>
+      <c r="H10" s="213">
+        <v>78.633119999999991</v>
+      </c>
+      <c r="I10" s="7"/>
+      <c r="J10" s="140" t="s">
+        <v>89</v>
+      </c>
+      <c r="K10" s="60">
+        <v>12.506762586626278</v>
+      </c>
+      <c r="L10" s="7"/>
+      <c r="M10" s="140" t="s">
+        <v>704</v>
+      </c>
+      <c r="N10" s="145">
+        <v>49.80188168341823</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="21">
+      <c r="A11" s="139" t="s">
+        <v>489</v>
+      </c>
+      <c r="B11" s="213">
+        <v>8.4407999999999994</v>
+      </c>
+      <c r="C11" s="7"/>
+      <c r="D11" s="140" t="s">
+        <v>550</v>
+      </c>
+      <c r="E11" s="213">
+        <v>121.29903999999999</v>
+      </c>
+      <c r="F11" s="101"/>
+      <c r="G11" s="140" t="s">
+        <v>607</v>
+      </c>
+      <c r="H11" s="213">
+        <v>83.669200000000004</v>
+      </c>
+      <c r="I11" s="7"/>
+      <c r="J11" s="140" t="s">
+        <v>647</v>
+      </c>
+      <c r="K11" s="60">
+        <v>12.819952728440954</v>
+      </c>
+      <c r="L11" s="7"/>
+      <c r="M11" s="140" t="s">
+        <v>705</v>
+      </c>
+      <c r="N11" s="145">
+        <v>56.946987011794931</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="21">
+      <c r="A12" s="139" t="s">
+        <v>490</v>
+      </c>
+      <c r="B12" s="213">
+        <v>8.8161599999999982</v>
+      </c>
+      <c r="C12" s="7"/>
+      <c r="D12" s="140" t="s">
+        <v>551</v>
+      </c>
+      <c r="E12" s="213">
+        <v>123.05071999999998</v>
+      </c>
+      <c r="F12" s="101"/>
+      <c r="G12" s="140" t="s">
+        <v>608</v>
+      </c>
+      <c r="H12" s="213">
+        <v>90.550799999999995</v>
+      </c>
+      <c r="I12" s="7"/>
+      <c r="J12" s="140" t="s">
+        <v>648</v>
+      </c>
+      <c r="K12" s="60">
+        <v>13.224186516131992</v>
+      </c>
+      <c r="L12" s="7"/>
+      <c r="M12" s="140" t="s">
+        <v>706</v>
+      </c>
+      <c r="N12" s="145">
+        <v>61.153203451282735</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="21">
+      <c r="A13" s="139" t="s">
+        <v>491</v>
+      </c>
+      <c r="B13" s="213">
+        <v>8.9725599999999996</v>
+      </c>
+      <c r="C13" s="7"/>
+      <c r="D13" s="140" t="s">
+        <v>552</v>
+      </c>
+      <c r="E13" s="213">
+        <v>124.70856000000001</v>
+      </c>
+      <c r="F13" s="101"/>
+      <c r="G13" s="140" t="s">
+        <v>609</v>
+      </c>
+      <c r="H13" s="213">
+        <v>105.15856000000001</v>
+      </c>
+      <c r="I13" s="7"/>
+      <c r="J13" s="140" t="s">
+        <v>649</v>
+      </c>
+      <c r="K13" s="60">
+        <v>13.66119601633852</v>
+      </c>
+      <c r="L13" s="7"/>
+      <c r="M13" s="140" t="s">
+        <v>707</v>
+      </c>
+      <c r="N13" s="145">
+        <v>66.18973794116296</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="21">
+      <c r="A14" s="139" t="s">
+        <v>492</v>
+      </c>
+      <c r="B14" s="213">
+        <v>9.1915199999999988</v>
+      </c>
+      <c r="C14" s="7"/>
+      <c r="D14" s="140" t="s">
+        <v>553</v>
+      </c>
+      <c r="E14" s="213">
+        <v>128.99392</v>
+      </c>
+      <c r="F14" s="101"/>
+      <c r="G14" s="140" t="s">
+        <v>610</v>
+      </c>
+      <c r="H14" s="213">
+        <v>130.68303999999998</v>
+      </c>
+      <c r="I14" s="7"/>
+      <c r="J14" s="140" t="s">
+        <v>650</v>
+      </c>
+      <c r="K14" s="60">
+        <v>14.039937583184171</v>
+      </c>
+      <c r="L14" s="7"/>
+      <c r="M14" s="140" t="s">
+        <v>708</v>
+      </c>
+      <c r="N14" s="145">
+        <v>71.240839414383387</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="21">
+      <c r="A15" s="139" t="s">
+        <v>493</v>
+      </c>
+      <c r="B15" s="213">
+        <v>9.3166399999999996</v>
+      </c>
+      <c r="C15" s="7"/>
+      <c r="D15" s="140" t="s">
+        <v>554</v>
+      </c>
+      <c r="E15" s="213">
+        <v>130.68303999999998</v>
+      </c>
+      <c r="F15" s="101"/>
+      <c r="G15" s="140" t="s">
+        <v>611</v>
+      </c>
+      <c r="H15" s="213">
+        <v>134.93711999999996</v>
+      </c>
+      <c r="I15" s="7"/>
+      <c r="J15" s="140" t="s">
+        <v>651</v>
+      </c>
+      <c r="K15" s="60">
+        <v>14.506081050071133</v>
+      </c>
+      <c r="L15" s="7"/>
+      <c r="M15" s="140" t="s">
+        <v>709</v>
+      </c>
+      <c r="N15" s="145">
+        <v>76.284657395933706</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="21">
+      <c r="A16" s="139" t="s">
+        <v>494</v>
+      </c>
+      <c r="B16" s="213">
+        <v>9.4730399999999992</v>
+      </c>
+      <c r="C16" s="7"/>
+      <c r="D16" s="140" t="s">
+        <v>252</v>
+      </c>
+      <c r="E16" s="213">
+        <v>134.09255999999999</v>
+      </c>
+      <c r="F16" s="101"/>
+      <c r="G16" s="140" t="s">
+        <v>612</v>
+      </c>
+      <c r="H16" s="213">
+        <v>199.96823999999998</v>
+      </c>
+      <c r="I16" s="7"/>
+      <c r="J16" s="140" t="s">
+        <v>90</v>
+      </c>
+      <c r="K16" s="60">
+        <v>14.611691679287711</v>
+      </c>
+      <c r="L16" s="7"/>
+      <c r="M16" s="140" t="s">
+        <v>710</v>
+      </c>
+      <c r="N16" s="145">
+        <v>85.112249300105546</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="21">
+      <c r="A17" s="139" t="s">
+        <v>495</v>
+      </c>
+      <c r="B17" s="213">
+        <v>9.8796799999999987</v>
+      </c>
+      <c r="C17" s="7"/>
+      <c r="D17" s="140" t="s">
+        <v>256</v>
+      </c>
+      <c r="E17" s="213">
+        <v>138.37791999999999</v>
+      </c>
+      <c r="F17" s="101"/>
+      <c r="G17" s="140" t="s">
+        <v>613</v>
+      </c>
+      <c r="H17" s="213">
+        <v>259.80687999999998</v>
+      </c>
+      <c r="I17" s="7"/>
+      <c r="J17" s="140" t="s">
+        <v>652</v>
+      </c>
+      <c r="K17" s="60">
+        <v>14.811987700215703</v>
+      </c>
+      <c r="L17" s="7"/>
+      <c r="M17" s="140" t="s">
+        <v>711</v>
+      </c>
+      <c r="N17" s="145">
+        <v>89.737266510624593</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="21">
+      <c r="A18" s="139" t="s">
+        <v>496</v>
+      </c>
+      <c r="B18" s="213">
+        <v>10.12992</v>
+      </c>
+      <c r="C18" s="7"/>
+      <c r="D18" s="140" t="s">
+        <v>555</v>
+      </c>
+      <c r="E18" s="213">
+        <v>143.57039999999998</v>
+      </c>
+      <c r="F18" s="101"/>
+      <c r="G18" s="140" t="s">
+        <v>614</v>
+      </c>
+      <c r="H18" s="213">
+        <v>275.25920000000002</v>
+      </c>
+      <c r="I18" s="7"/>
+      <c r="J18" s="140" t="s">
+        <v>653</v>
+      </c>
+      <c r="K18" s="60">
+        <v>15.299981642112991</v>
+      </c>
+      <c r="L18" s="7"/>
+      <c r="M18" s="140" t="s">
+        <v>712</v>
+      </c>
+      <c r="N18" s="145">
+        <v>90.990027077883312</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="21">
+      <c r="A19" s="139" t="s">
+        <v>497</v>
+      </c>
+      <c r="B19" s="213">
+        <v>10.474</v>
+      </c>
+      <c r="C19" s="7"/>
+      <c r="D19" s="140" t="s">
+        <v>556</v>
+      </c>
+      <c r="E19" s="213">
+        <v>147.01119999999997</v>
+      </c>
+      <c r="F19" s="101"/>
+      <c r="G19" s="140" t="s">
+        <v>615</v>
+      </c>
+      <c r="H19" s="213">
+        <v>286.73895999999996</v>
+      </c>
+      <c r="I19" s="7"/>
+      <c r="J19" s="140" t="s">
+        <v>654</v>
+      </c>
+      <c r="K19" s="60">
+        <v>15.343682592133645</v>
+      </c>
+      <c r="L19" s="7"/>
+      <c r="M19" s="140" t="s">
+        <v>713</v>
+      </c>
+      <c r="N19" s="145">
+        <v>93.094956170544762</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="21">
+      <c r="A20" s="139" t="s">
+        <v>498</v>
+      </c>
+      <c r="B20" s="213">
+        <v>10.911919999999999</v>
+      </c>
+      <c r="C20" s="7"/>
+      <c r="D20" s="140" t="s">
+        <v>557</v>
+      </c>
+      <c r="E20" s="213">
+        <v>150.38943999999998</v>
+      </c>
+      <c r="F20" s="101"/>
+      <c r="G20" s="140" t="s">
+        <v>616</v>
+      </c>
+      <c r="H20" s="213">
+        <v>297.46799999999996</v>
+      </c>
+      <c r="I20" s="7"/>
+      <c r="J20" s="140" t="s">
+        <v>91</v>
+      </c>
+      <c r="K20" s="60">
+        <v>15.726065904814353</v>
+      </c>
+      <c r="L20" s="7"/>
+      <c r="M20" s="140" t="s">
+        <v>714</v>
+      </c>
+      <c r="N20" s="145">
+        <v>95.196243517371116</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="21">
+      <c r="A21" s="139" t="s">
+        <v>499</v>
+      </c>
+      <c r="B21" s="213">
+        <v>11.50624</v>
+      </c>
+      <c r="C21" s="7"/>
+      <c r="D21" s="140" t="s">
+        <v>558</v>
+      </c>
+      <c r="E21" s="213">
+        <v>158.96015999999997</v>
+      </c>
+      <c r="F21" s="101"/>
+      <c r="G21" s="140" t="s">
+        <v>617</v>
+      </c>
+      <c r="H21" s="213">
+        <v>329.96791999999999</v>
+      </c>
+      <c r="I21" s="7"/>
+      <c r="J21" s="140" t="s">
+        <v>655</v>
+      </c>
+      <c r="K21" s="60">
+        <v>15.758841617329844</v>
+      </c>
+      <c r="L21" s="7"/>
+      <c r="M21" s="140" t="s">
+        <v>715</v>
+      </c>
+      <c r="N21" s="145">
+        <v>98.146057643765189</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="21">
+      <c r="A22" s="139" t="s">
+        <v>500</v>
+      </c>
+      <c r="B22" s="213">
+        <v>11.881599999999999</v>
+      </c>
+      <c r="C22" s="7"/>
+      <c r="D22" s="140" t="s">
+        <v>559</v>
+      </c>
+      <c r="E22" s="213">
+        <v>172.62952000000001</v>
+      </c>
+      <c r="F22" s="101"/>
+      <c r="G22" s="140" t="s">
+        <v>618</v>
+      </c>
+      <c r="H22" s="213">
+        <v>367.4726399999999</v>
+      </c>
+      <c r="I22" s="7"/>
+      <c r="J22" s="140" t="s">
+        <v>656</v>
+      </c>
+      <c r="K22" s="60">
+        <v>15.980988113268161</v>
+      </c>
+      <c r="L22" s="7"/>
+      <c r="M22" s="140" t="s">
+        <v>716</v>
+      </c>
+      <c r="N22" s="145">
+        <v>110.33133920785717</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="21">
+      <c r="A23" s="139" t="s">
+        <v>501</v>
+      </c>
+      <c r="B23" s="213">
+        <v>12.726160000000002</v>
+      </c>
+      <c r="C23" s="7"/>
+      <c r="D23" s="140" t="s">
+        <v>560</v>
+      </c>
+      <c r="E23" s="213">
+        <v>193.08664000000002</v>
+      </c>
+      <c r="F23" s="101"/>
+      <c r="G23" s="140" t="s">
+        <v>619</v>
+      </c>
+      <c r="H23" s="213">
+        <v>388.05487999999997</v>
+      </c>
+      <c r="I23" s="7"/>
+      <c r="J23" s="140" t="s">
+        <v>657</v>
+      </c>
+      <c r="K23" s="60">
+        <v>16.137583184175501</v>
+      </c>
+      <c r="L23" s="7"/>
+      <c r="M23" s="114"/>
+      <c r="N23" s="145">
+        <v>1.4686309605764374</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="21">
+      <c r="A24" s="139" t="s">
+        <v>502</v>
+      </c>
+      <c r="B24" s="213">
+        <v>12.88256</v>
+      </c>
+      <c r="C24" s="7"/>
+      <c r="D24" s="140" t="s">
+        <v>561</v>
+      </c>
+      <c r="E24" s="213">
+        <v>196.80895999999998</v>
+      </c>
+      <c r="F24" s="101"/>
+      <c r="G24" s="140" t="s">
+        <v>620</v>
+      </c>
+      <c r="H24" s="213">
+        <v>405.19632000000001</v>
+      </c>
+      <c r="I24" s="7"/>
+      <c r="J24" s="140" t="s">
+        <v>92</v>
+      </c>
+      <c r="K24" s="60">
+        <v>16.184925880031205</v>
+      </c>
+      <c r="L24" s="7"/>
+      <c r="M24" s="140" t="s">
+        <v>717</v>
+      </c>
+      <c r="N24" s="145">
+        <v>8.9305681766028702</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="21">
+      <c r="A25" s="139" t="s">
+        <v>503</v>
+      </c>
+      <c r="B25" s="213">
+        <v>13.977360000000001</v>
+      </c>
+      <c r="C25" s="7"/>
+      <c r="D25" s="140" t="s">
+        <v>562</v>
+      </c>
+      <c r="E25" s="213">
+        <v>199.96823999999998</v>
+      </c>
+      <c r="F25" s="101"/>
+      <c r="G25" s="140" t="s">
+        <v>621</v>
+      </c>
+      <c r="H25" s="213">
+        <v>483.83424000000002</v>
+      </c>
+      <c r="I25" s="7"/>
+      <c r="J25" s="140" t="s">
+        <v>658</v>
+      </c>
+      <c r="K25" s="60">
+        <v>16.603726651062459</v>
+      </c>
+      <c r="L25" s="7"/>
+      <c r="M25" s="140" t="s">
+        <v>718</v>
+      </c>
+      <c r="N25" s="145">
+        <v>9.9903162146036966</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="21">
+      <c r="A26" s="139" t="s">
+        <v>504</v>
+      </c>
+      <c r="B26" s="213">
+        <v>14.602959999999999</v>
+      </c>
+      <c r="C26" s="7"/>
+      <c r="D26" s="140" t="s">
+        <v>563</v>
+      </c>
+      <c r="E26" s="213">
+        <v>223.86615999999998</v>
+      </c>
+      <c r="F26" s="101"/>
+      <c r="G26" s="140" t="s">
+        <v>622</v>
+      </c>
+      <c r="H26" s="213">
+        <v>504.3852</v>
+      </c>
+      <c r="I26" s="7"/>
+      <c r="J26" s="140" t="s">
+        <v>659</v>
+      </c>
+      <c r="K26" s="60">
+        <v>17.120854559640183</v>
+      </c>
+      <c r="L26" s="7"/>
+      <c r="M26" s="140" t="s">
+        <v>719</v>
+      </c>
+      <c r="N26" s="145">
+        <v>10.725948873284684</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="21">
+      <c r="A27" s="139" t="s">
+        <v>505</v>
+      </c>
+      <c r="B27" s="213">
+        <v>15.322399999999998</v>
+      </c>
+      <c r="C27" s="7"/>
+      <c r="D27" s="140" t="s">
+        <v>564</v>
+      </c>
+      <c r="E27" s="213">
+        <v>225.71168</v>
+      </c>
+      <c r="F27" s="101"/>
+      <c r="H27" s="7">
+        <v>5</v>
+      </c>
+      <c r="I27" s="7"/>
+      <c r="J27" s="140" t="s">
+        <v>660</v>
+      </c>
+      <c r="K27" s="60">
+        <v>17.437686447289913</v>
+      </c>
+      <c r="L27" s="7"/>
+      <c r="M27" s="140" t="s">
+        <v>720</v>
+      </c>
+      <c r="N27" s="145">
+        <v>11.141107898480882</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" ht="21">
+      <c r="A28" s="139" t="s">
+        <v>506</v>
+      </c>
+      <c r="B28" s="213">
+        <v>16.16696</v>
+      </c>
+      <c r="C28" s="7"/>
+      <c r="D28" s="140" t="s">
+        <v>334</v>
+      </c>
+      <c r="E28" s="213">
+        <v>237.56679999999994</v>
+      </c>
+      <c r="F28" s="101"/>
+      <c r="G28" s="140" t="s">
+        <v>623</v>
+      </c>
+      <c r="H28" s="7">
+        <v>30.24296</v>
+      </c>
+      <c r="I28" s="7"/>
+      <c r="J28" s="140" t="s">
+        <v>661</v>
+      </c>
+      <c r="K28" s="60">
+        <v>17.860128964156225</v>
+      </c>
+      <c r="L28" s="7"/>
+      <c r="M28" s="140" t="s">
+        <v>721</v>
+      </c>
+      <c r="N28" s="145">
+        <v>11.570833907017301</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="21">
+      <c r="A29" s="139" t="s">
+        <v>507</v>
+      </c>
+      <c r="B29" s="213">
+        <v>16.354639999999996</v>
+      </c>
+      <c r="C29" s="7"/>
+      <c r="D29" s="140" t="s">
+        <v>565</v>
+      </c>
+      <c r="E29" s="213">
+        <v>240.94504000000001</v>
+      </c>
+      <c r="F29" s="101"/>
+      <c r="G29" s="140" t="s">
+        <v>624</v>
+      </c>
+      <c r="H29" s="7">
+        <v>31.963359999999994</v>
+      </c>
+      <c r="I29" s="7"/>
+      <c r="J29" s="140" t="s">
+        <v>662</v>
+      </c>
+      <c r="K29" s="60">
+        <v>17.965739593372803</v>
+      </c>
+      <c r="L29" s="7"/>
+      <c r="M29" s="140" t="s">
+        <v>722</v>
+      </c>
+      <c r="N29" s="145">
+        <v>11.975067694708338</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="21">
+      <c r="A30" s="139" t="s">
+        <v>508</v>
+      </c>
+      <c r="B30" s="213">
+        <v>17.011519999999997</v>
+      </c>
+      <c r="C30" s="7"/>
+      <c r="D30" s="140" t="s">
+        <v>335</v>
+      </c>
+      <c r="E30" s="213">
+        <v>242.72799999999998</v>
+      </c>
+      <c r="F30" s="101"/>
+      <c r="G30" s="140" t="s">
+        <v>625</v>
+      </c>
+      <c r="H30" s="7">
+        <v>366.28399999999999</v>
+      </c>
+      <c r="I30" s="7"/>
+      <c r="J30" s="140" t="s">
+        <v>663</v>
+      </c>
+      <c r="K30" s="60">
+        <v>18.395465601909216</v>
+      </c>
+      <c r="L30" s="7"/>
+      <c r="M30" s="140" t="s">
+        <v>723</v>
+      </c>
+      <c r="N30" s="145">
+        <v>12.4011519574097</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" ht="21">
+      <c r="A31" s="139" t="s">
+        <v>509</v>
+      </c>
+      <c r="B31" s="213">
+        <v>17.41816</v>
+      </c>
+      <c r="C31" s="7"/>
+      <c r="D31" s="140" t="s">
+        <v>566</v>
+      </c>
+      <c r="E31" s="213">
+        <v>247.88919999999999</v>
+      </c>
+      <c r="F31" s="101"/>
+      <c r="G31" s="140" t="s">
+        <v>626</v>
+      </c>
+      <c r="H31" s="7">
+        <v>411.42104</v>
+      </c>
+      <c r="I31" s="7"/>
+      <c r="J31" s="140" t="s">
+        <v>664</v>
+      </c>
+      <c r="K31" s="60">
+        <v>18.708655743723895</v>
+      </c>
+      <c r="L31" s="7"/>
+      <c r="M31" s="140" t="s">
+        <v>724</v>
+      </c>
+      <c r="N31" s="145">
+        <v>12.506762586626278</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" ht="21">
+      <c r="A32" s="139" t="s">
+        <v>510</v>
+      </c>
+      <c r="B32" s="213">
+        <v>18.356559999999995</v>
+      </c>
+      <c r="C32" s="7"/>
+      <c r="D32" s="140" t="s">
+        <v>567</v>
+      </c>
+      <c r="E32" s="213">
+        <v>261.55856</v>
+      </c>
+      <c r="F32" s="101"/>
+      <c r="G32" s="140" t="s">
+        <v>627</v>
+      </c>
+      <c r="H32" s="7">
+        <v>522.62143999999989</v>
+      </c>
+      <c r="I32" s="7"/>
+      <c r="J32" s="140" t="s">
+        <v>665</v>
+      </c>
+      <c r="K32" s="60">
+        <v>19.021845885538571</v>
+      </c>
+      <c r="L32" s="7"/>
+      <c r="M32" s="140" t="s">
+        <v>725</v>
+      </c>
+      <c r="N32" s="145">
+        <v>12.819952728440954</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" ht="21">
+      <c r="A33" s="139" t="s">
+        <v>511</v>
+      </c>
+      <c r="B33" s="213">
+        <v>18.669360000000001</v>
+      </c>
+      <c r="C33" s="7"/>
+      <c r="D33" s="140" t="s">
+        <v>568</v>
+      </c>
+      <c r="E33" s="213">
+        <v>275.25920000000002</v>
+      </c>
+      <c r="F33" s="101"/>
+      <c r="G33" s="140" t="s">
+        <v>628</v>
+      </c>
+      <c r="H33" s="7">
+        <v>557.40479999999991</v>
+      </c>
+      <c r="I33" s="7"/>
+      <c r="J33" s="140" t="s">
+        <v>666</v>
+      </c>
+      <c r="K33" s="60">
+        <v>19.542615539951353</v>
+      </c>
+      <c r="L33" s="7"/>
+      <c r="M33" s="140" t="s">
+        <v>726</v>
+      </c>
+      <c r="N33" s="145">
+        <v>13.224186516131992</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" ht="21">
+      <c r="A34" s="139" t="s">
+        <v>512</v>
+      </c>
+      <c r="B34" s="213">
+        <v>20.421040000000001</v>
+      </c>
+      <c r="C34" s="7"/>
+      <c r="D34" s="140" t="s">
+        <v>342</v>
+      </c>
+      <c r="E34" s="213">
+        <v>286.73895999999996</v>
+      </c>
+      <c r="F34" s="101"/>
+      <c r="G34" s="140" t="s">
+        <v>629</v>
+      </c>
+      <c r="H34" s="7">
+        <v>731.66567999999995</v>
+      </c>
+      <c r="I34" s="7"/>
+      <c r="J34" s="140" t="s">
+        <v>667</v>
+      </c>
+      <c r="K34" s="60">
+        <v>19.750195052549447</v>
+      </c>
+      <c r="L34" s="7"/>
+      <c r="M34" s="140" t="s">
+        <v>727</v>
+      </c>
+      <c r="N34" s="145">
+        <v>14.039937583184171</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" ht="21.6" thickBot="1">
+      <c r="A35" s="139" t="s">
+        <v>513</v>
+      </c>
+      <c r="B35" s="213">
+        <v>21.296879999999998</v>
+      </c>
+      <c r="C35" s="7"/>
+      <c r="D35" s="140" t="s">
+        <v>569</v>
+      </c>
+      <c r="E35" s="213">
+        <v>295.71631999999994</v>
+      </c>
+      <c r="F35" s="101"/>
+      <c r="G35" s="140" t="s">
+        <v>630</v>
+      </c>
+      <c r="H35" s="7">
+        <v>806.83151999999984</v>
+      </c>
+      <c r="I35" s="7"/>
+      <c r="J35" s="140" t="s">
+        <v>668</v>
+      </c>
+      <c r="K35" s="60">
+        <v>19.972341548487766</v>
+      </c>
+      <c r="L35" s="7"/>
+      <c r="M35" s="140" t="s">
+        <v>728</v>
+      </c>
+      <c r="N35" s="146">
+        <v>15.136103079535545</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" ht="21">
+      <c r="A36" s="139" t="s">
+        <v>514</v>
+      </c>
+      <c r="B36" s="213">
+        <v>22.078879999999998</v>
+      </c>
+      <c r="C36" s="7"/>
+      <c r="D36" s="140" t="s">
+        <v>570</v>
+      </c>
+      <c r="E36" s="213">
+        <v>297.46799999999996</v>
+      </c>
+      <c r="F36" s="101"/>
+      <c r="G36" s="140" t="s">
+        <v>631</v>
+      </c>
+      <c r="H36" s="7">
+        <v>1022.3194400000001</v>
+      </c>
+      <c r="I36" s="7"/>
+      <c r="J36" s="140" t="s">
+        <v>93</v>
+      </c>
+      <c r="K36" s="60">
+        <v>20.39114231951902</v>
+      </c>
+      <c r="L36" s="7"/>
+      <c r="M36" s="140" t="s">
+        <v>729</v>
+      </c>
+      <c r="N36" s="147">
+        <v>16.396147138464361</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" ht="21">
+      <c r="A37" s="139" t="s">
+        <v>515</v>
+      </c>
+      <c r="B37" s="213">
+        <v>22.985999999999997</v>
+      </c>
+      <c r="C37" s="7"/>
+      <c r="D37" s="140" t="s">
+        <v>349</v>
+      </c>
+      <c r="E37" s="213">
+        <v>309.41695999999996</v>
+      </c>
+      <c r="F37" s="101"/>
+      <c r="G37" s="140" t="s">
+        <v>632</v>
+      </c>
+      <c r="H37" s="7">
+        <v>1102.52136</v>
+      </c>
+      <c r="I37" s="7"/>
+      <c r="J37" s="140" t="s">
+        <v>669</v>
+      </c>
+      <c r="K37" s="60">
+        <v>20.984746890632888</v>
+      </c>
+      <c r="L37" s="7"/>
+      <c r="M37" s="140" t="s">
+        <v>730</v>
+      </c>
+      <c r="N37" s="148">
+        <v>17.120854559640183</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" ht="21">
+      <c r="A38" s="139" t="s">
+        <v>516</v>
+      </c>
+      <c r="B38" s="213">
+        <v>23.830559999999998</v>
+      </c>
+      <c r="C38" s="7"/>
+      <c r="D38" s="140" t="s">
+        <v>571</v>
+      </c>
+      <c r="E38" s="213">
+        <v>312.79520000000002</v>
+      </c>
+      <c r="F38" s="101"/>
+      <c r="G38" s="140" t="s">
+        <v>633</v>
+      </c>
+      <c r="H38" s="7">
+        <v>1971.7612799999999</v>
+      </c>
+      <c r="I38" s="7"/>
+      <c r="J38" s="140" t="s">
+        <v>670</v>
+      </c>
+      <c r="K38" s="60">
+        <v>21.531008765891041</v>
+      </c>
+      <c r="L38" s="7"/>
+      <c r="M38" s="140" t="s">
+        <v>731</v>
+      </c>
+      <c r="N38" s="148">
+        <v>17.437686447289913</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" ht="21">
+      <c r="A39" s="139" t="s">
+        <v>517</v>
+      </c>
+      <c r="B39" s="213">
+        <v>24.737679999999997</v>
+      </c>
+      <c r="C39" s="7"/>
+      <c r="D39" s="140" t="s">
+        <v>572</v>
+      </c>
+      <c r="E39" s="213">
+        <v>317.89384000000001</v>
+      </c>
+      <c r="F39" s="101"/>
+      <c r="G39" s="140" t="s">
+        <v>634</v>
+      </c>
+      <c r="H39" s="7">
+        <v>2067.8221599999997</v>
+      </c>
+      <c r="I39" s="7"/>
+      <c r="J39" s="140" t="s">
+        <v>671</v>
+      </c>
+      <c r="K39" s="60">
+        <v>21.636619395107616</v>
+      </c>
+      <c r="L39" s="7"/>
+      <c r="M39" s="140" t="s">
+        <v>732</v>
+      </c>
+      <c r="N39" s="148">
+        <v>17.965739593372803</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" ht="21">
+      <c r="A40" s="139" t="s">
+        <v>518</v>
+      </c>
+      <c r="B40" s="213">
+        <v>25.550959999999996</v>
+      </c>
+      <c r="C40" s="7"/>
+      <c r="D40" s="140" t="s">
+        <v>573</v>
+      </c>
+      <c r="E40" s="213">
+        <v>329.96791999999999</v>
+      </c>
+      <c r="F40" s="101"/>
+      <c r="G40" s="140" t="s">
+        <v>635</v>
+      </c>
+      <c r="H40" s="7">
+        <v>3408.9208799999997</v>
+      </c>
+      <c r="I40" s="7"/>
+      <c r="J40" s="140" t="s">
+        <v>672</v>
+      </c>
+      <c r="K40" s="60">
+        <v>22.073628895314144</v>
+      </c>
+      <c r="L40" s="7"/>
+      <c r="M40" s="140" t="s">
+        <v>733</v>
+      </c>
+      <c r="N40" s="148">
+        <v>18.708655743723895</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" ht="21">
+      <c r="A41" s="139" t="s">
+        <v>519</v>
+      </c>
+      <c r="B41" s="213">
+        <v>26.645759999999996</v>
+      </c>
+      <c r="C41" s="7"/>
+      <c r="D41" s="140" t="s">
+        <v>574</v>
+      </c>
+      <c r="E41" s="213">
+        <v>338.44479999999993</v>
+      </c>
+      <c r="F41" s="101"/>
+      <c r="G41" s="140" t="s">
+        <v>636</v>
+      </c>
+      <c r="H41" s="7">
+        <v>3631.9159999999997</v>
+      </c>
+      <c r="I41" s="7"/>
+      <c r="J41" s="140" t="s">
+        <v>673</v>
+      </c>
+      <c r="K41" s="60">
+        <v>22.164672541190502</v>
+      </c>
+      <c r="L41" s="7"/>
+      <c r="M41" s="140" t="s">
+        <v>734</v>
+      </c>
+      <c r="N41" s="148">
+        <v>19.542615539951353</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" ht="21">
+      <c r="A42" s="139" t="s">
+        <v>520</v>
+      </c>
+      <c r="B42" s="213">
+        <v>27.271359999999998</v>
+      </c>
+      <c r="C42" s="7"/>
+      <c r="D42" s="140" t="s">
+        <v>575</v>
+      </c>
+      <c r="E42" s="213">
+        <v>350.51887999999997</v>
+      </c>
+      <c r="F42" s="101"/>
+      <c r="G42" s="140" t="s">
+        <v>637</v>
+      </c>
+      <c r="H42" s="7">
+        <v>5951.04648</v>
+      </c>
+      <c r="I42" s="7"/>
+      <c r="J42" s="140" t="s">
+        <v>674</v>
+      </c>
+      <c r="K42" s="60">
+        <v>22.386819037128827</v>
+      </c>
+      <c r="L42" s="7"/>
+      <c r="M42" s="140" t="s">
+        <v>735</v>
+      </c>
+      <c r="N42" s="148">
+        <v>22.594398549726922</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" ht="21">
+      <c r="A43" s="139" t="s">
+        <v>521</v>
+      </c>
+      <c r="B43" s="213">
+        <v>28.053359999999998</v>
+      </c>
+      <c r="C43" s="7"/>
+      <c r="D43" s="140" t="s">
+        <v>576</v>
+      </c>
+      <c r="E43" s="213">
+        <v>370.88215999999994</v>
+      </c>
+      <c r="F43" s="101"/>
+      <c r="G43" s="140" t="s">
+        <v>638</v>
+      </c>
+      <c r="H43" s="7">
+        <v>6408.3913599999987</v>
+      </c>
+      <c r="I43" s="7"/>
+      <c r="J43" s="140" t="s">
+        <v>675</v>
+      </c>
+      <c r="K43" s="60">
+        <v>22.594398549726922</v>
+      </c>
+      <c r="L43" s="7"/>
+      <c r="M43" s="140" t="s">
+        <v>736</v>
+      </c>
+      <c r="N43" s="148">
+        <v>25.420393317729125</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" ht="21">
+      <c r="A44" s="139" t="s">
+        <v>522</v>
+      </c>
+      <c r="B44" s="213">
+        <v>28.929200000000002</v>
+      </c>
+      <c r="C44" s="7"/>
+      <c r="D44" s="140" t="s">
+        <v>577</v>
+      </c>
+      <c r="E44" s="213">
+        <v>388.05487999999997</v>
+      </c>
+      <c r="F44" s="101"/>
+      <c r="G44" s="140" t="s">
+        <v>639</v>
+      </c>
+      <c r="H44" s="7">
+        <v>6865.7987999999987</v>
+      </c>
+      <c r="I44" s="7"/>
+      <c r="J44" s="140" t="s">
+        <v>676</v>
+      </c>
+      <c r="K44" s="60">
+        <v>23.326389462572852</v>
+      </c>
+      <c r="L44" s="7"/>
+      <c r="M44" s="140" t="s">
+        <v>737</v>
+      </c>
+      <c r="N44" s="148">
+        <v>25.857402817935654</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" ht="21">
+      <c r="A45" s="139" t="s">
+        <v>523</v>
+      </c>
+      <c r="B45" s="213">
+        <v>30.712160000000001</v>
+      </c>
+      <c r="C45" s="7"/>
+      <c r="D45" s="140" t="s">
+        <v>578</v>
+      </c>
+      <c r="E45" s="213">
+        <v>429.18808000000001</v>
+      </c>
+      <c r="F45" s="101"/>
+      <c r="G45" s="140" t="s">
+        <v>640</v>
+      </c>
+      <c r="H45" s="7">
+        <v>7323.1749599999994</v>
+      </c>
+      <c r="I45" s="7"/>
+      <c r="J45" s="140" t="s">
+        <v>677</v>
+      </c>
+      <c r="K45" s="60">
+        <v>23.854442608655745</v>
+      </c>
+      <c r="L45" s="7"/>
+      <c r="M45" s="140" t="s">
+        <v>738</v>
+      </c>
+      <c r="N45" s="148">
+        <v>27.27404194777181</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" ht="21">
+      <c r="A46" s="139" t="s">
+        <v>524</v>
+      </c>
+      <c r="B46" s="213">
+        <v>33.183279999999996</v>
+      </c>
+      <c r="C46" s="7"/>
+      <c r="D46" s="140" t="s">
+        <v>579</v>
+      </c>
+      <c r="E46" s="213">
+        <v>432.53503999999998</v>
+      </c>
+      <c r="F46" s="101"/>
+      <c r="G46" s="140" t="s">
+        <v>641</v>
+      </c>
+      <c r="H46" s="7">
+        <v>7780.5511199999983</v>
+      </c>
+      <c r="I46" s="7"/>
+      <c r="J46" s="140" t="s">
+        <v>94</v>
+      </c>
+      <c r="K46" s="60">
+        <v>24.575508283996509</v>
+      </c>
+      <c r="L46" s="7"/>
+      <c r="M46" s="140" t="s">
+        <v>739</v>
+      </c>
+      <c r="N46" s="148">
+        <v>28.158986185690029</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" ht="21">
+      <c r="A47" s="139" t="s">
+        <v>525</v>
+      </c>
+      <c r="B47" s="213">
+        <v>34.121679999999998</v>
+      </c>
+      <c r="C47" s="7"/>
+      <c r="D47" s="140" t="s">
+        <v>580</v>
+      </c>
+      <c r="E47" s="213">
+        <v>446.23567999999995</v>
+      </c>
+      <c r="F47" s="101"/>
+      <c r="G47" s="140" t="s">
+        <v>642</v>
+      </c>
+      <c r="H47" s="7">
+        <v>8237.9585600000009</v>
+      </c>
+      <c r="I47" s="7"/>
+      <c r="J47" s="140" t="s">
+        <v>678</v>
+      </c>
+      <c r="K47" s="60">
+        <v>25.420393317729125</v>
+      </c>
+      <c r="L47" s="7"/>
+      <c r="M47" s="140" t="s">
+        <v>740</v>
+      </c>
+      <c r="N47" s="148">
+        <v>38.45784340722382</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" ht="21">
+      <c r="A48" s="139" t="s">
+        <v>526</v>
+      </c>
+      <c r="B48" s="213">
+        <v>35.8108</v>
+      </c>
+      <c r="C48" s="7"/>
+      <c r="D48" s="140" t="s">
+        <v>581</v>
+      </c>
+      <c r="E48" s="213">
+        <v>504.3852</v>
+      </c>
+      <c r="F48" s="101"/>
+      <c r="G48" s="140" t="s">
+        <v>643</v>
+      </c>
+      <c r="H48" s="7">
+        <v>8695.366</v>
+      </c>
+      <c r="I48" s="7"/>
+      <c r="J48" s="140" t="s">
+        <v>679</v>
+      </c>
+      <c r="K48" s="60">
+        <v>25.857402817935654</v>
+      </c>
+      <c r="L48" s="7"/>
+      <c r="M48" s="140" t="s">
+        <v>741</v>
+      </c>
+      <c r="N48" s="148">
+        <v>39.921825232915687</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" ht="21">
+      <c r="A49" s="139" t="s">
+        <v>527</v>
+      </c>
+      <c r="B49" s="213">
+        <v>36.624079999999992</v>
+      </c>
+      <c r="C49" s="7"/>
+      <c r="D49" s="140" t="s">
+        <v>582</v>
+      </c>
+      <c r="E49" s="213">
+        <v>528.22055999999998</v>
+      </c>
+      <c r="F49" s="101"/>
+      <c r="G49" s="140" t="s">
+        <v>644</v>
+      </c>
+      <c r="H49" s="7">
+        <v>9152.7108800000005</v>
+      </c>
+      <c r="I49" s="7"/>
+      <c r="J49" s="140" t="s">
+        <v>680</v>
+      </c>
+      <c r="K49" s="60">
+        <v>26.268920097296789</v>
+      </c>
+      <c r="L49" s="7"/>
+      <c r="M49" s="140" t="s">
+        <v>742</v>
+      </c>
+      <c r="N49" s="148">
+        <v>44.561409426774979</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" ht="21">
+      <c r="A50" s="139" t="s">
+        <v>528</v>
+      </c>
+      <c r="B50" s="213">
+        <v>37.531199999999998</v>
+      </c>
+      <c r="C50" s="7"/>
+      <c r="D50" s="140" t="s">
+        <v>583</v>
+      </c>
+      <c r="E50" s="213">
+        <v>559.09391999999991</v>
+      </c>
+      <c r="F50" s="101"/>
+      <c r="G50" s="140" t="s">
+        <v>645</v>
+      </c>
+      <c r="H50" s="7">
+        <v>10067.525759999999</v>
+      </c>
+      <c r="I50" s="7"/>
+      <c r="J50" s="140" t="s">
+        <v>681</v>
+      </c>
+      <c r="K50" s="60">
+        <v>26.695004359998162</v>
+      </c>
+      <c r="L50" s="7"/>
+      <c r="M50" s="140" t="s">
+        <v>743</v>
+      </c>
+      <c r="N50" s="148">
+        <v>46.86299279452934</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" ht="21">
+      <c r="A51" s="139" t="s">
+        <v>529</v>
+      </c>
+      <c r="B51" s="213">
+        <v>39.314160000000001</v>
+      </c>
+      <c r="C51" s="7"/>
+      <c r="D51" s="140" t="s">
+        <v>584</v>
+      </c>
+      <c r="E51" s="213">
+        <v>579.61359999999991</v>
+      </c>
+      <c r="F51" s="101"/>
+      <c r="G51" s="7"/>
+      <c r="H51" s="7"/>
+      <c r="I51" s="7"/>
+      <c r="J51" s="140" t="s">
+        <v>682</v>
+      </c>
+      <c r="K51" s="60">
+        <v>26.902583872596264</v>
+      </c>
+      <c r="L51" s="7"/>
+      <c r="M51" s="140" t="s">
+        <v>744</v>
+      </c>
+      <c r="N51" s="148">
+        <v>52.325611547110917</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" ht="21">
+      <c r="A52" s="139" t="s">
+        <v>530</v>
+      </c>
+      <c r="B52" s="213">
+        <v>40.12744</v>
+      </c>
+      <c r="C52" s="7"/>
+      <c r="D52" s="140" t="s">
+        <v>585</v>
+      </c>
+      <c r="E52" s="213">
+        <v>606.85847999999999</v>
+      </c>
+      <c r="F52" s="101"/>
+      <c r="G52" s="7"/>
+      <c r="H52" s="7"/>
+      <c r="I52" s="7"/>
+      <c r="J52" s="140" t="s">
+        <v>95</v>
+      </c>
+      <c r="K52" s="60">
+        <v>27.110163385194365</v>
+      </c>
+      <c r="L52" s="7"/>
+      <c r="M52" s="140" t="s">
+        <v>745</v>
+      </c>
+      <c r="N52" s="148">
+        <v>76.284657395933706</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" ht="21">
+      <c r="A53" s="139" t="s">
+        <v>531</v>
+      </c>
+      <c r="B53" s="213">
+        <v>42.661119999999997</v>
+      </c>
+      <c r="C53" s="7"/>
+      <c r="D53" s="140" t="s">
+        <v>586</v>
+      </c>
+      <c r="E53" s="213">
+        <v>665.13311999999996</v>
+      </c>
+      <c r="F53" s="101"/>
+      <c r="G53" s="7"/>
+      <c r="H53" s="7"/>
+      <c r="I53" s="7"/>
+      <c r="J53" s="140" t="s">
+        <v>683</v>
+      </c>
+      <c r="K53" s="60">
+        <v>27.27404194777181</v>
+      </c>
+      <c r="L53" s="7"/>
+      <c r="M53" s="140" t="s">
+        <v>746</v>
+      </c>
+      <c r="N53" s="148">
+        <v>89.737266510624593</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" ht="21">
+      <c r="A54" s="139" t="s">
+        <v>532</v>
+      </c>
+      <c r="B54" s="213">
+        <v>46.039359999999995</v>
+      </c>
+      <c r="C54" s="7"/>
+      <c r="D54" s="140" t="s">
+        <v>587</v>
+      </c>
+      <c r="E54" s="213">
+        <v>13.977360000000001</v>
+      </c>
+      <c r="F54" s="101"/>
+      <c r="G54" s="7"/>
+      <c r="H54" s="7"/>
+      <c r="I54" s="7"/>
+      <c r="J54" s="140" t="s">
+        <v>684</v>
+      </c>
+      <c r="K54" s="60">
+        <v>27.73654366882371</v>
+      </c>
+      <c r="L54" s="7"/>
+      <c r="N54" s="148">
+        <v>1.4686309605764374</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" ht="21">
+      <c r="A55" s="139" t="s">
+        <v>533</v>
+      </c>
+      <c r="B55" s="213">
+        <v>49.605279999999986</v>
+      </c>
+      <c r="C55" s="7"/>
+      <c r="D55" s="140" t="s">
+        <v>588</v>
+      </c>
+      <c r="E55" s="213">
+        <v>14.602959999999999</v>
+      </c>
+      <c r="F55" s="101"/>
+      <c r="G55" s="7"/>
+      <c r="H55" s="7"/>
+      <c r="I55" s="7"/>
+      <c r="J55" s="140" t="s">
+        <v>685</v>
+      </c>
+      <c r="K55" s="60">
+        <v>27.94776492725687</v>
+      </c>
+      <c r="L55" s="7"/>
+      <c r="M55" s="140" t="s">
+        <v>747</v>
+      </c>
+      <c r="N55" s="148">
+        <v>95.196243517371116</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" ht="21">
+      <c r="A56" s="139" t="s">
+        <v>534</v>
+      </c>
+      <c r="B56" s="213">
+        <v>52.920959999999994</v>
+      </c>
+      <c r="C56" s="7"/>
+      <c r="D56" s="140" t="s">
+        <v>589</v>
+      </c>
+      <c r="E56" s="213">
+        <v>16.16696</v>
+      </c>
+      <c r="F56" s="101"/>
+      <c r="G56" s="7"/>
+      <c r="H56" s="7"/>
+      <c r="I56" s="7"/>
+      <c r="J56" s="140" t="s">
+        <v>686</v>
+      </c>
+      <c r="K56" s="60">
+        <v>28.158986185690029</v>
+      </c>
+      <c r="L56" s="7"/>
+      <c r="M56" s="140" t="s">
+        <v>748</v>
+      </c>
+      <c r="N56" s="148">
+        <v>98.146057643765189</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" ht="21">
+      <c r="A57" s="139" t="s">
+        <v>535</v>
+      </c>
+      <c r="B57" s="213">
+        <v>55.548480000000005</v>
+      </c>
+      <c r="C57" s="7"/>
+      <c r="D57" s="140" t="s">
+        <v>590</v>
+      </c>
+      <c r="E57" s="213">
+        <v>16.354639999999996</v>
+      </c>
+      <c r="F57" s="101"/>
+      <c r="G57" s="7"/>
+      <c r="H57" s="7"/>
+      <c r="I57" s="7"/>
+      <c r="J57" s="140" t="s">
+        <v>687</v>
+      </c>
+      <c r="K57" s="60">
+        <v>28.789008215154428</v>
+      </c>
+      <c r="L57" s="7"/>
+      <c r="M57" s="140" t="s">
+        <v>749</v>
+      </c>
+      <c r="N57" s="148">
+        <v>110.33133920785717</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" ht="21">
+      <c r="A58" s="139" t="s">
+        <v>536</v>
+      </c>
+      <c r="B58" s="213">
+        <v>56.267919999999997</v>
+      </c>
+      <c r="C58" s="7"/>
+      <c r="D58" s="140" t="s">
+        <v>591</v>
+      </c>
+      <c r="E58" s="213">
+        <v>17.41816</v>
+      </c>
+      <c r="F58" s="101"/>
+      <c r="G58" s="7"/>
+      <c r="H58" s="7"/>
+      <c r="I58" s="7"/>
+      <c r="J58" s="140" t="s">
+        <v>688</v>
+      </c>
+      <c r="K58" s="60">
+        <v>29.215092477855794</v>
+      </c>
+      <c r="L58" s="7"/>
+      <c r="M58" s="141"/>
+      <c r="N58" s="148">
+        <v>1.4686309605764374</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" ht="21">
+      <c r="A59" s="139" t="s">
+        <v>537</v>
+      </c>
+      <c r="B59" s="213">
+        <v>59.677440000000004</v>
+      </c>
+      <c r="C59" s="7"/>
+      <c r="D59" s="140" t="s">
+        <v>592</v>
+      </c>
+      <c r="E59" s="213">
+        <v>18.356559999999995</v>
+      </c>
+      <c r="F59" s="101"/>
+      <c r="G59" s="7"/>
+      <c r="H59" s="7"/>
+      <c r="I59" s="7"/>
+      <c r="J59" s="140" t="s">
+        <v>689</v>
+      </c>
+      <c r="K59" s="60">
+        <v>29.375329294598188</v>
+      </c>
+      <c r="L59" s="7"/>
+      <c r="M59" s="140" t="s">
+        <v>750</v>
+      </c>
+      <c r="N59" s="148">
+        <v>15.944570654917618</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" ht="21">
+      <c r="A60" s="139" t="s">
+        <v>538</v>
+      </c>
+      <c r="B60" s="213">
+        <v>63.180799999999998</v>
+      </c>
+      <c r="C60" s="7"/>
+      <c r="D60" s="140" t="s">
+        <v>593</v>
+      </c>
+      <c r="E60" s="213">
+        <v>23.830559999999998</v>
+      </c>
+      <c r="F60" s="101"/>
+      <c r="G60" s="7"/>
+      <c r="H60" s="7"/>
+      <c r="I60" s="7"/>
+      <c r="J60" s="140" t="s">
+        <v>690</v>
+      </c>
+      <c r="K60" s="60">
+        <v>30.471494790949553</v>
+      </c>
+      <c r="L60" s="7"/>
+      <c r="M60" s="141"/>
+      <c r="N60" s="148">
+        <v>1.4686309605764374</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" ht="21">
+      <c r="A61" s="139" t="s">
+        <v>539</v>
+      </c>
+      <c r="B61" s="213">
+        <v>66.527760000000001</v>
+      </c>
+      <c r="C61" s="7"/>
+      <c r="D61" s="140" t="s">
+        <v>594</v>
+      </c>
+      <c r="E61" s="213">
+        <v>24.737679999999997</v>
+      </c>
+      <c r="F61" s="101"/>
+      <c r="G61" s="7"/>
+      <c r="H61" s="7"/>
+      <c r="I61" s="7"/>
+      <c r="J61" s="140" t="s">
+        <v>691</v>
+      </c>
+      <c r="K61" s="60">
+        <v>31.465691403919408</v>
+      </c>
+      <c r="L61" s="7"/>
+      <c r="M61" s="140" t="s">
+        <v>751</v>
+      </c>
+      <c r="N61" s="148">
+        <v>21.436323374179622</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" ht="21">
+      <c r="A62" s="139" t="s">
+        <v>540</v>
+      </c>
+      <c r="B62" s="213">
+        <v>69.968559999999982</v>
+      </c>
+      <c r="C62" s="7"/>
+      <c r="D62" s="140" t="s">
+        <v>595</v>
+      </c>
+      <c r="E62" s="213">
+        <v>34.121679999999998</v>
+      </c>
+      <c r="F62" s="101"/>
+      <c r="G62" s="7"/>
+      <c r="H62" s="7"/>
+      <c r="I62" s="7"/>
+      <c r="J62" s="140" t="s">
+        <v>692</v>
+      </c>
+      <c r="K62" s="60">
+        <v>31.942760108311528</v>
+      </c>
+      <c r="L62" s="7"/>
+      <c r="M62" s="140" t="s">
+        <v>752</v>
+      </c>
+      <c r="N62" s="148">
+        <v>21.702170820138601</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" ht="21">
+      <c r="A63" s="140" t="s">
+        <v>541</v>
+      </c>
+      <c r="B63" s="213">
+        <v>76.881439999999998</v>
+      </c>
+      <c r="C63" s="7"/>
+      <c r="D63" s="140" t="s">
+        <v>596</v>
+      </c>
+      <c r="E63" s="213">
+        <v>35.8108</v>
+      </c>
+      <c r="F63" s="101"/>
+      <c r="G63" s="7"/>
+      <c r="H63" s="7"/>
+      <c r="I63" s="7"/>
+      <c r="J63" s="140" t="s">
+        <v>693</v>
+      </c>
+      <c r="K63" s="60">
+        <v>32.995224654642243</v>
+      </c>
+      <c r="L63" s="7"/>
+      <c r="M63" s="140" t="s">
+        <v>753</v>
+      </c>
+      <c r="N63" s="148">
+        <v>22.237507457891596</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" ht="21">
+      <c r="A64" s="140" t="s">
+        <v>542</v>
+      </c>
+      <c r="B64" s="213">
+        <v>83.669200000000004</v>
+      </c>
+      <c r="C64" s="7"/>
+      <c r="D64" s="140" t="s">
+        <v>597</v>
+      </c>
+      <c r="E64" s="213">
+        <v>36.624079999999992</v>
+      </c>
+      <c r="F64" s="101"/>
+      <c r="G64" s="7"/>
+      <c r="H64" s="7"/>
+      <c r="I64" s="7"/>
+      <c r="J64" s="140" t="s">
+        <v>694</v>
+      </c>
+      <c r="K64" s="60">
+        <v>34.040405709302853</v>
+      </c>
+      <c r="L64" s="7"/>
+      <c r="M64" s="140" t="s">
+        <v>754</v>
+      </c>
+      <c r="N64" s="148">
+        <v>22.772844095644587</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" ht="21">
+      <c r="A65" s="140" t="s">
+        <v>543</v>
+      </c>
+      <c r="B65" s="213">
+        <v>87.11</v>
+      </c>
+      <c r="C65" s="7"/>
+      <c r="D65" s="140" t="s">
+        <v>598</v>
+      </c>
+      <c r="E65" s="213">
+        <v>37.531199999999998</v>
+      </c>
+      <c r="F65" s="101"/>
+      <c r="G65" s="7"/>
+      <c r="H65" s="7"/>
+      <c r="I65" s="7"/>
+      <c r="J65" s="140" t="s">
+        <v>695</v>
+      </c>
+      <c r="K65" s="60">
+        <v>35.744742760108302</v>
+      </c>
+      <c r="L65" s="7"/>
+      <c r="M65" s="140" t="s">
+        <v>755</v>
+      </c>
+      <c r="N65" s="148">
+        <v>23.038691541603558</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" ht="21">
+      <c r="A66" s="140" t="s">
+        <v>544</v>
+      </c>
+      <c r="B66" s="213">
+        <v>90.550799999999995</v>
+      </c>
+      <c r="C66" s="7"/>
+      <c r="D66" s="140" t="s">
+        <v>599</v>
+      </c>
+      <c r="E66" s="213">
+        <v>39.314160000000001</v>
+      </c>
+      <c r="F66" s="101"/>
+      <c r="G66" s="7"/>
+      <c r="H66" s="7"/>
+      <c r="I66" s="7"/>
+      <c r="J66" s="140" t="s">
+        <v>696</v>
+      </c>
+      <c r="K66" s="60">
+        <v>35.934113543531133</v>
+      </c>
+      <c r="L66" s="7"/>
+      <c r="M66" s="140" t="s">
+        <v>756</v>
+      </c>
+      <c r="N66" s="148">
+        <v>23.832592133645409</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" ht="21">
+      <c r="A67" s="140" t="s">
+        <v>244</v>
+      </c>
+      <c r="B67" s="213">
+        <v>93.897760000000005</v>
+      </c>
+      <c r="C67" s="7"/>
+      <c r="D67" s="140" t="s">
+        <v>600</v>
+      </c>
+      <c r="E67" s="213">
+        <v>42.661119999999997</v>
+      </c>
+      <c r="F67" s="101"/>
+      <c r="G67" s="7"/>
+      <c r="H67" s="7"/>
+      <c r="I67" s="7"/>
+      <c r="J67" s="140" t="s">
+        <v>697</v>
+      </c>
+      <c r="K67" s="60">
+        <v>36.145334801964282</v>
+      </c>
+      <c r="L67" s="7"/>
+      <c r="M67" s="140" t="s">
+        <v>757</v>
+      </c>
+      <c r="N67" s="148">
+        <v>27.030044976823163</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" ht="21">
+      <c r="A68" s="140" t="s">
+        <v>545</v>
+      </c>
+      <c r="B68" s="213">
+        <v>95.586879999999994</v>
+      </c>
+      <c r="C68" s="7"/>
+      <c r="D68" s="140" t="s">
+        <v>601</v>
+      </c>
+      <c r="E68" s="213">
+        <v>66.527760000000001</v>
+      </c>
+      <c r="F68" s="101"/>
+      <c r="G68" s="7"/>
+      <c r="H68" s="7"/>
+      <c r="I68" s="7"/>
+      <c r="J68" s="140" t="s">
+        <v>698</v>
+      </c>
+      <c r="K68" s="60">
+        <v>36.990219835696912</v>
+      </c>
+      <c r="L68" s="7"/>
+      <c r="M68" s="140" t="s">
+        <v>758</v>
+      </c>
+      <c r="N68" s="148">
+        <v>27.827587314700072</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" ht="21">
+      <c r="A69" s="140" t="s">
+        <v>546</v>
+      </c>
+      <c r="B69" s="213">
+        <v>99.99736</v>
+      </c>
+      <c r="C69" s="7"/>
+      <c r="D69" s="140" t="s">
+        <v>602</v>
+      </c>
+      <c r="E69" s="213">
+        <v>70.875680000000003</v>
+      </c>
+      <c r="F69" s="101"/>
+      <c r="G69" s="7"/>
+      <c r="H69" s="7"/>
+      <c r="I69" s="7"/>
+      <c r="J69" s="140" t="s">
+        <v>699</v>
+      </c>
+      <c r="K69" s="60">
+        <v>40.3515512414521</v>
+      </c>
+      <c r="L69" s="7"/>
+      <c r="M69" s="140" t="s">
+        <v>759</v>
+      </c>
+      <c r="N69" s="148">
+        <v>30.755550966083799</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" ht="21">
+      <c r="A70" s="140" t="s">
+        <v>547</v>
+      </c>
+      <c r="B70" s="213">
+        <v>106.81639999999997</v>
+      </c>
+      <c r="C70" s="7"/>
+      <c r="D70" s="140" t="s">
+        <v>603</v>
+      </c>
+      <c r="E70" s="213">
+        <v>73.471919999999997</v>
+      </c>
+      <c r="F70" s="101"/>
+      <c r="G70" s="7"/>
+      <c r="H70" s="7"/>
+      <c r="I70" s="7"/>
+      <c r="J70" s="140" t="s">
+        <v>700</v>
+      </c>
+      <c r="K70" s="60">
+        <v>41.185511037679561</v>
+      </c>
+      <c r="L70" s="7"/>
+      <c r="M70" s="140" t="s">
+        <v>760</v>
+      </c>
+      <c r="N70" s="148">
+        <v>33.21008765891046</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" ht="21.6" thickBot="1">
+      <c r="A71" s="7"/>
+      <c r="B71" s="7"/>
+      <c r="C71" s="7"/>
+      <c r="D71" s="140"/>
+      <c r="E71" s="213"/>
+      <c r="F71" s="101"/>
+      <c r="G71" s="7"/>
+      <c r="H71" s="7"/>
+      <c r="I71" s="7"/>
+      <c r="J71" s="140" t="s">
+        <v>701</v>
+      </c>
+      <c r="K71" s="61">
+        <v>42.667701592546678</v>
+      </c>
+      <c r="L71" s="7"/>
+      <c r="M71" s="140" t="s">
+        <v>761</v>
+      </c>
+      <c r="N71" s="148">
+        <v>38.676348157327084</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14" ht="21">
+      <c r="D72" s="140"/>
+      <c r="E72" s="213"/>
+      <c r="M72" s="140" t="s">
+        <v>762</v>
+      </c>
+      <c r="N72" s="149">
+        <v>40.293283308091233</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" ht="21">
+      <c r="D73" s="140"/>
+      <c r="E73" s="213"/>
+      <c r="M73" s="140" t="s">
+        <v>763</v>
+      </c>
+      <c r="N73" s="149">
+        <v>42.933549038505674</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" ht="21">
+      <c r="D74" s="140"/>
+      <c r="E74" s="213"/>
+      <c r="M74" s="140" t="s">
+        <v>764</v>
+      </c>
+      <c r="N74" s="149">
+        <v>43.326857588691531</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" ht="21">
+      <c r="D75" s="140"/>
+      <c r="E75" s="213"/>
+      <c r="M75" s="140" t="s">
+        <v>765</v>
+      </c>
+      <c r="N75" s="149">
+        <v>47.977367020055986</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14" ht="21">
+      <c r="D76" s="140"/>
+      <c r="E76" s="213"/>
+      <c r="M76" s="140" t="s">
+        <v>391</v>
+      </c>
+      <c r="N76" s="149">
+        <v>50.402769746202203</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" ht="21">
+      <c r="D77" s="140"/>
+      <c r="E77" s="213"/>
+      <c r="M77" s="140" t="s">
+        <v>766</v>
+      </c>
+      <c r="N77" s="149">
+        <v>55.257216944329684</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" ht="21">
+      <c r="D78" s="140"/>
+      <c r="E78" s="213"/>
+      <c r="J78" s="394" t="s">
+        <v>771</v>
+      </c>
+      <c r="K78" s="394"/>
+      <c r="L78" s="394"/>
+      <c r="M78" s="394"/>
+      <c r="N78" s="394"/>
+    </row>
+    <row r="79" spans="1:14">
+      <c r="D79" s="140"/>
+      <c r="E79" s="213"/>
+    </row>
+    <row r="80" spans="1:14" ht="41.4">
+      <c r="D80" s="140"/>
+      <c r="E80" s="213"/>
+      <c r="J80" s="142" t="s">
+        <v>767</v>
+      </c>
+      <c r="N80" s="117">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="81" spans="4:14" ht="27.6">
+      <c r="D81" s="140"/>
+      <c r="E81" s="213"/>
+      <c r="J81" s="142" t="s">
+        <v>768</v>
+      </c>
+      <c r="N81" s="117">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="82" spans="4:14" ht="27.6">
+      <c r="D82" s="140"/>
+      <c r="E82" s="213"/>
+      <c r="J82" s="142" t="s">
+        <v>769</v>
+      </c>
+      <c r="N82" s="117">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="83" spans="4:14" ht="27.6">
+      <c r="D83" s="140"/>
+      <c r="E83" s="213"/>
+      <c r="J83" s="142" t="s">
+        <v>770</v>
+      </c>
+      <c r="N83" s="117">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="84" spans="4:14">
+      <c r="D84" s="140"/>
+      <c r="E84" s="213"/>
+    </row>
+    <row r="85" spans="4:14">
+      <c r="D85" s="140"/>
+      <c r="E85" s="213"/>
+    </row>
+    <row r="86" spans="4:14">
+      <c r="D86" s="140"/>
+      <c r="E86" s="213"/>
+    </row>
+    <row r="87" spans="4:14">
+      <c r="D87" s="140"/>
+      <c r="E87" s="213"/>
+    </row>
+    <row r="88" spans="4:14">
+      <c r="D88" s="140"/>
+      <c r="E88" s="213"/>
+    </row>
+    <row r="89" spans="4:14">
+      <c r="D89" s="140"/>
+      <c r="E89" s="213"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="J78:N78"/>
+    <mergeCell ref="A2:N3"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="M6:M7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2700-000000000000}">
   <dimension ref="B1:L70"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.6"/>
@@ -31732,2472 +34526,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EED1ABC8-4161-BE4E-B620-33582EF339FF}">
-  <dimension ref="A2:N89"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.6"/>
-  <cols>
-    <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="10" max="10" width="9.796875" customWidth="1"/>
-    <col min="14" max="14" width="10.796875" style="143"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:14">
-      <c r="A2" s="387" t="s">
-        <v>1590</v>
-      </c>
-      <c r="B2" s="387"/>
-      <c r="C2" s="387"/>
-      <c r="D2" s="387"/>
-      <c r="E2" s="387"/>
-      <c r="F2" s="387"/>
-      <c r="G2" s="387"/>
-      <c r="H2" s="387"/>
-      <c r="I2" s="387"/>
-      <c r="J2" s="387"/>
-      <c r="K2" s="387"/>
-      <c r="L2" s="387"/>
-      <c r="M2" s="387"/>
-      <c r="N2" s="387"/>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="387"/>
-      <c r="B3" s="387"/>
-      <c r="C3" s="387"/>
-      <c r="D3" s="387"/>
-      <c r="E3" s="387"/>
-      <c r="F3" s="387"/>
-      <c r="G3" s="387"/>
-      <c r="H3" s="387"/>
-      <c r="I3" s="387"/>
-      <c r="J3" s="387"/>
-      <c r="K3" s="387"/>
-      <c r="L3" s="387"/>
-      <c r="M3" s="387"/>
-      <c r="N3" s="387"/>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" t="s">
-        <v>1586</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="16.2" thickBot="1"/>
-    <row r="6" spans="1:14" ht="21">
-      <c r="A6" s="391" t="s">
-        <v>99</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="C6" s="9"/>
-      <c r="D6" s="391" t="s">
-        <v>99</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="F6" s="100"/>
-      <c r="G6" s="391" t="s">
-        <v>99</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="I6" s="9"/>
-      <c r="J6" s="391" t="s">
-        <v>99</v>
-      </c>
-      <c r="K6" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="L6" s="9"/>
-      <c r="M6" s="391" t="s">
-        <v>99</v>
-      </c>
-      <c r="N6" s="43" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="21.6" thickBot="1">
-      <c r="A7" s="393"/>
-      <c r="B7" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="393"/>
-      <c r="E7" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="F7" s="100"/>
-      <c r="G7" s="393"/>
-      <c r="H7" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="I7" s="9"/>
-      <c r="J7" s="393"/>
-      <c r="K7" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="L7" s="9"/>
-      <c r="M7" s="393"/>
-      <c r="N7" s="44" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="21">
-      <c r="A8" s="117" t="s">
-        <v>1215</v>
-      </c>
-      <c r="B8" s="212">
-        <v>6.7203999999999997</v>
-      </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="140" t="s">
-        <v>246</v>
-      </c>
-      <c r="E8" s="213">
-        <v>111.07047999999999</v>
-      </c>
-      <c r="F8" s="101"/>
-      <c r="G8" s="140" t="s">
-        <v>604</v>
-      </c>
-      <c r="H8" s="213">
-        <v>76.068159999999992</v>
-      </c>
-      <c r="I8" s="7"/>
-      <c r="J8" t="s">
-        <v>1216</v>
-      </c>
-      <c r="K8" s="59">
-        <v>9.4476960851805938</v>
-      </c>
-      <c r="L8" s="7"/>
-      <c r="M8" s="140" t="s">
-        <v>702</v>
-      </c>
-      <c r="N8" s="144">
-        <v>44.561409426774979</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="21">
-      <c r="A9" s="139" t="s">
-        <v>487</v>
-      </c>
-      <c r="B9" s="213">
-        <v>7.0644799999999996</v>
-      </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="140" t="s">
-        <v>548</v>
-      </c>
-      <c r="E9" s="213">
-        <v>114.57384</v>
-      </c>
-      <c r="F9" s="101"/>
-      <c r="G9" s="140" t="s">
-        <v>605</v>
-      </c>
-      <c r="H9" s="213">
-        <v>76.881439999999998</v>
-      </c>
-      <c r="I9" s="7"/>
-      <c r="J9" s="140" t="s">
-        <v>646</v>
-      </c>
-      <c r="K9" s="60">
-        <v>11.570833907017301</v>
-      </c>
-      <c r="L9" s="7"/>
-      <c r="M9" s="140" t="s">
-        <v>703</v>
-      </c>
-      <c r="N9" s="145">
-        <v>46.86299279452934</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="21">
-      <c r="A10" s="139" t="s">
-        <v>488</v>
-      </c>
-      <c r="B10" s="213">
-        <v>8.1279999999999983</v>
-      </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="140" t="s">
-        <v>549</v>
-      </c>
-      <c r="E10" s="213">
-        <v>116.16911999999999</v>
-      </c>
-      <c r="F10" s="101"/>
-      <c r="G10" s="140" t="s">
-        <v>606</v>
-      </c>
-      <c r="H10" s="213">
-        <v>78.633119999999991</v>
-      </c>
-      <c r="I10" s="7"/>
-      <c r="J10" s="140" t="s">
-        <v>89</v>
-      </c>
-      <c r="K10" s="60">
-        <v>12.506762586626278</v>
-      </c>
-      <c r="L10" s="7"/>
-      <c r="M10" s="140" t="s">
-        <v>704</v>
-      </c>
-      <c r="N10" s="145">
-        <v>49.80188168341823</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="21">
-      <c r="A11" s="139" t="s">
-        <v>489</v>
-      </c>
-      <c r="B11" s="213">
-        <v>8.4407999999999994</v>
-      </c>
-      <c r="C11" s="7"/>
-      <c r="D11" s="140" t="s">
-        <v>550</v>
-      </c>
-      <c r="E11" s="213">
-        <v>121.29903999999999</v>
-      </c>
-      <c r="F11" s="101"/>
-      <c r="G11" s="140" t="s">
-        <v>607</v>
-      </c>
-      <c r="H11" s="213">
-        <v>83.669200000000004</v>
-      </c>
-      <c r="I11" s="7"/>
-      <c r="J11" s="140" t="s">
-        <v>647</v>
-      </c>
-      <c r="K11" s="60">
-        <v>12.819952728440954</v>
-      </c>
-      <c r="L11" s="7"/>
-      <c r="M11" s="140" t="s">
-        <v>705</v>
-      </c>
-      <c r="N11" s="145">
-        <v>56.946987011794931</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="21">
-      <c r="A12" s="139" t="s">
-        <v>490</v>
-      </c>
-      <c r="B12" s="213">
-        <v>8.8161599999999982</v>
-      </c>
-      <c r="C12" s="7"/>
-      <c r="D12" s="140" t="s">
-        <v>551</v>
-      </c>
-      <c r="E12" s="213">
-        <v>123.05071999999998</v>
-      </c>
-      <c r="F12" s="101"/>
-      <c r="G12" s="140" t="s">
-        <v>608</v>
-      </c>
-      <c r="H12" s="213">
-        <v>90.550799999999995</v>
-      </c>
-      <c r="I12" s="7"/>
-      <c r="J12" s="140" t="s">
-        <v>648</v>
-      </c>
-      <c r="K12" s="60">
-        <v>13.224186516131992</v>
-      </c>
-      <c r="L12" s="7"/>
-      <c r="M12" s="140" t="s">
-        <v>706</v>
-      </c>
-      <c r="N12" s="145">
-        <v>61.153203451282735</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="21">
-      <c r="A13" s="139" t="s">
-        <v>491</v>
-      </c>
-      <c r="B13" s="213">
-        <v>8.9725599999999996</v>
-      </c>
-      <c r="C13" s="7"/>
-      <c r="D13" s="140" t="s">
-        <v>552</v>
-      </c>
-      <c r="E13" s="213">
-        <v>124.70856000000001</v>
-      </c>
-      <c r="F13" s="101"/>
-      <c r="G13" s="140" t="s">
-        <v>609</v>
-      </c>
-      <c r="H13" s="213">
-        <v>105.15856000000001</v>
-      </c>
-      <c r="I13" s="7"/>
-      <c r="J13" s="140" t="s">
-        <v>649</v>
-      </c>
-      <c r="K13" s="60">
-        <v>13.66119601633852</v>
-      </c>
-      <c r="L13" s="7"/>
-      <c r="M13" s="140" t="s">
-        <v>707</v>
-      </c>
-      <c r="N13" s="145">
-        <v>66.18973794116296</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" ht="21">
-      <c r="A14" s="139" t="s">
-        <v>492</v>
-      </c>
-      <c r="B14" s="213">
-        <v>9.1915199999999988</v>
-      </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="140" t="s">
-        <v>553</v>
-      </c>
-      <c r="E14" s="213">
-        <v>128.99392</v>
-      </c>
-      <c r="F14" s="101"/>
-      <c r="G14" s="140" t="s">
-        <v>610</v>
-      </c>
-      <c r="H14" s="213">
-        <v>130.68303999999998</v>
-      </c>
-      <c r="I14" s="7"/>
-      <c r="J14" s="140" t="s">
-        <v>650</v>
-      </c>
-      <c r="K14" s="60">
-        <v>14.039937583184171</v>
-      </c>
-      <c r="L14" s="7"/>
-      <c r="M14" s="140" t="s">
-        <v>708</v>
-      </c>
-      <c r="N14" s="145">
-        <v>71.240839414383387</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="21">
-      <c r="A15" s="139" t="s">
-        <v>493</v>
-      </c>
-      <c r="B15" s="213">
-        <v>9.3166399999999996</v>
-      </c>
-      <c r="C15" s="7"/>
-      <c r="D15" s="140" t="s">
-        <v>554</v>
-      </c>
-      <c r="E15" s="213">
-        <v>130.68303999999998</v>
-      </c>
-      <c r="F15" s="101"/>
-      <c r="G15" s="140" t="s">
-        <v>611</v>
-      </c>
-      <c r="H15" s="213">
-        <v>134.93711999999996</v>
-      </c>
-      <c r="I15" s="7"/>
-      <c r="J15" s="140" t="s">
-        <v>651</v>
-      </c>
-      <c r="K15" s="60">
-        <v>14.506081050071133</v>
-      </c>
-      <c r="L15" s="7"/>
-      <c r="M15" s="140" t="s">
-        <v>709</v>
-      </c>
-      <c r="N15" s="145">
-        <v>76.284657395933706</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="21">
-      <c r="A16" s="139" t="s">
-        <v>494</v>
-      </c>
-      <c r="B16" s="213">
-        <v>9.4730399999999992</v>
-      </c>
-      <c r="C16" s="7"/>
-      <c r="D16" s="140" t="s">
-        <v>252</v>
-      </c>
-      <c r="E16" s="213">
-        <v>134.09255999999999</v>
-      </c>
-      <c r="F16" s="101"/>
-      <c r="G16" s="140" t="s">
-        <v>612</v>
-      </c>
-      <c r="H16" s="213">
-        <v>199.96823999999998</v>
-      </c>
-      <c r="I16" s="7"/>
-      <c r="J16" s="140" t="s">
-        <v>90</v>
-      </c>
-      <c r="K16" s="60">
-        <v>14.611691679287711</v>
-      </c>
-      <c r="L16" s="7"/>
-      <c r="M16" s="140" t="s">
-        <v>710</v>
-      </c>
-      <c r="N16" s="145">
-        <v>85.112249300105546</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" ht="21">
-      <c r="A17" s="139" t="s">
-        <v>495</v>
-      </c>
-      <c r="B17" s="213">
-        <v>9.8796799999999987</v>
-      </c>
-      <c r="C17" s="7"/>
-      <c r="D17" s="140" t="s">
-        <v>256</v>
-      </c>
-      <c r="E17" s="213">
-        <v>138.37791999999999</v>
-      </c>
-      <c r="F17" s="101"/>
-      <c r="G17" s="140" t="s">
-        <v>613</v>
-      </c>
-      <c r="H17" s="213">
-        <v>259.80687999999998</v>
-      </c>
-      <c r="I17" s="7"/>
-      <c r="J17" s="140" t="s">
-        <v>652</v>
-      </c>
-      <c r="K17" s="60">
-        <v>14.811987700215703</v>
-      </c>
-      <c r="L17" s="7"/>
-      <c r="M17" s="140" t="s">
-        <v>711</v>
-      </c>
-      <c r="N17" s="145">
-        <v>89.737266510624593</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" ht="21">
-      <c r="A18" s="139" t="s">
-        <v>496</v>
-      </c>
-      <c r="B18" s="213">
-        <v>10.12992</v>
-      </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="140" t="s">
-        <v>555</v>
-      </c>
-      <c r="E18" s="213">
-        <v>143.57039999999998</v>
-      </c>
-      <c r="F18" s="101"/>
-      <c r="G18" s="140" t="s">
-        <v>614</v>
-      </c>
-      <c r="H18" s="213">
-        <v>275.25920000000002</v>
-      </c>
-      <c r="I18" s="7"/>
-      <c r="J18" s="140" t="s">
-        <v>653</v>
-      </c>
-      <c r="K18" s="60">
-        <v>15.299981642112991</v>
-      </c>
-      <c r="L18" s="7"/>
-      <c r="M18" s="140" t="s">
-        <v>712</v>
-      </c>
-      <c r="N18" s="145">
-        <v>90.990027077883312</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" ht="21">
-      <c r="A19" s="139" t="s">
-        <v>497</v>
-      </c>
-      <c r="B19" s="213">
-        <v>10.474</v>
-      </c>
-      <c r="C19" s="7"/>
-      <c r="D19" s="140" t="s">
-        <v>556</v>
-      </c>
-      <c r="E19" s="213">
-        <v>147.01119999999997</v>
-      </c>
-      <c r="F19" s="101"/>
-      <c r="G19" s="140" t="s">
-        <v>615</v>
-      </c>
-      <c r="H19" s="213">
-        <v>286.73895999999996</v>
-      </c>
-      <c r="I19" s="7"/>
-      <c r="J19" s="140" t="s">
-        <v>654</v>
-      </c>
-      <c r="K19" s="60">
-        <v>15.343682592133645</v>
-      </c>
-      <c r="L19" s="7"/>
-      <c r="M19" s="140" t="s">
-        <v>713</v>
-      </c>
-      <c r="N19" s="145">
-        <v>93.094956170544762</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" ht="21">
-      <c r="A20" s="139" t="s">
-        <v>498</v>
-      </c>
-      <c r="B20" s="213">
-        <v>10.911919999999999</v>
-      </c>
-      <c r="C20" s="7"/>
-      <c r="D20" s="140" t="s">
-        <v>557</v>
-      </c>
-      <c r="E20" s="213">
-        <v>150.38943999999998</v>
-      </c>
-      <c r="F20" s="101"/>
-      <c r="G20" s="140" t="s">
-        <v>616</v>
-      </c>
-      <c r="H20" s="213">
-        <v>297.46799999999996</v>
-      </c>
-      <c r="I20" s="7"/>
-      <c r="J20" s="140" t="s">
-        <v>91</v>
-      </c>
-      <c r="K20" s="60">
-        <v>15.726065904814353</v>
-      </c>
-      <c r="L20" s="7"/>
-      <c r="M20" s="140" t="s">
-        <v>714</v>
-      </c>
-      <c r="N20" s="145">
-        <v>95.196243517371116</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" ht="21">
-      <c r="A21" s="139" t="s">
-        <v>499</v>
-      </c>
-      <c r="B21" s="213">
-        <v>11.50624</v>
-      </c>
-      <c r="C21" s="7"/>
-      <c r="D21" s="140" t="s">
-        <v>558</v>
-      </c>
-      <c r="E21" s="213">
-        <v>158.96015999999997</v>
-      </c>
-      <c r="F21" s="101"/>
-      <c r="G21" s="140" t="s">
-        <v>617</v>
-      </c>
-      <c r="H21" s="213">
-        <v>329.96791999999999</v>
-      </c>
-      <c r="I21" s="7"/>
-      <c r="J21" s="140" t="s">
-        <v>655</v>
-      </c>
-      <c r="K21" s="60">
-        <v>15.758841617329844</v>
-      </c>
-      <c r="L21" s="7"/>
-      <c r="M21" s="140" t="s">
-        <v>715</v>
-      </c>
-      <c r="N21" s="145">
-        <v>98.146057643765189</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" ht="21">
-      <c r="A22" s="139" t="s">
-        <v>500</v>
-      </c>
-      <c r="B22" s="213">
-        <v>11.881599999999999</v>
-      </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="140" t="s">
-        <v>559</v>
-      </c>
-      <c r="E22" s="213">
-        <v>172.62952000000001</v>
-      </c>
-      <c r="F22" s="101"/>
-      <c r="G22" s="140" t="s">
-        <v>618</v>
-      </c>
-      <c r="H22" s="213">
-        <v>367.4726399999999</v>
-      </c>
-      <c r="I22" s="7"/>
-      <c r="J22" s="140" t="s">
-        <v>656</v>
-      </c>
-      <c r="K22" s="60">
-        <v>15.980988113268161</v>
-      </c>
-      <c r="L22" s="7"/>
-      <c r="M22" s="140" t="s">
-        <v>716</v>
-      </c>
-      <c r="N22" s="145">
-        <v>110.33133920785717</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" ht="21">
-      <c r="A23" s="139" t="s">
-        <v>501</v>
-      </c>
-      <c r="B23" s="213">
-        <v>12.726160000000002</v>
-      </c>
-      <c r="C23" s="7"/>
-      <c r="D23" s="140" t="s">
-        <v>560</v>
-      </c>
-      <c r="E23" s="213">
-        <v>193.08664000000002</v>
-      </c>
-      <c r="F23" s="101"/>
-      <c r="G23" s="140" t="s">
-        <v>619</v>
-      </c>
-      <c r="H23" s="213">
-        <v>388.05487999999997</v>
-      </c>
-      <c r="I23" s="7"/>
-      <c r="J23" s="140" t="s">
-        <v>657</v>
-      </c>
-      <c r="K23" s="60">
-        <v>16.137583184175501</v>
-      </c>
-      <c r="L23" s="7"/>
-      <c r="M23" s="114"/>
-      <c r="N23" s="145">
-        <v>1.4686309605764374</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" ht="21">
-      <c r="A24" s="139" t="s">
-        <v>502</v>
-      </c>
-      <c r="B24" s="213">
-        <v>12.88256</v>
-      </c>
-      <c r="C24" s="7"/>
-      <c r="D24" s="140" t="s">
-        <v>561</v>
-      </c>
-      <c r="E24" s="213">
-        <v>196.80895999999998</v>
-      </c>
-      <c r="F24" s="101"/>
-      <c r="G24" s="140" t="s">
-        <v>620</v>
-      </c>
-      <c r="H24" s="213">
-        <v>405.19632000000001</v>
-      </c>
-      <c r="I24" s="7"/>
-      <c r="J24" s="140" t="s">
-        <v>92</v>
-      </c>
-      <c r="K24" s="60">
-        <v>16.184925880031205</v>
-      </c>
-      <c r="L24" s="7"/>
-      <c r="M24" s="140" t="s">
-        <v>717</v>
-      </c>
-      <c r="N24" s="145">
-        <v>8.9305681766028702</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" ht="21">
-      <c r="A25" s="139" t="s">
-        <v>503</v>
-      </c>
-      <c r="B25" s="213">
-        <v>13.977360000000001</v>
-      </c>
-      <c r="C25" s="7"/>
-      <c r="D25" s="140" t="s">
-        <v>562</v>
-      </c>
-      <c r="E25" s="213">
-        <v>199.96823999999998</v>
-      </c>
-      <c r="F25" s="101"/>
-      <c r="G25" s="140" t="s">
-        <v>621</v>
-      </c>
-      <c r="H25" s="213">
-        <v>483.83424000000002</v>
-      </c>
-      <c r="I25" s="7"/>
-      <c r="J25" s="140" t="s">
-        <v>658</v>
-      </c>
-      <c r="K25" s="60">
-        <v>16.603726651062459</v>
-      </c>
-      <c r="L25" s="7"/>
-      <c r="M25" s="140" t="s">
-        <v>718</v>
-      </c>
-      <c r="N25" s="145">
-        <v>9.9903162146036966</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" ht="21">
-      <c r="A26" s="139" t="s">
-        <v>504</v>
-      </c>
-      <c r="B26" s="213">
-        <v>14.602959999999999</v>
-      </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="140" t="s">
-        <v>563</v>
-      </c>
-      <c r="E26" s="213">
-        <v>223.86615999999998</v>
-      </c>
-      <c r="F26" s="101"/>
-      <c r="G26" s="140" t="s">
-        <v>622</v>
-      </c>
-      <c r="H26" s="213">
-        <v>504.3852</v>
-      </c>
-      <c r="I26" s="7"/>
-      <c r="J26" s="140" t="s">
-        <v>659</v>
-      </c>
-      <c r="K26" s="60">
-        <v>17.120854559640183</v>
-      </c>
-      <c r="L26" s="7"/>
-      <c r="M26" s="140" t="s">
-        <v>719</v>
-      </c>
-      <c r="N26" s="145">
-        <v>10.725948873284684</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" ht="21">
-      <c r="A27" s="139" t="s">
-        <v>505</v>
-      </c>
-      <c r="B27" s="213">
-        <v>15.322399999999998</v>
-      </c>
-      <c r="C27" s="7"/>
-      <c r="D27" s="140" t="s">
-        <v>564</v>
-      </c>
-      <c r="E27" s="213">
-        <v>225.71168</v>
-      </c>
-      <c r="F27" s="101"/>
-      <c r="H27" s="7">
-        <v>5</v>
-      </c>
-      <c r="I27" s="7"/>
-      <c r="J27" s="140" t="s">
-        <v>660</v>
-      </c>
-      <c r="K27" s="60">
-        <v>17.437686447289913</v>
-      </c>
-      <c r="L27" s="7"/>
-      <c r="M27" s="140" t="s">
-        <v>720</v>
-      </c>
-      <c r="N27" s="145">
-        <v>11.141107898480882</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" ht="21">
-      <c r="A28" s="139" t="s">
-        <v>506</v>
-      </c>
-      <c r="B28" s="213">
-        <v>16.16696</v>
-      </c>
-      <c r="C28" s="7"/>
-      <c r="D28" s="140" t="s">
-        <v>334</v>
-      </c>
-      <c r="E28" s="213">
-        <v>237.56679999999994</v>
-      </c>
-      <c r="F28" s="101"/>
-      <c r="G28" s="140" t="s">
-        <v>623</v>
-      </c>
-      <c r="H28" s="7">
-        <v>30.24296</v>
-      </c>
-      <c r="I28" s="7"/>
-      <c r="J28" s="140" t="s">
-        <v>661</v>
-      </c>
-      <c r="K28" s="60">
-        <v>17.860128964156225</v>
-      </c>
-      <c r="L28" s="7"/>
-      <c r="M28" s="140" t="s">
-        <v>721</v>
-      </c>
-      <c r="N28" s="145">
-        <v>11.570833907017301</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" ht="21">
-      <c r="A29" s="139" t="s">
-        <v>507</v>
-      </c>
-      <c r="B29" s="213">
-        <v>16.354639999999996</v>
-      </c>
-      <c r="C29" s="7"/>
-      <c r="D29" s="140" t="s">
-        <v>565</v>
-      </c>
-      <c r="E29" s="213">
-        <v>240.94504000000001</v>
-      </c>
-      <c r="F29" s="101"/>
-      <c r="G29" s="140" t="s">
-        <v>624</v>
-      </c>
-      <c r="H29" s="7">
-        <v>31.963359999999994</v>
-      </c>
-      <c r="I29" s="7"/>
-      <c r="J29" s="140" t="s">
-        <v>662</v>
-      </c>
-      <c r="K29" s="60">
-        <v>17.965739593372803</v>
-      </c>
-      <c r="L29" s="7"/>
-      <c r="M29" s="140" t="s">
-        <v>722</v>
-      </c>
-      <c r="N29" s="145">
-        <v>11.975067694708338</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" ht="21">
-      <c r="A30" s="139" t="s">
-        <v>508</v>
-      </c>
-      <c r="B30" s="213">
-        <v>17.011519999999997</v>
-      </c>
-      <c r="C30" s="7"/>
-      <c r="D30" s="140" t="s">
-        <v>335</v>
-      </c>
-      <c r="E30" s="213">
-        <v>242.72799999999998</v>
-      </c>
-      <c r="F30" s="101"/>
-      <c r="G30" s="140" t="s">
-        <v>625</v>
-      </c>
-      <c r="H30" s="7">
-        <v>366.28399999999999</v>
-      </c>
-      <c r="I30" s="7"/>
-      <c r="J30" s="140" t="s">
-        <v>663</v>
-      </c>
-      <c r="K30" s="60">
-        <v>18.395465601909216</v>
-      </c>
-      <c r="L30" s="7"/>
-      <c r="M30" s="140" t="s">
-        <v>723</v>
-      </c>
-      <c r="N30" s="145">
-        <v>12.4011519574097</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" ht="21">
-      <c r="A31" s="139" t="s">
-        <v>509</v>
-      </c>
-      <c r="B31" s="213">
-        <v>17.41816</v>
-      </c>
-      <c r="C31" s="7"/>
-      <c r="D31" s="140" t="s">
-        <v>566</v>
-      </c>
-      <c r="E31" s="213">
-        <v>247.88919999999999</v>
-      </c>
-      <c r="F31" s="101"/>
-      <c r="G31" s="140" t="s">
-        <v>626</v>
-      </c>
-      <c r="H31" s="7">
-        <v>411.42104</v>
-      </c>
-      <c r="I31" s="7"/>
-      <c r="J31" s="140" t="s">
-        <v>664</v>
-      </c>
-      <c r="K31" s="60">
-        <v>18.708655743723895</v>
-      </c>
-      <c r="L31" s="7"/>
-      <c r="M31" s="140" t="s">
-        <v>724</v>
-      </c>
-      <c r="N31" s="145">
-        <v>12.506762586626278</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" ht="21">
-      <c r="A32" s="139" t="s">
-        <v>510</v>
-      </c>
-      <c r="B32" s="213">
-        <v>18.356559999999995</v>
-      </c>
-      <c r="C32" s="7"/>
-      <c r="D32" s="140" t="s">
-        <v>567</v>
-      </c>
-      <c r="E32" s="213">
-        <v>261.55856</v>
-      </c>
-      <c r="F32" s="101"/>
-      <c r="G32" s="140" t="s">
-        <v>627</v>
-      </c>
-      <c r="H32" s="7">
-        <v>522.62143999999989</v>
-      </c>
-      <c r="I32" s="7"/>
-      <c r="J32" s="140" t="s">
-        <v>665</v>
-      </c>
-      <c r="K32" s="60">
-        <v>19.021845885538571</v>
-      </c>
-      <c r="L32" s="7"/>
-      <c r="M32" s="140" t="s">
-        <v>725</v>
-      </c>
-      <c r="N32" s="145">
-        <v>12.819952728440954</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" ht="21">
-      <c r="A33" s="139" t="s">
-        <v>511</v>
-      </c>
-      <c r="B33" s="213">
-        <v>18.669360000000001</v>
-      </c>
-      <c r="C33" s="7"/>
-      <c r="D33" s="140" t="s">
-        <v>568</v>
-      </c>
-      <c r="E33" s="213">
-        <v>275.25920000000002</v>
-      </c>
-      <c r="F33" s="101"/>
-      <c r="G33" s="140" t="s">
-        <v>628</v>
-      </c>
-      <c r="H33" s="7">
-        <v>557.40479999999991</v>
-      </c>
-      <c r="I33" s="7"/>
-      <c r="J33" s="140" t="s">
-        <v>666</v>
-      </c>
-      <c r="K33" s="60">
-        <v>19.542615539951353</v>
-      </c>
-      <c r="L33" s="7"/>
-      <c r="M33" s="140" t="s">
-        <v>726</v>
-      </c>
-      <c r="N33" s="145">
-        <v>13.224186516131992</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" ht="21">
-      <c r="A34" s="139" t="s">
-        <v>512</v>
-      </c>
-      <c r="B34" s="213">
-        <v>20.421040000000001</v>
-      </c>
-      <c r="C34" s="7"/>
-      <c r="D34" s="140" t="s">
-        <v>342</v>
-      </c>
-      <c r="E34" s="213">
-        <v>286.73895999999996</v>
-      </c>
-      <c r="F34" s="101"/>
-      <c r="G34" s="140" t="s">
-        <v>629</v>
-      </c>
-      <c r="H34" s="7">
-        <v>731.66567999999995</v>
-      </c>
-      <c r="I34" s="7"/>
-      <c r="J34" s="140" t="s">
-        <v>667</v>
-      </c>
-      <c r="K34" s="60">
-        <v>19.750195052549447</v>
-      </c>
-      <c r="L34" s="7"/>
-      <c r="M34" s="140" t="s">
-        <v>727</v>
-      </c>
-      <c r="N34" s="145">
-        <v>14.039937583184171</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" ht="21.6" thickBot="1">
-      <c r="A35" s="139" t="s">
-        <v>513</v>
-      </c>
-      <c r="B35" s="213">
-        <v>21.296879999999998</v>
-      </c>
-      <c r="C35" s="7"/>
-      <c r="D35" s="140" t="s">
-        <v>569</v>
-      </c>
-      <c r="E35" s="213">
-        <v>295.71631999999994</v>
-      </c>
-      <c r="F35" s="101"/>
-      <c r="G35" s="140" t="s">
-        <v>630</v>
-      </c>
-      <c r="H35" s="7">
-        <v>806.83151999999984</v>
-      </c>
-      <c r="I35" s="7"/>
-      <c r="J35" s="140" t="s">
-        <v>668</v>
-      </c>
-      <c r="K35" s="60">
-        <v>19.972341548487766</v>
-      </c>
-      <c r="L35" s="7"/>
-      <c r="M35" s="140" t="s">
-        <v>728</v>
-      </c>
-      <c r="N35" s="146">
-        <v>15.136103079535545</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" ht="21">
-      <c r="A36" s="139" t="s">
-        <v>514</v>
-      </c>
-      <c r="B36" s="213">
-        <v>22.078879999999998</v>
-      </c>
-      <c r="C36" s="7"/>
-      <c r="D36" s="140" t="s">
-        <v>570</v>
-      </c>
-      <c r="E36" s="213">
-        <v>297.46799999999996</v>
-      </c>
-      <c r="F36" s="101"/>
-      <c r="G36" s="140" t="s">
-        <v>631</v>
-      </c>
-      <c r="H36" s="7">
-        <v>1022.3194400000001</v>
-      </c>
-      <c r="I36" s="7"/>
-      <c r="J36" s="140" t="s">
-        <v>93</v>
-      </c>
-      <c r="K36" s="60">
-        <v>20.39114231951902</v>
-      </c>
-      <c r="L36" s="7"/>
-      <c r="M36" s="140" t="s">
-        <v>729</v>
-      </c>
-      <c r="N36" s="147">
-        <v>16.396147138464361</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" ht="21">
-      <c r="A37" s="139" t="s">
-        <v>515</v>
-      </c>
-      <c r="B37" s="213">
-        <v>22.985999999999997</v>
-      </c>
-      <c r="C37" s="7"/>
-      <c r="D37" s="140" t="s">
-        <v>349</v>
-      </c>
-      <c r="E37" s="213">
-        <v>309.41695999999996</v>
-      </c>
-      <c r="F37" s="101"/>
-      <c r="G37" s="140" t="s">
-        <v>632</v>
-      </c>
-      <c r="H37" s="7">
-        <v>1102.52136</v>
-      </c>
-      <c r="I37" s="7"/>
-      <c r="J37" s="140" t="s">
-        <v>669</v>
-      </c>
-      <c r="K37" s="60">
-        <v>20.984746890632888</v>
-      </c>
-      <c r="L37" s="7"/>
-      <c r="M37" s="140" t="s">
-        <v>730</v>
-      </c>
-      <c r="N37" s="148">
-        <v>17.120854559640183</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" ht="21">
-      <c r="A38" s="139" t="s">
-        <v>516</v>
-      </c>
-      <c r="B38" s="213">
-        <v>23.830559999999998</v>
-      </c>
-      <c r="C38" s="7"/>
-      <c r="D38" s="140" t="s">
-        <v>571</v>
-      </c>
-      <c r="E38" s="213">
-        <v>312.79520000000002</v>
-      </c>
-      <c r="F38" s="101"/>
-      <c r="G38" s="140" t="s">
-        <v>633</v>
-      </c>
-      <c r="H38" s="7">
-        <v>1971.7612799999999</v>
-      </c>
-      <c r="I38" s="7"/>
-      <c r="J38" s="140" t="s">
-        <v>670</v>
-      </c>
-      <c r="K38" s="60">
-        <v>21.531008765891041</v>
-      </c>
-      <c r="L38" s="7"/>
-      <c r="M38" s="140" t="s">
-        <v>731</v>
-      </c>
-      <c r="N38" s="148">
-        <v>17.437686447289913</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14" ht="21">
-      <c r="A39" s="139" t="s">
-        <v>517</v>
-      </c>
-      <c r="B39" s="213">
-        <v>24.737679999999997</v>
-      </c>
-      <c r="C39" s="7"/>
-      <c r="D39" s="140" t="s">
-        <v>572</v>
-      </c>
-      <c r="E39" s="213">
-        <v>317.89384000000001</v>
-      </c>
-      <c r="F39" s="101"/>
-      <c r="G39" s="140" t="s">
-        <v>634</v>
-      </c>
-      <c r="H39" s="7">
-        <v>2067.8221599999997</v>
-      </c>
-      <c r="I39" s="7"/>
-      <c r="J39" s="140" t="s">
-        <v>671</v>
-      </c>
-      <c r="K39" s="60">
-        <v>21.636619395107616</v>
-      </c>
-      <c r="L39" s="7"/>
-      <c r="M39" s="140" t="s">
-        <v>732</v>
-      </c>
-      <c r="N39" s="148">
-        <v>17.965739593372803</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14" ht="21">
-      <c r="A40" s="139" t="s">
-        <v>518</v>
-      </c>
-      <c r="B40" s="213">
-        <v>25.550959999999996</v>
-      </c>
-      <c r="C40" s="7"/>
-      <c r="D40" s="140" t="s">
-        <v>573</v>
-      </c>
-      <c r="E40" s="213">
-        <v>329.96791999999999</v>
-      </c>
-      <c r="F40" s="101"/>
-      <c r="G40" s="140" t="s">
-        <v>635</v>
-      </c>
-      <c r="H40" s="7">
-        <v>3408.9208799999997</v>
-      </c>
-      <c r="I40" s="7"/>
-      <c r="J40" s="140" t="s">
-        <v>672</v>
-      </c>
-      <c r="K40" s="60">
-        <v>22.073628895314144</v>
-      </c>
-      <c r="L40" s="7"/>
-      <c r="M40" s="140" t="s">
-        <v>733</v>
-      </c>
-      <c r="N40" s="148">
-        <v>18.708655743723895</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14" ht="21">
-      <c r="A41" s="139" t="s">
-        <v>519</v>
-      </c>
-      <c r="B41" s="213">
-        <v>26.645759999999996</v>
-      </c>
-      <c r="C41" s="7"/>
-      <c r="D41" s="140" t="s">
-        <v>574</v>
-      </c>
-      <c r="E41" s="213">
-        <v>338.44479999999993</v>
-      </c>
-      <c r="F41" s="101"/>
-      <c r="G41" s="140" t="s">
-        <v>636</v>
-      </c>
-      <c r="H41" s="7">
-        <v>3631.9159999999997</v>
-      </c>
-      <c r="I41" s="7"/>
-      <c r="J41" s="140" t="s">
-        <v>673</v>
-      </c>
-      <c r="K41" s="60">
-        <v>22.164672541190502</v>
-      </c>
-      <c r="L41" s="7"/>
-      <c r="M41" s="140" t="s">
-        <v>734</v>
-      </c>
-      <c r="N41" s="148">
-        <v>19.542615539951353</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14" ht="21">
-      <c r="A42" s="139" t="s">
-        <v>520</v>
-      </c>
-      <c r="B42" s="213">
-        <v>27.271359999999998</v>
-      </c>
-      <c r="C42" s="7"/>
-      <c r="D42" s="140" t="s">
-        <v>575</v>
-      </c>
-      <c r="E42" s="213">
-        <v>350.51887999999997</v>
-      </c>
-      <c r="F42" s="101"/>
-      <c r="G42" s="140" t="s">
-        <v>637</v>
-      </c>
-      <c r="H42" s="7">
-        <v>5951.04648</v>
-      </c>
-      <c r="I42" s="7"/>
-      <c r="J42" s="140" t="s">
-        <v>674</v>
-      </c>
-      <c r="K42" s="60">
-        <v>22.386819037128827</v>
-      </c>
-      <c r="L42" s="7"/>
-      <c r="M42" s="140" t="s">
-        <v>735</v>
-      </c>
-      <c r="N42" s="148">
-        <v>22.594398549726922</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14" ht="21">
-      <c r="A43" s="139" t="s">
-        <v>521</v>
-      </c>
-      <c r="B43" s="213">
-        <v>28.053359999999998</v>
-      </c>
-      <c r="C43" s="7"/>
-      <c r="D43" s="140" t="s">
-        <v>576</v>
-      </c>
-      <c r="E43" s="213">
-        <v>370.88215999999994</v>
-      </c>
-      <c r="F43" s="101"/>
-      <c r="G43" s="140" t="s">
-        <v>638</v>
-      </c>
-      <c r="H43" s="7">
-        <v>6408.3913599999987</v>
-      </c>
-      <c r="I43" s="7"/>
-      <c r="J43" s="140" t="s">
-        <v>675</v>
-      </c>
-      <c r="K43" s="60">
-        <v>22.594398549726922</v>
-      </c>
-      <c r="L43" s="7"/>
-      <c r="M43" s="140" t="s">
-        <v>736</v>
-      </c>
-      <c r="N43" s="148">
-        <v>25.420393317729125</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14" ht="21">
-      <c r="A44" s="139" t="s">
-        <v>522</v>
-      </c>
-      <c r="B44" s="213">
-        <v>28.929200000000002</v>
-      </c>
-      <c r="C44" s="7"/>
-      <c r="D44" s="140" t="s">
-        <v>577</v>
-      </c>
-      <c r="E44" s="213">
-        <v>388.05487999999997</v>
-      </c>
-      <c r="F44" s="101"/>
-      <c r="G44" s="140" t="s">
-        <v>639</v>
-      </c>
-      <c r="H44" s="7">
-        <v>6865.7987999999987</v>
-      </c>
-      <c r="I44" s="7"/>
-      <c r="J44" s="140" t="s">
-        <v>676</v>
-      </c>
-      <c r="K44" s="60">
-        <v>23.326389462572852</v>
-      </c>
-      <c r="L44" s="7"/>
-      <c r="M44" s="140" t="s">
-        <v>737</v>
-      </c>
-      <c r="N44" s="148">
-        <v>25.857402817935654</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14" ht="21">
-      <c r="A45" s="139" t="s">
-        <v>523</v>
-      </c>
-      <c r="B45" s="213">
-        <v>30.712160000000001</v>
-      </c>
-      <c r="C45" s="7"/>
-      <c r="D45" s="140" t="s">
-        <v>578</v>
-      </c>
-      <c r="E45" s="213">
-        <v>429.18808000000001</v>
-      </c>
-      <c r="F45" s="101"/>
-      <c r="G45" s="140" t="s">
-        <v>640</v>
-      </c>
-      <c r="H45" s="7">
-        <v>7323.1749599999994</v>
-      </c>
-      <c r="I45" s="7"/>
-      <c r="J45" s="140" t="s">
-        <v>677</v>
-      </c>
-      <c r="K45" s="60">
-        <v>23.854442608655745</v>
-      </c>
-      <c r="L45" s="7"/>
-      <c r="M45" s="140" t="s">
-        <v>738</v>
-      </c>
-      <c r="N45" s="148">
-        <v>27.27404194777181</v>
-      </c>
-    </row>
-    <row r="46" spans="1:14" ht="21">
-      <c r="A46" s="139" t="s">
-        <v>524</v>
-      </c>
-      <c r="B46" s="213">
-        <v>33.183279999999996</v>
-      </c>
-      <c r="C46" s="7"/>
-      <c r="D46" s="140" t="s">
-        <v>579</v>
-      </c>
-      <c r="E46" s="213">
-        <v>432.53503999999998</v>
-      </c>
-      <c r="F46" s="101"/>
-      <c r="G46" s="140" t="s">
-        <v>641</v>
-      </c>
-      <c r="H46" s="7">
-        <v>7780.5511199999983</v>
-      </c>
-      <c r="I46" s="7"/>
-      <c r="J46" s="140" t="s">
-        <v>94</v>
-      </c>
-      <c r="K46" s="60">
-        <v>24.575508283996509</v>
-      </c>
-      <c r="L46" s="7"/>
-      <c r="M46" s="140" t="s">
-        <v>739</v>
-      </c>
-      <c r="N46" s="148">
-        <v>28.158986185690029</v>
-      </c>
-    </row>
-    <row r="47" spans="1:14" ht="21">
-      <c r="A47" s="139" t="s">
-        <v>525</v>
-      </c>
-      <c r="B47" s="213">
-        <v>34.121679999999998</v>
-      </c>
-      <c r="C47" s="7"/>
-      <c r="D47" s="140" t="s">
-        <v>580</v>
-      </c>
-      <c r="E47" s="213">
-        <v>446.23567999999995</v>
-      </c>
-      <c r="F47" s="101"/>
-      <c r="G47" s="140" t="s">
-        <v>642</v>
-      </c>
-      <c r="H47" s="7">
-        <v>8237.9585600000009</v>
-      </c>
-      <c r="I47" s="7"/>
-      <c r="J47" s="140" t="s">
-        <v>678</v>
-      </c>
-      <c r="K47" s="60">
-        <v>25.420393317729125</v>
-      </c>
-      <c r="L47" s="7"/>
-      <c r="M47" s="140" t="s">
-        <v>740</v>
-      </c>
-      <c r="N47" s="148">
-        <v>38.45784340722382</v>
-      </c>
-    </row>
-    <row r="48" spans="1:14" ht="21">
-      <c r="A48" s="139" t="s">
-        <v>526</v>
-      </c>
-      <c r="B48" s="213">
-        <v>35.8108</v>
-      </c>
-      <c r="C48" s="7"/>
-      <c r="D48" s="140" t="s">
-        <v>581</v>
-      </c>
-      <c r="E48" s="213">
-        <v>504.3852</v>
-      </c>
-      <c r="F48" s="101"/>
-      <c r="G48" s="140" t="s">
-        <v>643</v>
-      </c>
-      <c r="H48" s="7">
-        <v>8695.366</v>
-      </c>
-      <c r="I48" s="7"/>
-      <c r="J48" s="140" t="s">
-        <v>679</v>
-      </c>
-      <c r="K48" s="60">
-        <v>25.857402817935654</v>
-      </c>
-      <c r="L48" s="7"/>
-      <c r="M48" s="140" t="s">
-        <v>741</v>
-      </c>
-      <c r="N48" s="148">
-        <v>39.921825232915687</v>
-      </c>
-    </row>
-    <row r="49" spans="1:14" ht="21">
-      <c r="A49" s="139" t="s">
-        <v>527</v>
-      </c>
-      <c r="B49" s="213">
-        <v>36.624079999999992</v>
-      </c>
-      <c r="C49" s="7"/>
-      <c r="D49" s="140" t="s">
-        <v>582</v>
-      </c>
-      <c r="E49" s="213">
-        <v>528.22055999999998</v>
-      </c>
-      <c r="F49" s="101"/>
-      <c r="G49" s="140" t="s">
-        <v>644</v>
-      </c>
-      <c r="H49" s="7">
-        <v>9152.7108800000005</v>
-      </c>
-      <c r="I49" s="7"/>
-      <c r="J49" s="140" t="s">
-        <v>680</v>
-      </c>
-      <c r="K49" s="60">
-        <v>26.268920097296789</v>
-      </c>
-      <c r="L49" s="7"/>
-      <c r="M49" s="140" t="s">
-        <v>742</v>
-      </c>
-      <c r="N49" s="148">
-        <v>44.561409426774979</v>
-      </c>
-    </row>
-    <row r="50" spans="1:14" ht="21">
-      <c r="A50" s="139" t="s">
-        <v>528</v>
-      </c>
-      <c r="B50" s="213">
-        <v>37.531199999999998</v>
-      </c>
-      <c r="C50" s="7"/>
-      <c r="D50" s="140" t="s">
-        <v>583</v>
-      </c>
-      <c r="E50" s="213">
-        <v>559.09391999999991</v>
-      </c>
-      <c r="F50" s="101"/>
-      <c r="G50" s="140" t="s">
-        <v>645</v>
-      </c>
-      <c r="H50" s="7">
-        <v>10067.525759999999</v>
-      </c>
-      <c r="I50" s="7"/>
-      <c r="J50" s="140" t="s">
-        <v>681</v>
-      </c>
-      <c r="K50" s="60">
-        <v>26.695004359998162</v>
-      </c>
-      <c r="L50" s="7"/>
-      <c r="M50" s="140" t="s">
-        <v>743</v>
-      </c>
-      <c r="N50" s="148">
-        <v>46.86299279452934</v>
-      </c>
-    </row>
-    <row r="51" spans="1:14" ht="21">
-      <c r="A51" s="139" t="s">
-        <v>529</v>
-      </c>
-      <c r="B51" s="213">
-        <v>39.314160000000001</v>
-      </c>
-      <c r="C51" s="7"/>
-      <c r="D51" s="140" t="s">
-        <v>584</v>
-      </c>
-      <c r="E51" s="213">
-        <v>579.61359999999991</v>
-      </c>
-      <c r="F51" s="101"/>
-      <c r="G51" s="7"/>
-      <c r="H51" s="7"/>
-      <c r="I51" s="7"/>
-      <c r="J51" s="140" t="s">
-        <v>682</v>
-      </c>
-      <c r="K51" s="60">
-        <v>26.902583872596264</v>
-      </c>
-      <c r="L51" s="7"/>
-      <c r="M51" s="140" t="s">
-        <v>744</v>
-      </c>
-      <c r="N51" s="148">
-        <v>52.325611547110917</v>
-      </c>
-    </row>
-    <row r="52" spans="1:14" ht="21">
-      <c r="A52" s="139" t="s">
-        <v>530</v>
-      </c>
-      <c r="B52" s="213">
-        <v>40.12744</v>
-      </c>
-      <c r="C52" s="7"/>
-      <c r="D52" s="140" t="s">
-        <v>585</v>
-      </c>
-      <c r="E52" s="213">
-        <v>606.85847999999999</v>
-      </c>
-      <c r="F52" s="101"/>
-      <c r="G52" s="7"/>
-      <c r="H52" s="7"/>
-      <c r="I52" s="7"/>
-      <c r="J52" s="140" t="s">
-        <v>95</v>
-      </c>
-      <c r="K52" s="60">
-        <v>27.110163385194365</v>
-      </c>
-      <c r="L52" s="7"/>
-      <c r="M52" s="140" t="s">
-        <v>745</v>
-      </c>
-      <c r="N52" s="148">
-        <v>76.284657395933706</v>
-      </c>
-    </row>
-    <row r="53" spans="1:14" ht="21">
-      <c r="A53" s="139" t="s">
-        <v>531</v>
-      </c>
-      <c r="B53" s="213">
-        <v>42.661119999999997</v>
-      </c>
-      <c r="C53" s="7"/>
-      <c r="D53" s="140" t="s">
-        <v>586</v>
-      </c>
-      <c r="E53" s="213">
-        <v>665.13311999999996</v>
-      </c>
-      <c r="F53" s="101"/>
-      <c r="G53" s="7"/>
-      <c r="H53" s="7"/>
-      <c r="I53" s="7"/>
-      <c r="J53" s="140" t="s">
-        <v>683</v>
-      </c>
-      <c r="K53" s="60">
-        <v>27.27404194777181</v>
-      </c>
-      <c r="L53" s="7"/>
-      <c r="M53" s="140" t="s">
-        <v>746</v>
-      </c>
-      <c r="N53" s="148">
-        <v>89.737266510624593</v>
-      </c>
-    </row>
-    <row r="54" spans="1:14" ht="21">
-      <c r="A54" s="139" t="s">
-        <v>532</v>
-      </c>
-      <c r="B54" s="213">
-        <v>46.039359999999995</v>
-      </c>
-      <c r="C54" s="7"/>
-      <c r="D54" s="140" t="s">
-        <v>587</v>
-      </c>
-      <c r="E54" s="213">
-        <v>13.977360000000001</v>
-      </c>
-      <c r="F54" s="101"/>
-      <c r="G54" s="7"/>
-      <c r="H54" s="7"/>
-      <c r="I54" s="7"/>
-      <c r="J54" s="140" t="s">
-        <v>684</v>
-      </c>
-      <c r="K54" s="60">
-        <v>27.73654366882371</v>
-      </c>
-      <c r="L54" s="7"/>
-      <c r="N54" s="148">
-        <v>1.4686309605764374</v>
-      </c>
-    </row>
-    <row r="55" spans="1:14" ht="21">
-      <c r="A55" s="139" t="s">
-        <v>533</v>
-      </c>
-      <c r="B55" s="213">
-        <v>49.605279999999986</v>
-      </c>
-      <c r="C55" s="7"/>
-      <c r="D55" s="140" t="s">
-        <v>588</v>
-      </c>
-      <c r="E55" s="213">
-        <v>14.602959999999999</v>
-      </c>
-      <c r="F55" s="101"/>
-      <c r="G55" s="7"/>
-      <c r="H55" s="7"/>
-      <c r="I55" s="7"/>
-      <c r="J55" s="140" t="s">
-        <v>685</v>
-      </c>
-      <c r="K55" s="60">
-        <v>27.94776492725687</v>
-      </c>
-      <c r="L55" s="7"/>
-      <c r="M55" s="140" t="s">
-        <v>747</v>
-      </c>
-      <c r="N55" s="148">
-        <v>95.196243517371116</v>
-      </c>
-    </row>
-    <row r="56" spans="1:14" ht="21">
-      <c r="A56" s="139" t="s">
-        <v>534</v>
-      </c>
-      <c r="B56" s="213">
-        <v>52.920959999999994</v>
-      </c>
-      <c r="C56" s="7"/>
-      <c r="D56" s="140" t="s">
-        <v>589</v>
-      </c>
-      <c r="E56" s="213">
-        <v>16.16696</v>
-      </c>
-      <c r="F56" s="101"/>
-      <c r="G56" s="7"/>
-      <c r="H56" s="7"/>
-      <c r="I56" s="7"/>
-      <c r="J56" s="140" t="s">
-        <v>686</v>
-      </c>
-      <c r="K56" s="60">
-        <v>28.158986185690029</v>
-      </c>
-      <c r="L56" s="7"/>
-      <c r="M56" s="140" t="s">
-        <v>748</v>
-      </c>
-      <c r="N56" s="148">
-        <v>98.146057643765189</v>
-      </c>
-    </row>
-    <row r="57" spans="1:14" ht="21">
-      <c r="A57" s="139" t="s">
-        <v>535</v>
-      </c>
-      <c r="B57" s="213">
-        <v>55.548480000000005</v>
-      </c>
-      <c r="C57" s="7"/>
-      <c r="D57" s="140" t="s">
-        <v>590</v>
-      </c>
-      <c r="E57" s="213">
-        <v>16.354639999999996</v>
-      </c>
-      <c r="F57" s="101"/>
-      <c r="G57" s="7"/>
-      <c r="H57" s="7"/>
-      <c r="I57" s="7"/>
-      <c r="J57" s="140" t="s">
-        <v>687</v>
-      </c>
-      <c r="K57" s="60">
-        <v>28.789008215154428</v>
-      </c>
-      <c r="L57" s="7"/>
-      <c r="M57" s="140" t="s">
-        <v>749</v>
-      </c>
-      <c r="N57" s="148">
-        <v>110.33133920785717</v>
-      </c>
-    </row>
-    <row r="58" spans="1:14" ht="21">
-      <c r="A58" s="139" t="s">
-        <v>536</v>
-      </c>
-      <c r="B58" s="213">
-        <v>56.267919999999997</v>
-      </c>
-      <c r="C58" s="7"/>
-      <c r="D58" s="140" t="s">
-        <v>591</v>
-      </c>
-      <c r="E58" s="213">
-        <v>17.41816</v>
-      </c>
-      <c r="F58" s="101"/>
-      <c r="G58" s="7"/>
-      <c r="H58" s="7"/>
-      <c r="I58" s="7"/>
-      <c r="J58" s="140" t="s">
-        <v>688</v>
-      </c>
-      <c r="K58" s="60">
-        <v>29.215092477855794</v>
-      </c>
-      <c r="L58" s="7"/>
-      <c r="M58" s="141"/>
-      <c r="N58" s="148">
-        <v>1.4686309605764374</v>
-      </c>
-    </row>
-    <row r="59" spans="1:14" ht="21">
-      <c r="A59" s="139" t="s">
-        <v>537</v>
-      </c>
-      <c r="B59" s="213">
-        <v>59.677440000000004</v>
-      </c>
-      <c r="C59" s="7"/>
-      <c r="D59" s="140" t="s">
-        <v>592</v>
-      </c>
-      <c r="E59" s="213">
-        <v>18.356559999999995</v>
-      </c>
-      <c r="F59" s="101"/>
-      <c r="G59" s="7"/>
-      <c r="H59" s="7"/>
-      <c r="I59" s="7"/>
-      <c r="J59" s="140" t="s">
-        <v>689</v>
-      </c>
-      <c r="K59" s="60">
-        <v>29.375329294598188</v>
-      </c>
-      <c r="L59" s="7"/>
-      <c r="M59" s="140" t="s">
-        <v>750</v>
-      </c>
-      <c r="N59" s="148">
-        <v>15.944570654917618</v>
-      </c>
-    </row>
-    <row r="60" spans="1:14" ht="21">
-      <c r="A60" s="139" t="s">
-        <v>538</v>
-      </c>
-      <c r="B60" s="213">
-        <v>63.180799999999998</v>
-      </c>
-      <c r="C60" s="7"/>
-      <c r="D60" s="140" t="s">
-        <v>593</v>
-      </c>
-      <c r="E60" s="213">
-        <v>23.830559999999998</v>
-      </c>
-      <c r="F60" s="101"/>
-      <c r="G60" s="7"/>
-      <c r="H60" s="7"/>
-      <c r="I60" s="7"/>
-      <c r="J60" s="140" t="s">
-        <v>690</v>
-      </c>
-      <c r="K60" s="60">
-        <v>30.471494790949553</v>
-      </c>
-      <c r="L60" s="7"/>
-      <c r="M60" s="141"/>
-      <c r="N60" s="148">
-        <v>1.4686309605764374</v>
-      </c>
-    </row>
-    <row r="61" spans="1:14" ht="21">
-      <c r="A61" s="139" t="s">
-        <v>539</v>
-      </c>
-      <c r="B61" s="213">
-        <v>66.527760000000001</v>
-      </c>
-      <c r="C61" s="7"/>
-      <c r="D61" s="140" t="s">
-        <v>594</v>
-      </c>
-      <c r="E61" s="213">
-        <v>24.737679999999997</v>
-      </c>
-      <c r="F61" s="101"/>
-      <c r="G61" s="7"/>
-      <c r="H61" s="7"/>
-      <c r="I61" s="7"/>
-      <c r="J61" s="140" t="s">
-        <v>691</v>
-      </c>
-      <c r="K61" s="60">
-        <v>31.465691403919408</v>
-      </c>
-      <c r="L61" s="7"/>
-      <c r="M61" s="140" t="s">
-        <v>751</v>
-      </c>
-      <c r="N61" s="148">
-        <v>21.436323374179622</v>
-      </c>
-    </row>
-    <row r="62" spans="1:14" ht="21">
-      <c r="A62" s="139" t="s">
-        <v>540</v>
-      </c>
-      <c r="B62" s="213">
-        <v>69.968559999999982</v>
-      </c>
-      <c r="C62" s="7"/>
-      <c r="D62" s="140" t="s">
-        <v>595</v>
-      </c>
-      <c r="E62" s="213">
-        <v>34.121679999999998</v>
-      </c>
-      <c r="F62" s="101"/>
-      <c r="G62" s="7"/>
-      <c r="H62" s="7"/>
-      <c r="I62" s="7"/>
-      <c r="J62" s="140" t="s">
-        <v>692</v>
-      </c>
-      <c r="K62" s="60">
-        <v>31.942760108311528</v>
-      </c>
-      <c r="L62" s="7"/>
-      <c r="M62" s="140" t="s">
-        <v>752</v>
-      </c>
-      <c r="N62" s="148">
-        <v>21.702170820138601</v>
-      </c>
-    </row>
-    <row r="63" spans="1:14" ht="21">
-      <c r="A63" s="140" t="s">
-        <v>541</v>
-      </c>
-      <c r="B63" s="213">
-        <v>76.881439999999998</v>
-      </c>
-      <c r="C63" s="7"/>
-      <c r="D63" s="140" t="s">
-        <v>596</v>
-      </c>
-      <c r="E63" s="213">
-        <v>35.8108</v>
-      </c>
-      <c r="F63" s="101"/>
-      <c r="G63" s="7"/>
-      <c r="H63" s="7"/>
-      <c r="I63" s="7"/>
-      <c r="J63" s="140" t="s">
-        <v>693</v>
-      </c>
-      <c r="K63" s="60">
-        <v>32.995224654642243</v>
-      </c>
-      <c r="L63" s="7"/>
-      <c r="M63" s="140" t="s">
-        <v>753</v>
-      </c>
-      <c r="N63" s="148">
-        <v>22.237507457891596</v>
-      </c>
-    </row>
-    <row r="64" spans="1:14" ht="21">
-      <c r="A64" s="140" t="s">
-        <v>542</v>
-      </c>
-      <c r="B64" s="213">
-        <v>83.669200000000004</v>
-      </c>
-      <c r="C64" s="7"/>
-      <c r="D64" s="140" t="s">
-        <v>597</v>
-      </c>
-      <c r="E64" s="213">
-        <v>36.624079999999992</v>
-      </c>
-      <c r="F64" s="101"/>
-      <c r="G64" s="7"/>
-      <c r="H64" s="7"/>
-      <c r="I64" s="7"/>
-      <c r="J64" s="140" t="s">
-        <v>694</v>
-      </c>
-      <c r="K64" s="60">
-        <v>34.040405709302853</v>
-      </c>
-      <c r="L64" s="7"/>
-      <c r="M64" s="140" t="s">
-        <v>754</v>
-      </c>
-      <c r="N64" s="148">
-        <v>22.772844095644587</v>
-      </c>
-    </row>
-    <row r="65" spans="1:14" ht="21">
-      <c r="A65" s="140" t="s">
-        <v>543</v>
-      </c>
-      <c r="B65" s="213">
-        <v>87.11</v>
-      </c>
-      <c r="C65" s="7"/>
-      <c r="D65" s="140" t="s">
-        <v>598</v>
-      </c>
-      <c r="E65" s="213">
-        <v>37.531199999999998</v>
-      </c>
-      <c r="F65" s="101"/>
-      <c r="G65" s="7"/>
-      <c r="H65" s="7"/>
-      <c r="I65" s="7"/>
-      <c r="J65" s="140" t="s">
-        <v>695</v>
-      </c>
-      <c r="K65" s="60">
-        <v>35.744742760108302</v>
-      </c>
-      <c r="L65" s="7"/>
-      <c r="M65" s="140" t="s">
-        <v>755</v>
-      </c>
-      <c r="N65" s="148">
-        <v>23.038691541603558</v>
-      </c>
-    </row>
-    <row r="66" spans="1:14" ht="21">
-      <c r="A66" s="140" t="s">
-        <v>544</v>
-      </c>
-      <c r="B66" s="213">
-        <v>90.550799999999995</v>
-      </c>
-      <c r="C66" s="7"/>
-      <c r="D66" s="140" t="s">
-        <v>599</v>
-      </c>
-      <c r="E66" s="213">
-        <v>39.314160000000001</v>
-      </c>
-      <c r="F66" s="101"/>
-      <c r="G66" s="7"/>
-      <c r="H66" s="7"/>
-      <c r="I66" s="7"/>
-      <c r="J66" s="140" t="s">
-        <v>696</v>
-      </c>
-      <c r="K66" s="60">
-        <v>35.934113543531133</v>
-      </c>
-      <c r="L66" s="7"/>
-      <c r="M66" s="140" t="s">
-        <v>756</v>
-      </c>
-      <c r="N66" s="148">
-        <v>23.832592133645409</v>
-      </c>
-    </row>
-    <row r="67" spans="1:14" ht="21">
-      <c r="A67" s="140" t="s">
-        <v>244</v>
-      </c>
-      <c r="B67" s="213">
-        <v>93.897760000000005</v>
-      </c>
-      <c r="C67" s="7"/>
-      <c r="D67" s="140" t="s">
-        <v>600</v>
-      </c>
-      <c r="E67" s="213">
-        <v>42.661119999999997</v>
-      </c>
-      <c r="F67" s="101"/>
-      <c r="G67" s="7"/>
-      <c r="H67" s="7"/>
-      <c r="I67" s="7"/>
-      <c r="J67" s="140" t="s">
-        <v>697</v>
-      </c>
-      <c r="K67" s="60">
-        <v>36.145334801964282</v>
-      </c>
-      <c r="L67" s="7"/>
-      <c r="M67" s="140" t="s">
-        <v>757</v>
-      </c>
-      <c r="N67" s="148">
-        <v>27.030044976823163</v>
-      </c>
-    </row>
-    <row r="68" spans="1:14" ht="21">
-      <c r="A68" s="140" t="s">
-        <v>545</v>
-      </c>
-      <c r="B68" s="213">
-        <v>95.586879999999994</v>
-      </c>
-      <c r="C68" s="7"/>
-      <c r="D68" s="140" t="s">
-        <v>601</v>
-      </c>
-      <c r="E68" s="213">
-        <v>66.527760000000001</v>
-      </c>
-      <c r="F68" s="101"/>
-      <c r="G68" s="7"/>
-      <c r="H68" s="7"/>
-      <c r="I68" s="7"/>
-      <c r="J68" s="140" t="s">
-        <v>698</v>
-      </c>
-      <c r="K68" s="60">
-        <v>36.990219835696912</v>
-      </c>
-      <c r="L68" s="7"/>
-      <c r="M68" s="140" t="s">
-        <v>758</v>
-      </c>
-      <c r="N68" s="148">
-        <v>27.827587314700072</v>
-      </c>
-    </row>
-    <row r="69" spans="1:14" ht="21">
-      <c r="A69" s="140" t="s">
-        <v>546</v>
-      </c>
-      <c r="B69" s="213">
-        <v>99.99736</v>
-      </c>
-      <c r="C69" s="7"/>
-      <c r="D69" s="140" t="s">
-        <v>602</v>
-      </c>
-      <c r="E69" s="213">
-        <v>70.875680000000003</v>
-      </c>
-      <c r="F69" s="101"/>
-      <c r="G69" s="7"/>
-      <c r="H69" s="7"/>
-      <c r="I69" s="7"/>
-      <c r="J69" s="140" t="s">
-        <v>699</v>
-      </c>
-      <c r="K69" s="60">
-        <v>40.3515512414521</v>
-      </c>
-      <c r="L69" s="7"/>
-      <c r="M69" s="140" t="s">
-        <v>759</v>
-      </c>
-      <c r="N69" s="148">
-        <v>30.755550966083799</v>
-      </c>
-    </row>
-    <row r="70" spans="1:14" ht="21">
-      <c r="A70" s="140" t="s">
-        <v>547</v>
-      </c>
-      <c r="B70" s="213">
-        <v>106.81639999999997</v>
-      </c>
-      <c r="C70" s="7"/>
-      <c r="D70" s="140" t="s">
-        <v>603</v>
-      </c>
-      <c r="E70" s="213">
-        <v>73.471919999999997</v>
-      </c>
-      <c r="F70" s="101"/>
-      <c r="G70" s="7"/>
-      <c r="H70" s="7"/>
-      <c r="I70" s="7"/>
-      <c r="J70" s="140" t="s">
-        <v>700</v>
-      </c>
-      <c r="K70" s="60">
-        <v>41.185511037679561</v>
-      </c>
-      <c r="L70" s="7"/>
-      <c r="M70" s="140" t="s">
-        <v>760</v>
-      </c>
-      <c r="N70" s="148">
-        <v>33.21008765891046</v>
-      </c>
-    </row>
-    <row r="71" spans="1:14" ht="21.6" thickBot="1">
-      <c r="A71" s="7"/>
-      <c r="B71" s="7"/>
-      <c r="C71" s="7"/>
-      <c r="D71" s="140"/>
-      <c r="E71" s="213"/>
-      <c r="F71" s="101"/>
-      <c r="G71" s="7"/>
-      <c r="H71" s="7"/>
-      <c r="I71" s="7"/>
-      <c r="J71" s="140" t="s">
-        <v>701</v>
-      </c>
-      <c r="K71" s="61">
-        <v>42.667701592546678</v>
-      </c>
-      <c r="L71" s="7"/>
-      <c r="M71" s="140" t="s">
-        <v>761</v>
-      </c>
-      <c r="N71" s="148">
-        <v>38.676348157327084</v>
-      </c>
-    </row>
-    <row r="72" spans="1:14" ht="21">
-      <c r="D72" s="140"/>
-      <c r="E72" s="213"/>
-      <c r="M72" s="140" t="s">
-        <v>762</v>
-      </c>
-      <c r="N72" s="149">
-        <v>40.293283308091233</v>
-      </c>
-    </row>
-    <row r="73" spans="1:14" ht="21">
-      <c r="D73" s="140"/>
-      <c r="E73" s="213"/>
-      <c r="M73" s="140" t="s">
-        <v>763</v>
-      </c>
-      <c r="N73" s="149">
-        <v>42.933549038505674</v>
-      </c>
-    </row>
-    <row r="74" spans="1:14" ht="21">
-      <c r="D74" s="140"/>
-      <c r="E74" s="213"/>
-      <c r="M74" s="140" t="s">
-        <v>764</v>
-      </c>
-      <c r="N74" s="149">
-        <v>43.326857588691531</v>
-      </c>
-    </row>
-    <row r="75" spans="1:14" ht="21">
-      <c r="D75" s="140"/>
-      <c r="E75" s="213"/>
-      <c r="M75" s="140" t="s">
-        <v>765</v>
-      </c>
-      <c r="N75" s="149">
-        <v>47.977367020055986</v>
-      </c>
-    </row>
-    <row r="76" spans="1:14" ht="21">
-      <c r="D76" s="140"/>
-      <c r="E76" s="213"/>
-      <c r="M76" s="140" t="s">
-        <v>391</v>
-      </c>
-      <c r="N76" s="149">
-        <v>50.402769746202203</v>
-      </c>
-    </row>
-    <row r="77" spans="1:14" ht="21">
-      <c r="D77" s="140"/>
-      <c r="E77" s="213"/>
-      <c r="M77" s="140" t="s">
-        <v>766</v>
-      </c>
-      <c r="N77" s="149">
-        <v>55.257216944329684</v>
-      </c>
-    </row>
-    <row r="78" spans="1:14" ht="21">
-      <c r="D78" s="140"/>
-      <c r="E78" s="213"/>
-      <c r="J78" s="394" t="s">
-        <v>771</v>
-      </c>
-      <c r="K78" s="394"/>
-      <c r="L78" s="394"/>
-      <c r="M78" s="394"/>
-      <c r="N78" s="394"/>
-    </row>
-    <row r="79" spans="1:14">
-      <c r="D79" s="140"/>
-      <c r="E79" s="213"/>
-    </row>
-    <row r="80" spans="1:14" ht="41.4">
-      <c r="D80" s="140"/>
-      <c r="E80" s="213"/>
-      <c r="J80" s="142" t="s">
-        <v>767</v>
-      </c>
-      <c r="N80" s="117">
-        <v>17.5</v>
-      </c>
-    </row>
-    <row r="81" spans="4:14" ht="27.6">
-      <c r="D81" s="140"/>
-      <c r="E81" s="213"/>
-      <c r="J81" s="142" t="s">
-        <v>768</v>
-      </c>
-      <c r="N81" s="117">
-        <v>17.5</v>
-      </c>
-    </row>
-    <row r="82" spans="4:14" ht="27.6">
-      <c r="D82" s="140"/>
-      <c r="E82" s="213"/>
-      <c r="J82" s="142" t="s">
-        <v>769</v>
-      </c>
-      <c r="N82" s="117">
-        <v>17.5</v>
-      </c>
-    </row>
-    <row r="83" spans="4:14" ht="27.6">
-      <c r="D83" s="140"/>
-      <c r="E83" s="213"/>
-      <c r="J83" s="142" t="s">
-        <v>770</v>
-      </c>
-      <c r="N83" s="117">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="84" spans="4:14">
-      <c r="D84" s="140"/>
-      <c r="E84" s="213"/>
-    </row>
-    <row r="85" spans="4:14">
-      <c r="D85" s="140"/>
-      <c r="E85" s="213"/>
-    </row>
-    <row r="86" spans="4:14">
-      <c r="D86" s="140"/>
-      <c r="E86" s="213"/>
-    </row>
-    <row r="87" spans="4:14">
-      <c r="D87" s="140"/>
-      <c r="E87" s="213"/>
-    </row>
-    <row r="88" spans="4:14">
-      <c r="D88" s="140"/>
-      <c r="E88" s="213"/>
-    </row>
-    <row r="89" spans="4:14">
-      <c r="D89" s="140"/>
-      <c r="E89" s="213"/>
-    </row>
-  </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="J78:N78"/>
-    <mergeCell ref="A2:N3"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="M6:M7"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2900-000000000000}">
   <dimension ref="B1:Y81"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.6"/>
@@ -34223,55 +34552,55 @@
   <sheetData>
     <row r="1" spans="2:25" ht="19.05" customHeight="1"/>
     <row r="2" spans="2:25" ht="19.05" customHeight="1">
-      <c r="B2" s="447" t="s">
+      <c r="B2" s="456" t="s">
         <v>1660</v>
       </c>
-      <c r="C2" s="447"/>
-      <c r="D2" s="447"/>
-      <c r="E2" s="447"/>
-      <c r="F2" s="447"/>
-      <c r="G2" s="447"/>
-      <c r="H2" s="447"/>
-      <c r="I2" s="447"/>
-      <c r="J2" s="447"/>
-      <c r="K2" s="447"/>
-      <c r="L2" s="447"/>
-      <c r="M2" s="447"/>
-      <c r="P2" s="446" t="s">
+      <c r="C2" s="456"/>
+      <c r="D2" s="456"/>
+      <c r="E2" s="456"/>
+      <c r="F2" s="456"/>
+      <c r="G2" s="456"/>
+      <c r="H2" s="456"/>
+      <c r="I2" s="456"/>
+      <c r="J2" s="456"/>
+      <c r="K2" s="456"/>
+      <c r="L2" s="456"/>
+      <c r="M2" s="456"/>
+      <c r="P2" s="455" t="s">
         <v>1660</v>
       </c>
-      <c r="Q2" s="446"/>
-      <c r="R2" s="446"/>
-      <c r="S2" s="446"/>
-      <c r="T2" s="446"/>
-      <c r="U2" s="446"/>
-      <c r="V2" s="446"/>
-      <c r="W2" s="446"/>
-      <c r="X2" s="446"/>
+      <c r="Q2" s="455"/>
+      <c r="R2" s="455"/>
+      <c r="S2" s="455"/>
+      <c r="T2" s="455"/>
+      <c r="U2" s="455"/>
+      <c r="V2" s="455"/>
+      <c r="W2" s="455"/>
+      <c r="X2" s="455"/>
       <c r="Y2" s="47"/>
     </row>
     <row r="3" spans="2:25" ht="19.05" customHeight="1">
-      <c r="B3" s="447"/>
-      <c r="C3" s="447"/>
-      <c r="D3" s="447"/>
-      <c r="E3" s="447"/>
-      <c r="F3" s="447"/>
-      <c r="G3" s="447"/>
-      <c r="H3" s="447"/>
-      <c r="I3" s="447"/>
-      <c r="J3" s="447"/>
-      <c r="K3" s="447"/>
-      <c r="L3" s="447"/>
-      <c r="M3" s="447"/>
-      <c r="P3" s="446"/>
-      <c r="Q3" s="446"/>
-      <c r="R3" s="446"/>
-      <c r="S3" s="446"/>
-      <c r="T3" s="446"/>
-      <c r="U3" s="446"/>
-      <c r="V3" s="446"/>
-      <c r="W3" s="446"/>
-      <c r="X3" s="446"/>
+      <c r="B3" s="456"/>
+      <c r="C3" s="456"/>
+      <c r="D3" s="456"/>
+      <c r="E3" s="456"/>
+      <c r="F3" s="456"/>
+      <c r="G3" s="456"/>
+      <c r="H3" s="456"/>
+      <c r="I3" s="456"/>
+      <c r="J3" s="456"/>
+      <c r="K3" s="456"/>
+      <c r="L3" s="456"/>
+      <c r="M3" s="456"/>
+      <c r="P3" s="455"/>
+      <c r="Q3" s="455"/>
+      <c r="R3" s="455"/>
+      <c r="S3" s="455"/>
+      <c r="T3" s="455"/>
+      <c r="U3" s="455"/>
+      <c r="V3" s="455"/>
+      <c r="W3" s="455"/>
+      <c r="X3" s="455"/>
       <c r="Y3" s="47"/>
     </row>
     <row r="4" spans="2:25" ht="19.05" customHeight="1">
@@ -34311,7 +34640,7 @@
         <v>98</v>
       </c>
       <c r="G7" s="20"/>
-      <c r="H7" s="435"/>
+      <c r="H7" s="440"/>
       <c r="I7" s="348" t="s">
         <v>100</v>
       </c>
@@ -34336,11 +34665,11 @@
       <c r="I8" s="91">
         <v>5.03</v>
       </c>
-      <c r="P8" s="436" t="s">
+      <c r="P8" s="441" t="s">
         <v>82</v>
       </c>
-      <c r="Q8" s="437"/>
-      <c r="R8" s="438"/>
+      <c r="Q8" s="442"/>
+      <c r="R8" s="443"/>
     </row>
     <row r="9" spans="2:25" s="7" customFormat="1" ht="19.05" customHeight="1" thickBot="1">
       <c r="B9" s="342">
@@ -34362,9 +34691,9 @@
       <c r="I9" s="91">
         <v>5.5328193124971312</v>
       </c>
-      <c r="P9" s="449"/>
-      <c r="Q9" s="450"/>
-      <c r="R9" s="451"/>
+      <c r="P9" s="452"/>
+      <c r="Q9" s="453"/>
+      <c r="R9" s="454"/>
     </row>
     <row r="10" spans="2:25" s="7" customFormat="1" ht="19.05" customHeight="1">
       <c r="B10" s="343">
@@ -34416,10 +34745,10 @@
       <c r="I11" s="91">
         <v>7.6508586901647604</v>
       </c>
-      <c r="P11" s="448" t="s">
+      <c r="P11" s="451" t="s">
         <v>480</v>
       </c>
-      <c r="Q11" s="448"/>
+      <c r="Q11" s="451"/>
       <c r="R11" s="193">
         <v>10.080053500127852</v>
       </c>
@@ -34444,10 +34773,10 @@
       <c r="I12" s="91">
         <v>5.6027408325301762</v>
       </c>
-      <c r="P12" s="448" t="s">
+      <c r="P12" s="451" t="s">
         <v>481</v>
       </c>
-      <c r="Q12" s="448"/>
+      <c r="Q12" s="451"/>
       <c r="R12" s="193">
         <v>8.0737987057689669</v>
       </c>
@@ -34472,10 +34801,10 @@
       <c r="I13" s="91">
         <v>5.876600119326266</v>
       </c>
-      <c r="P13" s="448" t="s">
+      <c r="P13" s="451" t="s">
         <v>482</v>
       </c>
-      <c r="Q13" s="448"/>
+      <c r="Q13" s="451"/>
       <c r="R13" s="193">
         <v>7.9935485139946119</v>
       </c>
@@ -34500,10 +34829,10 @@
       <c r="I14" s="91">
         <v>5.9902225893799619</v>
       </c>
-      <c r="P14" s="448" t="s">
+      <c r="P14" s="451" t="s">
         <v>483</v>
       </c>
-      <c r="Q14" s="448"/>
+      <c r="Q14" s="451"/>
       <c r="R14" s="193">
         <v>7.3515469797997683</v>
       </c>
@@ -35449,16 +35778,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="P2:X3"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="B2:M3"/>
+    <mergeCell ref="H6:H7"/>
     <mergeCell ref="P11:Q11"/>
     <mergeCell ref="P12:Q12"/>
     <mergeCell ref="P13:Q13"/>
     <mergeCell ref="P14:Q14"/>
     <mergeCell ref="P8:R9"/>
-    <mergeCell ref="P2:X3"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="B2:M3"/>
-    <mergeCell ref="H6:H7"/>
   </mergeCells>
   <phoneticPr fontId="43" type="noConversion"/>
   <pageMargins left="0.5" right="0.5" top="0.39000000000000007" bottom="0.39000000000000007" header="0" footer="0"/>
@@ -36226,10 +36555,10 @@
       <c r="Q4" s="41"/>
     </row>
     <row r="5" spans="1:17" s="30" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B5" s="383" t="s">
+      <c r="B5" s="384" t="s">
         <v>102</v>
       </c>
-      <c r="C5" s="383" t="s">
+      <c r="C5" s="384" t="s">
         <v>0</v>
       </c>
       <c r="D5" s="110" t="s">
@@ -36247,8 +36576,8 @@
       <c r="Q5" s="41"/>
     </row>
     <row r="6" spans="1:17" s="30" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B6" s="383"/>
-      <c r="C6" s="383"/>
+      <c r="B6" s="384"/>
+      <c r="C6" s="384"/>
       <c r="D6" s="110" t="s">
         <v>104</v>
       </c>
